--- a/Другое/study_chart.xlsx
+++ b/Другое/study_chart.xlsx
@@ -1,13 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROG\Git\Repository_1\Другое\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10530"/>
   </bookViews>
@@ -16,7 +11,7 @@
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
     <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="125725"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -91,16 +86,19 @@
   </si>
   <si>
     <t>Пт</t>
+  </si>
+  <si>
+    <t>Итого за отчетный период:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="dd\.mmm"/>
+    <numFmt numFmtId="164" formatCode="dd\.mmm"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -128,8 +126,23 @@
       <name val="Courier New"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1C1917"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1C1917"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -154,6 +167,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -219,7 +238,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -232,7 +251,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -244,12 +263,53 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -565,14 +625,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="H9:Q21"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="H9:Q22"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="7" width="9.140625" style="1"/>
     <col min="8" max="8" width="5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="16.85546875" style="1" customWidth="1"/>
     <col min="11" max="11" width="14.28515625" style="1" customWidth="1"/>
     <col min="12" max="13" width="11.28515625" style="1" customWidth="1"/>
     <col min="14" max="14" width="11.5703125" style="1" customWidth="1"/>
@@ -581,7 +641,7 @@
     <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="8:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="8:17" ht="45" customHeight="1">
       <c r="H9" s="8" t="s">
         <v>0</v>
       </c>
@@ -595,7 +655,7 @@
       <c r="P9" s="9"/>
       <c r="Q9" s="10"/>
     </row>
-    <row r="10" spans="8:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="8:17" ht="30" customHeight="1">
       <c r="H10" s="2" t="s">
         <v>1</v>
       </c>
@@ -627,57 +687,57 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="8:17" x14ac:dyDescent="0.25">
-      <c r="H11" s="3">
+    <row r="11" spans="8:17">
+      <c r="H11" s="15">
         <v>1</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="17">
         <v>46193</v>
       </c>
-      <c r="K11" s="7" t="s">
+      <c r="K11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="L11" s="7" t="s">
+      <c r="L11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="M11" s="7" t="s">
+      <c r="M11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="N11" s="7" t="s">
+      <c r="N11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7"/>
-    </row>
-    <row r="12" spans="8:17" x14ac:dyDescent="0.25">
-      <c r="H12" s="3">
+      <c r="O11" s="18"/>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="18"/>
+    </row>
+    <row r="12" spans="8:17">
+      <c r="H12" s="15">
         <v>2</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="17">
         <v>46194</v>
       </c>
-      <c r="K12" s="7" t="s">
+      <c r="K12" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7" t="s">
+      <c r="L12" s="18"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="O12" s="7" t="s">
+      <c r="O12" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="7"/>
-    </row>
-    <row r="13" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="P12" s="18"/>
+      <c r="Q12" s="18"/>
+    </row>
+    <row r="13" spans="8:17">
       <c r="H13" s="3">
         <v>3</v>
       </c>
@@ -687,15 +747,19 @@
       <c r="J13" s="6">
         <v>46195</v>
       </c>
-      <c r="K13" s="7"/>
+      <c r="K13" s="14" t="s">
+        <v>12</v>
+      </c>
       <c r="L13" s="7"/>
       <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
+      <c r="N13" s="14" t="s">
+        <v>12</v>
+      </c>
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
     </row>
-    <row r="14" spans="8:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="8:17">
       <c r="H14" s="3">
         <v>4</v>
       </c>
@@ -713,7 +777,7 @@
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
     </row>
-    <row r="15" spans="8:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="8:17">
       <c r="H15" s="3">
         <v>5</v>
       </c>
@@ -731,7 +795,7 @@
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
     </row>
-    <row r="16" spans="8:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="8:17">
       <c r="H16" s="3">
         <v>6</v>
       </c>
@@ -749,7 +813,7 @@
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
     </row>
-    <row r="17" spans="8:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="8:17">
       <c r="H17" s="3">
         <v>7</v>
       </c>
@@ -767,7 +831,7 @@
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
     </row>
-    <row r="18" spans="8:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="8:17">
       <c r="H18" s="3">
         <v>8</v>
       </c>
@@ -785,7 +849,7 @@
       <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
     </row>
-    <row r="19" spans="8:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="8:17">
       <c r="H19" s="3">
         <v>9</v>
       </c>
@@ -803,7 +867,7 @@
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
     </row>
-    <row r="20" spans="8:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="8:17">
       <c r="H20" s="3">
         <v>10</v>
       </c>
@@ -821,7 +885,7 @@
       <c r="P20" s="7"/>
       <c r="Q20" s="7"/>
     </row>
-    <row r="21" spans="8:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="8:17">
       <c r="H21" s="3">
         <v>11</v>
       </c>
@@ -839,24 +903,65 @@
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
     </row>
+    <row r="22" spans="8:17" ht="15.75">
+      <c r="H22" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" s="12"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="7">
+        <f>COUNTA(K11:K21)</f>
+        <v>3</v>
+      </c>
+      <c r="L22" s="7">
+        <f t="shared" ref="L22:Q22" si="0">COUNTA(L11:L21)</f>
+        <v>1</v>
+      </c>
+      <c r="M22" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="N22" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="O22" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="P22" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="H9:Q9"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <conditionalFormatting sqref="K11:Q21">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>Q11="+"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="K22:Q22">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>Q22="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180"/>
@@ -864,9 +969,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180"/>

--- a/Другое/study_chart.xlsx
+++ b/Другое/study_chart.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="20">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -255,54 +255,40 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -642,18 +628,18 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:17" ht="45" customHeight="1">
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="10"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="14"/>
     </row>
     <row r="10" spans="8:17" ht="30" customHeight="1">
       <c r="H10" s="2" t="s">
@@ -688,76 +674,76 @@
       </c>
     </row>
     <row r="11" spans="8:17">
-      <c r="H11" s="15">
+      <c r="H11" s="8">
         <v>1</v>
       </c>
-      <c r="I11" s="16" t="s">
+      <c r="I11" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J11" s="17">
+      <c r="J11" s="10">
         <v>46193</v>
       </c>
-      <c r="K11" s="18" t="s">
+      <c r="K11" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="L11" s="18" t="s">
+      <c r="L11" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="M11" s="18" t="s">
+      <c r="M11" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="N11" s="18" t="s">
+      <c r="N11" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="O11" s="18"/>
-      <c r="P11" s="18"/>
-      <c r="Q11" s="18"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11"/>
     </row>
     <row r="12" spans="8:17">
-      <c r="H12" s="15">
+      <c r="H12" s="8">
         <v>2</v>
       </c>
-      <c r="I12" s="16" t="s">
+      <c r="I12" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J12" s="17">
+      <c r="J12" s="10">
         <v>46194</v>
       </c>
-      <c r="K12" s="18" t="s">
+      <c r="K12" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="L12" s="18"/>
-      <c r="M12" s="18"/>
-      <c r="N12" s="18" t="s">
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="O12" s="18" t="s">
+      <c r="O12" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="P12" s="18"/>
-      <c r="Q12" s="18"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
     </row>
     <row r="13" spans="8:17">
-      <c r="H13" s="3">
+      <c r="H13" s="8">
         <v>3</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J13" s="10">
         <v>46195</v>
       </c>
-      <c r="K13" s="14" t="s">
+      <c r="K13" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="14" t="s">
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
+      <c r="N13" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
     </row>
     <row r="14" spans="8:17">
       <c r="H14" s="3">
@@ -772,7 +758,9 @@
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
+      <c r="N14" s="7" t="s">
+        <v>12</v>
+      </c>
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
@@ -904,11 +892,11 @@
       <c r="Q21" s="7"/>
     </row>
     <row r="22" spans="8:17" ht="15.75">
-      <c r="H22" s="11" t="s">
+      <c r="H22" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="12"/>
-      <c r="J22" s="13"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="17"/>
       <c r="K22" s="7">
         <f>COUNTA(K11:K21)</f>
         <v>3</v>
@@ -923,7 +911,7 @@
       </c>
       <c r="N22" s="7">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O22" s="7">
         <f t="shared" si="0"/>
@@ -944,12 +932,12 @@
     <mergeCell ref="H22:J22"/>
   </mergeCells>
   <conditionalFormatting sqref="K11:Q21">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>Q11="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K22:Q22">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>Q22="+"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Другое/study_chart.xlsx
+++ b/Другое/study_chart.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="20">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -263,6 +263,9 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -280,15 +283,19 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -628,18 +635,18 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:17" ht="45" customHeight="1">
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="15"/>
     </row>
     <row r="10" spans="8:17" ht="30" customHeight="1">
       <c r="H10" s="2" t="s">
@@ -733,12 +740,12 @@
       <c r="J13" s="10">
         <v>46195</v>
       </c>
-      <c r="K13" s="18" t="s">
+      <c r="K13" s="12" t="s">
         <v>12</v>
       </c>
       <c r="L13" s="11"/>
       <c r="M13" s="11"/>
-      <c r="N13" s="18" t="s">
+      <c r="N13" s="12" t="s">
         <v>12</v>
       </c>
       <c r="O13" s="11"/>
@@ -746,24 +753,26 @@
       <c r="Q13" s="11"/>
     </row>
     <row r="14" spans="8:17">
-      <c r="H14" s="3">
+      <c r="H14" s="8">
         <v>4</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="10">
         <v>46196</v>
       </c>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="7"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="M14" s="11"/>
+      <c r="N14" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
     </row>
     <row r="15" spans="8:17">
       <c r="H15" s="3">
@@ -775,7 +784,9 @@
       <c r="J15" s="6">
         <v>46197</v>
       </c>
-      <c r="K15" s="7"/>
+      <c r="K15" s="7" t="s">
+        <v>12</v>
+      </c>
       <c r="L15" s="7"/>
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
@@ -892,18 +903,18 @@
       <c r="Q21" s="7"/>
     </row>
     <row r="22" spans="8:17" ht="15.75">
-      <c r="H22" s="15" t="s">
+      <c r="H22" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="16"/>
-      <c r="J22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="18"/>
       <c r="K22" s="7">
         <f>COUNTA(K11:K21)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L22" s="7">
         <f t="shared" ref="L22:Q22" si="0">COUNTA(L11:L21)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M22" s="7">
         <f t="shared" si="0"/>
@@ -932,12 +943,12 @@
     <mergeCell ref="H22:J22"/>
   </mergeCells>
   <conditionalFormatting sqref="K11:Q21">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>Q11="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K22:Q22">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>Q22="+"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Другое/study_chart.xlsx
+++ b/Другое/study_chart.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROG\Git\Repository_1\Другое\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10530"/>
   </bookViews>
@@ -11,7 +16,7 @@
     <sheet name="Лист2" sheetId="2" r:id="rId2"/>
     <sheet name="Лист3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="20">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -94,11 +99,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mmm"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -288,14 +293,7 @@
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -377,7 +375,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -409,9 +407,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -443,6 +442,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -618,9 +618,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="H9:Q22"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="7" width="9.140625" style="1"/>
     <col min="8" max="8" width="5" style="1" customWidth="1"/>
@@ -634,7 +634,7 @@
     <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="8:17" ht="45" customHeight="1">
+    <row r="9" spans="8:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H9" s="13" t="s">
         <v>0</v>
       </c>
@@ -648,7 +648,7 @@
       <c r="P9" s="14"/>
       <c r="Q9" s="15"/>
     </row>
-    <row r="10" spans="8:17" ht="30" customHeight="1">
+    <row r="10" spans="8:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H10" s="2" t="s">
         <v>1</v>
       </c>
@@ -680,7 +680,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="8:17">
+    <row r="11" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H11" s="8">
         <v>1</v>
       </c>
@@ -706,7 +706,7 @@
       <c r="P11" s="11"/>
       <c r="Q11" s="11"/>
     </row>
-    <row r="12" spans="8:17">
+    <row r="12" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H12" s="8">
         <v>2</v>
       </c>
@@ -730,7 +730,7 @@
       <c r="P12" s="11"/>
       <c r="Q12" s="11"/>
     </row>
-    <row r="13" spans="8:17">
+    <row r="13" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H13" s="8">
         <v>3</v>
       </c>
@@ -752,7 +752,7 @@
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
     </row>
-    <row r="14" spans="8:17">
+    <row r="14" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H14" s="8">
         <v>4</v>
       </c>
@@ -774,63 +774,73 @@
       <c r="P14" s="11"/>
       <c r="Q14" s="11"/>
     </row>
-    <row r="15" spans="8:17">
-      <c r="H15" s="3">
+    <row r="15" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H15" s="8">
         <v>5</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="I15" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J15" s="10">
         <v>46197</v>
       </c>
-      <c r="K15" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
-    </row>
-    <row r="16" spans="8:17">
-      <c r="H16" s="3">
+      <c r="K15" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+    </row>
+    <row r="16" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H16" s="8">
         <v>6</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="I16" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J16" s="10">
         <v>46198</v>
       </c>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="7"/>
-    </row>
-    <row r="17" spans="8:17">
-      <c r="H17" s="3">
+      <c r="K16" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="N16" s="11"/>
+      <c r="O16" s="11"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11"/>
+    </row>
+    <row r="17" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="H17" s="8">
         <v>7</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="I17" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="J17" s="6">
+      <c r="J17" s="10">
         <v>46199</v>
       </c>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="7"/>
-    </row>
-    <row r="18" spans="8:17">
+      <c r="K17" s="11"/>
+      <c r="L17" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
+    </row>
+    <row r="18" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H18" s="3">
         <v>8</v>
       </c>
@@ -848,7 +858,7 @@
       <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
     </row>
-    <row r="19" spans="8:17">
+    <row r="19" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H19" s="3">
         <v>9</v>
       </c>
@@ -866,7 +876,7 @@
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
     </row>
-    <row r="20" spans="8:17">
+    <row r="20" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H20" s="3">
         <v>10</v>
       </c>
@@ -884,7 +894,7 @@
       <c r="P20" s="7"/>
       <c r="Q20" s="7"/>
     </row>
-    <row r="21" spans="8:17">
+    <row r="21" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H21" s="3">
         <v>11</v>
       </c>
@@ -902,7 +912,7 @@
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
     </row>
-    <row r="22" spans="8:17" ht="15.75">
+    <row r="22" spans="8:17" ht="15.75" x14ac:dyDescent="0.3">
       <c r="H22" s="16" t="s">
         <v>19</v>
       </c>
@@ -910,15 +920,15 @@
       <c r="J22" s="18"/>
       <c r="K22" s="7">
         <f>COUNTA(K11:K21)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L22" s="7">
         <f t="shared" ref="L22:Q22" si="0">COUNTA(L11:L21)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M22" s="7">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N22" s="7">
         <f t="shared" si="0"/>
@@ -943,12 +953,12 @@
     <mergeCell ref="H22:J22"/>
   </mergeCells>
   <conditionalFormatting sqref="K11:Q21">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>Q11="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K22:Q22">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>Q22="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -958,9 +968,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180"/>
@@ -968,9 +978,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180"/>

--- a/Другое/study_chart.xlsx
+++ b/Другое/study_chart.xlsx
@@ -1,22 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROG\Git\Repository_1\Другое\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10530"/>
   </bookViews>
   <sheets>
     <sheet name="Июнь" sheetId="1" r:id="rId1"/>
-    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
-    <sheet name="Лист3" sheetId="3" r:id="rId3"/>
+    <sheet name="Июль" sheetId="4" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="125725"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="23">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -94,16 +88,25 @@
   </si>
   <si>
     <t>Итого за отчетный период:</t>
+  </si>
+  <si>
+    <t>Зарядка</t>
+  </si>
+  <si>
+    <t>Осанка</t>
+  </si>
+  <si>
+    <t>Планирование</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mmm"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -147,7 +150,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -178,8 +181,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -239,11 +254,57 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </left>
+      <right style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </right>
+      <top style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF4A3B32"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF4A3B32"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF4A3B32"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF4A3B32"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF4A3B32"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -289,11 +350,78 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="7">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -375,7 +503,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -407,10 +535,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -442,7 +569,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -618,9 +744,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="H9:Q22"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="7" width="9.140625" style="1"/>
     <col min="8" max="8" width="5" style="1" customWidth="1"/>
@@ -634,7 +760,7 @@
     <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="8:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="8:17" ht="45" customHeight="1">
       <c r="H9" s="13" t="s">
         <v>0</v>
       </c>
@@ -648,7 +774,7 @@
       <c r="P9" s="14"/>
       <c r="Q9" s="15"/>
     </row>
-    <row r="10" spans="8:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="8:17" ht="30" customHeight="1">
       <c r="H10" s="2" t="s">
         <v>1</v>
       </c>
@@ -680,7 +806,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="8:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="8:17">
       <c r="H11" s="8">
         <v>1</v>
       </c>
@@ -706,7 +832,7 @@
       <c r="P11" s="11"/>
       <c r="Q11" s="11"/>
     </row>
-    <row r="12" spans="8:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="8:17">
       <c r="H12" s="8">
         <v>2</v>
       </c>
@@ -730,7 +856,7 @@
       <c r="P12" s="11"/>
       <c r="Q12" s="11"/>
     </row>
-    <row r="13" spans="8:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="8:17">
       <c r="H13" s="8">
         <v>3</v>
       </c>
@@ -752,7 +878,7 @@
       <c r="P13" s="11"/>
       <c r="Q13" s="11"/>
     </row>
-    <row r="14" spans="8:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="8:17">
       <c r="H14" s="8">
         <v>4</v>
       </c>
@@ -774,7 +900,7 @@
       <c r="P14" s="11"/>
       <c r="Q14" s="11"/>
     </row>
-    <row r="15" spans="8:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="8:17">
       <c r="H15" s="8">
         <v>5</v>
       </c>
@@ -794,7 +920,7 @@
       <c r="P15" s="11"/>
       <c r="Q15" s="11"/>
     </row>
-    <row r="16" spans="8:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="8:17">
       <c r="H16" s="8">
         <v>6</v>
       </c>
@@ -818,7 +944,7 @@
       <c r="P16" s="11"/>
       <c r="Q16" s="11"/>
     </row>
-    <row r="17" spans="8:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="8:17">
       <c r="H17" s="8">
         <v>7</v>
       </c>
@@ -840,43 +966,45 @@
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
     </row>
-    <row r="18" spans="8:17" x14ac:dyDescent="0.25">
-      <c r="H18" s="3">
+    <row r="18" spans="8:17">
+      <c r="H18" s="8">
         <v>8</v>
       </c>
-      <c r="I18" s="5" t="s">
+      <c r="I18" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J18" s="6">
+      <c r="J18" s="10">
         <v>46200</v>
       </c>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="7"/>
-    </row>
-    <row r="19" spans="8:17" x14ac:dyDescent="0.25">
-      <c r="H19" s="3">
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="11"/>
+      <c r="P18" s="11"/>
+      <c r="Q18" s="11"/>
+    </row>
+    <row r="19" spans="8:17">
+      <c r="H19" s="8">
         <v>9</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="I19" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="J19" s="6">
+      <c r="J19" s="10">
         <v>46201</v>
       </c>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7"/>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="7"/>
-    </row>
-    <row r="20" spans="8:17" x14ac:dyDescent="0.25">
+      <c r="K19" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="L19" s="11"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="11"/>
+      <c r="P19" s="11"/>
+      <c r="Q19" s="11"/>
+    </row>
+    <row r="20" spans="8:17">
       <c r="H20" s="3">
         <v>10</v>
       </c>
@@ -894,7 +1022,7 @@
       <c r="P20" s="7"/>
       <c r="Q20" s="7"/>
     </row>
-    <row r="21" spans="8:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="8:17">
       <c r="H21" s="3">
         <v>11</v>
       </c>
@@ -912,7 +1040,7 @@
       <c r="P21" s="7"/>
       <c r="Q21" s="7"/>
     </row>
-    <row r="22" spans="8:17" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="22" spans="8:17" ht="15.75">
       <c r="H22" s="16" t="s">
         <v>19</v>
       </c>
@@ -920,7 +1048,7 @@
       <c r="J22" s="18"/>
       <c r="K22" s="7">
         <f>COUNTA(K11:K21)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L22" s="7">
         <f t="shared" ref="L22:Q22" si="0">COUNTA(L11:L21)</f>
@@ -953,12 +1081,12 @@
     <mergeCell ref="H22:J22"/>
   </mergeCells>
   <conditionalFormatting sqref="K11:Q21">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>Q11="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K22:Q22">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>Q22="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -968,21 +1096,795 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="H9:T42"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="7" width="9.140625" style="1"/>
+    <col min="8" max="8" width="5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="16.85546875" style="1" customWidth="1"/>
+    <col min="11" max="13" width="14.28515625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="18.7109375" style="1" customWidth="1"/>
+    <col min="15" max="16" width="11.28515625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="11.5703125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" customWidth="1"/>
+    <col min="19" max="20" width="10" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="9" spans="8:20" ht="45" customHeight="1">
+      <c r="H9" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="20"/>
+      <c r="T9" s="21"/>
+    </row>
+    <row r="10" spans="8:20" ht="30" customHeight="1">
+      <c r="H10" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="J10" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="L10" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="M10" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="N10" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="O10" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q10" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="R10" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="S10" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="T10" s="22" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="8:20">
+      <c r="H11" s="24">
+        <v>1</v>
+      </c>
+      <c r="I11" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="26">
+        <v>46204</v>
+      </c>
+      <c r="K11" s="27"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="27"/>
+      <c r="P11" s="27"/>
+      <c r="Q11" s="27"/>
+      <c r="R11" s="27"/>
+      <c r="S11" s="27"/>
+      <c r="T11" s="27"/>
+    </row>
+    <row r="12" spans="8:20">
+      <c r="H12" s="24">
+        <v>2</v>
+      </c>
+      <c r="I12" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="26">
+        <v>46205</v>
+      </c>
+      <c r="K12" s="27"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="27"/>
+      <c r="N12" s="27"/>
+      <c r="O12" s="27"/>
+      <c r="P12" s="27"/>
+      <c r="Q12" s="27"/>
+      <c r="R12" s="27"/>
+      <c r="S12" s="27"/>
+      <c r="T12" s="27"/>
+    </row>
+    <row r="13" spans="8:20">
+      <c r="H13" s="24">
+        <v>3</v>
+      </c>
+      <c r="I13" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" s="26">
+        <v>46206</v>
+      </c>
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
+      <c r="M13" s="28"/>
+      <c r="N13" s="28"/>
+      <c r="O13" s="27"/>
+      <c r="P13" s="27"/>
+      <c r="Q13" s="28"/>
+      <c r="R13" s="27"/>
+      <c r="S13" s="27"/>
+      <c r="T13" s="27"/>
+    </row>
+    <row r="14" spans="8:20">
+      <c r="H14" s="24">
+        <v>4</v>
+      </c>
+      <c r="I14" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="J14" s="26">
+        <v>46207</v>
+      </c>
+      <c r="K14" s="28"/>
+      <c r="L14" s="28"/>
+      <c r="M14" s="28"/>
+      <c r="N14" s="28"/>
+      <c r="O14" s="27"/>
+      <c r="P14" s="27"/>
+      <c r="Q14" s="28"/>
+      <c r="R14" s="27"/>
+      <c r="S14" s="27"/>
+      <c r="T14" s="27"/>
+    </row>
+    <row r="15" spans="8:20">
+      <c r="H15" s="24">
+        <v>5</v>
+      </c>
+      <c r="I15" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="26">
+        <v>46208</v>
+      </c>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="27"/>
+      <c r="O15" s="27"/>
+      <c r="P15" s="27"/>
+      <c r="Q15" s="27"/>
+      <c r="R15" s="27"/>
+      <c r="S15" s="27"/>
+      <c r="T15" s="27"/>
+    </row>
+    <row r="16" spans="8:20">
+      <c r="H16" s="24">
+        <v>6</v>
+      </c>
+      <c r="I16" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="J16" s="26">
+        <v>46209</v>
+      </c>
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="27"/>
+      <c r="O16" s="27"/>
+      <c r="P16" s="27"/>
+      <c r="Q16" s="27"/>
+      <c r="R16" s="27"/>
+      <c r="S16" s="27"/>
+      <c r="T16" s="27"/>
+    </row>
+    <row r="17" spans="8:20">
+      <c r="H17" s="24">
+        <v>7</v>
+      </c>
+      <c r="I17" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="J17" s="26">
+        <v>46210</v>
+      </c>
+      <c r="K17" s="28"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="27"/>
+      <c r="N17" s="27"/>
+      <c r="O17" s="27"/>
+      <c r="P17" s="27"/>
+      <c r="Q17" s="27"/>
+      <c r="R17" s="27"/>
+      <c r="S17" s="27"/>
+      <c r="T17" s="27"/>
+    </row>
+    <row r="18" spans="8:20">
+      <c r="H18" s="24">
+        <v>8</v>
+      </c>
+      <c r="I18" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="26">
+        <v>46211</v>
+      </c>
+      <c r="K18" s="28"/>
+      <c r="L18" s="27"/>
+      <c r="M18" s="27"/>
+      <c r="N18" s="27"/>
+      <c r="O18" s="27"/>
+      <c r="P18" s="27"/>
+      <c r="Q18" s="27"/>
+      <c r="R18" s="27"/>
+      <c r="S18" s="27"/>
+      <c r="T18" s="27"/>
+    </row>
+    <row r="19" spans="8:20">
+      <c r="H19" s="24">
+        <v>9</v>
+      </c>
+      <c r="I19" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="26">
+        <v>46212</v>
+      </c>
+      <c r="K19" s="27"/>
+      <c r="L19" s="27"/>
+      <c r="M19" s="27"/>
+      <c r="N19" s="27"/>
+      <c r="O19" s="27"/>
+      <c r="P19" s="27"/>
+      <c r="Q19" s="27"/>
+      <c r="R19" s="27"/>
+      <c r="S19" s="27"/>
+      <c r="T19" s="27"/>
+    </row>
+    <row r="20" spans="8:20">
+      <c r="H20" s="24">
+        <v>10</v>
+      </c>
+      <c r="I20" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20" s="26">
+        <v>46213</v>
+      </c>
+      <c r="K20" s="27"/>
+      <c r="L20" s="27"/>
+      <c r="M20" s="27"/>
+      <c r="N20" s="27"/>
+      <c r="O20" s="27"/>
+      <c r="P20" s="27"/>
+      <c r="Q20" s="27"/>
+      <c r="R20" s="27"/>
+      <c r="S20" s="27"/>
+      <c r="T20" s="27"/>
+    </row>
+    <row r="21" spans="8:20">
+      <c r="H21" s="24">
+        <v>11</v>
+      </c>
+      <c r="I21" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="J21" s="26">
+        <v>46214</v>
+      </c>
+      <c r="K21" s="28"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="27"/>
+      <c r="N21" s="27"/>
+      <c r="O21" s="27"/>
+      <c r="P21" s="27"/>
+      <c r="Q21" s="27"/>
+      <c r="R21" s="27"/>
+      <c r="S21" s="27"/>
+      <c r="T21" s="27"/>
+    </row>
+    <row r="22" spans="8:20">
+      <c r="H22" s="24">
+        <v>12</v>
+      </c>
+      <c r="I22" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="J22" s="26">
+        <v>46215</v>
+      </c>
+      <c r="K22" s="28"/>
+      <c r="L22" s="27"/>
+      <c r="M22" s="27"/>
+      <c r="N22" s="27"/>
+      <c r="O22" s="27"/>
+      <c r="P22" s="27"/>
+      <c r="Q22" s="27"/>
+      <c r="R22" s="27"/>
+      <c r="S22" s="27"/>
+      <c r="T22" s="27"/>
+    </row>
+    <row r="23" spans="8:20">
+      <c r="H23" s="24">
+        <v>13</v>
+      </c>
+      <c r="I23" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="J23" s="26">
+        <v>46216</v>
+      </c>
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="27"/>
+      <c r="N23" s="27"/>
+      <c r="O23" s="27"/>
+      <c r="P23" s="27"/>
+      <c r="Q23" s="27"/>
+      <c r="R23" s="27"/>
+      <c r="S23" s="27"/>
+      <c r="T23" s="27"/>
+    </row>
+    <row r="24" spans="8:20">
+      <c r="H24" s="24">
+        <v>14</v>
+      </c>
+      <c r="I24" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" s="26">
+        <v>46217</v>
+      </c>
+      <c r="K24" s="27"/>
+      <c r="L24" s="27"/>
+      <c r="M24" s="27"/>
+      <c r="N24" s="27"/>
+      <c r="O24" s="27"/>
+      <c r="P24" s="27"/>
+      <c r="Q24" s="27"/>
+      <c r="R24" s="27"/>
+      <c r="S24" s="27"/>
+      <c r="T24" s="27"/>
+    </row>
+    <row r="25" spans="8:20">
+      <c r="H25" s="24">
+        <v>15</v>
+      </c>
+      <c r="I25" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" s="26">
+        <v>46218</v>
+      </c>
+      <c r="K25" s="28"/>
+      <c r="L25" s="27"/>
+      <c r="M25" s="27"/>
+      <c r="N25" s="27"/>
+      <c r="O25" s="27"/>
+      <c r="P25" s="27"/>
+      <c r="Q25" s="27"/>
+      <c r="R25" s="27"/>
+      <c r="S25" s="27"/>
+      <c r="T25" s="27"/>
+    </row>
+    <row r="26" spans="8:20">
+      <c r="H26" s="24">
+        <v>16</v>
+      </c>
+      <c r="I26" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" s="26">
+        <v>46219</v>
+      </c>
+      <c r="K26" s="28"/>
+      <c r="L26" s="27"/>
+      <c r="M26" s="27"/>
+      <c r="N26" s="27"/>
+      <c r="O26" s="27"/>
+      <c r="P26" s="27"/>
+      <c r="Q26" s="27"/>
+      <c r="R26" s="27"/>
+      <c r="S26" s="27"/>
+      <c r="T26" s="27"/>
+    </row>
+    <row r="27" spans="8:20">
+      <c r="H27" s="24">
+        <v>17</v>
+      </c>
+      <c r="I27" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" s="26">
+        <v>46220</v>
+      </c>
+      <c r="K27" s="27"/>
+      <c r="L27" s="27"/>
+      <c r="M27" s="27"/>
+      <c r="N27" s="27"/>
+      <c r="O27" s="27"/>
+      <c r="P27" s="27"/>
+      <c r="Q27" s="27"/>
+      <c r="R27" s="27"/>
+      <c r="S27" s="27"/>
+      <c r="T27" s="27"/>
+    </row>
+    <row r="28" spans="8:20">
+      <c r="H28" s="24">
+        <v>18</v>
+      </c>
+      <c r="I28" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="J28" s="26">
+        <v>46221</v>
+      </c>
+      <c r="K28" s="27"/>
+      <c r="L28" s="27"/>
+      <c r="M28" s="27"/>
+      <c r="N28" s="27"/>
+      <c r="O28" s="27"/>
+      <c r="P28" s="27"/>
+      <c r="Q28" s="27"/>
+      <c r="R28" s="27"/>
+      <c r="S28" s="27"/>
+      <c r="T28" s="27"/>
+    </row>
+    <row r="29" spans="8:20">
+      <c r="H29" s="24">
+        <v>19</v>
+      </c>
+      <c r="I29" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="J29" s="26">
+        <v>46222</v>
+      </c>
+      <c r="K29" s="28"/>
+      <c r="L29" s="27"/>
+      <c r="M29" s="27"/>
+      <c r="N29" s="27"/>
+      <c r="O29" s="27"/>
+      <c r="P29" s="27"/>
+      <c r="Q29" s="27"/>
+      <c r="R29" s="27"/>
+      <c r="S29" s="27"/>
+      <c r="T29" s="27"/>
+    </row>
+    <row r="30" spans="8:20">
+      <c r="H30" s="24">
+        <v>20</v>
+      </c>
+      <c r="I30" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="J30" s="26">
+        <v>46223</v>
+      </c>
+      <c r="K30" s="28"/>
+      <c r="L30" s="27"/>
+      <c r="M30" s="27"/>
+      <c r="N30" s="27"/>
+      <c r="O30" s="27"/>
+      <c r="P30" s="27"/>
+      <c r="Q30" s="27"/>
+      <c r="R30" s="27"/>
+      <c r="S30" s="27"/>
+      <c r="T30" s="27"/>
+    </row>
+    <row r="31" spans="8:20">
+      <c r="H31" s="24">
+        <v>21</v>
+      </c>
+      <c r="I31" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="J31" s="26">
+        <v>46224</v>
+      </c>
+      <c r="K31" s="27"/>
+      <c r="L31" s="27"/>
+      <c r="M31" s="27"/>
+      <c r="N31" s="27"/>
+      <c r="O31" s="27"/>
+      <c r="P31" s="27"/>
+      <c r="Q31" s="27"/>
+      <c r="R31" s="27"/>
+      <c r="S31" s="27"/>
+      <c r="T31" s="27"/>
+    </row>
+    <row r="32" spans="8:20">
+      <c r="H32" s="24">
+        <v>22</v>
+      </c>
+      <c r="I32" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="26">
+        <v>46225</v>
+      </c>
+      <c r="K32" s="27"/>
+      <c r="L32" s="27"/>
+      <c r="M32" s="27"/>
+      <c r="N32" s="27"/>
+      <c r="O32" s="27"/>
+      <c r="P32" s="27"/>
+      <c r="Q32" s="27"/>
+      <c r="R32" s="27"/>
+      <c r="S32" s="27"/>
+      <c r="T32" s="27"/>
+    </row>
+    <row r="33" spans="8:20">
+      <c r="H33" s="24">
+        <v>23</v>
+      </c>
+      <c r="I33" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="J33" s="26">
+        <v>46226</v>
+      </c>
+      <c r="K33" s="28"/>
+      <c r="L33" s="27"/>
+      <c r="M33" s="27"/>
+      <c r="N33" s="27"/>
+      <c r="O33" s="27"/>
+      <c r="P33" s="27"/>
+      <c r="Q33" s="27"/>
+      <c r="R33" s="27"/>
+      <c r="S33" s="27"/>
+      <c r="T33" s="27"/>
+    </row>
+    <row r="34" spans="8:20">
+      <c r="H34" s="24">
+        <v>24</v>
+      </c>
+      <c r="I34" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J34" s="26">
+        <v>46227</v>
+      </c>
+      <c r="K34" s="28"/>
+      <c r="L34" s="27"/>
+      <c r="M34" s="27"/>
+      <c r="N34" s="27"/>
+      <c r="O34" s="27"/>
+      <c r="P34" s="27"/>
+      <c r="Q34" s="27"/>
+      <c r="R34" s="27"/>
+      <c r="S34" s="27"/>
+      <c r="T34" s="27"/>
+    </row>
+    <row r="35" spans="8:20">
+      <c r="H35" s="24">
+        <v>25</v>
+      </c>
+      <c r="I35" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="J35" s="26">
+        <v>46228</v>
+      </c>
+      <c r="K35" s="27"/>
+      <c r="L35" s="27"/>
+      <c r="M35" s="27"/>
+      <c r="N35" s="27"/>
+      <c r="O35" s="27"/>
+      <c r="P35" s="27"/>
+      <c r="Q35" s="27"/>
+      <c r="R35" s="27"/>
+      <c r="S35" s="27"/>
+      <c r="T35" s="27"/>
+    </row>
+    <row r="36" spans="8:20">
+      <c r="H36" s="24">
+        <v>26</v>
+      </c>
+      <c r="I36" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="J36" s="26">
+        <v>46229</v>
+      </c>
+      <c r="K36" s="27"/>
+      <c r="L36" s="27"/>
+      <c r="M36" s="27"/>
+      <c r="N36" s="27"/>
+      <c r="O36" s="27"/>
+      <c r="P36" s="27"/>
+      <c r="Q36" s="27"/>
+      <c r="R36" s="27"/>
+      <c r="S36" s="27"/>
+      <c r="T36" s="27"/>
+    </row>
+    <row r="37" spans="8:20">
+      <c r="H37" s="24">
+        <v>27</v>
+      </c>
+      <c r="I37" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="J37" s="26">
+        <v>46230</v>
+      </c>
+      <c r="K37" s="28"/>
+      <c r="L37" s="27"/>
+      <c r="M37" s="27"/>
+      <c r="N37" s="27"/>
+      <c r="O37" s="27"/>
+      <c r="P37" s="27"/>
+      <c r="Q37" s="27"/>
+      <c r="R37" s="27"/>
+      <c r="S37" s="27"/>
+      <c r="T37" s="27"/>
+    </row>
+    <row r="38" spans="8:20">
+      <c r="H38" s="24">
+        <v>28</v>
+      </c>
+      <c r="I38" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="J38" s="26">
+        <v>46231</v>
+      </c>
+      <c r="K38" s="28"/>
+      <c r="L38" s="27"/>
+      <c r="M38" s="27"/>
+      <c r="N38" s="27"/>
+      <c r="O38" s="27"/>
+      <c r="P38" s="27"/>
+      <c r="Q38" s="27"/>
+      <c r="R38" s="27"/>
+      <c r="S38" s="27"/>
+      <c r="T38" s="27"/>
+    </row>
+    <row r="39" spans="8:20">
+      <c r="H39" s="24">
+        <v>29</v>
+      </c>
+      <c r="I39" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="J39" s="26">
+        <v>46232</v>
+      </c>
+      <c r="K39" s="27"/>
+      <c r="L39" s="27"/>
+      <c r="M39" s="27"/>
+      <c r="N39" s="27"/>
+      <c r="O39" s="27"/>
+      <c r="P39" s="27"/>
+      <c r="Q39" s="27"/>
+      <c r="R39" s="27"/>
+      <c r="S39" s="27"/>
+      <c r="T39" s="27"/>
+    </row>
+    <row r="40" spans="8:20">
+      <c r="H40" s="24">
+        <v>30</v>
+      </c>
+      <c r="I40" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="J40" s="26">
+        <v>46233</v>
+      </c>
+      <c r="K40" s="27"/>
+      <c r="L40" s="27"/>
+      <c r="M40" s="27"/>
+      <c r="N40" s="27"/>
+      <c r="O40" s="27"/>
+      <c r="P40" s="27"/>
+      <c r="Q40" s="27"/>
+      <c r="R40" s="27"/>
+      <c r="S40" s="27"/>
+      <c r="T40" s="27"/>
+    </row>
+    <row r="41" spans="8:20">
+      <c r="H41" s="24">
+        <v>31</v>
+      </c>
+      <c r="I41" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J41" s="26">
+        <v>46234</v>
+      </c>
+      <c r="K41" s="28"/>
+      <c r="L41" s="27"/>
+      <c r="M41" s="27"/>
+      <c r="N41" s="27"/>
+      <c r="O41" s="27"/>
+      <c r="P41" s="27"/>
+      <c r="Q41" s="27"/>
+      <c r="R41" s="27"/>
+      <c r="S41" s="27"/>
+      <c r="T41" s="27"/>
+    </row>
+    <row r="42" spans="8:20" ht="15.75">
+      <c r="H42" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="I42" s="29"/>
+      <c r="J42" s="29"/>
+      <c r="K42" s="30">
+        <f>COUNTA(K11:K41)</f>
+        <v>0</v>
+      </c>
+      <c r="L42" s="30">
+        <f t="shared" ref="L42:T42" si="0">COUNTA(L11:L41)</f>
+        <v>0</v>
+      </c>
+      <c r="M42" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N42" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O42" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P42" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q42" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R42" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="S42" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="H9:T9"/>
+    <mergeCell ref="H42:J42"/>
+  </mergeCells>
+  <conditionalFormatting sqref="O11:T42">
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>U11="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K11:N42 L42:T42">
+    <cfRule type="expression" dxfId="3" priority="3">
+      <formula>T11="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Другое/study_chart.xlsx
+++ b/Другое/study_chart.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="32">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -133,7 +133,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mmm"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -210,6 +210,13 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="Impact"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1C1917"/>
       <name val="Impact"/>
       <family val="2"/>
       <charset val="204"/>
@@ -418,7 +425,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -461,27 +468,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -504,12 +490,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -537,6 +517,42 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -899,18 +915,18 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:17" ht="45" customHeight="1">
-      <c r="H9" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="19"/>
-      <c r="Q9" s="20"/>
+      <c r="H9" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="37"/>
+      <c r="L9" s="37"/>
+      <c r="M9" s="37"/>
+      <c r="N9" s="37"/>
+      <c r="O9" s="37"/>
+      <c r="P9" s="37"/>
+      <c r="Q9" s="38"/>
     </row>
     <row r="10" spans="8:17" ht="30" customHeight="1">
       <c r="H10" s="2" t="s">
@@ -1179,11 +1195,11 @@
       <c r="Q21" s="8"/>
     </row>
     <row r="22" spans="8:17" ht="15.75">
-      <c r="H22" s="21" t="s">
+      <c r="H22" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="22"/>
-      <c r="J22" s="23"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="41"/>
       <c r="K22" s="4">
         <f>COUNTA(K11:K21)</f>
         <v>6</v>
@@ -1259,31 +1275,31 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:30" ht="45" customHeight="1">
-      <c r="H9" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="34"/>
-      <c r="M9" s="34"/>
-      <c r="N9" s="34"/>
-      <c r="O9" s="34"/>
-      <c r="P9" s="34"/>
-      <c r="Q9" s="34"/>
-      <c r="R9" s="34"/>
-      <c r="S9" s="34"/>
-      <c r="T9" s="34"/>
-      <c r="U9" s="34"/>
-      <c r="V9" s="34"/>
-      <c r="W9" s="34"/>
-      <c r="X9" s="34"/>
-      <c r="Y9" s="34"/>
-      <c r="Z9" s="34"/>
-      <c r="AA9" s="34"/>
-      <c r="AB9" s="34"/>
-      <c r="AC9" s="34"/>
-      <c r="AD9" s="34"/>
+      <c r="H9" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="I9" s="44"/>
+      <c r="J9" s="44"/>
+      <c r="K9" s="44"/>
+      <c r="L9" s="44"/>
+      <c r="M9" s="44"/>
+      <c r="N9" s="44"/>
+      <c r="O9" s="44"/>
+      <c r="P9" s="44"/>
+      <c r="Q9" s="44"/>
+      <c r="R9" s="44"/>
+      <c r="S9" s="44"/>
+      <c r="T9" s="44"/>
+      <c r="U9" s="44"/>
+      <c r="V9" s="44"/>
+      <c r="W9" s="44"/>
+      <c r="X9" s="44"/>
+      <c r="Y9" s="44"/>
+      <c r="Z9" s="44"/>
+      <c r="AA9" s="44"/>
+      <c r="AB9" s="44"/>
+      <c r="AC9" s="44"/>
+      <c r="AD9" s="44"/>
     </row>
     <row r="10" spans="8:30" ht="30" customHeight="1">
       <c r="H10" s="10" t="s">
@@ -1295,137 +1311,144 @@
       <c r="J10" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="K10" s="25" t="s">
+      <c r="K10" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="L10" s="25" t="s">
+      <c r="L10" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="M10" s="26" t="s">
+      <c r="M10" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="N10" s="27" t="s">
+      <c r="N10" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="O10" s="27" t="s">
+      <c r="O10" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="P10" s="27" t="s">
+      <c r="P10" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="Q10" s="27" t="s">
+      <c r="Q10" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="R10" s="29" t="s">
+      <c r="R10" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="S10" s="29" t="s">
+      <c r="S10" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="T10" s="30" t="s">
+      <c r="T10" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="U10" s="30" t="s">
+      <c r="U10" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="V10" s="29" t="s">
+      <c r="V10" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="W10" s="31" t="s">
+      <c r="W10" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="X10" s="32" t="s">
+      <c r="X10" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="Y10" s="31" t="s">
+      <c r="Y10" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="Z10" s="41" t="s">
+      <c r="Z10" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="AA10" s="43" t="s">
+      <c r="AA10" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="AB10" s="44" t="s">
+      <c r="AB10" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="AC10" s="44" t="s">
+      <c r="AC10" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="AD10" s="35" t="s">
+      <c r="AD10" s="26" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="8:30">
-      <c r="H11" s="36">
+    <row r="11" spans="8:30" ht="15.75">
+      <c r="H11" s="27">
         <v>1</v>
       </c>
-      <c r="I11" s="37" t="s">
+      <c r="I11" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="J11" s="38">
+      <c r="J11" s="29">
         <v>46204</v>
       </c>
-      <c r="K11" s="38"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="39"/>
-      <c r="N11" s="40"/>
-      <c r="O11" s="39"/>
-      <c r="P11" s="39"/>
-      <c r="Q11" s="39"/>
-      <c r="R11" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="S11" s="39"/>
-      <c r="T11" s="39"/>
-      <c r="U11" s="39"/>
-      <c r="V11" s="39"/>
-      <c r="W11" s="39"/>
-      <c r="X11" s="39"/>
-      <c r="Y11" s="39"/>
-      <c r="Z11" s="39"/>
-      <c r="AA11" s="42"/>
-      <c r="AB11" s="42"/>
-      <c r="AC11" s="42"/>
-      <c r="AD11" s="15">
-        <f>COUNTA(K11:Z11)</f>
+      <c r="K11" s="29"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="30"/>
+      <c r="P11" s="30"/>
+      <c r="Q11" s="30"/>
+      <c r="R11" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="S11" s="30"/>
+      <c r="T11" s="30"/>
+      <c r="U11" s="30"/>
+      <c r="V11" s="30"/>
+      <c r="W11" s="30"/>
+      <c r="X11" s="30"/>
+      <c r="Y11" s="30"/>
+      <c r="Z11" s="30"/>
+      <c r="AA11" s="33"/>
+      <c r="AB11" s="33"/>
+      <c r="AC11" s="33"/>
+      <c r="AD11" s="45">
+        <f>COUNTA(K11:AC11)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="8:30">
-      <c r="H12" s="12">
+    <row r="12" spans="8:30" ht="15.75">
+      <c r="H12" s="27">
         <v>2</v>
       </c>
-      <c r="I12" s="13" t="s">
+      <c r="I12" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="14">
+      <c r="J12" s="29">
         <v>46205</v>
       </c>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="15"/>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="15"/>
-      <c r="R12" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="S12" s="15"/>
-      <c r="T12" s="15"/>
-      <c r="U12" s="15"/>
-      <c r="V12" s="15"/>
-      <c r="W12" s="15"/>
-      <c r="X12" s="15"/>
-      <c r="Y12" s="15"/>
-      <c r="Z12" s="15"/>
-      <c r="AA12" s="15"/>
-      <c r="AB12" s="15"/>
-      <c r="AC12" s="15"/>
-      <c r="AD12" s="15"/>
-    </row>
-    <row r="13" spans="8:30">
+      <c r="K12" s="29"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="30"/>
+      <c r="N12" s="30"/>
+      <c r="O12" s="30"/>
+      <c r="P12" s="30"/>
+      <c r="Q12" s="30"/>
+      <c r="R12" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="S12" s="30"/>
+      <c r="T12" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="U12" s="30"/>
+      <c r="V12" s="30"/>
+      <c r="W12" s="30"/>
+      <c r="X12" s="30"/>
+      <c r="Y12" s="30"/>
+      <c r="Z12" s="30"/>
+      <c r="AA12" s="30"/>
+      <c r="AB12" s="30"/>
+      <c r="AC12" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD12" s="45">
+        <f t="shared" ref="AD12:AD41" si="0">COUNTA(K12:AC12)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="8:30" ht="15.75">
       <c r="H13" s="12">
         <v>3</v>
       </c>
@@ -1435,13 +1458,27 @@
       <c r="J13" s="14">
         <v>46206</v>
       </c>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16"/>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="16"/>
+      <c r="K13" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="L13" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="N13" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="O13" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="P13" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q13" s="16" t="s">
+        <v>12</v>
+      </c>
       <c r="R13" s="16"/>
       <c r="S13" s="16"/>
       <c r="T13" s="15"/>
@@ -1454,9 +1491,12 @@
       <c r="AA13" s="15"/>
       <c r="AB13" s="15"/>
       <c r="AC13" s="15"/>
-      <c r="AD13" s="15"/>
-    </row>
-    <row r="14" spans="8:30">
+      <c r="AD13" s="45">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="8:30" ht="15.75">
       <c r="H14" s="12">
         <v>4</v>
       </c>
@@ -1466,8 +1506,8 @@
       <c r="J14" s="14">
         <v>46207</v>
       </c>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
+      <c r="K14" s="47"/>
+      <c r="L14" s="47"/>
       <c r="M14" s="16"/>
       <c r="N14" s="16"/>
       <c r="O14" s="16"/>
@@ -1485,9 +1525,12 @@
       <c r="AA14" s="15"/>
       <c r="AB14" s="15"/>
       <c r="AC14" s="15"/>
-      <c r="AD14" s="15"/>
-    </row>
-    <row r="15" spans="8:30">
+      <c r="AD14" s="45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="8:30" ht="15.75">
       <c r="H15" s="12">
         <v>5</v>
       </c>
@@ -1497,8 +1540,8 @@
       <c r="J15" s="14">
         <v>46208</v>
       </c>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
+      <c r="K15" s="47"/>
+      <c r="L15" s="47"/>
       <c r="M15" s="15"/>
       <c r="N15" s="15"/>
       <c r="O15" s="15"/>
@@ -1516,9 +1559,12 @@
       <c r="AA15" s="15"/>
       <c r="AB15" s="15"/>
       <c r="AC15" s="15"/>
-      <c r="AD15" s="15"/>
-    </row>
-    <row r="16" spans="8:30">
+      <c r="AD15" s="45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="8:30" ht="15.75">
       <c r="H16" s="12">
         <v>6</v>
       </c>
@@ -1528,8 +1574,8 @@
       <c r="J16" s="14">
         <v>46209</v>
       </c>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
+      <c r="K16" s="47"/>
+      <c r="L16" s="47"/>
       <c r="M16" s="15"/>
       <c r="N16" s="15"/>
       <c r="O16" s="15"/>
@@ -1547,9 +1593,12 @@
       <c r="AA16" s="15"/>
       <c r="AB16" s="15"/>
       <c r="AC16" s="15"/>
-      <c r="AD16" s="15"/>
-    </row>
-    <row r="17" spans="8:30">
+      <c r="AD16" s="45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="8:30" ht="15.75">
       <c r="H17" s="12">
         <v>7</v>
       </c>
@@ -1559,8 +1608,8 @@
       <c r="J17" s="14">
         <v>46210</v>
       </c>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
+      <c r="K17" s="47"/>
+      <c r="L17" s="47"/>
       <c r="M17" s="16"/>
       <c r="N17" s="16"/>
       <c r="O17" s="16"/>
@@ -1578,9 +1627,12 @@
       <c r="AA17" s="15"/>
       <c r="AB17" s="15"/>
       <c r="AC17" s="15"/>
-      <c r="AD17" s="15"/>
-    </row>
-    <row r="18" spans="8:30">
+      <c r="AD17" s="45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="8:30" ht="15.75">
       <c r="H18" s="12">
         <v>8</v>
       </c>
@@ -1590,8 +1642,8 @@
       <c r="J18" s="14">
         <v>46211</v>
       </c>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
+      <c r="K18" s="47"/>
+      <c r="L18" s="47"/>
       <c r="M18" s="16"/>
       <c r="N18" s="16"/>
       <c r="O18" s="16"/>
@@ -1609,9 +1661,12 @@
       <c r="AA18" s="15"/>
       <c r="AB18" s="15"/>
       <c r="AC18" s="15"/>
-      <c r="AD18" s="15"/>
-    </row>
-    <row r="19" spans="8:30">
+      <c r="AD18" s="45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="8:30" ht="15.75">
       <c r="H19" s="12">
         <v>9</v>
       </c>
@@ -1621,8 +1676,8 @@
       <c r="J19" s="14">
         <v>46212</v>
       </c>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
+      <c r="K19" s="47"/>
+      <c r="L19" s="47"/>
       <c r="M19" s="15"/>
       <c r="N19" s="15"/>
       <c r="O19" s="15"/>
@@ -1640,9 +1695,12 @@
       <c r="AA19" s="15"/>
       <c r="AB19" s="15"/>
       <c r="AC19" s="15"/>
-      <c r="AD19" s="15"/>
-    </row>
-    <row r="20" spans="8:30">
+      <c r="AD19" s="45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="8:30" ht="15.75">
       <c r="H20" s="12">
         <v>10</v>
       </c>
@@ -1652,8 +1710,8 @@
       <c r="J20" s="14">
         <v>46213</v>
       </c>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
+      <c r="K20" s="47"/>
+      <c r="L20" s="47"/>
       <c r="M20" s="15"/>
       <c r="N20" s="15"/>
       <c r="O20" s="15"/>
@@ -1671,9 +1729,12 @@
       <c r="AA20" s="15"/>
       <c r="AB20" s="15"/>
       <c r="AC20" s="15"/>
-      <c r="AD20" s="15"/>
-    </row>
-    <row r="21" spans="8:30">
+      <c r="AD20" s="45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="8:30" ht="15.75">
       <c r="H21" s="12">
         <v>11</v>
       </c>
@@ -1683,8 +1744,8 @@
       <c r="J21" s="14">
         <v>46214</v>
       </c>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
+      <c r="K21" s="47"/>
+      <c r="L21" s="47"/>
       <c r="M21" s="16"/>
       <c r="N21" s="16"/>
       <c r="O21" s="16"/>
@@ -1702,9 +1763,12 @@
       <c r="AA21" s="15"/>
       <c r="AB21" s="15"/>
       <c r="AC21" s="15"/>
-      <c r="AD21" s="15"/>
-    </row>
-    <row r="22" spans="8:30">
+      <c r="AD21" s="45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="8:30" ht="15.75">
       <c r="H22" s="12">
         <v>12</v>
       </c>
@@ -1714,8 +1778,8 @@
       <c r="J22" s="14">
         <v>46215</v>
       </c>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
+      <c r="K22" s="47"/>
+      <c r="L22" s="47"/>
       <c r="M22" s="16"/>
       <c r="N22" s="16"/>
       <c r="O22" s="16"/>
@@ -1733,9 +1797,12 @@
       <c r="AA22" s="15"/>
       <c r="AB22" s="15"/>
       <c r="AC22" s="15"/>
-      <c r="AD22" s="15"/>
-    </row>
-    <row r="23" spans="8:30">
+      <c r="AD22" s="45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="8:30" ht="15.75">
       <c r="H23" s="12">
         <v>13</v>
       </c>
@@ -1745,8 +1812,8 @@
       <c r="J23" s="14">
         <v>46216</v>
       </c>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
+      <c r="K23" s="47"/>
+      <c r="L23" s="47"/>
       <c r="M23" s="15"/>
       <c r="N23" s="15"/>
       <c r="O23" s="15"/>
@@ -1764,9 +1831,12 @@
       <c r="AA23" s="15"/>
       <c r="AB23" s="15"/>
       <c r="AC23" s="15"/>
-      <c r="AD23" s="15"/>
-    </row>
-    <row r="24" spans="8:30">
+      <c r="AD23" s="45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="8:30" ht="15.75">
       <c r="H24" s="12">
         <v>14</v>
       </c>
@@ -1776,8 +1846,8 @@
       <c r="J24" s="14">
         <v>46217</v>
       </c>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
+      <c r="K24" s="47"/>
+      <c r="L24" s="47"/>
       <c r="M24" s="15"/>
       <c r="N24" s="15"/>
       <c r="O24" s="15"/>
@@ -1795,9 +1865,12 @@
       <c r="AA24" s="15"/>
       <c r="AB24" s="15"/>
       <c r="AC24" s="15"/>
-      <c r="AD24" s="15"/>
-    </row>
-    <row r="25" spans="8:30">
+      <c r="AD24" s="45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="8:30" ht="15.75">
       <c r="H25" s="12">
         <v>15</v>
       </c>
@@ -1807,8 +1880,8 @@
       <c r="J25" s="14">
         <v>46218</v>
       </c>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
+      <c r="K25" s="47"/>
+      <c r="L25" s="47"/>
       <c r="M25" s="16"/>
       <c r="N25" s="16"/>
       <c r="O25" s="16"/>
@@ -1826,9 +1899,12 @@
       <c r="AA25" s="15"/>
       <c r="AB25" s="15"/>
       <c r="AC25" s="15"/>
-      <c r="AD25" s="15"/>
-    </row>
-    <row r="26" spans="8:30">
+      <c r="AD25" s="45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="8:30" ht="15.75">
       <c r="H26" s="12">
         <v>16</v>
       </c>
@@ -1838,8 +1914,8 @@
       <c r="J26" s="14">
         <v>46219</v>
       </c>
-      <c r="K26" s="14"/>
-      <c r="L26" s="14"/>
+      <c r="K26" s="47"/>
+      <c r="L26" s="47"/>
       <c r="M26" s="16"/>
       <c r="N26" s="16"/>
       <c r="O26" s="16"/>
@@ -1857,9 +1933,12 @@
       <c r="AA26" s="15"/>
       <c r="AB26" s="15"/>
       <c r="AC26" s="15"/>
-      <c r="AD26" s="15"/>
-    </row>
-    <row r="27" spans="8:30">
+      <c r="AD26" s="45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="8:30" ht="15.75">
       <c r="H27" s="12">
         <v>17</v>
       </c>
@@ -1869,8 +1948,8 @@
       <c r="J27" s="14">
         <v>46220</v>
       </c>
-      <c r="K27" s="14"/>
-      <c r="L27" s="14"/>
+      <c r="K27" s="47"/>
+      <c r="L27" s="47"/>
       <c r="M27" s="15"/>
       <c r="N27" s="15"/>
       <c r="O27" s="15"/>
@@ -1888,9 +1967,12 @@
       <c r="AA27" s="15"/>
       <c r="AB27" s="15"/>
       <c r="AC27" s="15"/>
-      <c r="AD27" s="15"/>
-    </row>
-    <row r="28" spans="8:30">
+      <c r="AD27" s="45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="8:30" ht="15.75">
       <c r="H28" s="12">
         <v>18</v>
       </c>
@@ -1900,8 +1982,8 @@
       <c r="J28" s="14">
         <v>46221</v>
       </c>
-      <c r="K28" s="14"/>
-      <c r="L28" s="14"/>
+      <c r="K28" s="47"/>
+      <c r="L28" s="47"/>
       <c r="M28" s="15"/>
       <c r="N28" s="15"/>
       <c r="O28" s="15"/>
@@ -1919,9 +2001,12 @@
       <c r="AA28" s="15"/>
       <c r="AB28" s="15"/>
       <c r="AC28" s="15"/>
-      <c r="AD28" s="15"/>
-    </row>
-    <row r="29" spans="8:30">
+      <c r="AD28" s="45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="8:30" ht="15.75">
       <c r="H29" s="12">
         <v>19</v>
       </c>
@@ -1931,8 +2016,8 @@
       <c r="J29" s="14">
         <v>46222</v>
       </c>
-      <c r="K29" s="14"/>
-      <c r="L29" s="14"/>
+      <c r="K29" s="47"/>
+      <c r="L29" s="47"/>
       <c r="M29" s="16"/>
       <c r="N29" s="16"/>
       <c r="O29" s="16"/>
@@ -1950,9 +2035,12 @@
       <c r="AA29" s="15"/>
       <c r="AB29" s="15"/>
       <c r="AC29" s="15"/>
-      <c r="AD29" s="15"/>
-    </row>
-    <row r="30" spans="8:30">
+      <c r="AD29" s="45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="8:30" ht="15.75">
       <c r="H30" s="12">
         <v>20</v>
       </c>
@@ -1962,8 +2050,8 @@
       <c r="J30" s="14">
         <v>46223</v>
       </c>
-      <c r="K30" s="14"/>
-      <c r="L30" s="14"/>
+      <c r="K30" s="47"/>
+      <c r="L30" s="47"/>
       <c r="M30" s="16"/>
       <c r="N30" s="16"/>
       <c r="O30" s="16"/>
@@ -1981,9 +2069,12 @@
       <c r="AA30" s="15"/>
       <c r="AB30" s="15"/>
       <c r="AC30" s="15"/>
-      <c r="AD30" s="15"/>
-    </row>
-    <row r="31" spans="8:30">
+      <c r="AD30" s="45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="8:30" ht="15.75">
       <c r="H31" s="12">
         <v>21</v>
       </c>
@@ -1993,8 +2084,8 @@
       <c r="J31" s="14">
         <v>46224</v>
       </c>
-      <c r="K31" s="14"/>
-      <c r="L31" s="14"/>
+      <c r="K31" s="47"/>
+      <c r="L31" s="47"/>
       <c r="M31" s="15"/>
       <c r="N31" s="15"/>
       <c r="O31" s="15"/>
@@ -2012,9 +2103,12 @@
       <c r="AA31" s="15"/>
       <c r="AB31" s="15"/>
       <c r="AC31" s="15"/>
-      <c r="AD31" s="15"/>
-    </row>
-    <row r="32" spans="8:30">
+      <c r="AD31" s="45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="8:30" ht="15.75">
       <c r="H32" s="12">
         <v>22</v>
       </c>
@@ -2024,8 +2118,8 @@
       <c r="J32" s="14">
         <v>46225</v>
       </c>
-      <c r="K32" s="14"/>
-      <c r="L32" s="14"/>
+      <c r="K32" s="47"/>
+      <c r="L32" s="47"/>
       <c r="M32" s="15"/>
       <c r="N32" s="15"/>
       <c r="O32" s="15"/>
@@ -2043,9 +2137,12 @@
       <c r="AA32" s="15"/>
       <c r="AB32" s="15"/>
       <c r="AC32" s="15"/>
-      <c r="AD32" s="15"/>
-    </row>
-    <row r="33" spans="8:30">
+      <c r="AD32" s="45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="8:30" ht="15.75">
       <c r="H33" s="12">
         <v>23</v>
       </c>
@@ -2055,8 +2152,8 @@
       <c r="J33" s="14">
         <v>46226</v>
       </c>
-      <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
+      <c r="K33" s="47"/>
+      <c r="L33" s="47"/>
       <c r="M33" s="16"/>
       <c r="N33" s="16"/>
       <c r="O33" s="16"/>
@@ -2074,9 +2171,12 @@
       <c r="AA33" s="15"/>
       <c r="AB33" s="15"/>
       <c r="AC33" s="15"/>
-      <c r="AD33" s="15"/>
-    </row>
-    <row r="34" spans="8:30">
+      <c r="AD33" s="45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="8:30" ht="15.75">
       <c r="H34" s="12">
         <v>24</v>
       </c>
@@ -2086,8 +2186,8 @@
       <c r="J34" s="14">
         <v>46227</v>
       </c>
-      <c r="K34" s="14"/>
-      <c r="L34" s="14"/>
+      <c r="K34" s="47"/>
+      <c r="L34" s="47"/>
       <c r="M34" s="16"/>
       <c r="N34" s="16"/>
       <c r="O34" s="16"/>
@@ -2105,9 +2205,12 @@
       <c r="AA34" s="15"/>
       <c r="AB34" s="15"/>
       <c r="AC34" s="15"/>
-      <c r="AD34" s="15"/>
-    </row>
-    <row r="35" spans="8:30">
+      <c r="AD34" s="45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="8:30" ht="15.75">
       <c r="H35" s="12">
         <v>25</v>
       </c>
@@ -2117,8 +2220,8 @@
       <c r="J35" s="14">
         <v>46228</v>
       </c>
-      <c r="K35" s="14"/>
-      <c r="L35" s="14"/>
+      <c r="K35" s="47"/>
+      <c r="L35" s="47"/>
       <c r="M35" s="15"/>
       <c r="N35" s="15"/>
       <c r="O35" s="15"/>
@@ -2136,9 +2239,12 @@
       <c r="AA35" s="15"/>
       <c r="AB35" s="15"/>
       <c r="AC35" s="15"/>
-      <c r="AD35" s="15"/>
-    </row>
-    <row r="36" spans="8:30">
+      <c r="AD35" s="45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="8:30" ht="15.75">
       <c r="H36" s="12">
         <v>26</v>
       </c>
@@ -2148,8 +2254,8 @@
       <c r="J36" s="14">
         <v>46229</v>
       </c>
-      <c r="K36" s="14"/>
-      <c r="L36" s="14"/>
+      <c r="K36" s="47"/>
+      <c r="L36" s="47"/>
       <c r="M36" s="15"/>
       <c r="N36" s="15"/>
       <c r="O36" s="15"/>
@@ -2167,9 +2273,12 @@
       <c r="AA36" s="15"/>
       <c r="AB36" s="15"/>
       <c r="AC36" s="15"/>
-      <c r="AD36" s="15"/>
-    </row>
-    <row r="37" spans="8:30">
+      <c r="AD36" s="45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="8:30" ht="15.75">
       <c r="H37" s="12">
         <v>27</v>
       </c>
@@ -2179,8 +2288,8 @@
       <c r="J37" s="14">
         <v>46230</v>
       </c>
-      <c r="K37" s="14"/>
-      <c r="L37" s="14"/>
+      <c r="K37" s="47"/>
+      <c r="L37" s="47"/>
       <c r="M37" s="16"/>
       <c r="N37" s="16"/>
       <c r="O37" s="16"/>
@@ -2198,9 +2307,12 @@
       <c r="AA37" s="15"/>
       <c r="AB37" s="15"/>
       <c r="AC37" s="15"/>
-      <c r="AD37" s="15"/>
-    </row>
-    <row r="38" spans="8:30">
+      <c r="AD37" s="45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="8:30" ht="15.75">
       <c r="H38" s="12">
         <v>28</v>
       </c>
@@ -2210,8 +2322,8 @@
       <c r="J38" s="14">
         <v>46231</v>
       </c>
-      <c r="K38" s="14"/>
-      <c r="L38" s="14"/>
+      <c r="K38" s="47"/>
+      <c r="L38" s="47"/>
       <c r="M38" s="16"/>
       <c r="N38" s="16"/>
       <c r="O38" s="16"/>
@@ -2229,9 +2341,12 @@
       <c r="AA38" s="15"/>
       <c r="AB38" s="15"/>
       <c r="AC38" s="15"/>
-      <c r="AD38" s="15"/>
-    </row>
-    <row r="39" spans="8:30">
+      <c r="AD38" s="45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="8:30" ht="15.75">
       <c r="H39" s="12">
         <v>29</v>
       </c>
@@ -2241,8 +2356,8 @@
       <c r="J39" s="14">
         <v>46232</v>
       </c>
-      <c r="K39" s="14"/>
-      <c r="L39" s="14"/>
+      <c r="K39" s="47"/>
+      <c r="L39" s="47"/>
       <c r="M39" s="15"/>
       <c r="N39" s="15"/>
       <c r="O39" s="15"/>
@@ -2260,9 +2375,12 @@
       <c r="AA39" s="15"/>
       <c r="AB39" s="15"/>
       <c r="AC39" s="15"/>
-      <c r="AD39" s="15"/>
-    </row>
-    <row r="40" spans="8:30">
+      <c r="AD39" s="45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="8:30" ht="15.75">
       <c r="H40" s="12">
         <v>30</v>
       </c>
@@ -2272,8 +2390,8 @@
       <c r="J40" s="14">
         <v>46233</v>
       </c>
-      <c r="K40" s="14"/>
-      <c r="L40" s="14"/>
+      <c r="K40" s="47"/>
+      <c r="L40" s="47"/>
       <c r="M40" s="15"/>
       <c r="N40" s="15"/>
       <c r="O40" s="15"/>
@@ -2291,9 +2409,12 @@
       <c r="AA40" s="15"/>
       <c r="AB40" s="15"/>
       <c r="AC40" s="15"/>
-      <c r="AD40" s="15"/>
-    </row>
-    <row r="41" spans="8:30">
+      <c r="AD40" s="45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="8:30" ht="15.75">
       <c r="H41" s="12">
         <v>31</v>
       </c>
@@ -2303,8 +2424,8 @@
       <c r="J41" s="14">
         <v>46234</v>
       </c>
-      <c r="K41" s="14"/>
-      <c r="L41" s="14"/>
+      <c r="K41" s="47"/>
+      <c r="L41" s="47"/>
       <c r="M41" s="16"/>
       <c r="N41" s="16"/>
       <c r="O41" s="16"/>
@@ -2322,84 +2443,87 @@
       <c r="AA41" s="15"/>
       <c r="AB41" s="15"/>
       <c r="AC41" s="15"/>
-      <c r="AD41" s="15"/>
+      <c r="AD41" s="45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="42" spans="8:30" ht="15.75">
-      <c r="H42" s="24" t="s">
+      <c r="H42" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="I42" s="24"/>
-      <c r="J42" s="24"/>
-      <c r="K42" s="28">
+      <c r="I42" s="42"/>
+      <c r="J42" s="42"/>
+      <c r="K42" s="21">
         <f>COUNTA(K11:K41)</f>
-        <v>0</v>
-      </c>
-      <c r="L42" s="28">
-        <f t="shared" ref="L42:Z42" si="0">COUNTA(L11:L41)</f>
-        <v>0</v>
-      </c>
-      <c r="M42" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N42" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O42" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P42" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q42" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R42" s="28">
-        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L42" s="21">
+        <f t="shared" ref="L42:Z42" si="1">COUNTA(L11:L41)</f>
+        <v>1</v>
+      </c>
+      <c r="M42" s="21">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N42" s="21">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="O42" s="21">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P42" s="21">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Q42" s="21">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="R42" s="21">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="S42" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T42" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U42" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V42" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W42" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X42" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y42" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Z42" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AA42" s="28"/>
-      <c r="AB42" s="28"/>
-      <c r="AC42" s="28"/>
+      <c r="S42" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="21">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="U42" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V42" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W42" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X42" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y42" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z42" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA42" s="21"/>
+      <c r="AB42" s="21"/>
+      <c r="AC42" s="21"/>
       <c r="AD42" s="17">
-        <f t="shared" ref="AD42" si="1">COUNTA(AD11:AD41)</f>
-        <v>1</v>
+        <f t="shared" ref="AD42" si="2">COUNTA(AD11:AD41)</f>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/Другое/study_chart.xlsx
+++ b/Другое/study_chart.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROG\Git\Repository_1\Другое\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10530" activeTab="1"/>
   </bookViews>
@@ -10,7 +15,7 @@
     <sheet name="Июнь" sheetId="1" r:id="rId1"/>
     <sheet name="Июль" sheetId="4" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="32">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -129,11 +134,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mmm"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -518,6 +523,12 @@
     <xf numFmtId="0" fontId="8" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -545,13 +556,7 @@
     <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -657,7 +662,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -689,9 +694,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -723,6 +729,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -898,9 +905,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="H9:Q22"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="7" width="9.140625" style="1"/>
     <col min="8" max="8" width="5" style="1" customWidth="1"/>
@@ -914,21 +921,21 @@
     <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="8:17" ht="45" customHeight="1">
-      <c r="H9" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="I9" s="37"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="37"/>
-      <c r="L9" s="37"/>
-      <c r="M9" s="37"/>
-      <c r="N9" s="37"/>
-      <c r="O9" s="37"/>
-      <c r="P9" s="37"/>
-      <c r="Q9" s="38"/>
-    </row>
-    <row r="10" spans="8:17" ht="30" customHeight="1">
+    <row r="9" spans="8:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H9" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="I9" s="39"/>
+      <c r="J9" s="39"/>
+      <c r="K9" s="39"/>
+      <c r="L9" s="39"/>
+      <c r="M9" s="39"/>
+      <c r="N9" s="39"/>
+      <c r="O9" s="39"/>
+      <c r="P9" s="39"/>
+      <c r="Q9" s="40"/>
+    </row>
+    <row r="10" spans="8:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H10" s="2" t="s">
         <v>1</v>
       </c>
@@ -960,7 +967,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="8:17">
+    <row r="11" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H11" s="5">
         <v>1</v>
       </c>
@@ -986,7 +993,7 @@
       <c r="P11" s="8"/>
       <c r="Q11" s="8"/>
     </row>
-    <row r="12" spans="8:17">
+    <row r="12" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H12" s="5">
         <v>2</v>
       </c>
@@ -1010,7 +1017,7 @@
       <c r="P12" s="8"/>
       <c r="Q12" s="8"/>
     </row>
-    <row r="13" spans="8:17">
+    <row r="13" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H13" s="5">
         <v>3</v>
       </c>
@@ -1032,7 +1039,7 @@
       <c r="P13" s="8"/>
       <c r="Q13" s="8"/>
     </row>
-    <row r="14" spans="8:17">
+    <row r="14" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H14" s="5">
         <v>4</v>
       </c>
@@ -1054,7 +1061,7 @@
       <c r="P14" s="8"/>
       <c r="Q14" s="8"/>
     </row>
-    <row r="15" spans="8:17">
+    <row r="15" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H15" s="5">
         <v>5</v>
       </c>
@@ -1074,7 +1081,7 @@
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
     </row>
-    <row r="16" spans="8:17">
+    <row r="16" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H16" s="5">
         <v>6</v>
       </c>
@@ -1098,7 +1105,7 @@
       <c r="P16" s="8"/>
       <c r="Q16" s="8"/>
     </row>
-    <row r="17" spans="8:17">
+    <row r="17" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H17" s="5">
         <v>7</v>
       </c>
@@ -1120,7 +1127,7 @@
       <c r="P17" s="8"/>
       <c r="Q17" s="8"/>
     </row>
-    <row r="18" spans="8:17">
+    <row r="18" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H18" s="5">
         <v>8</v>
       </c>
@@ -1138,7 +1145,7 @@
       <c r="P18" s="8"/>
       <c r="Q18" s="8"/>
     </row>
-    <row r="19" spans="8:17">
+    <row r="19" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H19" s="5">
         <v>9</v>
       </c>
@@ -1158,7 +1165,7 @@
       <c r="P19" s="8"/>
       <c r="Q19" s="8"/>
     </row>
-    <row r="20" spans="8:17">
+    <row r="20" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H20" s="5">
         <v>10</v>
       </c>
@@ -1176,7 +1183,7 @@
       <c r="P20" s="8"/>
       <c r="Q20" s="8"/>
     </row>
-    <row r="21" spans="8:17">
+    <row r="21" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H21" s="5">
         <v>11</v>
       </c>
@@ -1194,12 +1201,12 @@
       <c r="P21" s="8"/>
       <c r="Q21" s="8"/>
     </row>
-    <row r="22" spans="8:17" ht="15.75">
-      <c r="H22" s="39" t="s">
+    <row r="22" spans="8:17" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="H22" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="40"/>
-      <c r="J22" s="41"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="43"/>
       <c r="K22" s="4">
         <f>COUNTA(K11:K21)</f>
         <v>6</v>
@@ -1250,9 +1257,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="H9:AD42"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="7" width="9.140625" style="1"/>
     <col min="8" max="8" width="5" style="1" customWidth="1"/>
@@ -1274,34 +1281,34 @@
     <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="9" spans="8:30" ht="45" customHeight="1">
-      <c r="H9" s="43" t="s">
-        <v>0</v>
-      </c>
-      <c r="I9" s="44"/>
-      <c r="J9" s="44"/>
-      <c r="K9" s="44"/>
-      <c r="L9" s="44"/>
-      <c r="M9" s="44"/>
-      <c r="N9" s="44"/>
-      <c r="O9" s="44"/>
-      <c r="P9" s="44"/>
-      <c r="Q9" s="44"/>
-      <c r="R9" s="44"/>
-      <c r="S9" s="44"/>
-      <c r="T9" s="44"/>
-      <c r="U9" s="44"/>
-      <c r="V9" s="44"/>
-      <c r="W9" s="44"/>
-      <c r="X9" s="44"/>
-      <c r="Y9" s="44"/>
-      <c r="Z9" s="44"/>
-      <c r="AA9" s="44"/>
-      <c r="AB9" s="44"/>
-      <c r="AC9" s="44"/>
-      <c r="AD9" s="44"/>
-    </row>
-    <row r="10" spans="8:30" ht="30" customHeight="1">
+    <row r="9" spans="8:30" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H9" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="I9" s="46"/>
+      <c r="J9" s="46"/>
+      <c r="K9" s="46"/>
+      <c r="L9" s="46"/>
+      <c r="M9" s="46"/>
+      <c r="N9" s="46"/>
+      <c r="O9" s="46"/>
+      <c r="P9" s="46"/>
+      <c r="Q9" s="46"/>
+      <c r="R9" s="46"/>
+      <c r="S9" s="46"/>
+      <c r="T9" s="46"/>
+      <c r="U9" s="46"/>
+      <c r="V9" s="46"/>
+      <c r="W9" s="46"/>
+      <c r="X9" s="46"/>
+      <c r="Y9" s="46"/>
+      <c r="Z9" s="46"/>
+      <c r="AA9" s="46"/>
+      <c r="AB9" s="46"/>
+      <c r="AC9" s="46"/>
+      <c r="AD9" s="46"/>
+    </row>
+    <row r="10" spans="8:30" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H10" s="10" t="s">
         <v>1</v>
       </c>
@@ -1372,7 +1379,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="8:30" ht="15.75">
+    <row r="11" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H11" s="27">
         <v>1</v>
       </c>
@@ -1403,12 +1410,12 @@
       <c r="AA11" s="33"/>
       <c r="AB11" s="33"/>
       <c r="AC11" s="33"/>
-      <c r="AD11" s="45">
+      <c r="AD11" s="36">
         <f>COUNTA(K11:AC11)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="8:30" ht="15.75">
+    <row r="12" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H12" s="27">
         <v>2</v>
       </c>
@@ -1443,60 +1450,62 @@
       <c r="AC12" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="AD12" s="45">
+      <c r="AD12" s="36">
         <f t="shared" ref="AD12:AD41" si="0">COUNTA(K12:AC12)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="8:30" ht="15.75">
-      <c r="H13" s="12">
+    <row r="13" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="H13" s="27">
         <v>3</v>
       </c>
-      <c r="I13" s="13" t="s">
+      <c r="I13" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="J13" s="14">
+      <c r="J13" s="29">
         <v>46206</v>
       </c>
-      <c r="K13" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="L13" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="M13" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="N13" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="O13" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="P13" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q13" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="R13" s="16"/>
-      <c r="S13" s="16"/>
-      <c r="T13" s="15"/>
-      <c r="U13" s="15"/>
-      <c r="V13" s="15"/>
-      <c r="W13" s="16"/>
-      <c r="X13" s="15"/>
-      <c r="Y13" s="15"/>
-      <c r="Z13" s="15"/>
-      <c r="AA13" s="15"/>
-      <c r="AB13" s="15"/>
-      <c r="AC13" s="15"/>
-      <c r="AD13" s="45">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="8:30" ht="15.75">
+      <c r="K13" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="L13" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="M13" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="N13" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="O13" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="P13" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q13" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="R13" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="S13" s="31"/>
+      <c r="T13" s="30"/>
+      <c r="U13" s="30"/>
+      <c r="V13" s="30"/>
+      <c r="W13" s="31"/>
+      <c r="X13" s="30"/>
+      <c r="Y13" s="30"/>
+      <c r="Z13" s="30"/>
+      <c r="AA13" s="30"/>
+      <c r="AB13" s="30"/>
+      <c r="AC13" s="30"/>
+      <c r="AD13" s="36">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H14" s="12">
         <v>4</v>
       </c>
@@ -1506,12 +1515,16 @@
       <c r="J14" s="14">
         <v>46207</v>
       </c>
-      <c r="K14" s="47"/>
-      <c r="L14" s="47"/>
+      <c r="K14" s="37"/>
+      <c r="L14" s="37"/>
       <c r="M14" s="16"/>
       <c r="N14" s="16"/>
-      <c r="O14" s="16"/>
-      <c r="P14" s="16"/>
+      <c r="O14" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="P14" s="16" t="s">
+        <v>12</v>
+      </c>
       <c r="Q14" s="16"/>
       <c r="R14" s="16"/>
       <c r="S14" s="16"/>
@@ -1525,12 +1538,12 @@
       <c r="AA14" s="15"/>
       <c r="AB14" s="15"/>
       <c r="AC14" s="15"/>
-      <c r="AD14" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="8:30" ht="15.75">
+      <c r="AD14" s="36">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H15" s="12">
         <v>5</v>
       </c>
@@ -1540,8 +1553,8 @@
       <c r="J15" s="14">
         <v>46208</v>
       </c>
-      <c r="K15" s="47"/>
-      <c r="L15" s="47"/>
+      <c r="K15" s="37"/>
+      <c r="L15" s="37"/>
       <c r="M15" s="15"/>
       <c r="N15" s="15"/>
       <c r="O15" s="15"/>
@@ -1559,12 +1572,12 @@
       <c r="AA15" s="15"/>
       <c r="AB15" s="15"/>
       <c r="AC15" s="15"/>
-      <c r="AD15" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="8:30" ht="15.75">
+      <c r="AD15" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H16" s="12">
         <v>6</v>
       </c>
@@ -1574,8 +1587,8 @@
       <c r="J16" s="14">
         <v>46209</v>
       </c>
-      <c r="K16" s="47"/>
-      <c r="L16" s="47"/>
+      <c r="K16" s="37"/>
+      <c r="L16" s="37"/>
       <c r="M16" s="15"/>
       <c r="N16" s="15"/>
       <c r="O16" s="15"/>
@@ -1593,12 +1606,12 @@
       <c r="AA16" s="15"/>
       <c r="AB16" s="15"/>
       <c r="AC16" s="15"/>
-      <c r="AD16" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="8:30" ht="15.75">
+      <c r="AD16" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H17" s="12">
         <v>7</v>
       </c>
@@ -1608,8 +1621,8 @@
       <c r="J17" s="14">
         <v>46210</v>
       </c>
-      <c r="K17" s="47"/>
-      <c r="L17" s="47"/>
+      <c r="K17" s="37"/>
+      <c r="L17" s="37"/>
       <c r="M17" s="16"/>
       <c r="N17" s="16"/>
       <c r="O17" s="16"/>
@@ -1627,12 +1640,12 @@
       <c r="AA17" s="15"/>
       <c r="AB17" s="15"/>
       <c r="AC17" s="15"/>
-      <c r="AD17" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="8:30" ht="15.75">
+      <c r="AD17" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H18" s="12">
         <v>8</v>
       </c>
@@ -1642,8 +1655,8 @@
       <c r="J18" s="14">
         <v>46211</v>
       </c>
-      <c r="K18" s="47"/>
-      <c r="L18" s="47"/>
+      <c r="K18" s="37"/>
+      <c r="L18" s="37"/>
       <c r="M18" s="16"/>
       <c r="N18" s="16"/>
       <c r="O18" s="16"/>
@@ -1661,12 +1674,12 @@
       <c r="AA18" s="15"/>
       <c r="AB18" s="15"/>
       <c r="AC18" s="15"/>
-      <c r="AD18" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="8:30" ht="15.75">
+      <c r="AD18" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H19" s="12">
         <v>9</v>
       </c>
@@ -1676,8 +1689,8 @@
       <c r="J19" s="14">
         <v>46212</v>
       </c>
-      <c r="K19" s="47"/>
-      <c r="L19" s="47"/>
+      <c r="K19" s="37"/>
+      <c r="L19" s="37"/>
       <c r="M19" s="15"/>
       <c r="N19" s="15"/>
       <c r="O19" s="15"/>
@@ -1695,12 +1708,12 @@
       <c r="AA19" s="15"/>
       <c r="AB19" s="15"/>
       <c r="AC19" s="15"/>
-      <c r="AD19" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="8:30" ht="15.75">
+      <c r="AD19" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H20" s="12">
         <v>10</v>
       </c>
@@ -1710,8 +1723,8 @@
       <c r="J20" s="14">
         <v>46213</v>
       </c>
-      <c r="K20" s="47"/>
-      <c r="L20" s="47"/>
+      <c r="K20" s="37"/>
+      <c r="L20" s="37"/>
       <c r="M20" s="15"/>
       <c r="N20" s="15"/>
       <c r="O20" s="15"/>
@@ -1729,12 +1742,12 @@
       <c r="AA20" s="15"/>
       <c r="AB20" s="15"/>
       <c r="AC20" s="15"/>
-      <c r="AD20" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="8:30" ht="15.75">
+      <c r="AD20" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H21" s="12">
         <v>11</v>
       </c>
@@ -1744,8 +1757,8 @@
       <c r="J21" s="14">
         <v>46214</v>
       </c>
-      <c r="K21" s="47"/>
-      <c r="L21" s="47"/>
+      <c r="K21" s="37"/>
+      <c r="L21" s="37"/>
       <c r="M21" s="16"/>
       <c r="N21" s="16"/>
       <c r="O21" s="16"/>
@@ -1763,12 +1776,12 @@
       <c r="AA21" s="15"/>
       <c r="AB21" s="15"/>
       <c r="AC21" s="15"/>
-      <c r="AD21" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="8:30" ht="15.75">
+      <c r="AD21" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H22" s="12">
         <v>12</v>
       </c>
@@ -1778,8 +1791,8 @@
       <c r="J22" s="14">
         <v>46215</v>
       </c>
-      <c r="K22" s="47"/>
-      <c r="L22" s="47"/>
+      <c r="K22" s="37"/>
+      <c r="L22" s="37"/>
       <c r="M22" s="16"/>
       <c r="N22" s="16"/>
       <c r="O22" s="16"/>
@@ -1797,12 +1810,12 @@
       <c r="AA22" s="15"/>
       <c r="AB22" s="15"/>
       <c r="AC22" s="15"/>
-      <c r="AD22" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="8:30" ht="15.75">
+      <c r="AD22" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H23" s="12">
         <v>13</v>
       </c>
@@ -1812,8 +1825,8 @@
       <c r="J23" s="14">
         <v>46216</v>
       </c>
-      <c r="K23" s="47"/>
-      <c r="L23" s="47"/>
+      <c r="K23" s="37"/>
+      <c r="L23" s="37"/>
       <c r="M23" s="15"/>
       <c r="N23" s="15"/>
       <c r="O23" s="15"/>
@@ -1831,12 +1844,12 @@
       <c r="AA23" s="15"/>
       <c r="AB23" s="15"/>
       <c r="AC23" s="15"/>
-      <c r="AD23" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="8:30" ht="15.75">
+      <c r="AD23" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H24" s="12">
         <v>14</v>
       </c>
@@ -1846,8 +1859,8 @@
       <c r="J24" s="14">
         <v>46217</v>
       </c>
-      <c r="K24" s="47"/>
-      <c r="L24" s="47"/>
+      <c r="K24" s="37"/>
+      <c r="L24" s="37"/>
       <c r="M24" s="15"/>
       <c r="N24" s="15"/>
       <c r="O24" s="15"/>
@@ -1865,12 +1878,12 @@
       <c r="AA24" s="15"/>
       <c r="AB24" s="15"/>
       <c r="AC24" s="15"/>
-      <c r="AD24" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="8:30" ht="15.75">
+      <c r="AD24" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H25" s="12">
         <v>15</v>
       </c>
@@ -1880,8 +1893,8 @@
       <c r="J25" s="14">
         <v>46218</v>
       </c>
-      <c r="K25" s="47"/>
-      <c r="L25" s="47"/>
+      <c r="K25" s="37"/>
+      <c r="L25" s="37"/>
       <c r="M25" s="16"/>
       <c r="N25" s="16"/>
       <c r="O25" s="16"/>
@@ -1899,12 +1912,12 @@
       <c r="AA25" s="15"/>
       <c r="AB25" s="15"/>
       <c r="AC25" s="15"/>
-      <c r="AD25" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="8:30" ht="15.75">
+      <c r="AD25" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H26" s="12">
         <v>16</v>
       </c>
@@ -1914,8 +1927,8 @@
       <c r="J26" s="14">
         <v>46219</v>
       </c>
-      <c r="K26" s="47"/>
-      <c r="L26" s="47"/>
+      <c r="K26" s="37"/>
+      <c r="L26" s="37"/>
       <c r="M26" s="16"/>
       <c r="N26" s="16"/>
       <c r="O26" s="16"/>
@@ -1933,12 +1946,12 @@
       <c r="AA26" s="15"/>
       <c r="AB26" s="15"/>
       <c r="AC26" s="15"/>
-      <c r="AD26" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="8:30" ht="15.75">
+      <c r="AD26" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H27" s="12">
         <v>17</v>
       </c>
@@ -1948,8 +1961,8 @@
       <c r="J27" s="14">
         <v>46220</v>
       </c>
-      <c r="K27" s="47"/>
-      <c r="L27" s="47"/>
+      <c r="K27" s="37"/>
+      <c r="L27" s="37"/>
       <c r="M27" s="15"/>
       <c r="N27" s="15"/>
       <c r="O27" s="15"/>
@@ -1967,12 +1980,12 @@
       <c r="AA27" s="15"/>
       <c r="AB27" s="15"/>
       <c r="AC27" s="15"/>
-      <c r="AD27" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="8:30" ht="15.75">
+      <c r="AD27" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H28" s="12">
         <v>18</v>
       </c>
@@ -1982,8 +1995,8 @@
       <c r="J28" s="14">
         <v>46221</v>
       </c>
-      <c r="K28" s="47"/>
-      <c r="L28" s="47"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="37"/>
       <c r="M28" s="15"/>
       <c r="N28" s="15"/>
       <c r="O28" s="15"/>
@@ -2001,12 +2014,12 @@
       <c r="AA28" s="15"/>
       <c r="AB28" s="15"/>
       <c r="AC28" s="15"/>
-      <c r="AD28" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="8:30" ht="15.75">
+      <c r="AD28" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H29" s="12">
         <v>19</v>
       </c>
@@ -2016,8 +2029,8 @@
       <c r="J29" s="14">
         <v>46222</v>
       </c>
-      <c r="K29" s="47"/>
-      <c r="L29" s="47"/>
+      <c r="K29" s="37"/>
+      <c r="L29" s="37"/>
       <c r="M29" s="16"/>
       <c r="N29" s="16"/>
       <c r="O29" s="16"/>
@@ -2035,12 +2048,12 @@
       <c r="AA29" s="15"/>
       <c r="AB29" s="15"/>
       <c r="AC29" s="15"/>
-      <c r="AD29" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="8:30" ht="15.75">
+      <c r="AD29" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H30" s="12">
         <v>20</v>
       </c>
@@ -2050,8 +2063,8 @@
       <c r="J30" s="14">
         <v>46223</v>
       </c>
-      <c r="K30" s="47"/>
-      <c r="L30" s="47"/>
+      <c r="K30" s="37"/>
+      <c r="L30" s="37"/>
       <c r="M30" s="16"/>
       <c r="N30" s="16"/>
       <c r="O30" s="16"/>
@@ -2069,12 +2082,12 @@
       <c r="AA30" s="15"/>
       <c r="AB30" s="15"/>
       <c r="AC30" s="15"/>
-      <c r="AD30" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="8:30" ht="15.75">
+      <c r="AD30" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H31" s="12">
         <v>21</v>
       </c>
@@ -2084,8 +2097,8 @@
       <c r="J31" s="14">
         <v>46224</v>
       </c>
-      <c r="K31" s="47"/>
-      <c r="L31" s="47"/>
+      <c r="K31" s="37"/>
+      <c r="L31" s="37"/>
       <c r="M31" s="15"/>
       <c r="N31" s="15"/>
       <c r="O31" s="15"/>
@@ -2103,12 +2116,12 @@
       <c r="AA31" s="15"/>
       <c r="AB31" s="15"/>
       <c r="AC31" s="15"/>
-      <c r="AD31" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="8:30" ht="15.75">
+      <c r="AD31" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H32" s="12">
         <v>22</v>
       </c>
@@ -2118,8 +2131,8 @@
       <c r="J32" s="14">
         <v>46225</v>
       </c>
-      <c r="K32" s="47"/>
-      <c r="L32" s="47"/>
+      <c r="K32" s="37"/>
+      <c r="L32" s="37"/>
       <c r="M32" s="15"/>
       <c r="N32" s="15"/>
       <c r="O32" s="15"/>
@@ -2137,12 +2150,12 @@
       <c r="AA32" s="15"/>
       <c r="AB32" s="15"/>
       <c r="AC32" s="15"/>
-      <c r="AD32" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="8:30" ht="15.75">
+      <c r="AD32" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H33" s="12">
         <v>23</v>
       </c>
@@ -2152,8 +2165,8 @@
       <c r="J33" s="14">
         <v>46226</v>
       </c>
-      <c r="K33" s="47"/>
-      <c r="L33" s="47"/>
+      <c r="K33" s="37"/>
+      <c r="L33" s="37"/>
       <c r="M33" s="16"/>
       <c r="N33" s="16"/>
       <c r="O33" s="16"/>
@@ -2171,12 +2184,12 @@
       <c r="AA33" s="15"/>
       <c r="AB33" s="15"/>
       <c r="AC33" s="15"/>
-      <c r="AD33" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="8:30" ht="15.75">
+      <c r="AD33" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H34" s="12">
         <v>24</v>
       </c>
@@ -2186,8 +2199,8 @@
       <c r="J34" s="14">
         <v>46227</v>
       </c>
-      <c r="K34" s="47"/>
-      <c r="L34" s="47"/>
+      <c r="K34" s="37"/>
+      <c r="L34" s="37"/>
       <c r="M34" s="16"/>
       <c r="N34" s="16"/>
       <c r="O34" s="16"/>
@@ -2205,12 +2218,12 @@
       <c r="AA34" s="15"/>
       <c r="AB34" s="15"/>
       <c r="AC34" s="15"/>
-      <c r="AD34" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="8:30" ht="15.75">
+      <c r="AD34" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H35" s="12">
         <v>25</v>
       </c>
@@ -2220,8 +2233,8 @@
       <c r="J35" s="14">
         <v>46228</v>
       </c>
-      <c r="K35" s="47"/>
-      <c r="L35" s="47"/>
+      <c r="K35" s="37"/>
+      <c r="L35" s="37"/>
       <c r="M35" s="15"/>
       <c r="N35" s="15"/>
       <c r="O35" s="15"/>
@@ -2239,12 +2252,12 @@
       <c r="AA35" s="15"/>
       <c r="AB35" s="15"/>
       <c r="AC35" s="15"/>
-      <c r="AD35" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="8:30" ht="15.75">
+      <c r="AD35" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H36" s="12">
         <v>26</v>
       </c>
@@ -2254,8 +2267,8 @@
       <c r="J36" s="14">
         <v>46229</v>
       </c>
-      <c r="K36" s="47"/>
-      <c r="L36" s="47"/>
+      <c r="K36" s="37"/>
+      <c r="L36" s="37"/>
       <c r="M36" s="15"/>
       <c r="N36" s="15"/>
       <c r="O36" s="15"/>
@@ -2273,12 +2286,12 @@
       <c r="AA36" s="15"/>
       <c r="AB36" s="15"/>
       <c r="AC36" s="15"/>
-      <c r="AD36" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="8:30" ht="15.75">
+      <c r="AD36" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H37" s="12">
         <v>27</v>
       </c>
@@ -2288,8 +2301,8 @@
       <c r="J37" s="14">
         <v>46230</v>
       </c>
-      <c r="K37" s="47"/>
-      <c r="L37" s="47"/>
+      <c r="K37" s="37"/>
+      <c r="L37" s="37"/>
       <c r="M37" s="16"/>
       <c r="N37" s="16"/>
       <c r="O37" s="16"/>
@@ -2307,12 +2320,12 @@
       <c r="AA37" s="15"/>
       <c r="AB37" s="15"/>
       <c r="AC37" s="15"/>
-      <c r="AD37" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="8:30" ht="15.75">
+      <c r="AD37" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H38" s="12">
         <v>28</v>
       </c>
@@ -2322,8 +2335,8 @@
       <c r="J38" s="14">
         <v>46231</v>
       </c>
-      <c r="K38" s="47"/>
-      <c r="L38" s="47"/>
+      <c r="K38" s="37"/>
+      <c r="L38" s="37"/>
       <c r="M38" s="16"/>
       <c r="N38" s="16"/>
       <c r="O38" s="16"/>
@@ -2341,12 +2354,12 @@
       <c r="AA38" s="15"/>
       <c r="AB38" s="15"/>
       <c r="AC38" s="15"/>
-      <c r="AD38" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="8:30" ht="15.75">
+      <c r="AD38" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H39" s="12">
         <v>29</v>
       </c>
@@ -2356,8 +2369,8 @@
       <c r="J39" s="14">
         <v>46232</v>
       </c>
-      <c r="K39" s="47"/>
-      <c r="L39" s="47"/>
+      <c r="K39" s="37"/>
+      <c r="L39" s="37"/>
       <c r="M39" s="15"/>
       <c r="N39" s="15"/>
       <c r="O39" s="15"/>
@@ -2375,12 +2388,12 @@
       <c r="AA39" s="15"/>
       <c r="AB39" s="15"/>
       <c r="AC39" s="15"/>
-      <c r="AD39" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="8:30" ht="15.75">
+      <c r="AD39" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H40" s="12">
         <v>30</v>
       </c>
@@ -2390,8 +2403,8 @@
       <c r="J40" s="14">
         <v>46233</v>
       </c>
-      <c r="K40" s="47"/>
-      <c r="L40" s="47"/>
+      <c r="K40" s="37"/>
+      <c r="L40" s="37"/>
       <c r="M40" s="15"/>
       <c r="N40" s="15"/>
       <c r="O40" s="15"/>
@@ -2409,12 +2422,12 @@
       <c r="AA40" s="15"/>
       <c r="AB40" s="15"/>
       <c r="AC40" s="15"/>
-      <c r="AD40" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="8:30" ht="15.75">
+      <c r="AD40" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H41" s="12">
         <v>31</v>
       </c>
@@ -2424,8 +2437,8 @@
       <c r="J41" s="14">
         <v>46234</v>
       </c>
-      <c r="K41" s="47"/>
-      <c r="L41" s="47"/>
+      <c r="K41" s="37"/>
+      <c r="L41" s="37"/>
       <c r="M41" s="16"/>
       <c r="N41" s="16"/>
       <c r="O41" s="16"/>
@@ -2443,17 +2456,17 @@
       <c r="AA41" s="15"/>
       <c r="AB41" s="15"/>
       <c r="AC41" s="15"/>
-      <c r="AD41" s="45">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="8:30" ht="15.75">
-      <c r="H42" s="42" t="s">
+      <c r="AD41" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="8:30" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="H42" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
+      <c r="I42" s="44"/>
+      <c r="J42" s="44"/>
       <c r="K42" s="21">
         <f>COUNTA(K11:K41)</f>
         <v>1</v>
@@ -2472,11 +2485,11 @@
       </c>
       <c r="O42" s="21">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P42" s="21">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q42" s="21">
         <f t="shared" si="1"/>
@@ -2484,7 +2497,7 @@
       </c>
       <c r="R42" s="21">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S42" s="21">
         <f t="shared" si="1"/>

--- a/Другое/study_chart.xlsx
+++ b/Другое/study_chart.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="32">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -284,12 +284,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -297,6 +291,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF99CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -430,7 +430,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -497,7 +497,7 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -517,10 +517,10 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -529,6 +529,9 @@
     <xf numFmtId="164" fontId="3" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -550,14 +553,14 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -922,18 +925,18 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H9" s="38" t="s">
-        <v>0</v>
-      </c>
-      <c r="I9" s="39"/>
-      <c r="J9" s="39"/>
-      <c r="K9" s="39"/>
-      <c r="L9" s="39"/>
-      <c r="M9" s="39"/>
-      <c r="N9" s="39"/>
-      <c r="O9" s="39"/>
-      <c r="P9" s="39"/>
-      <c r="Q9" s="40"/>
+      <c r="H9" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="I9" s="40"/>
+      <c r="J9" s="40"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="40"/>
+      <c r="M9" s="40"/>
+      <c r="N9" s="40"/>
+      <c r="O9" s="40"/>
+      <c r="P9" s="40"/>
+      <c r="Q9" s="41"/>
     </row>
     <row r="10" spans="8:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H10" s="2" t="s">
@@ -1202,11 +1205,11 @@
       <c r="Q21" s="8"/>
     </row>
     <row r="22" spans="8:17" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="H22" s="41" t="s">
+      <c r="H22" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="42"/>
-      <c r="J22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="44"/>
       <c r="K22" s="4">
         <f>COUNTA(K11:K21)</f>
         <v>6</v>
@@ -1282,31 +1285,31 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:30" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="H9" s="45" t="s">
-        <v>0</v>
-      </c>
-      <c r="I9" s="46"/>
-      <c r="J9" s="46"/>
-      <c r="K9" s="46"/>
-      <c r="L9" s="46"/>
-      <c r="M9" s="46"/>
-      <c r="N9" s="46"/>
-      <c r="O9" s="46"/>
-      <c r="P9" s="46"/>
-      <c r="Q9" s="46"/>
-      <c r="R9" s="46"/>
-      <c r="S9" s="46"/>
-      <c r="T9" s="46"/>
-      <c r="U9" s="46"/>
-      <c r="V9" s="46"/>
-      <c r="W9" s="46"/>
-      <c r="X9" s="46"/>
-      <c r="Y9" s="46"/>
-      <c r="Z9" s="46"/>
-      <c r="AA9" s="46"/>
-      <c r="AB9" s="46"/>
-      <c r="AC9" s="46"/>
-      <c r="AD9" s="46"/>
+      <c r="H9" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="I9" s="48"/>
+      <c r="J9" s="48"/>
+      <c r="K9" s="48"/>
+      <c r="L9" s="48"/>
+      <c r="M9" s="48"/>
+      <c r="N9" s="48"/>
+      <c r="O9" s="48"/>
+      <c r="P9" s="48"/>
+      <c r="Q9" s="48"/>
+      <c r="R9" s="48"/>
+      <c r="S9" s="48"/>
+      <c r="T9" s="48"/>
+      <c r="U9" s="48"/>
+      <c r="V9" s="48"/>
+      <c r="W9" s="48"/>
+      <c r="X9" s="48"/>
+      <c r="Y9" s="48"/>
+      <c r="Z9" s="48"/>
+      <c r="AA9" s="48"/>
+      <c r="AB9" s="48"/>
+      <c r="AC9" s="48"/>
+      <c r="AD9" s="48"/>
     </row>
     <row r="10" spans="8:30" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H10" s="10" t="s">
@@ -1465,10 +1468,10 @@
       <c r="J13" s="29">
         <v>46206</v>
       </c>
-      <c r="K13" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="L13" s="47" t="s">
+      <c r="K13" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="L13" s="38" t="s">
         <v>12</v>
       </c>
       <c r="M13" s="31" t="s">
@@ -1506,38 +1509,38 @@
       </c>
     </row>
     <row r="14" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="H14" s="12">
+      <c r="H14" s="27">
         <v>4</v>
       </c>
-      <c r="I14" s="13" t="s">
+      <c r="I14" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J14" s="14">
+      <c r="J14" s="29">
         <v>46207</v>
       </c>
-      <c r="K14" s="37"/>
-      <c r="L14" s="37"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="P14" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="16"/>
-      <c r="S14" s="16"/>
-      <c r="T14" s="15"/>
-      <c r="U14" s="15"/>
-      <c r="V14" s="15"/>
-      <c r="W14" s="16"/>
-      <c r="X14" s="15"/>
-      <c r="Y14" s="15"/>
-      <c r="Z14" s="15"/>
-      <c r="AA14" s="15"/>
-      <c r="AB14" s="15"/>
-      <c r="AC14" s="15"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="31"/>
+      <c r="N14" s="31"/>
+      <c r="O14" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="P14" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q14" s="31"/>
+      <c r="R14" s="31"/>
+      <c r="S14" s="31"/>
+      <c r="T14" s="30"/>
+      <c r="U14" s="30"/>
+      <c r="V14" s="30"/>
+      <c r="W14" s="31"/>
+      <c r="X14" s="30"/>
+      <c r="Y14" s="30"/>
+      <c r="Z14" s="30"/>
+      <c r="AA14" s="30"/>
+      <c r="AB14" s="30"/>
+      <c r="AC14" s="30"/>
       <c r="AD14" s="36">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -1556,9 +1559,15 @@
       <c r="K15" s="37"/>
       <c r="L15" s="37"/>
       <c r="M15" s="15"/>
-      <c r="N15" s="15"/>
-      <c r="O15" s="15"/>
-      <c r="P15" s="15"/>
+      <c r="N15" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="O15" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="P15" s="15" t="s">
+        <v>12</v>
+      </c>
       <c r="Q15" s="15"/>
       <c r="R15" s="15"/>
       <c r="S15" s="15"/>
@@ -1574,7 +1583,7 @@
       <c r="AC15" s="15"/>
       <c r="AD15" s="36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="8:30" ht="15.75" x14ac:dyDescent="0.25">
@@ -2462,11 +2471,11 @@
       </c>
     </row>
     <row r="42" spans="8:30" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="H42" s="44" t="s">
+      <c r="H42" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="I42" s="44"/>
-      <c r="J42" s="44"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="45"/>
       <c r="K42" s="21">
         <f>COUNTA(K11:K41)</f>
         <v>1</v>
@@ -2481,15 +2490,15 @@
       </c>
       <c r="N42" s="21">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O42" s="21">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P42" s="21">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q42" s="21">
         <f t="shared" si="1"/>

--- a/Другое/study_chart.xlsx
+++ b/Другое/study_chart.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12300" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="11700" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Июнь" sheetId="1" r:id="rId1"/>
@@ -740,7 +740,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="36">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -1094,12 +1094,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="204"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="204"/>
@@ -1116,7 +1116,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="45">
+  <fills count="46">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1186,6 +1186,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.35"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1629,7 +1635,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1653,16 +1659,16 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1671,89 +1677,89 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1824,6 +1830,9 @@
     <xf numFmtId="0" fontId="9" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1838,13 +1847,13 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2265,316 +2274,316 @@
   </cols>
   <sheetData>
     <row r="9" ht="45" customHeight="1" spans="8:17">
-      <c r="H9" s="32" t="s">
+      <c r="H9" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="33"/>
-      <c r="M9" s="33"/>
-      <c r="N9" s="33"/>
-      <c r="O9" s="33"/>
-      <c r="P9" s="33"/>
-      <c r="Q9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
+      <c r="K9" s="34"/>
+      <c r="L9" s="34"/>
+      <c r="M9" s="34"/>
+      <c r="N9" s="34"/>
+      <c r="O9" s="34"/>
+      <c r="P9" s="34"/>
+      <c r="Q9" s="35"/>
     </row>
     <row r="10" ht="30" customHeight="1" spans="8:17">
-      <c r="H10" s="35" t="s">
+      <c r="H10" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="I10" s="36" t="s">
+      <c r="I10" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="J10" s="35" t="s">
+      <c r="J10" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="K10" s="35" t="s">
+      <c r="K10" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="L10" s="35" t="s">
+      <c r="L10" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="M10" s="35" t="s">
+      <c r="M10" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="N10" s="35" t="s">
+      <c r="N10" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="O10" s="36" t="s">
+      <c r="O10" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="P10" s="35" t="s">
+      <c r="P10" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="Q10" s="35" t="s">
+      <c r="Q10" s="36" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="8:17">
-      <c r="H11" s="37">
+      <c r="H11" s="38">
         <v>1</v>
       </c>
-      <c r="I11" s="38" t="s">
+      <c r="I11" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="J11" s="39">
+      <c r="J11" s="40">
         <v>46193</v>
       </c>
-      <c r="K11" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="L11" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="M11" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="N11" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="O11" s="40"/>
-      <c r="P11" s="40"/>
-      <c r="Q11" s="40"/>
+      <c r="K11" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="L11" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="M11" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="N11" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="O11" s="41"/>
+      <c r="P11" s="41"/>
+      <c r="Q11" s="41"/>
     </row>
     <row r="12" spans="8:17">
-      <c r="H12" s="37">
+      <c r="H12" s="38">
         <v>2</v>
       </c>
-      <c r="I12" s="38" t="s">
+      <c r="I12" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="J12" s="39">
+      <c r="J12" s="40">
         <v>46194</v>
       </c>
-      <c r="K12" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="L12" s="40"/>
-      <c r="M12" s="40"/>
-      <c r="N12" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="O12" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="P12" s="40"/>
-      <c r="Q12" s="40"/>
+      <c r="K12" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="L12" s="41"/>
+      <c r="M12" s="41"/>
+      <c r="N12" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="O12" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="P12" s="41"/>
+      <c r="Q12" s="41"/>
     </row>
     <row r="13" spans="8:17">
-      <c r="H13" s="37">
+      <c r="H13" s="38">
         <v>3</v>
       </c>
-      <c r="I13" s="38" t="s">
+      <c r="I13" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="J13" s="39">
+      <c r="J13" s="40">
         <v>46195</v>
       </c>
-      <c r="K13" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="L13" s="40"/>
-      <c r="M13" s="40"/>
-      <c r="N13" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="O13" s="40"/>
-      <c r="P13" s="40"/>
-      <c r="Q13" s="40"/>
+      <c r="K13" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="L13" s="41"/>
+      <c r="M13" s="41"/>
+      <c r="N13" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="O13" s="41"/>
+      <c r="P13" s="41"/>
+      <c r="Q13" s="41"/>
     </row>
     <row r="14" spans="8:17">
-      <c r="H14" s="37">
+      <c r="H14" s="38">
         <v>4</v>
       </c>
-      <c r="I14" s="38" t="s">
+      <c r="I14" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="J14" s="39">
+      <c r="J14" s="40">
         <v>46196</v>
       </c>
-      <c r="K14" s="40"/>
-      <c r="L14" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="M14" s="40"/>
-      <c r="N14" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="O14" s="40"/>
-      <c r="P14" s="40"/>
-      <c r="Q14" s="40"/>
+      <c r="K14" s="41"/>
+      <c r="L14" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="M14" s="41"/>
+      <c r="N14" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="O14" s="41"/>
+      <c r="P14" s="41"/>
+      <c r="Q14" s="41"/>
     </row>
     <row r="15" spans="8:17">
-      <c r="H15" s="37">
+      <c r="H15" s="38">
         <v>5</v>
       </c>
-      <c r="I15" s="38" t="s">
+      <c r="I15" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="J15" s="39">
+      <c r="J15" s="40">
         <v>46197</v>
       </c>
-      <c r="K15" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="L15" s="40"/>
-      <c r="M15" s="40"/>
-      <c r="N15" s="40"/>
-      <c r="O15" s="40"/>
-      <c r="P15" s="40"/>
-      <c r="Q15" s="40"/>
+      <c r="K15" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="L15" s="41"/>
+      <c r="M15" s="41"/>
+      <c r="N15" s="41"/>
+      <c r="O15" s="41"/>
+      <c r="P15" s="41"/>
+      <c r="Q15" s="41"/>
     </row>
     <row r="16" spans="8:17">
-      <c r="H16" s="37">
+      <c r="H16" s="38">
         <v>6</v>
       </c>
-      <c r="I16" s="38" t="s">
+      <c r="I16" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="J16" s="39">
+      <c r="J16" s="40">
         <v>46198</v>
       </c>
-      <c r="K16" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="L16" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="M16" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="N16" s="40"/>
-      <c r="O16" s="40"/>
-      <c r="P16" s="40"/>
-      <c r="Q16" s="40"/>
+      <c r="K16" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="L16" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="M16" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="N16" s="41"/>
+      <c r="O16" s="41"/>
+      <c r="P16" s="41"/>
+      <c r="Q16" s="41"/>
     </row>
     <row r="17" spans="8:17">
-      <c r="H17" s="37">
+      <c r="H17" s="38">
         <v>7</v>
       </c>
-      <c r="I17" s="38" t="s">
+      <c r="I17" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="J17" s="39">
+      <c r="J17" s="40">
         <v>46199</v>
       </c>
-      <c r="K17" s="40"/>
-      <c r="L17" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="M17" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="N17" s="40"/>
-      <c r="O17" s="40"/>
-      <c r="P17" s="40"/>
-      <c r="Q17" s="40"/>
+      <c r="K17" s="41"/>
+      <c r="L17" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="M17" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="N17" s="41"/>
+      <c r="O17" s="41"/>
+      <c r="P17" s="41"/>
+      <c r="Q17" s="41"/>
     </row>
     <row r="18" spans="8:17">
-      <c r="H18" s="37">
+      <c r="H18" s="38">
         <v>8</v>
       </c>
-      <c r="I18" s="38" t="s">
+      <c r="I18" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="J18" s="39">
+      <c r="J18" s="40">
         <v>46200</v>
       </c>
-      <c r="K18" s="40"/>
-      <c r="L18" s="40"/>
-      <c r="M18" s="40"/>
-      <c r="N18" s="40"/>
-      <c r="O18" s="40"/>
-      <c r="P18" s="40"/>
-      <c r="Q18" s="40"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="41"/>
+      <c r="M18" s="41"/>
+      <c r="N18" s="41"/>
+      <c r="O18" s="41"/>
+      <c r="P18" s="41"/>
+      <c r="Q18" s="41"/>
     </row>
     <row r="19" spans="8:17">
-      <c r="H19" s="37">
+      <c r="H19" s="38">
         <v>9</v>
       </c>
-      <c r="I19" s="38" t="s">
+      <c r="I19" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="J19" s="39">
+      <c r="J19" s="40">
         <v>46201</v>
       </c>
-      <c r="K19" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="L19" s="40"/>
-      <c r="M19" s="40"/>
-      <c r="N19" s="40"/>
-      <c r="O19" s="40"/>
-      <c r="P19" s="40"/>
-      <c r="Q19" s="40"/>
+      <c r="K19" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="L19" s="41"/>
+      <c r="M19" s="41"/>
+      <c r="N19" s="41"/>
+      <c r="O19" s="41"/>
+      <c r="P19" s="41"/>
+      <c r="Q19" s="41"/>
     </row>
     <row r="20" spans="8:17">
-      <c r="H20" s="37">
+      <c r="H20" s="38">
         <v>10</v>
       </c>
-      <c r="I20" s="38" t="s">
+      <c r="I20" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="J20" s="39">
+      <c r="J20" s="40">
         <v>46202</v>
       </c>
-      <c r="K20" s="40"/>
-      <c r="L20" s="40"/>
-      <c r="M20" s="40"/>
-      <c r="N20" s="40"/>
-      <c r="O20" s="40"/>
-      <c r="P20" s="40"/>
-      <c r="Q20" s="40"/>
+      <c r="K20" s="41"/>
+      <c r="L20" s="41"/>
+      <c r="M20" s="41"/>
+      <c r="N20" s="41"/>
+      <c r="O20" s="41"/>
+      <c r="P20" s="41"/>
+      <c r="Q20" s="41"/>
     </row>
     <row r="21" spans="8:17">
-      <c r="H21" s="37">
+      <c r="H21" s="38">
         <v>11</v>
       </c>
-      <c r="I21" s="38" t="s">
+      <c r="I21" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="J21" s="39">
+      <c r="J21" s="40">
         <v>46203</v>
       </c>
-      <c r="K21" s="40"/>
-      <c r="L21" s="40"/>
-      <c r="M21" s="40"/>
-      <c r="N21" s="40"/>
-      <c r="O21" s="40"/>
-      <c r="P21" s="40"/>
-      <c r="Q21" s="40"/>
+      <c r="K21" s="41"/>
+      <c r="L21" s="41"/>
+      <c r="M21" s="41"/>
+      <c r="N21" s="41"/>
+      <c r="O21" s="41"/>
+      <c r="P21" s="41"/>
+      <c r="Q21" s="41"/>
     </row>
     <row r="22" ht="15.75" spans="8:17">
-      <c r="H22" s="41" t="s">
+      <c r="H22" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="42"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="44">
+      <c r="I22" s="43"/>
+      <c r="J22" s="44"/>
+      <c r="K22" s="45">
         <f>COUNTA(K11:K21)</f>
         <v>6</v>
       </c>
-      <c r="L22" s="44">
+      <c r="L22" s="45">
         <f t="shared" ref="L22:Q22" si="0">COUNTA(L11:L21)</f>
         <v>4</v>
       </c>
-      <c r="M22" s="44">
+      <c r="M22" s="45">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="N22" s="44">
+      <c r="N22" s="45">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="O22" s="44">
+      <c r="O22" s="45">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="P22" s="44">
+      <c r="P22" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q22" s="44">
+      <c r="Q22" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4204,58 +4213,64 @@
       <c r="M39" s="24"/>
       <c r="N39" s="21"/>
       <c r="O39" s="21"/>
-      <c r="P39" s="21"/>
-      <c r="Q39" s="21"/>
-      <c r="R39" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="S39" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="T39" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="U39" s="25"/>
-      <c r="V39" s="25"/>
-      <c r="W39" s="25"/>
-      <c r="X39" s="25"/>
-      <c r="Y39" s="25"/>
-      <c r="Z39" s="25"/>
-      <c r="AA39" s="25"/>
-      <c r="AB39" s="25"/>
-      <c r="AC39" s="25"/>
-      <c r="AD39" s="25"/>
-      <c r="AE39" s="25"/>
-      <c r="AF39" s="25"/>
-      <c r="AG39" s="25"/>
-      <c r="AH39" s="25"/>
-      <c r="AI39" s="25"/>
-      <c r="AJ39" s="25"/>
-      <c r="AK39" s="25"/>
+      <c r="P39" s="26"/>
+      <c r="Q39" s="26"/>
+      <c r="R39" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="S39" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="T39" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="U39" s="26"/>
+      <c r="V39" s="26"/>
+      <c r="W39" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="X39" s="26"/>
+      <c r="Y39" s="26"/>
+      <c r="Z39" s="26"/>
+      <c r="AA39" s="26"/>
+      <c r="AB39" s="26"/>
+      <c r="AC39" s="26"/>
+      <c r="AD39" s="26"/>
+      <c r="AE39" s="26"/>
+      <c r="AF39" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG39" s="26"/>
+      <c r="AH39" s="26"/>
+      <c r="AI39" s="26"/>
+      <c r="AJ39" s="26"/>
+      <c r="AK39" s="26"/>
       <c r="AL39" s="23">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" ht="15.75" spans="8:38">
-      <c r="H40" s="26">
+      <c r="H40" s="27">
         <v>30</v>
       </c>
-      <c r="I40" s="27" t="s">
+      <c r="I40" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="J40" s="28">
+      <c r="J40" s="29">
         <v>46233</v>
       </c>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="30"/>
       <c r="N40" s="25"/>
       <c r="O40" s="25"/>
       <c r="P40" s="25"/>
       <c r="Q40" s="25"/>
       <c r="R40" s="25"/>
-      <c r="S40" s="25"/>
+      <c r="S40" s="25" t="s">
+        <v>12</v>
+      </c>
       <c r="T40" s="25"/>
       <c r="U40" s="25"/>
       <c r="V40" s="25"/>
@@ -4276,22 +4291,22 @@
       <c r="AK40" s="25"/>
       <c r="AL40" s="23">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" ht="15.75" spans="8:38">
-      <c r="H41" s="26">
+      <c r="H41" s="27">
         <v>31</v>
       </c>
-      <c r="I41" s="27" t="s">
+      <c r="I41" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="J41" s="28">
+      <c r="J41" s="29">
         <v>46234</v>
       </c>
-      <c r="K41" s="29"/>
-      <c r="L41" s="29"/>
-      <c r="M41" s="29"/>
+      <c r="K41" s="30"/>
+      <c r="L41" s="30"/>
+      <c r="M41" s="30"/>
       <c r="N41" s="25"/>
       <c r="O41" s="25"/>
       <c r="P41" s="25"/>
@@ -4322,11 +4337,11 @@
       </c>
     </row>
     <row r="42" ht="15.75" spans="8:38">
-      <c r="H42" s="30" t="s">
+      <c r="H42" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="I42" s="30"/>
-      <c r="J42" s="30"/>
+      <c r="I42" s="31"/>
+      <c r="J42" s="31"/>
       <c r="K42" s="4">
         <f>COUNTA(K11:K41)</f>
         <v>6</v>
@@ -4361,7 +4376,7 @@
       </c>
       <c r="S42" s="4">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T42" s="4">
         <f t="shared" si="1"/>
@@ -4377,7 +4392,7 @@
       </c>
       <c r="W42" s="4">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X42" s="4">
         <f t="shared" si="1"/>
@@ -4413,7 +4428,7 @@
       </c>
       <c r="AF42" s="4">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG42" s="4">
         <f t="shared" si="1"/>
@@ -4429,7 +4444,7 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="AL42" s="31">
+      <c r="AL42" s="32">
         <f t="shared" ref="AL42" si="2">COUNTA(AL11:AL41)</f>
         <v>31</v>
       </c>

--- a/Другое/study_chart.xlsx
+++ b/Другое/study_chart.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11700" activeTab="1"/>
+    <workbookView windowWidth="24000" windowHeight="10380" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Июнь" sheetId="1" r:id="rId1"/>
     <sheet name="Июль" sheetId="4" r:id="rId2"/>
+    <sheet name="Август" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -740,7 +741,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="48">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -848,6 +849,42 @@
   </si>
   <si>
     <t>ИТОГО</t>
+  </si>
+  <si>
+    <t>Группа</t>
+  </si>
+  <si>
+    <t>Утренняя рутина</t>
+  </si>
+  <si>
+    <t>Работа</t>
+  </si>
+  <si>
+    <t>Показатель</t>
+  </si>
+  <si>
+    <t>Встать до 6:20</t>
+  </si>
+  <si>
+    <t>Встать с 1 будильника</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Распланировать день </t>
+  </si>
+  <si>
+    <t>Выполнить срочные/важные задачи</t>
+  </si>
+  <si>
+    <t>Обучение Эксперт</t>
+  </si>
+  <si>
+    <t>Руководство по смете.ру</t>
+  </si>
+  <si>
+    <t>Книга по строительству дорог</t>
+  </si>
+  <si>
+    <t>Балл за выполнение</t>
   </si>
 </sst>
 </file>
@@ -1094,6 +1131,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
@@ -1103,11 +1145,6 @@
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="204"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -1759,8 +1796,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1833,12 +1873,12 @@
     <xf numFmtId="0" fontId="9" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="9" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="9" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="9" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="9" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1884,55 +1924,55 @@
     </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Запятая" xfId="1" builtinId="3"/>
-    <cellStyle name="Денежный" xfId="2" builtinId="4"/>
-    <cellStyle name="Процент" xfId="3" builtinId="5"/>
-    <cellStyle name="Запятая [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Денежный [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Гиперссылка" xfId="6" builtinId="8"/>
-    <cellStyle name="Открывавшаяся гиперссылка" xfId="7" builtinId="9"/>
-    <cellStyle name="Примечание" xfId="8" builtinId="10"/>
-    <cellStyle name="Предупреждающий текст" xfId="9" builtinId="11"/>
-    <cellStyle name="Заголовок" xfId="10" builtinId="15"/>
-    <cellStyle name="Пояснительный текст" xfId="11" builtinId="53"/>
-    <cellStyle name="Заголовок 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Заголовок 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Заголовок 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Заголовок 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Ввод" xfId="16" builtinId="20"/>
-    <cellStyle name="Вывод" xfId="17" builtinId="21"/>
-    <cellStyle name="Вычисление" xfId="18" builtinId="22"/>
-    <cellStyle name="Проверить ячейку" xfId="19" builtinId="23"/>
-    <cellStyle name="Связанная ячейка" xfId="20" builtinId="24"/>
-    <cellStyle name="Итого" xfId="21" builtinId="25"/>
-    <cellStyle name="Хороший" xfId="22" builtinId="26"/>
-    <cellStyle name="Плохой" xfId="23" builtinId="27"/>
-    <cellStyle name="Нейтральный" xfId="24" builtinId="28"/>
-    <cellStyle name="Акцент1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% — Акцент1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% — Акцент1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% — Акцент1" xfId="28" builtinId="32"/>
-    <cellStyle name="Акцент2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% — Акцент2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% — Акцент2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% — Акцент2" xfId="32" builtinId="36"/>
-    <cellStyle name="Акцент3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% — Акцент3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% — Акцент3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% — Акцент3" xfId="36" builtinId="40"/>
-    <cellStyle name="Акцент4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% — Акцент4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% — Акцент4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% — Акцент4" xfId="40" builtinId="44"/>
-    <cellStyle name="Акцент5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% — Акцент5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% — Акцент5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% — Акцент5" xfId="44" builtinId="48"/>
-    <cellStyle name="Акцент6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% — Акцент6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% — Акцент6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% — Акцент6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -2259,331 +2299,331 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="H9:Q22"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.14159292035398" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="7" width="9.14285714285714" style="1"/>
-    <col min="8" max="8" width="5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7142857142857" style="1" customWidth="1"/>
-    <col min="10" max="10" width="16.8571428571429" style="1" customWidth="1"/>
-    <col min="11" max="11" width="14.2857142857143" style="1" customWidth="1"/>
-    <col min="12" max="13" width="11.2857142857143" style="1" customWidth="1"/>
-    <col min="14" max="14" width="11.5714285714286" style="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5714285714286" style="1" customWidth="1"/>
-    <col min="16" max="17" width="10" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.14285714285714" style="1"/>
+    <col min="1" max="7" width="9.14159292035398" style="2"/>
+    <col min="8" max="8" width="5" style="2" customWidth="1"/>
+    <col min="9" max="9" width="14.716814159292" style="2" customWidth="1"/>
+    <col min="10" max="10" width="16.858407079646" style="2" customWidth="1"/>
+    <col min="11" max="11" width="14.283185840708" style="2" customWidth="1"/>
+    <col min="12" max="13" width="11.283185840708" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11.5752212389381" style="2" customWidth="1"/>
+    <col min="15" max="15" width="14.5752212389381" style="2" customWidth="1"/>
+    <col min="16" max="17" width="10" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="9.14159292035398" style="2"/>
   </cols>
   <sheetData>
     <row r="9" ht="45" customHeight="1" spans="8:17">
-      <c r="H9" s="33" t="s">
+      <c r="H9" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="34"/>
-      <c r="M9" s="34"/>
-      <c r="N9" s="34"/>
-      <c r="O9" s="34"/>
-      <c r="P9" s="34"/>
-      <c r="Q9" s="35"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="35"/>
+      <c r="L9" s="35"/>
+      <c r="M9" s="35"/>
+      <c r="N9" s="35"/>
+      <c r="O9" s="35"/>
+      <c r="P9" s="35"/>
+      <c r="Q9" s="36"/>
     </row>
     <row r="10" ht="30" customHeight="1" spans="8:17">
-      <c r="H10" s="36" t="s">
+      <c r="H10" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="I10" s="37" t="s">
+      <c r="I10" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="J10" s="36" t="s">
+      <c r="J10" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="K10" s="36" t="s">
+      <c r="K10" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="L10" s="36" t="s">
+      <c r="L10" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="M10" s="36" t="s">
+      <c r="M10" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="N10" s="36" t="s">
+      <c r="N10" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="O10" s="37" t="s">
+      <c r="O10" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="P10" s="36" t="s">
+      <c r="P10" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="Q10" s="36" t="s">
+      <c r="Q10" s="37" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="8:17">
-      <c r="H11" s="38">
+      <c r="H11" s="39">
         <v>1</v>
       </c>
-      <c r="I11" s="39" t="s">
+      <c r="I11" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="J11" s="40">
+      <c r="J11" s="41">
         <v>46193</v>
       </c>
-      <c r="K11" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="L11" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="M11" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="N11" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="O11" s="41"/>
-      <c r="P11" s="41"/>
-      <c r="Q11" s="41"/>
+      <c r="K11" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="L11" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="M11" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="N11" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="O11" s="42"/>
+      <c r="P11" s="42"/>
+      <c r="Q11" s="42"/>
     </row>
     <row r="12" spans="8:17">
-      <c r="H12" s="38">
+      <c r="H12" s="39">
         <v>2</v>
       </c>
-      <c r="I12" s="39" t="s">
+      <c r="I12" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="J12" s="40">
+      <c r="J12" s="41">
         <v>46194</v>
       </c>
-      <c r="K12" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="L12" s="41"/>
-      <c r="M12" s="41"/>
-      <c r="N12" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="O12" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="P12" s="41"/>
-      <c r="Q12" s="41"/>
+      <c r="K12" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="L12" s="42"/>
+      <c r="M12" s="42"/>
+      <c r="N12" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="O12" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="P12" s="42"/>
+      <c r="Q12" s="42"/>
     </row>
     <row r="13" spans="8:17">
-      <c r="H13" s="38">
+      <c r="H13" s="39">
         <v>3</v>
       </c>
-      <c r="I13" s="39" t="s">
+      <c r="I13" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="J13" s="40">
+      <c r="J13" s="41">
         <v>46195</v>
       </c>
-      <c r="K13" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="L13" s="41"/>
-      <c r="M13" s="41"/>
-      <c r="N13" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="O13" s="41"/>
-      <c r="P13" s="41"/>
-      <c r="Q13" s="41"/>
+      <c r="K13" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="L13" s="42"/>
+      <c r="M13" s="42"/>
+      <c r="N13" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="O13" s="42"/>
+      <c r="P13" s="42"/>
+      <c r="Q13" s="42"/>
     </row>
     <row r="14" spans="8:17">
-      <c r="H14" s="38">
+      <c r="H14" s="39">
         <v>4</v>
       </c>
-      <c r="I14" s="39" t="s">
+      <c r="I14" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="J14" s="40">
+      <c r="J14" s="41">
         <v>46196</v>
       </c>
-      <c r="K14" s="41"/>
-      <c r="L14" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="M14" s="41"/>
-      <c r="N14" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="O14" s="41"/>
-      <c r="P14" s="41"/>
-      <c r="Q14" s="41"/>
+      <c r="K14" s="42"/>
+      <c r="L14" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="M14" s="42"/>
+      <c r="N14" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="O14" s="42"/>
+      <c r="P14" s="42"/>
+      <c r="Q14" s="42"/>
     </row>
     <row r="15" spans="8:17">
-      <c r="H15" s="38">
+      <c r="H15" s="39">
         <v>5</v>
       </c>
-      <c r="I15" s="39" t="s">
+      <c r="I15" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="J15" s="40">
+      <c r="J15" s="41">
         <v>46197</v>
       </c>
-      <c r="K15" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="L15" s="41"/>
-      <c r="M15" s="41"/>
-      <c r="N15" s="41"/>
-      <c r="O15" s="41"/>
-      <c r="P15" s="41"/>
-      <c r="Q15" s="41"/>
+      <c r="K15" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="L15" s="42"/>
+      <c r="M15" s="42"/>
+      <c r="N15" s="42"/>
+      <c r="O15" s="42"/>
+      <c r="P15" s="42"/>
+      <c r="Q15" s="42"/>
     </row>
     <row r="16" spans="8:17">
-      <c r="H16" s="38">
+      <c r="H16" s="39">
         <v>6</v>
       </c>
-      <c r="I16" s="39" t="s">
+      <c r="I16" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="J16" s="40">
+      <c r="J16" s="41">
         <v>46198</v>
       </c>
-      <c r="K16" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="L16" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="M16" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="N16" s="41"/>
-      <c r="O16" s="41"/>
-      <c r="P16" s="41"/>
-      <c r="Q16" s="41"/>
+      <c r="K16" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="L16" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="M16" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="N16" s="42"/>
+      <c r="O16" s="42"/>
+      <c r="P16" s="42"/>
+      <c r="Q16" s="42"/>
     </row>
     <row r="17" spans="8:17">
-      <c r="H17" s="38">
+      <c r="H17" s="39">
         <v>7</v>
       </c>
-      <c r="I17" s="39" t="s">
+      <c r="I17" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="J17" s="40">
+      <c r="J17" s="41">
         <v>46199</v>
       </c>
-      <c r="K17" s="41"/>
-      <c r="L17" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="M17" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="N17" s="41"/>
-      <c r="O17" s="41"/>
-      <c r="P17" s="41"/>
-      <c r="Q17" s="41"/>
+      <c r="K17" s="42"/>
+      <c r="L17" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="M17" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="N17" s="42"/>
+      <c r="O17" s="42"/>
+      <c r="P17" s="42"/>
+      <c r="Q17" s="42"/>
     </row>
     <row r="18" spans="8:17">
-      <c r="H18" s="38">
+      <c r="H18" s="39">
         <v>8</v>
       </c>
-      <c r="I18" s="39" t="s">
+      <c r="I18" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="J18" s="40">
+      <c r="J18" s="41">
         <v>46200</v>
       </c>
-      <c r="K18" s="41"/>
-      <c r="L18" s="41"/>
-      <c r="M18" s="41"/>
-      <c r="N18" s="41"/>
-      <c r="O18" s="41"/>
-      <c r="P18" s="41"/>
-      <c r="Q18" s="41"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="42"/>
+      <c r="M18" s="42"/>
+      <c r="N18" s="42"/>
+      <c r="O18" s="42"/>
+      <c r="P18" s="42"/>
+      <c r="Q18" s="42"/>
     </row>
     <row r="19" spans="8:17">
-      <c r="H19" s="38">
+      <c r="H19" s="39">
         <v>9</v>
       </c>
-      <c r="I19" s="39" t="s">
+      <c r="I19" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="J19" s="40">
+      <c r="J19" s="41">
         <v>46201</v>
       </c>
-      <c r="K19" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="L19" s="41"/>
-      <c r="M19" s="41"/>
-      <c r="N19" s="41"/>
-      <c r="O19" s="41"/>
-      <c r="P19" s="41"/>
-      <c r="Q19" s="41"/>
+      <c r="K19" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="L19" s="42"/>
+      <c r="M19" s="42"/>
+      <c r="N19" s="42"/>
+      <c r="O19" s="42"/>
+      <c r="P19" s="42"/>
+      <c r="Q19" s="42"/>
     </row>
     <row r="20" spans="8:17">
-      <c r="H20" s="38">
+      <c r="H20" s="39">
         <v>10</v>
       </c>
-      <c r="I20" s="39" t="s">
+      <c r="I20" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="J20" s="40">
+      <c r="J20" s="41">
         <v>46202</v>
       </c>
-      <c r="K20" s="41"/>
-      <c r="L20" s="41"/>
-      <c r="M20" s="41"/>
-      <c r="N20" s="41"/>
-      <c r="O20" s="41"/>
-      <c r="P20" s="41"/>
-      <c r="Q20" s="41"/>
+      <c r="K20" s="42"/>
+      <c r="L20" s="42"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="42"/>
+      <c r="O20" s="42"/>
+      <c r="P20" s="42"/>
+      <c r="Q20" s="42"/>
     </row>
     <row r="21" spans="8:17">
-      <c r="H21" s="38">
+      <c r="H21" s="39">
         <v>11</v>
       </c>
-      <c r="I21" s="39" t="s">
+      <c r="I21" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="J21" s="40">
+      <c r="J21" s="41">
         <v>46203</v>
       </c>
-      <c r="K21" s="41"/>
-      <c r="L21" s="41"/>
-      <c r="M21" s="41"/>
-      <c r="N21" s="41"/>
-      <c r="O21" s="41"/>
-      <c r="P21" s="41"/>
-      <c r="Q21" s="41"/>
-    </row>
-    <row r="22" ht="15.75" spans="8:17">
-      <c r="H22" s="42" t="s">
+      <c r="K21" s="42"/>
+      <c r="L21" s="42"/>
+      <c r="M21" s="42"/>
+      <c r="N21" s="42"/>
+      <c r="O21" s="42"/>
+      <c r="P21" s="42"/>
+      <c r="Q21" s="42"/>
+    </row>
+    <row r="22" ht="14.6" spans="8:17">
+      <c r="H22" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="43"/>
-      <c r="J22" s="44"/>
-      <c r="K22" s="45">
+      <c r="I22" s="44"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="46">
         <f>COUNTA(K11:K21)</f>
         <v>6</v>
       </c>
-      <c r="L22" s="45">
+      <c r="L22" s="46">
         <f t="shared" ref="L22:Q22" si="0">COUNTA(L11:L21)</f>
         <v>4</v>
       </c>
-      <c r="M22" s="45">
+      <c r="M22" s="46">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="N22" s="45">
+      <c r="N22" s="46">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="O22" s="45">
+      <c r="O22" s="46">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="P22" s="45">
+      <c r="P22" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q22" s="45">
+      <c r="Q22" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -2613,1838 +2653,1850 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="H9:AL42"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.14159292035398" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="7" width="9.14285714285714" style="1"/>
-    <col min="8" max="8" width="5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7142857142857" style="1" customWidth="1"/>
-    <col min="10" max="11" width="16.8571428571429" style="1" customWidth="1"/>
-    <col min="12" max="13" width="24.1428571428571" style="1" customWidth="1"/>
-    <col min="14" max="17" width="14.2857142857143" style="1" customWidth="1"/>
-    <col min="18" max="18" width="20.5714285714286" style="1" customWidth="1"/>
-    <col min="19" max="20" width="23.2857142857143" style="1" customWidth="1"/>
-    <col min="21" max="22" width="11.2857142857143" style="1" customWidth="1"/>
-    <col min="23" max="23" width="30.2857142857143" style="1" customWidth="1"/>
-    <col min="24" max="24" width="11.5714285714286" style="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5714285714286" style="1" customWidth="1"/>
-    <col min="26" max="27" width="10" style="1" customWidth="1"/>
-    <col min="28" max="28" width="28" style="1" customWidth="1"/>
-    <col min="29" max="29" width="14.1428571428571" style="1" customWidth="1"/>
-    <col min="30" max="30" width="13.8571428571429" style="1" customWidth="1"/>
-    <col min="31" max="37" width="18.4285714285714" style="1" customWidth="1"/>
-    <col min="38" max="38" width="18" style="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.14285714285714" style="1"/>
+    <col min="1" max="7" width="9.14159292035398" style="2"/>
+    <col min="8" max="8" width="5" style="2" customWidth="1"/>
+    <col min="9" max="9" width="14.716814159292" style="2" customWidth="1"/>
+    <col min="10" max="11" width="16.858407079646" style="2" customWidth="1"/>
+    <col min="12" max="13" width="24.141592920354" style="2" customWidth="1"/>
+    <col min="14" max="17" width="14.283185840708" style="2" customWidth="1"/>
+    <col min="18" max="18" width="20.5752212389381" style="2" customWidth="1"/>
+    <col min="19" max="20" width="23.283185840708" style="2" customWidth="1"/>
+    <col min="21" max="22" width="11.283185840708" style="2" customWidth="1"/>
+    <col min="23" max="23" width="30.283185840708" style="2" customWidth="1"/>
+    <col min="24" max="24" width="11.5752212389381" style="2" customWidth="1"/>
+    <col min="25" max="25" width="14.5752212389381" style="2" customWidth="1"/>
+    <col min="26" max="27" width="10" style="2" customWidth="1"/>
+    <col min="28" max="28" width="28" style="2" customWidth="1"/>
+    <col min="29" max="29" width="14.141592920354" style="2" customWidth="1"/>
+    <col min="30" max="30" width="13.858407079646" style="2" customWidth="1"/>
+    <col min="31" max="37" width="18.4247787610619" style="2" customWidth="1"/>
+    <col min="38" max="38" width="18" style="2" customWidth="1"/>
+    <col min="39" max="16384" width="9.14159292035398" style="2"/>
   </cols>
   <sheetData>
     <row r="9" ht="45" customHeight="1" spans="8:38">
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="3"/>
-      <c r="AA9" s="3"/>
-      <c r="AB9" s="3"/>
-      <c r="AC9" s="3"/>
-      <c r="AD9" s="3"/>
-      <c r="AE9" s="3"/>
-      <c r="AF9" s="3"/>
-      <c r="AG9" s="3"/>
-      <c r="AH9" s="3"/>
-      <c r="AI9" s="3"/>
-      <c r="AJ9" s="3"/>
-      <c r="AK9" s="3"/>
-      <c r="AL9" s="3"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+      <c r="X9" s="4"/>
+      <c r="Y9" s="4"/>
+      <c r="Z9" s="4"/>
+      <c r="AA9" s="4"/>
+      <c r="AB9" s="4"/>
+      <c r="AC9" s="4"/>
+      <c r="AD9" s="4"/>
+      <c r="AE9" s="4"/>
+      <c r="AF9" s="4"/>
+      <c r="AG9" s="4"/>
+      <c r="AH9" s="4"/>
+      <c r="AI9" s="4"/>
+      <c r="AJ9" s="4"/>
+      <c r="AK9" s="4"/>
+      <c r="AL9" s="4"/>
     </row>
     <row r="10" ht="30" customHeight="1" spans="8:38">
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J10" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="L10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="M10" s="6" t="s">
+      <c r="M10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="N10" s="7" t="s">
+      <c r="N10" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="O10" s="8" t="s">
+      <c r="O10" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="P10" s="8" t="s">
+      <c r="P10" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="Q10" s="8" t="s">
+      <c r="Q10" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="R10" s="8" t="s">
+      <c r="R10" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="S10" s="9" t="s">
+      <c r="S10" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="T10" s="9" t="s">
+      <c r="T10" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="U10" s="10" t="s">
+      <c r="U10" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="V10" s="10" t="s">
+      <c r="V10" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="W10" s="9" t="s">
+      <c r="W10" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="X10" s="11" t="s">
+      <c r="X10" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="Y10" s="12" t="s">
+      <c r="Y10" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="Z10" s="11" t="s">
+      <c r="Z10" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="AA10" s="13" t="s">
+      <c r="AA10" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="AB10" s="14" t="s">
+      <c r="AB10" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="AC10" s="15" t="s">
+      <c r="AC10" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="AD10" s="14" t="s">
+      <c r="AD10" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="AE10" s="14" t="s">
+      <c r="AE10" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="AF10" s="14" t="s">
+      <c r="AF10" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="AG10" s="16" t="s">
+      <c r="AG10" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="AH10" s="16" t="s">
+      <c r="AH10" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="AI10" s="16" t="s">
+      <c r="AI10" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="AJ10" s="16" t="s">
+      <c r="AJ10" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="AK10" s="16" t="s">
+      <c r="AK10" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="AL10" s="17" t="s">
+      <c r="AL10" s="18" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" ht="15.75" spans="8:38">
-      <c r="H11" s="18">
+    <row r="11" spans="8:38">
+      <c r="H11" s="19">
         <v>1</v>
       </c>
-      <c r="I11" s="19" t="s">
+      <c r="I11" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="J11" s="20">
+      <c r="J11" s="21">
         <v>46204</v>
       </c>
-      <c r="K11" s="20"/>
-      <c r="L11" s="20"/>
-      <c r="M11" s="20"/>
-      <c r="N11" s="21"/>
-      <c r="O11" s="21"/>
-      <c r="P11" s="21"/>
-      <c r="Q11" s="21"/>
-      <c r="R11" s="21"/>
-      <c r="S11" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="T11" s="21"/>
-      <c r="U11" s="21"/>
-      <c r="V11" s="21"/>
-      <c r="W11" s="21"/>
-      <c r="X11" s="21"/>
-      <c r="Y11" s="21"/>
-      <c r="Z11" s="21"/>
-      <c r="AA11" s="21"/>
-      <c r="AB11" s="22"/>
-      <c r="AC11" s="22"/>
-      <c r="AD11" s="22"/>
-      <c r="AE11" s="22"/>
-      <c r="AF11" s="22"/>
-      <c r="AG11" s="22"/>
-      <c r="AH11" s="22"/>
-      <c r="AI11" s="22"/>
-      <c r="AJ11" s="22"/>
-      <c r="AK11" s="22"/>
-      <c r="AL11" s="23">
+      <c r="K11" s="21"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="21"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22"/>
+      <c r="R11" s="22"/>
+      <c r="S11" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="T11" s="22"/>
+      <c r="U11" s="22"/>
+      <c r="V11" s="22"/>
+      <c r="W11" s="22"/>
+      <c r="X11" s="22"/>
+      <c r="Y11" s="22"/>
+      <c r="Z11" s="22"/>
+      <c r="AA11" s="22"/>
+      <c r="AB11" s="23"/>
+      <c r="AC11" s="23"/>
+      <c r="AD11" s="23"/>
+      <c r="AE11" s="23"/>
+      <c r="AF11" s="23"/>
+      <c r="AG11" s="23"/>
+      <c r="AH11" s="23"/>
+      <c r="AI11" s="23"/>
+      <c r="AJ11" s="23"/>
+      <c r="AK11" s="23"/>
+      <c r="AL11" s="24">
         <f>COUNTA(K11:AK11)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="12" ht="15.75" spans="8:38">
-      <c r="H12" s="18">
+    <row r="12" spans="8:38">
+      <c r="H12" s="19">
         <v>2</v>
       </c>
-      <c r="I12" s="19" t="s">
+      <c r="I12" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="20">
+      <c r="J12" s="21">
         <v>46205</v>
       </c>
-      <c r="K12" s="20"/>
-      <c r="L12" s="20"/>
-      <c r="M12" s="20"/>
-      <c r="N12" s="21"/>
-      <c r="O12" s="21"/>
-      <c r="P12" s="21"/>
-      <c r="Q12" s="21"/>
-      <c r="R12" s="21"/>
-      <c r="S12" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="T12" s="21"/>
-      <c r="U12" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="V12" s="21"/>
-      <c r="W12" s="21"/>
-      <c r="X12" s="21"/>
-      <c r="Y12" s="21"/>
-      <c r="Z12" s="21"/>
-      <c r="AA12" s="21"/>
-      <c r="AB12" s="21"/>
-      <c r="AC12" s="21"/>
-      <c r="AD12" s="21"/>
-      <c r="AE12" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="AF12" s="21"/>
-      <c r="AG12" s="21"/>
-      <c r="AH12" s="21"/>
-      <c r="AI12" s="21"/>
-      <c r="AJ12" s="21"/>
-      <c r="AK12" s="21"/>
-      <c r="AL12" s="23">
+      <c r="K12" s="21"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="21"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22"/>
+      <c r="R12" s="22"/>
+      <c r="S12" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="T12" s="22"/>
+      <c r="U12" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="V12" s="22"/>
+      <c r="W12" s="22"/>
+      <c r="X12" s="22"/>
+      <c r="Y12" s="22"/>
+      <c r="Z12" s="22"/>
+      <c r="AA12" s="22"/>
+      <c r="AB12" s="22"/>
+      <c r="AC12" s="22"/>
+      <c r="AD12" s="22"/>
+      <c r="AE12" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF12" s="22"/>
+      <c r="AG12" s="22"/>
+      <c r="AH12" s="22"/>
+      <c r="AI12" s="22"/>
+      <c r="AJ12" s="22"/>
+      <c r="AK12" s="22"/>
+      <c r="AL12" s="24">
         <f t="shared" ref="AL12:AL41" si="0">COUNTA(K12:AK12)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="13" ht="15.75" spans="8:38">
-      <c r="H13" s="18">
+    <row r="13" spans="8:38">
+      <c r="H13" s="19">
         <v>3</v>
       </c>
-      <c r="I13" s="19" t="s">
+      <c r="I13" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="J13" s="20">
+      <c r="J13" s="21">
         <v>46206</v>
       </c>
-      <c r="K13" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="L13" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="M13" s="24"/>
-      <c r="N13" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="O13" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="P13" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q13" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="R13" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="S13" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="T13" s="21"/>
-      <c r="U13" s="21"/>
-      <c r="V13" s="21"/>
-      <c r="W13" s="21"/>
-      <c r="X13" s="21"/>
-      <c r="Y13" s="21"/>
-      <c r="Z13" s="21"/>
-      <c r="AA13" s="21"/>
-      <c r="AB13" s="21"/>
-      <c r="AC13" s="21"/>
-      <c r="AD13" s="21"/>
-      <c r="AE13" s="21"/>
-      <c r="AF13" s="21"/>
-      <c r="AG13" s="21"/>
-      <c r="AH13" s="21"/>
-      <c r="AI13" s="21"/>
-      <c r="AJ13" s="21"/>
-      <c r="AK13" s="21"/>
-      <c r="AL13" s="23">
+      <c r="K13" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="L13" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="M13" s="25"/>
+      <c r="N13" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="O13" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="P13" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q13" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="R13" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="S13" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="T13" s="22"/>
+      <c r="U13" s="22"/>
+      <c r="V13" s="22"/>
+      <c r="W13" s="22"/>
+      <c r="X13" s="22"/>
+      <c r="Y13" s="22"/>
+      <c r="Z13" s="22"/>
+      <c r="AA13" s="22"/>
+      <c r="AB13" s="22"/>
+      <c r="AC13" s="22"/>
+      <c r="AD13" s="22"/>
+      <c r="AE13" s="22"/>
+      <c r="AF13" s="22"/>
+      <c r="AG13" s="22"/>
+      <c r="AH13" s="22"/>
+      <c r="AI13" s="22"/>
+      <c r="AJ13" s="22"/>
+      <c r="AK13" s="22"/>
+      <c r="AL13" s="24">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="14" ht="15.75" spans="8:38">
-      <c r="H14" s="18">
+    <row r="14" spans="8:38">
+      <c r="H14" s="19">
         <v>4</v>
       </c>
-      <c r="I14" s="19" t="s">
+      <c r="I14" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J14" s="20">
+      <c r="J14" s="21">
         <v>46207</v>
       </c>
-      <c r="K14" s="24"/>
-      <c r="L14" s="24"/>
-      <c r="M14" s="24"/>
-      <c r="N14" s="21"/>
-      <c r="O14" s="21"/>
-      <c r="P14" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q14" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="R14" s="21"/>
-      <c r="S14" s="21"/>
-      <c r="T14" s="21"/>
-      <c r="U14" s="21"/>
-      <c r="V14" s="21"/>
-      <c r="W14" s="21"/>
-      <c r="X14" s="21"/>
-      <c r="Y14" s="21"/>
-      <c r="Z14" s="21"/>
-      <c r="AA14" s="21"/>
-      <c r="AB14" s="21"/>
-      <c r="AC14" s="21"/>
-      <c r="AD14" s="21"/>
-      <c r="AE14" s="21"/>
-      <c r="AF14" s="21"/>
-      <c r="AG14" s="21"/>
-      <c r="AH14" s="21"/>
-      <c r="AI14" s="21"/>
-      <c r="AJ14" s="21"/>
-      <c r="AK14" s="21"/>
-      <c r="AL14" s="23">
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
+      <c r="M14" s="25"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q14" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="R14" s="22"/>
+      <c r="S14" s="22"/>
+      <c r="T14" s="22"/>
+      <c r="U14" s="22"/>
+      <c r="V14" s="22"/>
+      <c r="W14" s="22"/>
+      <c r="X14" s="22"/>
+      <c r="Y14" s="22"/>
+      <c r="Z14" s="22"/>
+      <c r="AA14" s="22"/>
+      <c r="AB14" s="22"/>
+      <c r="AC14" s="22"/>
+      <c r="AD14" s="22"/>
+      <c r="AE14" s="22"/>
+      <c r="AF14" s="22"/>
+      <c r="AG14" s="22"/>
+      <c r="AH14" s="22"/>
+      <c r="AI14" s="22"/>
+      <c r="AJ14" s="22"/>
+      <c r="AK14" s="22"/>
+      <c r="AL14" s="24">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="15" ht="15.75" spans="8:38">
-      <c r="H15" s="18">
+    <row r="15" spans="8:38">
+      <c r="H15" s="19">
         <v>5</v>
       </c>
-      <c r="I15" s="19" t="s">
+      <c r="I15" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="J15" s="20">
+      <c r="J15" s="21">
         <v>46208</v>
       </c>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="24"/>
-      <c r="N15" s="21"/>
-      <c r="O15" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="P15" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q15" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="R15" s="21"/>
-      <c r="S15" s="21"/>
-      <c r="T15" s="21"/>
-      <c r="U15" s="21"/>
-      <c r="V15" s="21"/>
-      <c r="W15" s="21"/>
-      <c r="X15" s="21"/>
-      <c r="Y15" s="21"/>
-      <c r="Z15" s="21"/>
-      <c r="AA15" s="21"/>
-      <c r="AB15" s="21"/>
-      <c r="AC15" s="21"/>
-      <c r="AD15" s="21"/>
-      <c r="AE15" s="21"/>
-      <c r="AF15" s="21"/>
-      <c r="AG15" s="21"/>
-      <c r="AH15" s="21"/>
-      <c r="AI15" s="21"/>
-      <c r="AJ15" s="21"/>
-      <c r="AK15" s="21"/>
-      <c r="AL15" s="23">
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
+      <c r="M15" s="25"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="P15" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q15" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="R15" s="22"/>
+      <c r="S15" s="22"/>
+      <c r="T15" s="22"/>
+      <c r="U15" s="22"/>
+      <c r="V15" s="22"/>
+      <c r="W15" s="22"/>
+      <c r="X15" s="22"/>
+      <c r="Y15" s="22"/>
+      <c r="Z15" s="22"/>
+      <c r="AA15" s="22"/>
+      <c r="AB15" s="22"/>
+      <c r="AC15" s="22"/>
+      <c r="AD15" s="22"/>
+      <c r="AE15" s="22"/>
+      <c r="AF15" s="22"/>
+      <c r="AG15" s="22"/>
+      <c r="AH15" s="22"/>
+      <c r="AI15" s="22"/>
+      <c r="AJ15" s="22"/>
+      <c r="AK15" s="22"/>
+      <c r="AL15" s="24">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="16" ht="15.75" spans="8:38">
-      <c r="H16" s="18">
+    <row r="16" spans="8:38">
+      <c r="H16" s="19">
         <v>6</v>
       </c>
-      <c r="I16" s="19" t="s">
+      <c r="I16" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="J16" s="20">
+      <c r="J16" s="21">
         <v>46209</v>
       </c>
-      <c r="K16" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="L16" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="M16" s="24"/>
-      <c r="N16" s="21"/>
-      <c r="O16" s="21"/>
-      <c r="P16" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q16" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="R16" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="S16" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="T16" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="U16" s="21"/>
-      <c r="V16" s="21"/>
-      <c r="W16" s="21"/>
-      <c r="X16" s="21"/>
-      <c r="Y16" s="21"/>
-      <c r="Z16" s="21"/>
-      <c r="AA16" s="21"/>
-      <c r="AB16" s="21"/>
-      <c r="AC16" s="21"/>
-      <c r="AD16" s="21"/>
-      <c r="AE16" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="AF16" s="21"/>
-      <c r="AG16" s="21"/>
-      <c r="AH16" s="21"/>
-      <c r="AI16" s="21"/>
-      <c r="AJ16" s="21"/>
-      <c r="AK16" s="21"/>
-      <c r="AL16" s="23">
+      <c r="K16" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="L16" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="M16" s="25"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q16" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="R16" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="S16" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="T16" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="U16" s="22"/>
+      <c r="V16" s="22"/>
+      <c r="W16" s="22"/>
+      <c r="X16" s="22"/>
+      <c r="Y16" s="22"/>
+      <c r="Z16" s="22"/>
+      <c r="AA16" s="22"/>
+      <c r="AB16" s="22"/>
+      <c r="AC16" s="22"/>
+      <c r="AD16" s="22"/>
+      <c r="AE16" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF16" s="22"/>
+      <c r="AG16" s="22"/>
+      <c r="AH16" s="22"/>
+      <c r="AI16" s="22"/>
+      <c r="AJ16" s="22"/>
+      <c r="AK16" s="22"/>
+      <c r="AL16" s="24">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="17" ht="15.75" spans="8:38">
-      <c r="H17" s="18">
+    <row r="17" spans="8:38">
+      <c r="H17" s="19">
         <v>7</v>
       </c>
-      <c r="I17" s="19" t="s">
+      <c r="I17" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="J17" s="20">
+      <c r="J17" s="21">
         <v>46210</v>
       </c>
-      <c r="K17" s="24"/>
-      <c r="L17" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="M17" s="24"/>
-      <c r="N17" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="O17" s="21"/>
-      <c r="P17" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q17" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="R17" s="21"/>
-      <c r="S17" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="T17" s="21"/>
-      <c r="U17" s="21"/>
-      <c r="V17" s="21"/>
-      <c r="W17" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="X17" s="21"/>
-      <c r="Y17" s="21"/>
-      <c r="Z17" s="21"/>
-      <c r="AA17" s="21"/>
-      <c r="AB17" s="21"/>
-      <c r="AC17" s="21"/>
-      <c r="AD17" s="21"/>
-      <c r="AE17" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="AF17" s="21"/>
-      <c r="AG17" s="21"/>
-      <c r="AH17" s="21"/>
-      <c r="AI17" s="21"/>
-      <c r="AJ17" s="21"/>
-      <c r="AK17" s="21"/>
-      <c r="AL17" s="23">
+      <c r="K17" s="25"/>
+      <c r="L17" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="M17" s="25"/>
+      <c r="N17" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q17" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="R17" s="22"/>
+      <c r="S17" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="T17" s="22"/>
+      <c r="U17" s="22"/>
+      <c r="V17" s="22"/>
+      <c r="W17" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="X17" s="22"/>
+      <c r="Y17" s="22"/>
+      <c r="Z17" s="22"/>
+      <c r="AA17" s="22"/>
+      <c r="AB17" s="22"/>
+      <c r="AC17" s="22"/>
+      <c r="AD17" s="22"/>
+      <c r="AE17" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF17" s="22"/>
+      <c r="AG17" s="22"/>
+      <c r="AH17" s="22"/>
+      <c r="AI17" s="22"/>
+      <c r="AJ17" s="22"/>
+      <c r="AK17" s="22"/>
+      <c r="AL17" s="24">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="18" ht="15.75" spans="8:38">
-      <c r="H18" s="18">
+    <row r="18" spans="8:38">
+      <c r="H18" s="19">
         <v>8</v>
       </c>
-      <c r="I18" s="19" t="s">
+      <c r="I18" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="J18" s="20">
+      <c r="J18" s="21">
         <v>46211</v>
       </c>
-      <c r="K18" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="L18" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="M18" s="24"/>
-      <c r="N18" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="O18" s="21"/>
-      <c r="P18" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q18" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="R18" s="21"/>
-      <c r="S18" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="T18" s="21"/>
-      <c r="U18" s="21"/>
-      <c r="V18" s="21"/>
-      <c r="W18" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="X18" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y18" s="21"/>
-      <c r="Z18" s="21"/>
-      <c r="AA18" s="21"/>
-      <c r="AB18" s="21"/>
-      <c r="AC18" s="21"/>
-      <c r="AD18" s="21"/>
-      <c r="AE18" s="21"/>
-      <c r="AF18" s="21"/>
-      <c r="AG18" s="21"/>
-      <c r="AH18" s="21"/>
-      <c r="AI18" s="21"/>
-      <c r="AJ18" s="21"/>
-      <c r="AK18" s="21"/>
-      <c r="AL18" s="23">
+      <c r="K18" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="L18" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="M18" s="25"/>
+      <c r="N18" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q18" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="R18" s="22"/>
+      <c r="S18" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="T18" s="22"/>
+      <c r="U18" s="22"/>
+      <c r="V18" s="22"/>
+      <c r="W18" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="X18" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y18" s="22"/>
+      <c r="Z18" s="22"/>
+      <c r="AA18" s="22"/>
+      <c r="AB18" s="22"/>
+      <c r="AC18" s="22"/>
+      <c r="AD18" s="22"/>
+      <c r="AE18" s="22"/>
+      <c r="AF18" s="22"/>
+      <c r="AG18" s="22"/>
+      <c r="AH18" s="22"/>
+      <c r="AI18" s="22"/>
+      <c r="AJ18" s="22"/>
+      <c r="AK18" s="22"/>
+      <c r="AL18" s="24">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="19" ht="15.75" spans="8:38">
-      <c r="H19" s="18">
+    <row r="19" spans="8:38">
+      <c r="H19" s="19">
         <v>9</v>
       </c>
-      <c r="I19" s="19" t="s">
+      <c r="I19" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="J19" s="20">
+      <c r="J19" s="21">
         <v>46212</v>
       </c>
-      <c r="K19" s="24"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="24"/>
-      <c r="N19" s="21"/>
-      <c r="O19" s="21"/>
-      <c r="P19" s="21"/>
-      <c r="Q19" s="21"/>
-      <c r="R19" s="21"/>
-      <c r="S19" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="T19" s="21"/>
-      <c r="U19" s="21"/>
-      <c r="V19" s="21"/>
-      <c r="W19" s="21"/>
-      <c r="X19" s="21"/>
-      <c r="Y19" s="21"/>
-      <c r="Z19" s="21"/>
-      <c r="AA19" s="21"/>
-      <c r="AB19" s="21"/>
-      <c r="AC19" s="21"/>
-      <c r="AD19" s="21"/>
-      <c r="AE19" s="21"/>
-      <c r="AF19" s="21"/>
-      <c r="AG19" s="21"/>
-      <c r="AH19" s="21"/>
-      <c r="AI19" s="21"/>
-      <c r="AJ19" s="21"/>
-      <c r="AK19" s="21"/>
-      <c r="AL19" s="23">
+      <c r="K19" s="25"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="25"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22"/>
+      <c r="R19" s="22"/>
+      <c r="S19" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="T19" s="22"/>
+      <c r="U19" s="22"/>
+      <c r="V19" s="22"/>
+      <c r="W19" s="22"/>
+      <c r="X19" s="22"/>
+      <c r="Y19" s="22"/>
+      <c r="Z19" s="22"/>
+      <c r="AA19" s="22"/>
+      <c r="AB19" s="22"/>
+      <c r="AC19" s="22"/>
+      <c r="AD19" s="22"/>
+      <c r="AE19" s="22"/>
+      <c r="AF19" s="22"/>
+      <c r="AG19" s="22"/>
+      <c r="AH19" s="22"/>
+      <c r="AI19" s="22"/>
+      <c r="AJ19" s="22"/>
+      <c r="AK19" s="22"/>
+      <c r="AL19" s="24">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="20" ht="15.75" spans="8:38">
-      <c r="H20" s="18">
+    <row r="20" spans="8:38">
+      <c r="H20" s="19">
         <v>10</v>
       </c>
-      <c r="I20" s="19" t="s">
+      <c r="I20" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="J20" s="20">
+      <c r="J20" s="21">
         <v>46213</v>
       </c>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="24"/>
-      <c r="N20" s="21"/>
-      <c r="O20" s="21"/>
-      <c r="P20" s="21"/>
-      <c r="Q20" s="21"/>
-      <c r="R20" s="21"/>
-      <c r="S20" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="T20" s="21"/>
-      <c r="U20" s="21"/>
-      <c r="V20" s="21"/>
-      <c r="W20" s="21"/>
-      <c r="X20" s="21"/>
-      <c r="Y20" s="21"/>
-      <c r="Z20" s="21"/>
-      <c r="AA20" s="21"/>
-      <c r="AB20" s="21"/>
-      <c r="AC20" s="21"/>
-      <c r="AD20" s="21"/>
-      <c r="AE20" s="21"/>
-      <c r="AF20" s="21"/>
-      <c r="AG20" s="21"/>
-      <c r="AH20" s="21"/>
-      <c r="AI20" s="21"/>
-      <c r="AJ20" s="21"/>
-      <c r="AK20" s="21"/>
-      <c r="AL20" s="23">
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
+      <c r="M20" s="25"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22"/>
+      <c r="R20" s="22"/>
+      <c r="S20" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="T20" s="22"/>
+      <c r="U20" s="22"/>
+      <c r="V20" s="22"/>
+      <c r="W20" s="22"/>
+      <c r="X20" s="22"/>
+      <c r="Y20" s="22"/>
+      <c r="Z20" s="22"/>
+      <c r="AA20" s="22"/>
+      <c r="AB20" s="22"/>
+      <c r="AC20" s="22"/>
+      <c r="AD20" s="22"/>
+      <c r="AE20" s="22"/>
+      <c r="AF20" s="22"/>
+      <c r="AG20" s="22"/>
+      <c r="AH20" s="22"/>
+      <c r="AI20" s="22"/>
+      <c r="AJ20" s="22"/>
+      <c r="AK20" s="22"/>
+      <c r="AL20" s="24">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="21" ht="15.75" spans="8:38">
-      <c r="H21" s="18">
+    <row r="21" spans="8:38">
+      <c r="H21" s="19">
         <v>11</v>
       </c>
-      <c r="I21" s="19" t="s">
+      <c r="I21" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J21" s="20">
+      <c r="J21" s="21">
         <v>46214</v>
       </c>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="24"/>
-      <c r="N21" s="21"/>
-      <c r="O21" s="21"/>
-      <c r="P21" s="21"/>
-      <c r="Q21" s="21"/>
-      <c r="R21" s="21"/>
-      <c r="S21" s="21"/>
-      <c r="T21" s="21"/>
-      <c r="U21" s="21"/>
-      <c r="V21" s="21"/>
-      <c r="W21" s="21"/>
-      <c r="X21" s="21"/>
-      <c r="Y21" s="21"/>
-      <c r="Z21" s="21"/>
-      <c r="AA21" s="21"/>
-      <c r="AB21" s="21"/>
-      <c r="AC21" s="21"/>
-      <c r="AD21" s="21"/>
-      <c r="AE21" s="21"/>
-      <c r="AF21" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG21" s="21"/>
-      <c r="AH21" s="21"/>
-      <c r="AI21" s="21"/>
-      <c r="AJ21" s="21"/>
-      <c r="AK21" s="21"/>
-      <c r="AL21" s="23">
+      <c r="K21" s="25"/>
+      <c r="L21" s="25"/>
+      <c r="M21" s="25"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="22"/>
+      <c r="R21" s="22"/>
+      <c r="S21" s="22"/>
+      <c r="T21" s="22"/>
+      <c r="U21" s="22"/>
+      <c r="V21" s="22"/>
+      <c r="W21" s="22"/>
+      <c r="X21" s="22"/>
+      <c r="Y21" s="22"/>
+      <c r="Z21" s="22"/>
+      <c r="AA21" s="22"/>
+      <c r="AB21" s="22"/>
+      <c r="AC21" s="22"/>
+      <c r="AD21" s="22"/>
+      <c r="AE21" s="22"/>
+      <c r="AF21" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG21" s="22"/>
+      <c r="AH21" s="22"/>
+      <c r="AI21" s="22"/>
+      <c r="AJ21" s="22"/>
+      <c r="AK21" s="22"/>
+      <c r="AL21" s="24">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="22" ht="15.75" spans="8:38">
-      <c r="H22" s="18">
-        <v>12</v>
-      </c>
-      <c r="I22" s="19" t="s">
+    <row r="22" spans="8:38">
+      <c r="H22" s="19">
+        <v>12</v>
+      </c>
+      <c r="I22" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="J22" s="20">
+      <c r="J22" s="21">
         <v>46215</v>
       </c>
-      <c r="K22" s="24"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="24"/>
-      <c r="N22" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="O22" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="P22" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q22" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="R22" s="21"/>
-      <c r="S22" s="21"/>
-      <c r="T22" s="21"/>
-      <c r="U22" s="21"/>
-      <c r="V22" s="21"/>
-      <c r="W22" s="21"/>
-      <c r="X22" s="21"/>
-      <c r="Y22" s="21"/>
-      <c r="Z22" s="21"/>
-      <c r="AA22" s="21"/>
-      <c r="AB22" s="21"/>
-      <c r="AC22" s="21"/>
-      <c r="AD22" s="21"/>
-      <c r="AE22" s="21"/>
-      <c r="AF22" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG22" s="21"/>
-      <c r="AH22" s="21"/>
-      <c r="AI22" s="21"/>
-      <c r="AJ22" s="21"/>
-      <c r="AK22" s="21"/>
-      <c r="AL22" s="23">
+      <c r="K22" s="25"/>
+      <c r="L22" s="25"/>
+      <c r="M22" s="25"/>
+      <c r="N22" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="O22" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="P22" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q22" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="R22" s="22"/>
+      <c r="S22" s="22"/>
+      <c r="T22" s="22"/>
+      <c r="U22" s="22"/>
+      <c r="V22" s="22"/>
+      <c r="W22" s="22"/>
+      <c r="X22" s="22"/>
+      <c r="Y22" s="22"/>
+      <c r="Z22" s="22"/>
+      <c r="AA22" s="22"/>
+      <c r="AB22" s="22"/>
+      <c r="AC22" s="22"/>
+      <c r="AD22" s="22"/>
+      <c r="AE22" s="22"/>
+      <c r="AF22" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG22" s="22"/>
+      <c r="AH22" s="22"/>
+      <c r="AI22" s="22"/>
+      <c r="AJ22" s="22"/>
+      <c r="AK22" s="22"/>
+      <c r="AL22" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="23" ht="15.75" spans="8:38">
-      <c r="H23" s="18">
+    <row r="23" spans="8:38">
+      <c r="H23" s="19">
         <v>13</v>
       </c>
-      <c r="I23" s="19" t="s">
+      <c r="I23" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="J23" s="20">
+      <c r="J23" s="21">
         <v>46216</v>
       </c>
-      <c r="K23" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="L23" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="M23" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="N23" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="O23" s="21"/>
-      <c r="P23" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q23" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="R23" s="21"/>
-      <c r="S23" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="T23" s="21"/>
-      <c r="U23" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="V23" s="21"/>
-      <c r="W23" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="X23" s="21"/>
-      <c r="Y23" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z23" s="21"/>
-      <c r="AA23" s="21"/>
-      <c r="AB23" s="21"/>
-      <c r="AC23" s="21"/>
-      <c r="AD23" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE23" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="AF23" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG23" s="21"/>
-      <c r="AH23" s="21"/>
-      <c r="AI23" s="21"/>
-      <c r="AJ23" s="21"/>
-      <c r="AK23" s="21"/>
-      <c r="AL23" s="23">
+      <c r="K23" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="L23" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="M23" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="N23" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q23" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="R23" s="22"/>
+      <c r="S23" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="T23" s="22"/>
+      <c r="U23" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="V23" s="22"/>
+      <c r="W23" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="X23" s="22"/>
+      <c r="Y23" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z23" s="22"/>
+      <c r="AA23" s="22"/>
+      <c r="AB23" s="22"/>
+      <c r="AC23" s="22"/>
+      <c r="AD23" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE23" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF23" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG23" s="22"/>
+      <c r="AH23" s="22"/>
+      <c r="AI23" s="22"/>
+      <c r="AJ23" s="22"/>
+      <c r="AK23" s="22"/>
+      <c r="AL23" s="24">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
     </row>
-    <row r="24" ht="15.75" spans="8:38">
-      <c r="H24" s="18">
+    <row r="24" spans="8:38">
+      <c r="H24" s="19">
         <v>14</v>
       </c>
-      <c r="I24" s="19" t="s">
+      <c r="I24" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="J24" s="20">
+      <c r="J24" s="21">
         <v>46217</v>
       </c>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
-      <c r="M24" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="N24" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="O24" s="21"/>
-      <c r="P24" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q24" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="R24" s="21"/>
-      <c r="S24" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="T24" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="U24" s="21"/>
-      <c r="V24" s="21"/>
-      <c r="W24" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="X24" s="21"/>
-      <c r="Y24" s="21"/>
-      <c r="Z24" s="21"/>
-      <c r="AA24" s="21"/>
-      <c r="AB24" s="21"/>
-      <c r="AC24" s="21"/>
-      <c r="AD24" s="21"/>
-      <c r="AE24" s="21"/>
-      <c r="AF24" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG24" s="21"/>
-      <c r="AH24" s="21"/>
-      <c r="AI24" s="21"/>
-      <c r="AJ24" s="21"/>
-      <c r="AK24" s="21"/>
-      <c r="AL24" s="23">
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
+      <c r="M24" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="N24" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="O24" s="22"/>
+      <c r="P24" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q24" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="R24" s="22"/>
+      <c r="S24" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="T24" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="U24" s="22"/>
+      <c r="V24" s="22"/>
+      <c r="W24" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="X24" s="22"/>
+      <c r="Y24" s="22"/>
+      <c r="Z24" s="22"/>
+      <c r="AA24" s="22"/>
+      <c r="AB24" s="22"/>
+      <c r="AC24" s="22"/>
+      <c r="AD24" s="22"/>
+      <c r="AE24" s="22"/>
+      <c r="AF24" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG24" s="22"/>
+      <c r="AH24" s="22"/>
+      <c r="AI24" s="22"/>
+      <c r="AJ24" s="22"/>
+      <c r="AK24" s="22"/>
+      <c r="AL24" s="24">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="25" ht="15.75" spans="8:38">
-      <c r="H25" s="18">
+    <row r="25" spans="8:38">
+      <c r="H25" s="19">
         <v>15</v>
       </c>
-      <c r="I25" s="19" t="s">
+      <c r="I25" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="J25" s="20">
+      <c r="J25" s="21">
         <v>46218</v>
       </c>
-      <c r="K25" s="24"/>
-      <c r="L25" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="M25" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="N25" s="21"/>
-      <c r="O25" s="21"/>
-      <c r="P25" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q25" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="R25" s="21"/>
-      <c r="S25" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="T25" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="U25" s="21"/>
-      <c r="V25" s="21"/>
-      <c r="W25" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="X25" s="21"/>
-      <c r="Y25" s="21"/>
-      <c r="Z25" s="21"/>
-      <c r="AA25" s="21"/>
-      <c r="AB25" s="21"/>
-      <c r="AC25" s="21"/>
-      <c r="AD25" s="21"/>
-      <c r="AE25" s="21"/>
-      <c r="AF25" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG25" s="21"/>
-      <c r="AH25" s="21"/>
-      <c r="AI25" s="21"/>
-      <c r="AJ25" s="21"/>
-      <c r="AK25" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="AL25" s="23">
+      <c r="K25" s="25"/>
+      <c r="L25" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="M25" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q25" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="R25" s="22"/>
+      <c r="S25" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="T25" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="U25" s="22"/>
+      <c r="V25" s="22"/>
+      <c r="W25" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="X25" s="22"/>
+      <c r="Y25" s="22"/>
+      <c r="Z25" s="22"/>
+      <c r="AA25" s="22"/>
+      <c r="AB25" s="22"/>
+      <c r="AC25" s="22"/>
+      <c r="AD25" s="22"/>
+      <c r="AE25" s="22"/>
+      <c r="AF25" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG25" s="22"/>
+      <c r="AH25" s="22"/>
+      <c r="AI25" s="22"/>
+      <c r="AJ25" s="22"/>
+      <c r="AK25" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL25" s="24">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="26" ht="15.75" spans="8:38">
-      <c r="H26" s="18">
+    <row r="26" spans="8:38">
+      <c r="H26" s="19">
         <v>16</v>
       </c>
-      <c r="I26" s="19" t="s">
+      <c r="I26" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="J26" s="20">
+      <c r="J26" s="21">
         <v>46219</v>
       </c>
-      <c r="K26" s="24"/>
-      <c r="L26" s="24"/>
-      <c r="M26" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="N26" s="21"/>
-      <c r="O26" s="21"/>
-      <c r="P26" s="21"/>
-      <c r="Q26" s="21"/>
-      <c r="R26" s="21"/>
-      <c r="S26" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="T26" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="U26" s="21"/>
-      <c r="V26" s="21"/>
-      <c r="W26" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="X26" s="21"/>
-      <c r="Y26" s="21"/>
-      <c r="Z26" s="21"/>
-      <c r="AA26" s="21"/>
-      <c r="AB26" s="21"/>
-      <c r="AC26" s="21"/>
-      <c r="AD26" s="21"/>
-      <c r="AE26" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="AF26" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG26" s="21"/>
-      <c r="AH26" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="AI26" s="21"/>
-      <c r="AJ26" s="21"/>
-      <c r="AK26" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="AL26" s="23">
+      <c r="K26" s="25"/>
+      <c r="L26" s="25"/>
+      <c r="M26" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22"/>
+      <c r="R26" s="22"/>
+      <c r="S26" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="T26" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="U26" s="22"/>
+      <c r="V26" s="22"/>
+      <c r="W26" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="X26" s="22"/>
+      <c r="Y26" s="22"/>
+      <c r="Z26" s="22"/>
+      <c r="AA26" s="22"/>
+      <c r="AB26" s="22"/>
+      <c r="AC26" s="22"/>
+      <c r="AD26" s="22"/>
+      <c r="AE26" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF26" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG26" s="22"/>
+      <c r="AH26" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AI26" s="22"/>
+      <c r="AJ26" s="22"/>
+      <c r="AK26" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL26" s="24">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="27" ht="15.75" spans="8:38">
-      <c r="H27" s="18">
+    <row r="27" spans="8:38">
+      <c r="H27" s="19">
         <v>17</v>
       </c>
-      <c r="I27" s="19" t="s">
+      <c r="I27" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="J27" s="20">
+      <c r="J27" s="21">
         <v>46220</v>
       </c>
-      <c r="K27" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="L27" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="M27" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="N27" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="O27" s="21"/>
-      <c r="P27" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q27" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="R27" s="21"/>
-      <c r="S27" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="T27" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="U27" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="V27" s="21"/>
-      <c r="W27" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="X27" s="21"/>
-      <c r="Y27" s="21"/>
-      <c r="Z27" s="21"/>
-      <c r="AA27" s="21"/>
-      <c r="AB27" s="21"/>
-      <c r="AC27" s="21"/>
-      <c r="AD27" s="21"/>
-      <c r="AE27" s="21"/>
-      <c r="AF27" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG27" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="AH27" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="AI27" s="21"/>
-      <c r="AJ27" s="21"/>
-      <c r="AK27" s="21"/>
-      <c r="AL27" s="23">
+      <c r="K27" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="L27" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="M27" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="N27" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="O27" s="22"/>
+      <c r="P27" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q27" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="R27" s="22"/>
+      <c r="S27" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="T27" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="U27" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="V27" s="22"/>
+      <c r="W27" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="X27" s="22"/>
+      <c r="Y27" s="22"/>
+      <c r="Z27" s="22"/>
+      <c r="AA27" s="22"/>
+      <c r="AB27" s="22"/>
+      <c r="AC27" s="22"/>
+      <c r="AD27" s="22"/>
+      <c r="AE27" s="22"/>
+      <c r="AF27" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG27" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AH27" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AI27" s="22"/>
+      <c r="AJ27" s="22"/>
+      <c r="AK27" s="22"/>
+      <c r="AL27" s="24">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
     </row>
-    <row r="28" ht="15.75" spans="8:38">
-      <c r="H28" s="18">
+    <row r="28" spans="8:38">
+      <c r="H28" s="19">
         <v>18</v>
       </c>
-      <c r="I28" s="19" t="s">
+      <c r="I28" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J28" s="20">
+      <c r="J28" s="21">
         <v>46221</v>
       </c>
-      <c r="K28" s="24"/>
-      <c r="L28" s="24"/>
-      <c r="M28" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="N28" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="O28" s="21"/>
-      <c r="P28" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q28" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="R28" s="21"/>
-      <c r="S28" s="21"/>
-      <c r="T28" s="21"/>
-      <c r="U28" s="21"/>
-      <c r="V28" s="21"/>
-      <c r="W28" s="21"/>
-      <c r="X28" s="21"/>
-      <c r="Y28" s="21"/>
-      <c r="Z28" s="21"/>
-      <c r="AA28" s="21"/>
-      <c r="AB28" s="21"/>
-      <c r="AC28" s="21"/>
-      <c r="AD28" s="21"/>
-      <c r="AE28" s="21"/>
-      <c r="AF28" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG28" s="21"/>
-      <c r="AH28" s="21"/>
-      <c r="AI28" s="21"/>
-      <c r="AJ28" s="21"/>
-      <c r="AK28" s="21"/>
-      <c r="AL28" s="23">
+      <c r="K28" s="25"/>
+      <c r="L28" s="25"/>
+      <c r="M28" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="N28" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="O28" s="22"/>
+      <c r="P28" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q28" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="R28" s="22"/>
+      <c r="S28" s="22"/>
+      <c r="T28" s="22"/>
+      <c r="U28" s="22"/>
+      <c r="V28" s="22"/>
+      <c r="W28" s="22"/>
+      <c r="X28" s="22"/>
+      <c r="Y28" s="22"/>
+      <c r="Z28" s="22"/>
+      <c r="AA28" s="22"/>
+      <c r="AB28" s="22"/>
+      <c r="AC28" s="22"/>
+      <c r="AD28" s="22"/>
+      <c r="AE28" s="22"/>
+      <c r="AF28" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG28" s="22"/>
+      <c r="AH28" s="22"/>
+      <c r="AI28" s="22"/>
+      <c r="AJ28" s="22"/>
+      <c r="AK28" s="22"/>
+      <c r="AL28" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="29" ht="15.75" spans="8:38">
-      <c r="H29" s="18">
+    <row r="29" spans="8:38">
+      <c r="H29" s="19">
         <v>19</v>
       </c>
-      <c r="I29" s="19" t="s">
+      <c r="I29" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="J29" s="20">
+      <c r="J29" s="21">
         <v>46222</v>
       </c>
-      <c r="K29" s="24"/>
-      <c r="L29" s="24"/>
-      <c r="M29" s="24"/>
-      <c r="N29" s="21"/>
-      <c r="O29" s="21"/>
-      <c r="P29" s="21"/>
-      <c r="Q29" s="21"/>
-      <c r="R29" s="21"/>
-      <c r="S29" s="21"/>
-      <c r="T29" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="U29" s="21"/>
-      <c r="V29" s="21"/>
-      <c r="W29" s="21"/>
-      <c r="X29" s="21"/>
-      <c r="Y29" s="21"/>
-      <c r="Z29" s="21"/>
-      <c r="AA29" s="21"/>
-      <c r="AB29" s="21"/>
-      <c r="AC29" s="21"/>
-      <c r="AD29" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE29" s="21"/>
-      <c r="AF29" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG29" s="21"/>
-      <c r="AH29" s="21"/>
-      <c r="AI29" s="21"/>
-      <c r="AJ29" s="21"/>
-      <c r="AK29" s="21"/>
-      <c r="AL29" s="23">
+      <c r="K29" s="25"/>
+      <c r="L29" s="25"/>
+      <c r="M29" s="25"/>
+      <c r="N29" s="22"/>
+      <c r="O29" s="22"/>
+      <c r="P29" s="22"/>
+      <c r="Q29" s="22"/>
+      <c r="R29" s="22"/>
+      <c r="S29" s="22"/>
+      <c r="T29" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="U29" s="22"/>
+      <c r="V29" s="22"/>
+      <c r="W29" s="22"/>
+      <c r="X29" s="22"/>
+      <c r="Y29" s="22"/>
+      <c r="Z29" s="22"/>
+      <c r="AA29" s="22"/>
+      <c r="AB29" s="22"/>
+      <c r="AC29" s="22"/>
+      <c r="AD29" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE29" s="22"/>
+      <c r="AF29" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG29" s="22"/>
+      <c r="AH29" s="22"/>
+      <c r="AI29" s="22"/>
+      <c r="AJ29" s="22"/>
+      <c r="AK29" s="22"/>
+      <c r="AL29" s="24">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="30" ht="15.75" spans="8:38">
-      <c r="H30" s="18">
+    <row r="30" spans="8:38">
+      <c r="H30" s="19">
         <v>20</v>
       </c>
-      <c r="I30" s="19" t="s">
+      <c r="I30" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="J30" s="20">
+      <c r="J30" s="21">
         <v>46223</v>
       </c>
-      <c r="K30" s="24"/>
-      <c r="L30" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="M30" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="N30" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="O30" s="21"/>
-      <c r="P30" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q30" s="21"/>
-      <c r="R30" s="21"/>
-      <c r="S30" s="21"/>
-      <c r="T30" s="21"/>
-      <c r="U30" s="21"/>
-      <c r="V30" s="21"/>
-      <c r="W30" s="21"/>
-      <c r="X30" s="21"/>
-      <c r="Y30" s="21"/>
-      <c r="Z30" s="21"/>
-      <c r="AA30" s="21"/>
-      <c r="AB30" s="21"/>
-      <c r="AC30" s="21"/>
-      <c r="AD30" s="21"/>
-      <c r="AE30" s="21"/>
-      <c r="AF30" s="21"/>
-      <c r="AG30" s="21"/>
-      <c r="AH30" s="21"/>
-      <c r="AI30" s="21"/>
-      <c r="AJ30" s="21"/>
-      <c r="AK30" s="21"/>
-      <c r="AL30" s="23">
+      <c r="K30" s="25"/>
+      <c r="L30" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="M30" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="N30" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="O30" s="22"/>
+      <c r="P30" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q30" s="22"/>
+      <c r="R30" s="22"/>
+      <c r="S30" s="22"/>
+      <c r="T30" s="22"/>
+      <c r="U30" s="22"/>
+      <c r="V30" s="22"/>
+      <c r="W30" s="22"/>
+      <c r="X30" s="22"/>
+      <c r="Y30" s="22"/>
+      <c r="Z30" s="22"/>
+      <c r="AA30" s="22"/>
+      <c r="AB30" s="22"/>
+      <c r="AC30" s="22"/>
+      <c r="AD30" s="22"/>
+      <c r="AE30" s="22"/>
+      <c r="AF30" s="22"/>
+      <c r="AG30" s="22"/>
+      <c r="AH30" s="22"/>
+      <c r="AI30" s="22"/>
+      <c r="AJ30" s="22"/>
+      <c r="AK30" s="22"/>
+      <c r="AL30" s="24">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="31" ht="15.75" spans="8:38">
-      <c r="H31" s="18">
+    <row r="31" spans="8:38">
+      <c r="H31" s="19">
         <v>21</v>
       </c>
-      <c r="I31" s="19" t="s">
+      <c r="I31" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="J31" s="20">
+      <c r="J31" s="21">
         <v>46224</v>
       </c>
-      <c r="K31" s="24"/>
-      <c r="L31" s="24"/>
-      <c r="M31" s="24"/>
-      <c r="N31" s="21"/>
-      <c r="O31" s="21"/>
-      <c r="P31" s="21"/>
-      <c r="Q31" s="21"/>
-      <c r="R31" s="21"/>
-      <c r="S31" s="21"/>
-      <c r="T31" s="21"/>
-      <c r="U31" s="21"/>
-      <c r="V31" s="21"/>
-      <c r="W31" s="21"/>
-      <c r="X31" s="21"/>
-      <c r="Y31" s="21"/>
-      <c r="Z31" s="21"/>
-      <c r="AA31" s="21"/>
-      <c r="AB31" s="21"/>
-      <c r="AC31" s="21"/>
-      <c r="AD31" s="21"/>
-      <c r="AE31" s="21"/>
-      <c r="AF31" s="21"/>
-      <c r="AG31" s="21"/>
-      <c r="AH31" s="21"/>
-      <c r="AI31" s="21"/>
-      <c r="AJ31" s="21"/>
-      <c r="AK31" s="21"/>
-      <c r="AL31" s="23">
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
+      <c r="M31" s="25"/>
+      <c r="N31" s="22"/>
+      <c r="O31" s="22"/>
+      <c r="P31" s="22"/>
+      <c r="Q31" s="22"/>
+      <c r="R31" s="22"/>
+      <c r="S31" s="22"/>
+      <c r="T31" s="22"/>
+      <c r="U31" s="22"/>
+      <c r="V31" s="22"/>
+      <c r="W31" s="22"/>
+      <c r="X31" s="22"/>
+      <c r="Y31" s="22"/>
+      <c r="Z31" s="22"/>
+      <c r="AA31" s="22"/>
+      <c r="AB31" s="22"/>
+      <c r="AC31" s="22"/>
+      <c r="AD31" s="22"/>
+      <c r="AE31" s="22"/>
+      <c r="AF31" s="22"/>
+      <c r="AG31" s="22"/>
+      <c r="AH31" s="22"/>
+      <c r="AI31" s="22"/>
+      <c r="AJ31" s="22"/>
+      <c r="AK31" s="22"/>
+      <c r="AL31" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="32" ht="15.75" spans="8:38">
-      <c r="H32" s="18">
+    <row r="32" spans="8:38">
+      <c r="H32" s="19">
         <v>22</v>
       </c>
-      <c r="I32" s="19" t="s">
+      <c r="I32" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="J32" s="20">
+      <c r="J32" s="21">
         <v>46225</v>
       </c>
-      <c r="K32" s="24"/>
-      <c r="L32" s="24"/>
-      <c r="M32" s="24"/>
-      <c r="N32" s="21"/>
-      <c r="O32" s="21"/>
-      <c r="P32" s="21"/>
-      <c r="Q32" s="21"/>
-      <c r="R32" s="21"/>
-      <c r="S32" s="21"/>
-      <c r="T32" s="21"/>
-      <c r="U32" s="21"/>
-      <c r="V32" s="21"/>
-      <c r="W32" s="21"/>
-      <c r="X32" s="21"/>
-      <c r="Y32" s="21"/>
-      <c r="Z32" s="21"/>
-      <c r="AA32" s="21"/>
-      <c r="AB32" s="21"/>
-      <c r="AC32" s="21"/>
-      <c r="AD32" s="21"/>
-      <c r="AE32" s="21"/>
-      <c r="AF32" s="21"/>
-      <c r="AG32" s="21"/>
-      <c r="AH32" s="21"/>
-      <c r="AI32" s="21"/>
-      <c r="AJ32" s="21"/>
-      <c r="AK32" s="21"/>
-      <c r="AL32" s="23">
+      <c r="K32" s="25"/>
+      <c r="L32" s="25"/>
+      <c r="M32" s="25"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="22"/>
+      <c r="P32" s="22"/>
+      <c r="Q32" s="22"/>
+      <c r="R32" s="22"/>
+      <c r="S32" s="22"/>
+      <c r="T32" s="22"/>
+      <c r="U32" s="22"/>
+      <c r="V32" s="22"/>
+      <c r="W32" s="22"/>
+      <c r="X32" s="22"/>
+      <c r="Y32" s="22"/>
+      <c r="Z32" s="22"/>
+      <c r="AA32" s="22"/>
+      <c r="AB32" s="22"/>
+      <c r="AC32" s="22"/>
+      <c r="AD32" s="22"/>
+      <c r="AE32" s="22"/>
+      <c r="AF32" s="22"/>
+      <c r="AG32" s="22"/>
+      <c r="AH32" s="22"/>
+      <c r="AI32" s="22"/>
+      <c r="AJ32" s="22"/>
+      <c r="AK32" s="22"/>
+      <c r="AL32" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" ht="15.75" spans="8:38">
-      <c r="H33" s="18">
+    <row r="33" spans="8:38">
+      <c r="H33" s="19">
         <v>23</v>
       </c>
-      <c r="I33" s="19" t="s">
+      <c r="I33" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="J33" s="20">
+      <c r="J33" s="21">
         <v>46226</v>
       </c>
-      <c r="K33" s="24"/>
-      <c r="L33" s="24"/>
-      <c r="M33" s="24"/>
-      <c r="N33" s="21"/>
-      <c r="O33" s="21"/>
-      <c r="P33" s="21"/>
-      <c r="Q33" s="21"/>
-      <c r="R33" s="21"/>
-      <c r="S33" s="21"/>
-      <c r="T33" s="21"/>
-      <c r="U33" s="21"/>
-      <c r="V33" s="21"/>
-      <c r="W33" s="21"/>
-      <c r="X33" s="21"/>
-      <c r="Y33" s="21"/>
-      <c r="Z33" s="21"/>
-      <c r="AA33" s="21"/>
-      <c r="AB33" s="21"/>
-      <c r="AC33" s="21"/>
-      <c r="AD33" s="21"/>
-      <c r="AE33" s="21"/>
-      <c r="AF33" s="21"/>
-      <c r="AG33" s="21"/>
-      <c r="AH33" s="21"/>
-      <c r="AI33" s="21"/>
-      <c r="AJ33" s="21"/>
-      <c r="AK33" s="21"/>
-      <c r="AL33" s="23">
+      <c r="K33" s="25"/>
+      <c r="L33" s="25"/>
+      <c r="M33" s="25"/>
+      <c r="N33" s="22"/>
+      <c r="O33" s="22"/>
+      <c r="P33" s="22"/>
+      <c r="Q33" s="22"/>
+      <c r="R33" s="22"/>
+      <c r="S33" s="22"/>
+      <c r="T33" s="22"/>
+      <c r="U33" s="22"/>
+      <c r="V33" s="22"/>
+      <c r="W33" s="22"/>
+      <c r="X33" s="22"/>
+      <c r="Y33" s="22"/>
+      <c r="Z33" s="22"/>
+      <c r="AA33" s="22"/>
+      <c r="AB33" s="22"/>
+      <c r="AC33" s="22"/>
+      <c r="AD33" s="22"/>
+      <c r="AE33" s="22"/>
+      <c r="AF33" s="22"/>
+      <c r="AG33" s="22"/>
+      <c r="AH33" s="22"/>
+      <c r="AI33" s="22"/>
+      <c r="AJ33" s="22"/>
+      <c r="AK33" s="22"/>
+      <c r="AL33" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" ht="15.75" spans="8:38">
-      <c r="H34" s="18">
+    <row r="34" spans="8:38">
+      <c r="H34" s="19">
         <v>24</v>
       </c>
-      <c r="I34" s="19" t="s">
+      <c r="I34" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="J34" s="20">
+      <c r="J34" s="21">
         <v>46227</v>
       </c>
-      <c r="K34" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="L34" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="M34" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="N34" s="21"/>
-      <c r="O34" s="21"/>
-      <c r="P34" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q34" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="R34" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="S34" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="T34" s="21"/>
-      <c r="U34" s="21"/>
-      <c r="V34" s="21"/>
-      <c r="W34" s="21"/>
-      <c r="X34" s="21"/>
-      <c r="Y34" s="21"/>
-      <c r="Z34" s="21"/>
-      <c r="AA34" s="21"/>
-      <c r="AB34" s="21"/>
-      <c r="AC34" s="21"/>
-      <c r="AD34" s="21"/>
-      <c r="AE34" s="21"/>
-      <c r="AF34" s="21"/>
-      <c r="AG34" s="21"/>
-      <c r="AH34" s="21"/>
-      <c r="AI34" s="21"/>
-      <c r="AJ34" s="21"/>
-      <c r="AK34" s="21"/>
-      <c r="AL34" s="23">
+      <c r="K34" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="L34" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="M34" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="N34" s="22"/>
+      <c r="O34" s="22"/>
+      <c r="P34" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="R34" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="S34" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="T34" s="22"/>
+      <c r="U34" s="22"/>
+      <c r="V34" s="22"/>
+      <c r="W34" s="22"/>
+      <c r="X34" s="22"/>
+      <c r="Y34" s="22"/>
+      <c r="Z34" s="22"/>
+      <c r="AA34" s="22"/>
+      <c r="AB34" s="22"/>
+      <c r="AC34" s="22"/>
+      <c r="AD34" s="22"/>
+      <c r="AE34" s="22"/>
+      <c r="AF34" s="22"/>
+      <c r="AG34" s="22"/>
+      <c r="AH34" s="22"/>
+      <c r="AI34" s="22"/>
+      <c r="AJ34" s="22"/>
+      <c r="AK34" s="22"/>
+      <c r="AL34" s="24">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="35" ht="15.75" spans="8:38">
-      <c r="H35" s="18">
+    <row r="35" spans="8:38">
+      <c r="H35" s="19">
         <v>25</v>
       </c>
-      <c r="I35" s="19" t="s">
+      <c r="I35" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="J35" s="20">
+      <c r="J35" s="21">
         <v>46228</v>
       </c>
-      <c r="K35" s="24"/>
-      <c r="L35" s="24"/>
-      <c r="M35" s="24"/>
-      <c r="N35" s="21"/>
-      <c r="O35" s="21"/>
-      <c r="P35" s="21"/>
-      <c r="Q35" s="21"/>
-      <c r="R35" s="21"/>
-      <c r="S35" s="21"/>
-      <c r="T35" s="21"/>
-      <c r="U35" s="21"/>
-      <c r="V35" s="21"/>
-      <c r="W35" s="21"/>
-      <c r="X35" s="21"/>
-      <c r="Y35" s="21"/>
-      <c r="Z35" s="21"/>
-      <c r="AA35" s="21"/>
-      <c r="AB35" s="21"/>
-      <c r="AC35" s="21"/>
-      <c r="AD35" s="21"/>
-      <c r="AE35" s="21"/>
-      <c r="AF35" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG35" s="21"/>
-      <c r="AH35" s="21"/>
-      <c r="AI35" s="21"/>
-      <c r="AJ35" s="21"/>
-      <c r="AK35" s="21"/>
-      <c r="AL35" s="23">
+      <c r="K35" s="25"/>
+      <c r="L35" s="25"/>
+      <c r="M35" s="25"/>
+      <c r="N35" s="22"/>
+      <c r="O35" s="22"/>
+      <c r="P35" s="22"/>
+      <c r="Q35" s="22"/>
+      <c r="R35" s="22"/>
+      <c r="S35" s="22"/>
+      <c r="T35" s="22"/>
+      <c r="U35" s="22"/>
+      <c r="V35" s="22"/>
+      <c r="W35" s="22"/>
+      <c r="X35" s="22"/>
+      <c r="Y35" s="22"/>
+      <c r="Z35" s="22"/>
+      <c r="AA35" s="22"/>
+      <c r="AB35" s="22"/>
+      <c r="AC35" s="22"/>
+      <c r="AD35" s="22"/>
+      <c r="AE35" s="22"/>
+      <c r="AF35" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG35" s="22"/>
+      <c r="AH35" s="22"/>
+      <c r="AI35" s="22"/>
+      <c r="AJ35" s="22"/>
+      <c r="AK35" s="22"/>
+      <c r="AL35" s="24">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="36" ht="15.75" spans="8:38">
-      <c r="H36" s="18">
+    <row r="36" spans="8:38">
+      <c r="H36" s="19">
         <v>26</v>
       </c>
-      <c r="I36" s="19" t="s">
+      <c r="I36" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="J36" s="20">
+      <c r="J36" s="21">
         <v>46229</v>
       </c>
-      <c r="K36" s="24"/>
-      <c r="L36" s="24"/>
-      <c r="M36" s="24"/>
-      <c r="N36" s="21"/>
-      <c r="O36" s="21"/>
-      <c r="P36" s="21"/>
-      <c r="Q36" s="21"/>
-      <c r="R36" s="21"/>
-      <c r="S36" s="21"/>
-      <c r="T36" s="21"/>
-      <c r="U36" s="21"/>
-      <c r="V36" s="21"/>
-      <c r="W36" s="21"/>
-      <c r="X36" s="21"/>
-      <c r="Y36" s="21"/>
-      <c r="Z36" s="21"/>
-      <c r="AA36" s="21"/>
-      <c r="AB36" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="AC36" s="21"/>
-      <c r="AD36" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE36" s="21"/>
-      <c r="AF36" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG36" s="21"/>
-      <c r="AH36" s="21"/>
-      <c r="AI36" s="21"/>
-      <c r="AJ36" s="21"/>
-      <c r="AK36" s="21"/>
-      <c r="AL36" s="23">
+      <c r="K36" s="25"/>
+      <c r="L36" s="25"/>
+      <c r="M36" s="25"/>
+      <c r="N36" s="22"/>
+      <c r="O36" s="22"/>
+      <c r="P36" s="22"/>
+      <c r="Q36" s="22"/>
+      <c r="R36" s="22"/>
+      <c r="S36" s="22"/>
+      <c r="T36" s="22"/>
+      <c r="U36" s="22"/>
+      <c r="V36" s="22"/>
+      <c r="W36" s="22"/>
+      <c r="X36" s="22"/>
+      <c r="Y36" s="22"/>
+      <c r="Z36" s="22"/>
+      <c r="AA36" s="22"/>
+      <c r="AB36" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC36" s="22"/>
+      <c r="AD36" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE36" s="22"/>
+      <c r="AF36" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG36" s="22"/>
+      <c r="AH36" s="22"/>
+      <c r="AI36" s="22"/>
+      <c r="AJ36" s="22"/>
+      <c r="AK36" s="22"/>
+      <c r="AL36" s="24">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="37" ht="15.75" spans="8:38">
-      <c r="H37" s="18">
+    <row r="37" spans="8:38">
+      <c r="H37" s="19">
         <v>27</v>
       </c>
-      <c r="I37" s="19" t="s">
+      <c r="I37" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="J37" s="20">
+      <c r="J37" s="21">
         <v>46230</v>
       </c>
-      <c r="K37" s="24"/>
-      <c r="L37" s="24"/>
-      <c r="M37" s="24"/>
-      <c r="N37" s="21"/>
-      <c r="O37" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="P37" s="21"/>
-      <c r="Q37" s="21"/>
-      <c r="R37" s="21"/>
-      <c r="S37" s="21"/>
-      <c r="T37" s="21"/>
-      <c r="U37" s="21"/>
-      <c r="V37" s="21"/>
-      <c r="W37" s="21"/>
-      <c r="X37" s="21"/>
-      <c r="Y37" s="21"/>
-      <c r="Z37" s="21"/>
-      <c r="AA37" s="21"/>
-      <c r="AB37" s="21"/>
-      <c r="AC37" s="21"/>
-      <c r="AD37" s="21"/>
-      <c r="AE37" s="21"/>
-      <c r="AF37" s="21"/>
-      <c r="AG37" s="21"/>
-      <c r="AH37" s="21"/>
-      <c r="AI37" s="21"/>
-      <c r="AJ37" s="21"/>
-      <c r="AK37" s="21"/>
-      <c r="AL37" s="23">
+      <c r="K37" s="25"/>
+      <c r="L37" s="25"/>
+      <c r="M37" s="25"/>
+      <c r="N37" s="22"/>
+      <c r="O37" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="P37" s="22"/>
+      <c r="Q37" s="22"/>
+      <c r="R37" s="22"/>
+      <c r="S37" s="22"/>
+      <c r="T37" s="22"/>
+      <c r="U37" s="22"/>
+      <c r="V37" s="22"/>
+      <c r="W37" s="22"/>
+      <c r="X37" s="22"/>
+      <c r="Y37" s="22"/>
+      <c r="Z37" s="22"/>
+      <c r="AA37" s="22"/>
+      <c r="AB37" s="22"/>
+      <c r="AC37" s="22"/>
+      <c r="AD37" s="22"/>
+      <c r="AE37" s="22"/>
+      <c r="AF37" s="22"/>
+      <c r="AG37" s="22"/>
+      <c r="AH37" s="22"/>
+      <c r="AI37" s="22"/>
+      <c r="AJ37" s="22"/>
+      <c r="AK37" s="22"/>
+      <c r="AL37" s="24">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="38" ht="15.75" spans="8:38">
-      <c r="H38" s="18">
+    <row r="38" spans="8:38">
+      <c r="H38" s="19">
         <v>28</v>
       </c>
-      <c r="I38" s="19" t="s">
+      <c r="I38" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="J38" s="20">
+      <c r="J38" s="21">
         <v>46231</v>
       </c>
-      <c r="K38" s="24"/>
-      <c r="L38" s="24"/>
-      <c r="M38" s="24"/>
-      <c r="N38" s="21"/>
-      <c r="O38" s="21"/>
-      <c r="P38" s="21"/>
-      <c r="Q38" s="21"/>
-      <c r="R38" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="S38" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="T38" s="21"/>
-      <c r="U38" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="V38" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="W38" s="21"/>
-      <c r="X38" s="21"/>
-      <c r="Y38" s="21"/>
-      <c r="Z38" s="21"/>
-      <c r="AA38" s="21"/>
-      <c r="AB38" s="21"/>
-      <c r="AC38" s="21"/>
-      <c r="AD38" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE38" s="21"/>
-      <c r="AF38" s="21"/>
-      <c r="AG38" s="21"/>
-      <c r="AH38" s="21"/>
-      <c r="AI38" s="21"/>
-      <c r="AJ38" s="21"/>
-      <c r="AK38" s="21"/>
-      <c r="AL38" s="23">
+      <c r="K38" s="25"/>
+      <c r="L38" s="25"/>
+      <c r="M38" s="25"/>
+      <c r="N38" s="22"/>
+      <c r="O38" s="22"/>
+      <c r="P38" s="22"/>
+      <c r="Q38" s="22"/>
+      <c r="R38" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="S38" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="T38" s="22"/>
+      <c r="U38" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="V38" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="W38" s="22"/>
+      <c r="X38" s="22"/>
+      <c r="Y38" s="22"/>
+      <c r="Z38" s="22"/>
+      <c r="AA38" s="22"/>
+      <c r="AB38" s="22"/>
+      <c r="AC38" s="22"/>
+      <c r="AD38" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE38" s="22"/>
+      <c r="AF38" s="22"/>
+      <c r="AG38" s="22"/>
+      <c r="AH38" s="22"/>
+      <c r="AI38" s="22"/>
+      <c r="AJ38" s="22"/>
+      <c r="AK38" s="22"/>
+      <c r="AL38" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="39" ht="15.75" spans="8:38">
-      <c r="H39" s="18">
+    <row r="39" spans="8:38">
+      <c r="H39" s="19">
         <v>29</v>
       </c>
-      <c r="I39" s="19" t="s">
+      <c r="I39" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="J39" s="20">
+      <c r="J39" s="21">
         <v>46232</v>
       </c>
-      <c r="K39" s="24"/>
-      <c r="L39" s="24"/>
-      <c r="M39" s="24"/>
-      <c r="N39" s="21"/>
-      <c r="O39" s="21"/>
-      <c r="P39" s="26"/>
-      <c r="Q39" s="26"/>
-      <c r="R39" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="S39" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="T39" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="U39" s="26"/>
-      <c r="V39" s="26"/>
-      <c r="W39" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="X39" s="26"/>
-      <c r="Y39" s="26"/>
-      <c r="Z39" s="26"/>
-      <c r="AA39" s="26"/>
-      <c r="AB39" s="26"/>
-      <c r="AC39" s="26"/>
-      <c r="AD39" s="26"/>
-      <c r="AE39" s="26"/>
-      <c r="AF39" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG39" s="26"/>
-      <c r="AH39" s="26"/>
-      <c r="AI39" s="26"/>
-      <c r="AJ39" s="26"/>
-      <c r="AK39" s="26"/>
-      <c r="AL39" s="23">
+      <c r="K39" s="25"/>
+      <c r="L39" s="25"/>
+      <c r="M39" s="25"/>
+      <c r="N39" s="22"/>
+      <c r="O39" s="22"/>
+      <c r="P39" s="27"/>
+      <c r="Q39" s="27"/>
+      <c r="R39" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="S39" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="T39" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="U39" s="27"/>
+      <c r="V39" s="27"/>
+      <c r="W39" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="X39" s="27"/>
+      <c r="Y39" s="27"/>
+      <c r="Z39" s="27"/>
+      <c r="AA39" s="27"/>
+      <c r="AB39" s="27"/>
+      <c r="AC39" s="27"/>
+      <c r="AD39" s="27"/>
+      <c r="AE39" s="27"/>
+      <c r="AF39" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG39" s="27"/>
+      <c r="AH39" s="27"/>
+      <c r="AI39" s="27"/>
+      <c r="AJ39" s="27"/>
+      <c r="AK39" s="27"/>
+      <c r="AL39" s="24">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="40" ht="15.75" spans="8:38">
-      <c r="H40" s="27">
+    <row r="40" spans="8:38">
+      <c r="H40" s="28">
         <v>30</v>
       </c>
-      <c r="I40" s="28" t="s">
+      <c r="I40" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="J40" s="29">
+      <c r="J40" s="30">
         <v>46233</v>
       </c>
-      <c r="K40" s="30"/>
-      <c r="L40" s="30"/>
-      <c r="M40" s="30"/>
-      <c r="N40" s="25"/>
-      <c r="O40" s="25"/>
-      <c r="P40" s="25"/>
-      <c r="Q40" s="25"/>
-      <c r="R40" s="25"/>
-      <c r="S40" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="T40" s="25"/>
-      <c r="U40" s="25"/>
-      <c r="V40" s="25"/>
-      <c r="W40" s="25"/>
-      <c r="X40" s="25"/>
-      <c r="Y40" s="25"/>
-      <c r="Z40" s="25"/>
-      <c r="AA40" s="25"/>
-      <c r="AB40" s="25"/>
-      <c r="AC40" s="25"/>
-      <c r="AD40" s="25"/>
-      <c r="AE40" s="25"/>
-      <c r="AF40" s="25"/>
-      <c r="AG40" s="25"/>
-      <c r="AH40" s="25"/>
-      <c r="AI40" s="25"/>
-      <c r="AJ40" s="25"/>
-      <c r="AK40" s="25"/>
-      <c r="AL40" s="23">
+      <c r="K40" s="31"/>
+      <c r="L40" s="31"/>
+      <c r="M40" s="31"/>
+      <c r="N40" s="27"/>
+      <c r="O40" s="27"/>
+      <c r="P40" s="27"/>
+      <c r="Q40" s="27"/>
+      <c r="R40" s="27"/>
+      <c r="S40" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="T40" s="27"/>
+      <c r="U40" s="27"/>
+      <c r="V40" s="27"/>
+      <c r="W40" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="X40" s="27"/>
+      <c r="Y40" s="27"/>
+      <c r="Z40" s="27"/>
+      <c r="AA40" s="27"/>
+      <c r="AB40" s="27"/>
+      <c r="AC40" s="27"/>
+      <c r="AD40" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE40" s="27"/>
+      <c r="AF40" s="27"/>
+      <c r="AG40" s="27"/>
+      <c r="AH40" s="27"/>
+      <c r="AI40" s="27"/>
+      <c r="AJ40" s="27"/>
+      <c r="AK40" s="27"/>
+      <c r="AL40" s="24">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" spans="8:38">
-      <c r="H41" s="27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="8:38">
+      <c r="H41" s="28">
         <v>31</v>
       </c>
-      <c r="I41" s="28" t="s">
+      <c r="I41" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="J41" s="29">
+      <c r="J41" s="30">
         <v>46234</v>
       </c>
-      <c r="K41" s="30"/>
-      <c r="L41" s="30"/>
-      <c r="M41" s="30"/>
-      <c r="N41" s="25"/>
-      <c r="O41" s="25"/>
-      <c r="P41" s="25"/>
-      <c r="Q41" s="25"/>
-      <c r="R41" s="25"/>
-      <c r="S41" s="25"/>
-      <c r="T41" s="25"/>
-      <c r="U41" s="25"/>
-      <c r="V41" s="25"/>
-      <c r="W41" s="25"/>
-      <c r="X41" s="25"/>
-      <c r="Y41" s="25"/>
-      <c r="Z41" s="25"/>
-      <c r="AA41" s="25"/>
-      <c r="AB41" s="25"/>
-      <c r="AC41" s="25"/>
-      <c r="AD41" s="25"/>
-      <c r="AE41" s="25"/>
-      <c r="AF41" s="25"/>
-      <c r="AG41" s="25"/>
-      <c r="AH41" s="25"/>
-      <c r="AI41" s="25"/>
-      <c r="AJ41" s="25"/>
-      <c r="AK41" s="25"/>
-      <c r="AL41" s="23">
+      <c r="K41" s="31"/>
+      <c r="L41" s="31"/>
+      <c r="M41" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="N41" s="27"/>
+      <c r="O41" s="27"/>
+      <c r="P41" s="27"/>
+      <c r="Q41" s="27"/>
+      <c r="R41" s="27"/>
+      <c r="S41" s="27"/>
+      <c r="T41" s="27"/>
+      <c r="U41" s="27"/>
+      <c r="V41" s="27"/>
+      <c r="W41" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="X41" s="27"/>
+      <c r="Y41" s="27"/>
+      <c r="Z41" s="27"/>
+      <c r="AA41" s="27"/>
+      <c r="AB41" s="27"/>
+      <c r="AC41" s="27"/>
+      <c r="AD41" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE41" s="27"/>
+      <c r="AF41" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG41" s="27"/>
+      <c r="AH41" s="27"/>
+      <c r="AI41" s="27"/>
+      <c r="AJ41" s="27"/>
+      <c r="AK41" s="27"/>
+      <c r="AL41" s="24">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" ht="15.75" spans="8:38">
-      <c r="H42" s="31" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" ht="14.6" spans="8:38">
+      <c r="H42" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="I42" s="31"/>
-      <c r="J42" s="31"/>
-      <c r="K42" s="4">
+      <c r="I42" s="32"/>
+      <c r="J42" s="32"/>
+      <c r="K42" s="5">
         <f>COUNTA(K11:K41)</f>
         <v>6</v>
       </c>
-      <c r="L42" s="4">
+      <c r="L42" s="5">
         <f t="shared" ref="L42:AK42" si="1">COUNTA(L11:L41)</f>
         <v>9</v>
       </c>
-      <c r="M42" s="4">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="N42" s="4">
+      <c r="M42" s="5">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="O42" s="4">
+      <c r="N42" s="5">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="O42" s="5">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="P42" s="4">
+      <c r="P42" s="5">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="Q42" s="4">
+      <c r="Q42" s="5">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="R42" s="4">
+      <c r="R42" s="5">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="S42" s="4">
+      <c r="S42" s="5">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="T42" s="4">
+      <c r="T42" s="5">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="U42" s="4">
+      <c r="U42" s="5">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="V42" s="4">
+      <c r="V42" s="5">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="W42" s="4">
+      <c r="W42" s="5">
         <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="X42" s="4">
+        <v>10</v>
+      </c>
+      <c r="X42" s="5">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="Y42" s="4">
+      <c r="Y42" s="5">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="Z42" s="4">
+      <c r="Z42" s="5">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AA42" s="4">
+      <c r="AA42" s="5">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AB42" s="4">
+      <c r="AB42" s="5">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AC42" s="4">
+      <c r="AC42" s="5">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AD42" s="4">
+      <c r="AD42" s="5">
         <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="AE42" s="4">
+        <v>6</v>
+      </c>
+      <c r="AE42" s="5">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="AF42" s="4">
+      <c r="AF42" s="5">
         <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="AG42" s="4">
+        <v>13</v>
+      </c>
+      <c r="AG42" s="5">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH42" s="4">
+      <c r="AH42" s="5">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="AI42" s="4"/>
-      <c r="AJ42" s="4"/>
-      <c r="AK42" s="4">
+      <c r="AI42" s="5"/>
+      <c r="AJ42" s="5"/>
+      <c r="AK42" s="5">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="AL42" s="32">
+      <c r="AL42" s="33">
         <f t="shared" ref="AL42" si="2">COUNTA(AL11:AL41)</f>
         <v>31</v>
       </c>
@@ -4469,4 +4521,110 @@
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="E4:S6"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="14.25" outlineLevelRow="5"/>
+  <cols>
+    <col min="5" max="5" width="18.7256637168142" customWidth="1"/>
+    <col min="6" max="6" width="16.5309734513274" customWidth="1"/>
+    <col min="7" max="7" width="19.2566371681416" customWidth="1"/>
+    <col min="8" max="8" width="26.353982300885" customWidth="1"/>
+    <col min="9" max="12" width="16.5309734513274" customWidth="1"/>
+    <col min="13" max="13" width="23.0353982300885" customWidth="1"/>
+    <col min="14" max="14" width="21.3097345132743" customWidth="1"/>
+    <col min="15" max="15" width="32.4601769911504" customWidth="1"/>
+    <col min="16" max="16" width="28.6106194690265" customWidth="1"/>
+    <col min="17" max="17" width="16.5309734513274" customWidth="1"/>
+    <col min="18" max="18" width="20.7787610619469" customWidth="1"/>
+    <col min="19" max="19" width="27.212389380531" customWidth="1"/>
+    <col min="20" max="20" width="16.5309734513274" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="5:19">
+      <c r="E4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+    </row>
+    <row r="5" spans="5:19">
+      <c r="E5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" t="s">
+        <v>4</v>
+      </c>
+      <c r="J5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" t="s">
+        <v>42</v>
+      </c>
+      <c r="O5" t="s">
+        <v>43</v>
+      </c>
+      <c r="P5" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>44</v>
+      </c>
+      <c r="R5" t="s">
+        <v>45</v>
+      </c>
+      <c r="S5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="5:19">
+      <c r="E6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="F4:L4"/>
+    <mergeCell ref="M4:S4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Другое/study_chart.xlsx
+++ b/Другое/study_chart.xlsx
@@ -741,7 +741,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="64">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -4849,59 +4849,69 @@
         <v>46206</v>
       </c>
       <c r="D6" s="40"/>
-      <c r="E6" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6" s="50" t="s">
+      <c r="E6" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="60" t="s">
         <v>12</v>
       </c>
       <c r="K6" s="60"/>
       <c r="L6" s="60"/>
-      <c r="M6" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="N6" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="O6" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="P6" s="50"/>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50"/>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
-      <c r="V6" s="50"/>
-      <c r="W6" s="50"/>
-      <c r="X6" s="50"/>
-      <c r="Y6" s="50"/>
-      <c r="Z6" s="50"/>
-      <c r="AA6" s="50"/>
-      <c r="AB6" s="50"/>
-      <c r="AC6" s="50"/>
-      <c r="AD6" s="50"/>
-      <c r="AE6" s="50"/>
-      <c r="AF6" s="50"/>
-      <c r="AG6" s="50"/>
-      <c r="AH6" s="50"/>
-      <c r="AI6" s="50"/>
-      <c r="AJ6" s="50"/>
+      <c r="M6" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="N6" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="O6" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="P6" s="60"/>
+      <c r="Q6" s="60"/>
+      <c r="R6" s="60"/>
+      <c r="S6" s="60"/>
+      <c r="T6" s="60"/>
+      <c r="U6" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="V6" s="60"/>
+      <c r="W6" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="X6" s="60"/>
+      <c r="Y6" s="60"/>
+      <c r="Z6" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA6" s="60"/>
+      <c r="AB6" s="60"/>
+      <c r="AC6" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD6" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE6" s="60"/>
+      <c r="AF6" s="60"/>
+      <c r="AG6" s="60"/>
+      <c r="AH6" s="60"/>
+      <c r="AI6" s="60"/>
+      <c r="AJ6" s="60"/>
       <c r="AK6" s="61">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -4915,12 +4925,24 @@
         <v>46207</v>
       </c>
       <c r="D7" s="40"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="50"/>
-      <c r="I7" s="50"/>
-      <c r="J7" s="50"/>
+      <c r="E7" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="50" t="s">
+        <v>12</v>
+      </c>
       <c r="K7" s="50"/>
       <c r="L7" s="50"/>
       <c r="M7" s="50"/>
@@ -4949,7 +4971,7 @@
       <c r="AJ7" s="50"/>
       <c r="AK7" s="61">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:37">

--- a/Другое/study_chart.xlsx
+++ b/Другое/study_chart.xlsx
@@ -741,7 +741,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="65">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -933,6 +933,9 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>90.00</t>
   </si>
 </sst>
 </file>
@@ -1617,7 +1620,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1783,6 +1786,9 @@
     </xf>
     <xf numFmtId="0" fontId="31" fillId="25" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2230,18 +2236,18 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:17" ht="45" customHeight="1">
-      <c r="H9" s="62" t="s">
+      <c r="H9" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="63"/>
-      <c r="J9" s="63"/>
-      <c r="K9" s="63"/>
-      <c r="L9" s="63"/>
-      <c r="M9" s="63"/>
-      <c r="N9" s="63"/>
-      <c r="O9" s="63"/>
-      <c r="P9" s="63"/>
-      <c r="Q9" s="64"/>
+      <c r="I9" s="64"/>
+      <c r="J9" s="64"/>
+      <c r="K9" s="64"/>
+      <c r="L9" s="64"/>
+      <c r="M9" s="64"/>
+      <c r="N9" s="64"/>
+      <c r="O9" s="64"/>
+      <c r="P9" s="64"/>
+      <c r="Q9" s="65"/>
     </row>
     <row r="10" spans="8:17" ht="30" customHeight="1">
       <c r="H10" s="30" t="s">
@@ -2510,11 +2516,11 @@
       <c r="Q21" s="35"/>
     </row>
     <row r="22" spans="8:17" ht="15.75">
-      <c r="H22" s="65" t="s">
+      <c r="H22" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="66"/>
-      <c r="J22" s="67"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="68"/>
       <c r="K22" s="36">
         <f>COUNTA(K11:K21)</f>
         <v>6</v>
@@ -2591,39 +2597,39 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:38" ht="45" customHeight="1">
-      <c r="H9" s="68" t="s">
+      <c r="H9" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="69"/>
-      <c r="J9" s="69"/>
-      <c r="K9" s="69"/>
-      <c r="L9" s="69"/>
-      <c r="M9" s="69"/>
-      <c r="N9" s="69"/>
-      <c r="O9" s="69"/>
-      <c r="P9" s="69"/>
-      <c r="Q9" s="69"/>
-      <c r="R9" s="69"/>
-      <c r="S9" s="69"/>
-      <c r="T9" s="69"/>
-      <c r="U9" s="69"/>
-      <c r="V9" s="69"/>
-      <c r="W9" s="69"/>
-      <c r="X9" s="69"/>
-      <c r="Y9" s="69"/>
-      <c r="Z9" s="69"/>
-      <c r="AA9" s="69"/>
-      <c r="AB9" s="69"/>
-      <c r="AC9" s="69"/>
-      <c r="AD9" s="69"/>
-      <c r="AE9" s="69"/>
-      <c r="AF9" s="69"/>
-      <c r="AG9" s="69"/>
-      <c r="AH9" s="69"/>
-      <c r="AI9" s="69"/>
-      <c r="AJ9" s="69"/>
-      <c r="AK9" s="69"/>
-      <c r="AL9" s="69"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="70"/>
+      <c r="K9" s="70"/>
+      <c r="L9" s="70"/>
+      <c r="M9" s="70"/>
+      <c r="N9" s="70"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="70"/>
+      <c r="Q9" s="70"/>
+      <c r="R9" s="70"/>
+      <c r="S9" s="70"/>
+      <c r="T9" s="70"/>
+      <c r="U9" s="70"/>
+      <c r="V9" s="70"/>
+      <c r="W9" s="70"/>
+      <c r="X9" s="70"/>
+      <c r="Y9" s="70"/>
+      <c r="Z9" s="70"/>
+      <c r="AA9" s="70"/>
+      <c r="AB9" s="70"/>
+      <c r="AC9" s="70"/>
+      <c r="AD9" s="70"/>
+      <c r="AE9" s="70"/>
+      <c r="AF9" s="70"/>
+      <c r="AG9" s="70"/>
+      <c r="AH9" s="70"/>
+      <c r="AI9" s="70"/>
+      <c r="AJ9" s="70"/>
+      <c r="AK9" s="70"/>
+      <c r="AL9" s="70"/>
     </row>
     <row r="10" spans="8:38" ht="30" customHeight="1">
       <c r="H10" s="2" t="s">
@@ -4303,11 +4309,11 @@
       </c>
     </row>
     <row r="42" spans="8:38" ht="15.75">
-      <c r="H42" s="70" t="s">
+      <c r="H42" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="I42" s="70"/>
-      <c r="J42" s="70"/>
+      <c r="I42" s="71"/>
+      <c r="J42" s="71"/>
       <c r="K42" s="2">
         <f>COUNTA(K11:K41)</f>
         <v>6</v>
@@ -4470,66 +4476,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="39" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="76"/>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
+      <c r="A1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="79"/>
       <c r="D1" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="85" t="s">
+      <c r="E1" s="86" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
-      <c r="H1" s="85"/>
-      <c r="I1" s="85"/>
-      <c r="J1" s="85"/>
-      <c r="K1" s="85"/>
-      <c r="L1" s="86" t="s">
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
+      <c r="J1" s="86"/>
+      <c r="K1" s="86"/>
+      <c r="L1" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="86"/>
-      <c r="N1" s="86"/>
-      <c r="O1" s="86"/>
-      <c r="P1" s="86"/>
-      <c r="Q1" s="86"/>
-      <c r="R1" s="86"/>
-      <c r="S1" s="87" t="s">
+      <c r="M1" s="87"/>
+      <c r="N1" s="87"/>
+      <c r="O1" s="87"/>
+      <c r="P1" s="87"/>
+      <c r="Q1" s="87"/>
+      <c r="R1" s="87"/>
+      <c r="S1" s="88" t="s">
         <v>49</v>
       </c>
-      <c r="T1" s="87"/>
-      <c r="U1" s="82" t="s">
+      <c r="T1" s="88"/>
+      <c r="U1" s="83" t="s">
         <v>53</v>
       </c>
-      <c r="V1" s="83"/>
-      <c r="W1" s="83"/>
-      <c r="X1" s="83"/>
-      <c r="Y1" s="84"/>
-      <c r="Z1" s="88" t="s">
+      <c r="V1" s="84"/>
+      <c r="W1" s="84"/>
+      <c r="X1" s="84"/>
+      <c r="Y1" s="85"/>
+      <c r="Z1" s="89" t="s">
         <v>59</v>
       </c>
-      <c r="AA1" s="88"/>
-      <c r="AB1" s="88"/>
-      <c r="AC1" s="88"/>
-      <c r="AD1" s="88"/>
-      <c r="AE1" s="71" t="s">
+      <c r="AA1" s="89"/>
+      <c r="AB1" s="89"/>
+      <c r="AC1" s="89"/>
+      <c r="AD1" s="89"/>
+      <c r="AE1" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="AF1" s="71"/>
-      <c r="AG1" s="71"/>
-      <c r="AH1" s="72" t="s">
+      <c r="AF1" s="72"/>
+      <c r="AG1" s="72"/>
+      <c r="AH1" s="73" t="s">
         <v>62</v>
       </c>
-      <c r="AI1" s="72"/>
-      <c r="AJ1" s="72"/>
-      <c r="AK1" s="73" t="s">
+      <c r="AI1" s="73"/>
+      <c r="AJ1" s="73"/>
+      <c r="AK1" s="74" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:37" s="38" customFormat="1" ht="30" customHeight="1">
-      <c r="A2" s="79"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="81"/>
+      <c r="A2" s="80"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="82"/>
       <c r="D2" s="49" t="s">
         <v>39</v>
       </c>
@@ -4623,7 +4629,7 @@
       <c r="AH2" s="47"/>
       <c r="AI2" s="47"/>
       <c r="AJ2" s="47"/>
-      <c r="AK2" s="74"/>
+      <c r="AK2" s="75"/>
     </row>
     <row r="3" spans="1:37">
       <c r="A3" s="52" t="s">
@@ -4699,7 +4705,7 @@
         <v>1</v>
       </c>
       <c r="Y3" s="56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z3" s="57">
         <v>3</v>
@@ -4724,7 +4730,7 @@
       <c r="AH3" s="59"/>
       <c r="AI3" s="59"/>
       <c r="AJ3" s="59"/>
-      <c r="AK3" s="75"/>
+      <c r="AK3" s="76"/>
     </row>
     <row r="4" spans="1:37">
       <c r="A4" s="50">
@@ -4848,7 +4854,7 @@
       <c r="C6" s="51">
         <v>46206</v>
       </c>
-      <c r="D6" s="40"/>
+      <c r="D6" s="62"/>
       <c r="E6" s="60" t="s">
         <v>12</v>
       </c>
@@ -4924,54 +4930,68 @@
       <c r="C7" s="51">
         <v>46207</v>
       </c>
-      <c r="D7" s="40"/>
-      <c r="E7" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="J7" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="K7" s="50"/>
-      <c r="L7" s="50"/>
-      <c r="M7" s="50"/>
-      <c r="N7" s="50"/>
-      <c r="O7" s="50"/>
-      <c r="P7" s="50"/>
-      <c r="Q7" s="50"/>
-      <c r="R7" s="50"/>
-      <c r="S7" s="50"/>
-      <c r="T7" s="50"/>
-      <c r="U7" s="50"/>
-      <c r="V7" s="50"/>
-      <c r="W7" s="50"/>
-      <c r="X7" s="50"/>
-      <c r="Y7" s="50"/>
-      <c r="Z7" s="50"/>
-      <c r="AA7" s="50"/>
-      <c r="AB7" s="50"/>
-      <c r="AC7" s="50"/>
-      <c r="AD7" s="50"/>
-      <c r="AE7" s="50"/>
-      <c r="AF7" s="50"/>
-      <c r="AG7" s="50"/>
-      <c r="AH7" s="50"/>
-      <c r="AI7" s="50"/>
-      <c r="AJ7" s="50"/>
+      <c r="D7" s="50" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="K7" s="60"/>
+      <c r="L7" s="60"/>
+      <c r="M7" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="N7" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="O7" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="P7" s="60"/>
+      <c r="Q7" s="60"/>
+      <c r="R7" s="60"/>
+      <c r="S7" s="60"/>
+      <c r="T7" s="60"/>
+      <c r="U7" s="60"/>
+      <c r="V7" s="60"/>
+      <c r="W7" s="60"/>
+      <c r="X7" s="60"/>
+      <c r="Y7" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z7" s="60"/>
+      <c r="AA7" s="60"/>
+      <c r="AB7" s="60"/>
+      <c r="AC7" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD7" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE7" s="60"/>
+      <c r="AF7" s="60"/>
+      <c r="AG7" s="60"/>
+      <c r="AH7" s="60"/>
+      <c r="AI7" s="60"/>
+      <c r="AJ7" s="60"/>
       <c r="AK7" s="61">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -4984,18 +5004,32 @@
       <c r="C8" s="51">
         <v>46208</v>
       </c>
-      <c r="D8" s="40"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
-      <c r="L8" s="50"/>
+      <c r="D8" s="50" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="60"/>
+      <c r="I8" s="60"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="60"/>
+      <c r="L8" s="50" t="s">
+        <v>12</v>
+      </c>
       <c r="M8" s="50"/>
-      <c r="N8" s="50"/>
-      <c r="O8" s="50"/>
+      <c r="N8" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="O8" s="50" t="s">
+        <v>12</v>
+      </c>
       <c r="P8" s="50"/>
       <c r="Q8" s="50"/>
       <c r="R8" s="50"/>
@@ -5019,7 +5053,7 @@
       <c r="AJ8" s="50"/>
       <c r="AK8" s="61">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:37">

--- a/Другое/study_chart.xlsx
+++ b/Другое/study_chart.xlsx
@@ -741,7 +741,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="66">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -936,6 +936,9 @@
   </si>
   <si>
     <t>90.00</t>
+  </si>
+  <si>
+    <t>89.8</t>
   </si>
 </sst>
 </file>
@@ -5020,40 +5023,48 @@
       <c r="I8" s="60"/>
       <c r="J8" s="60"/>
       <c r="K8" s="60"/>
-      <c r="L8" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="M8" s="50"/>
-      <c r="N8" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="O8" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="P8" s="50"/>
-      <c r="Q8" s="50"/>
-      <c r="R8" s="50"/>
-      <c r="S8" s="50"/>
-      <c r="T8" s="50"/>
-      <c r="U8" s="50"/>
-      <c r="V8" s="50"/>
-      <c r="W8" s="50"/>
-      <c r="X8" s="50"/>
-      <c r="Y8" s="50"/>
-      <c r="Z8" s="50"/>
-      <c r="AA8" s="50"/>
-      <c r="AB8" s="50"/>
-      <c r="AC8" s="50"/>
-      <c r="AD8" s="50"/>
-      <c r="AE8" s="50"/>
-      <c r="AF8" s="50"/>
-      <c r="AG8" s="50"/>
-      <c r="AH8" s="50"/>
-      <c r="AI8" s="50"/>
-      <c r="AJ8" s="50"/>
+      <c r="L8" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="M8" s="60"/>
+      <c r="N8" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="O8" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="P8" s="60"/>
+      <c r="Q8" s="60"/>
+      <c r="R8" s="60"/>
+      <c r="S8" s="60"/>
+      <c r="T8" s="60"/>
+      <c r="U8" s="60"/>
+      <c r="V8" s="60"/>
+      <c r="W8" s="60"/>
+      <c r="X8" s="60"/>
+      <c r="Y8" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z8" s="60"/>
+      <c r="AA8" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB8" s="60"/>
+      <c r="AC8" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD8" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE8" s="60"/>
+      <c r="AF8" s="60"/>
+      <c r="AG8" s="60"/>
+      <c r="AH8" s="60"/>
+      <c r="AI8" s="60"/>
+      <c r="AJ8" s="60"/>
       <c r="AK8" s="61">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -5066,14 +5077,26 @@
       <c r="C9" s="51">
         <v>46209</v>
       </c>
-      <c r="D9" s="40"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="50"/>
-      <c r="I9" s="50"/>
-      <c r="J9" s="50"/>
-      <c r="K9" s="50"/>
+      <c r="D9" s="50" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="60"/>
+      <c r="I9" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" s="60"/>
+      <c r="K9" s="60" t="s">
+        <v>12</v>
+      </c>
       <c r="L9" s="50"/>
       <c r="M9" s="50"/>
       <c r="N9" s="50"/>
@@ -5101,7 +5124,7 @@
       <c r="AJ9" s="50"/>
       <c r="AK9" s="61">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:37">

--- a/Другое/study_chart.xlsx
+++ b/Другое/study_chart.xlsx
@@ -741,7 +741,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="66">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -5098,7 +5098,9 @@
         <v>12</v>
       </c>
       <c r="L9" s="50"/>
-      <c r="M9" s="50"/>
+      <c r="M9" s="50" t="s">
+        <v>12</v>
+      </c>
       <c r="N9" s="50"/>
       <c r="O9" s="50"/>
       <c r="P9" s="50"/>
@@ -5124,7 +5126,7 @@
       <c r="AJ9" s="50"/>
       <c r="AK9" s="61">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:37">

--- a/Другое/study_chart.xlsx
+++ b/Другое/study_chart.xlsx
@@ -741,7 +741,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="66">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -5097,36 +5097,42 @@
       <c r="K9" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="L9" s="50"/>
-      <c r="M9" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="N9" s="50"/>
-      <c r="O9" s="50"/>
-      <c r="P9" s="50"/>
-      <c r="Q9" s="50"/>
-      <c r="R9" s="50"/>
-      <c r="S9" s="50"/>
-      <c r="T9" s="50"/>
-      <c r="U9" s="50"/>
-      <c r="V9" s="50"/>
-      <c r="W9" s="50"/>
-      <c r="X9" s="50"/>
-      <c r="Y9" s="50"/>
-      <c r="Z9" s="50"/>
-      <c r="AA9" s="50"/>
-      <c r="AB9" s="50"/>
-      <c r="AC9" s="50"/>
-      <c r="AD9" s="50"/>
-      <c r="AE9" s="50"/>
-      <c r="AF9" s="50"/>
-      <c r="AG9" s="50"/>
-      <c r="AH9" s="50"/>
-      <c r="AI9" s="50"/>
-      <c r="AJ9" s="50"/>
+      <c r="L9" s="60"/>
+      <c r="M9" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="N9" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="O9" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="P9" s="60"/>
+      <c r="Q9" s="60"/>
+      <c r="R9" s="60"/>
+      <c r="S9" s="60"/>
+      <c r="T9" s="60"/>
+      <c r="U9" s="60"/>
+      <c r="V9" s="60"/>
+      <c r="W9" s="60"/>
+      <c r="X9" s="60"/>
+      <c r="Y9" s="60"/>
+      <c r="Z9" s="60"/>
+      <c r="AA9" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB9" s="60"/>
+      <c r="AC9" s="60"/>
+      <c r="AD9" s="60"/>
+      <c r="AE9" s="60"/>
+      <c r="AF9" s="60"/>
+      <c r="AG9" s="60"/>
+      <c r="AH9" s="60"/>
+      <c r="AI9" s="60"/>
+      <c r="AJ9" s="60"/>
       <c r="AK9" s="61">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -5139,15 +5145,17 @@
       <c r="C10" s="51">
         <v>46210</v>
       </c>
-      <c r="D10" s="40"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="50"/>
-      <c r="I10" s="50"/>
-      <c r="J10" s="50"/>
-      <c r="K10" s="50"/>
-      <c r="L10" s="50"/>
+      <c r="D10" s="62" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="60"/>
+      <c r="F10" s="60"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="60"/>
+      <c r="K10" s="60"/>
+      <c r="L10" s="60"/>
       <c r="M10" s="50"/>
       <c r="N10" s="50"/>
       <c r="O10" s="50"/>

--- a/Другое/study_chart.xlsx
+++ b/Другое/study_chart.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="10980" activeTab="2"/>
+    <workbookView windowWidth="24000" windowHeight="10380" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Июнь" sheetId="1" r:id="rId1"/>
@@ -741,7 +741,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="68">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -942,6 +942,9 @@
   </si>
   <si>
     <t>89.6</t>
+  </si>
+  <si>
+    <t>89.1</t>
   </si>
 </sst>
 </file>
@@ -1312,15 +1315,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1334,7 +1337,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="57">
+  <fills count="58">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1404,6 +1407,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.15"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.15"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1656,12 +1671,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2085,7 +2094,7 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="24" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="24" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2109,16 +2118,16 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="27" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="29" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="28" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="30" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="28" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="30" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="29" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="31" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -2127,89 +2136,89 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2342,23 +2351,20 @@
     <xf numFmtId="0" fontId="1" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2367,92 +2373,101 @@
     <xf numFmtId="0" fontId="19" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="26" fillId="20" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="26" fillId="22" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="26" fillId="20" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="26" fillId="22" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="26" fillId="20" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="26" fillId="22" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2841,329 +2856,329 @@
   <dimension ref="H9:Q22"/>
   <sheetFormatPr defaultColWidth="9.14159292035398" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="7" width="9.14159292035398" style="47"/>
-    <col min="8" max="8" width="5" style="47" customWidth="1"/>
-    <col min="9" max="9" width="14.7079646017699" style="47" customWidth="1"/>
-    <col min="10" max="10" width="16.858407079646" style="47" customWidth="1"/>
-    <col min="11" max="11" width="14.283185840708" style="47" customWidth="1"/>
-    <col min="12" max="13" width="11.283185840708" style="47" customWidth="1"/>
-    <col min="14" max="14" width="11.5663716814159" style="47" customWidth="1"/>
-    <col min="15" max="15" width="14.5663716814159" style="47" customWidth="1"/>
-    <col min="16" max="17" width="10" style="47" customWidth="1"/>
-    <col min="18" max="16384" width="9.14159292035398" style="47"/>
+    <col min="1" max="7" width="9.14159292035398" style="49"/>
+    <col min="8" max="8" width="5" style="49" customWidth="1"/>
+    <col min="9" max="9" width="14.7079646017699" style="49" customWidth="1"/>
+    <col min="10" max="10" width="16.858407079646" style="49" customWidth="1"/>
+    <col min="11" max="11" width="14.283185840708" style="49" customWidth="1"/>
+    <col min="12" max="13" width="11.283185840708" style="49" customWidth="1"/>
+    <col min="14" max="14" width="11.5663716814159" style="49" customWidth="1"/>
+    <col min="15" max="15" width="14.5663716814159" style="49" customWidth="1"/>
+    <col min="16" max="17" width="10" style="49" customWidth="1"/>
+    <col min="18" max="16384" width="9.14159292035398" style="49"/>
   </cols>
   <sheetData>
     <row r="9" ht="45" customHeight="1" spans="8:17">
-      <c r="H9" s="74" t="s">
+      <c r="H9" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="75"/>
-      <c r="J9" s="75"/>
-      <c r="K9" s="75"/>
-      <c r="L9" s="75"/>
-      <c r="M9" s="75"/>
-      <c r="N9" s="75"/>
-      <c r="O9" s="75"/>
-      <c r="P9" s="75"/>
-      <c r="Q9" s="76"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="77"/>
+      <c r="K9" s="77"/>
+      <c r="L9" s="77"/>
+      <c r="M9" s="77"/>
+      <c r="N9" s="77"/>
+      <c r="O9" s="77"/>
+      <c r="P9" s="77"/>
+      <c r="Q9" s="78"/>
     </row>
     <row r="10" ht="30" customHeight="1" spans="8:17">
-      <c r="H10" s="77" t="s">
+      <c r="H10" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="I10" s="78" t="s">
+      <c r="I10" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="J10" s="77" t="s">
+      <c r="J10" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="K10" s="77" t="s">
+      <c r="K10" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="L10" s="77" t="s">
+      <c r="L10" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="M10" s="77" t="s">
+      <c r="M10" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="N10" s="77" t="s">
+      <c r="N10" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="O10" s="78" t="s">
+      <c r="O10" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="P10" s="77" t="s">
+      <c r="P10" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="Q10" s="77" t="s">
+      <c r="Q10" s="79" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="8:17">
-      <c r="H11" s="79">
+      <c r="H11" s="81">
         <v>1</v>
       </c>
-      <c r="I11" s="80" t="s">
+      <c r="I11" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="J11" s="81">
+      <c r="J11" s="83">
         <v>46193</v>
       </c>
-      <c r="K11" s="82" t="s">
-        <v>12</v>
-      </c>
-      <c r="L11" s="82" t="s">
-        <v>12</v>
-      </c>
-      <c r="M11" s="82" t="s">
-        <v>12</v>
-      </c>
-      <c r="N11" s="82" t="s">
-        <v>12</v>
-      </c>
-      <c r="O11" s="82"/>
-      <c r="P11" s="82"/>
-      <c r="Q11" s="82"/>
+      <c r="K11" s="84" t="s">
+        <v>12</v>
+      </c>
+      <c r="L11" s="84" t="s">
+        <v>12</v>
+      </c>
+      <c r="M11" s="84" t="s">
+        <v>12</v>
+      </c>
+      <c r="N11" s="84" t="s">
+        <v>12</v>
+      </c>
+      <c r="O11" s="84"/>
+      <c r="P11" s="84"/>
+      <c r="Q11" s="84"/>
     </row>
     <row r="12" spans="8:17">
-      <c r="H12" s="79">
+      <c r="H12" s="81">
         <v>2</v>
       </c>
-      <c r="I12" s="80" t="s">
+      <c r="I12" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="J12" s="81">
+      <c r="J12" s="83">
         <v>46194</v>
       </c>
-      <c r="K12" s="82" t="s">
-        <v>12</v>
-      </c>
-      <c r="L12" s="82"/>
-      <c r="M12" s="82"/>
-      <c r="N12" s="82" t="s">
-        <v>12</v>
-      </c>
-      <c r="O12" s="82" t="s">
-        <v>12</v>
-      </c>
-      <c r="P12" s="82"/>
-      <c r="Q12" s="82"/>
+      <c r="K12" s="84" t="s">
+        <v>12</v>
+      </c>
+      <c r="L12" s="84"/>
+      <c r="M12" s="84"/>
+      <c r="N12" s="84" t="s">
+        <v>12</v>
+      </c>
+      <c r="O12" s="84" t="s">
+        <v>12</v>
+      </c>
+      <c r="P12" s="84"/>
+      <c r="Q12" s="84"/>
     </row>
     <row r="13" spans="8:17">
-      <c r="H13" s="79">
+      <c r="H13" s="81">
         <v>3</v>
       </c>
-      <c r="I13" s="80" t="s">
+      <c r="I13" s="82" t="s">
         <v>14</v>
       </c>
-      <c r="J13" s="81">
+      <c r="J13" s="83">
         <v>46195</v>
       </c>
-      <c r="K13" s="82" t="s">
-        <v>12</v>
-      </c>
-      <c r="L13" s="82"/>
-      <c r="M13" s="82"/>
-      <c r="N13" s="82" t="s">
-        <v>12</v>
-      </c>
-      <c r="O13" s="82"/>
-      <c r="P13" s="82"/>
-      <c r="Q13" s="82"/>
+      <c r="K13" s="84" t="s">
+        <v>12</v>
+      </c>
+      <c r="L13" s="84"/>
+      <c r="M13" s="84"/>
+      <c r="N13" s="84" t="s">
+        <v>12</v>
+      </c>
+      <c r="O13" s="84"/>
+      <c r="P13" s="84"/>
+      <c r="Q13" s="84"/>
     </row>
     <row r="14" spans="8:17">
-      <c r="H14" s="79">
+      <c r="H14" s="81">
         <v>4</v>
       </c>
-      <c r="I14" s="80" t="s">
+      <c r="I14" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="J14" s="81">
+      <c r="J14" s="83">
         <v>46196</v>
       </c>
-      <c r="K14" s="82"/>
-      <c r="L14" s="82" t="s">
-        <v>12</v>
-      </c>
-      <c r="M14" s="82"/>
-      <c r="N14" s="82" t="s">
-        <v>12</v>
-      </c>
-      <c r="O14" s="82"/>
-      <c r="P14" s="82"/>
-      <c r="Q14" s="82"/>
+      <c r="K14" s="84"/>
+      <c r="L14" s="84" t="s">
+        <v>12</v>
+      </c>
+      <c r="M14" s="84"/>
+      <c r="N14" s="84" t="s">
+        <v>12</v>
+      </c>
+      <c r="O14" s="84"/>
+      <c r="P14" s="84"/>
+      <c r="Q14" s="84"/>
     </row>
     <row r="15" spans="8:17">
-      <c r="H15" s="79">
+      <c r="H15" s="81">
         <v>5</v>
       </c>
-      <c r="I15" s="80" t="s">
+      <c r="I15" s="82" t="s">
         <v>16</v>
       </c>
-      <c r="J15" s="81">
+      <c r="J15" s="83">
         <v>46197</v>
       </c>
-      <c r="K15" s="82" t="s">
-        <v>12</v>
-      </c>
-      <c r="L15" s="82"/>
-      <c r="M15" s="82"/>
-      <c r="N15" s="82"/>
-      <c r="O15" s="82"/>
-      <c r="P15" s="82"/>
-      <c r="Q15" s="82"/>
+      <c r="K15" s="84" t="s">
+        <v>12</v>
+      </c>
+      <c r="L15" s="84"/>
+      <c r="M15" s="84"/>
+      <c r="N15" s="84"/>
+      <c r="O15" s="84"/>
+      <c r="P15" s="84"/>
+      <c r="Q15" s="84"/>
     </row>
     <row r="16" spans="8:17">
-      <c r="H16" s="79">
+      <c r="H16" s="81">
         <v>6</v>
       </c>
-      <c r="I16" s="80" t="s">
+      <c r="I16" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="J16" s="81">
+      <c r="J16" s="83">
         <v>46198</v>
       </c>
-      <c r="K16" s="82" t="s">
-        <v>12</v>
-      </c>
-      <c r="L16" s="82" t="s">
-        <v>12</v>
-      </c>
-      <c r="M16" s="82" t="s">
-        <v>12</v>
-      </c>
-      <c r="N16" s="82"/>
-      <c r="O16" s="82"/>
-      <c r="P16" s="82"/>
-      <c r="Q16" s="82"/>
+      <c r="K16" s="84" t="s">
+        <v>12</v>
+      </c>
+      <c r="L16" s="84" t="s">
+        <v>12</v>
+      </c>
+      <c r="M16" s="84" t="s">
+        <v>12</v>
+      </c>
+      <c r="N16" s="84"/>
+      <c r="O16" s="84"/>
+      <c r="P16" s="84"/>
+      <c r="Q16" s="84"/>
     </row>
     <row r="17" spans="8:17">
-      <c r="H17" s="79">
+      <c r="H17" s="81">
         <v>7</v>
       </c>
-      <c r="I17" s="80" t="s">
+      <c r="I17" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="J17" s="81">
+      <c r="J17" s="83">
         <v>46199</v>
       </c>
-      <c r="K17" s="82"/>
-      <c r="L17" s="82" t="s">
-        <v>12</v>
-      </c>
-      <c r="M17" s="82" t="s">
-        <v>12</v>
-      </c>
-      <c r="N17" s="82"/>
-      <c r="O17" s="82"/>
-      <c r="P17" s="82"/>
-      <c r="Q17" s="82"/>
+      <c r="K17" s="84"/>
+      <c r="L17" s="84" t="s">
+        <v>12</v>
+      </c>
+      <c r="M17" s="84" t="s">
+        <v>12</v>
+      </c>
+      <c r="N17" s="84"/>
+      <c r="O17" s="84"/>
+      <c r="P17" s="84"/>
+      <c r="Q17" s="84"/>
     </row>
     <row r="18" spans="8:17">
-      <c r="H18" s="79">
+      <c r="H18" s="81">
         <v>8</v>
       </c>
-      <c r="I18" s="80" t="s">
+      <c r="I18" s="82" t="s">
         <v>11</v>
       </c>
-      <c r="J18" s="81">
+      <c r="J18" s="83">
         <v>46200</v>
       </c>
-      <c r="K18" s="82"/>
-      <c r="L18" s="82"/>
-      <c r="M18" s="82"/>
-      <c r="N18" s="82"/>
-      <c r="O18" s="82"/>
-      <c r="P18" s="82"/>
-      <c r="Q18" s="82"/>
+      <c r="K18" s="84"/>
+      <c r="L18" s="84"/>
+      <c r="M18" s="84"/>
+      <c r="N18" s="84"/>
+      <c r="O18" s="84"/>
+      <c r="P18" s="84"/>
+      <c r="Q18" s="84"/>
     </row>
     <row r="19" spans="8:17">
-      <c r="H19" s="79">
+      <c r="H19" s="81">
         <v>9</v>
       </c>
-      <c r="I19" s="80" t="s">
+      <c r="I19" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="J19" s="81">
+      <c r="J19" s="83">
         <v>46201</v>
       </c>
-      <c r="K19" s="82" t="s">
-        <v>12</v>
-      </c>
-      <c r="L19" s="82"/>
-      <c r="M19" s="82"/>
-      <c r="N19" s="82"/>
-      <c r="O19" s="82"/>
-      <c r="P19" s="82"/>
-      <c r="Q19" s="82"/>
+      <c r="K19" s="84" t="s">
+        <v>12</v>
+      </c>
+      <c r="L19" s="84"/>
+      <c r="M19" s="84"/>
+      <c r="N19" s="84"/>
+      <c r="O19" s="84"/>
+      <c r="P19" s="84"/>
+      <c r="Q19" s="84"/>
     </row>
     <row r="20" spans="8:17">
-      <c r="H20" s="79">
+      <c r="H20" s="81">
         <v>10</v>
       </c>
-      <c r="I20" s="80" t="s">
+      <c r="I20" s="82" t="s">
         <v>14</v>
       </c>
-      <c r="J20" s="81">
+      <c r="J20" s="83">
         <v>46202</v>
       </c>
-      <c r="K20" s="82"/>
-      <c r="L20" s="82"/>
-      <c r="M20" s="82"/>
-      <c r="N20" s="82"/>
-      <c r="O20" s="82"/>
-      <c r="P20" s="82"/>
-      <c r="Q20" s="82"/>
+      <c r="K20" s="84"/>
+      <c r="L20" s="84"/>
+      <c r="M20" s="84"/>
+      <c r="N20" s="84"/>
+      <c r="O20" s="84"/>
+      <c r="P20" s="84"/>
+      <c r="Q20" s="84"/>
     </row>
     <row r="21" spans="8:17">
-      <c r="H21" s="79">
+      <c r="H21" s="81">
         <v>11</v>
       </c>
-      <c r="I21" s="80" t="s">
+      <c r="I21" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="J21" s="81">
+      <c r="J21" s="83">
         <v>46203</v>
       </c>
-      <c r="K21" s="82"/>
-      <c r="L21" s="82"/>
-      <c r="M21" s="82"/>
-      <c r="N21" s="82"/>
-      <c r="O21" s="82"/>
-      <c r="P21" s="82"/>
-      <c r="Q21" s="82"/>
+      <c r="K21" s="84"/>
+      <c r="L21" s="84"/>
+      <c r="M21" s="84"/>
+      <c r="N21" s="84"/>
+      <c r="O21" s="84"/>
+      <c r="P21" s="84"/>
+      <c r="Q21" s="84"/>
     </row>
     <row r="22" ht="14.6" spans="8:17">
-      <c r="H22" s="83" t="s">
+      <c r="H22" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="84"/>
-      <c r="J22" s="85"/>
-      <c r="K22" s="86">
+      <c r="I22" s="86"/>
+      <c r="J22" s="87"/>
+      <c r="K22" s="88">
         <f>COUNTA(K11:K21)</f>
         <v>6</v>
       </c>
-      <c r="L22" s="86">
+      <c r="L22" s="88">
         <f t="shared" ref="L22:Q22" si="0">COUNTA(L11:L21)</f>
         <v>4</v>
       </c>
-      <c r="M22" s="86">
+      <c r="M22" s="88">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="N22" s="86">
+      <c r="N22" s="88">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="O22" s="86">
+      <c r="O22" s="88">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="P22" s="86">
+      <c r="P22" s="88">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q22" s="86">
+      <c r="Q22" s="88">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3195,1848 +3210,1848 @@
   <dimension ref="H9:AL42"/>
   <sheetFormatPr defaultColWidth="9.14159292035398" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="7" width="9.14159292035398" style="47"/>
-    <col min="8" max="8" width="5" style="47" customWidth="1"/>
-    <col min="9" max="9" width="14.7079646017699" style="47" customWidth="1"/>
-    <col min="10" max="11" width="16.858407079646" style="47" customWidth="1"/>
-    <col min="12" max="13" width="24.141592920354" style="47" customWidth="1"/>
-    <col min="14" max="17" width="14.283185840708" style="47" customWidth="1"/>
-    <col min="18" max="18" width="20.5663716814159" style="47" customWidth="1"/>
-    <col min="19" max="20" width="23.283185840708" style="47" customWidth="1"/>
-    <col min="21" max="22" width="11.283185840708" style="47" customWidth="1"/>
-    <col min="23" max="23" width="30.283185840708" style="47" customWidth="1"/>
-    <col min="24" max="24" width="11.5663716814159" style="47" customWidth="1"/>
-    <col min="25" max="25" width="14.5663716814159" style="47" customWidth="1"/>
-    <col min="26" max="27" width="10" style="47" customWidth="1"/>
-    <col min="28" max="28" width="28" style="47" customWidth="1"/>
-    <col min="29" max="29" width="14.141592920354" style="47" customWidth="1"/>
-    <col min="30" max="30" width="13.858407079646" style="47" customWidth="1"/>
-    <col min="31" max="37" width="18.4247787610619" style="47" customWidth="1"/>
-    <col min="38" max="38" width="18" style="47" customWidth="1"/>
-    <col min="39" max="16384" width="9.14159292035398" style="47"/>
+    <col min="1" max="7" width="9.14159292035398" style="49"/>
+    <col min="8" max="8" width="5" style="49" customWidth="1"/>
+    <col min="9" max="9" width="14.7079646017699" style="49" customWidth="1"/>
+    <col min="10" max="11" width="16.858407079646" style="49" customWidth="1"/>
+    <col min="12" max="13" width="24.141592920354" style="49" customWidth="1"/>
+    <col min="14" max="17" width="14.283185840708" style="49" customWidth="1"/>
+    <col min="18" max="18" width="20.5663716814159" style="49" customWidth="1"/>
+    <col min="19" max="20" width="23.283185840708" style="49" customWidth="1"/>
+    <col min="21" max="22" width="11.283185840708" style="49" customWidth="1"/>
+    <col min="23" max="23" width="30.283185840708" style="49" customWidth="1"/>
+    <col min="24" max="24" width="11.5663716814159" style="49" customWidth="1"/>
+    <col min="25" max="25" width="14.5663716814159" style="49" customWidth="1"/>
+    <col min="26" max="27" width="10" style="49" customWidth="1"/>
+    <col min="28" max="28" width="28" style="49" customWidth="1"/>
+    <col min="29" max="29" width="14.141592920354" style="49" customWidth="1"/>
+    <col min="30" max="30" width="13.858407079646" style="49" customWidth="1"/>
+    <col min="31" max="37" width="18.4247787610619" style="49" customWidth="1"/>
+    <col min="38" max="38" width="18" style="49" customWidth="1"/>
+    <col min="39" max="16384" width="9.14159292035398" style="49"/>
   </cols>
   <sheetData>
     <row r="9" ht="45" customHeight="1" spans="8:38">
-      <c r="H9" s="48" t="s">
+      <c r="H9" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="49"/>
-      <c r="J9" s="49"/>
-      <c r="K9" s="49"/>
-      <c r="L9" s="49"/>
-      <c r="M9" s="49"/>
-      <c r="N9" s="49"/>
-      <c r="O9" s="49"/>
-      <c r="P9" s="49"/>
-      <c r="Q9" s="49"/>
-      <c r="R9" s="49"/>
-      <c r="S9" s="49"/>
-      <c r="T9" s="49"/>
-      <c r="U9" s="49"/>
-      <c r="V9" s="49"/>
-      <c r="W9" s="49"/>
-      <c r="X9" s="49"/>
-      <c r="Y9" s="49"/>
-      <c r="Z9" s="49"/>
-      <c r="AA9" s="49"/>
-      <c r="AB9" s="49"/>
-      <c r="AC9" s="49"/>
-      <c r="AD9" s="49"/>
-      <c r="AE9" s="49"/>
-      <c r="AF9" s="49"/>
-      <c r="AG9" s="49"/>
-      <c r="AH9" s="49"/>
-      <c r="AI9" s="49"/>
-      <c r="AJ9" s="49"/>
-      <c r="AK9" s="49"/>
-      <c r="AL9" s="49"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="51"/>
+      <c r="K9" s="51"/>
+      <c r="L9" s="51"/>
+      <c r="M9" s="51"/>
+      <c r="N9" s="51"/>
+      <c r="O9" s="51"/>
+      <c r="P9" s="51"/>
+      <c r="Q9" s="51"/>
+      <c r="R9" s="51"/>
+      <c r="S9" s="51"/>
+      <c r="T9" s="51"/>
+      <c r="U9" s="51"/>
+      <c r="V9" s="51"/>
+      <c r="W9" s="51"/>
+      <c r="X9" s="51"/>
+      <c r="Y9" s="51"/>
+      <c r="Z9" s="51"/>
+      <c r="AA9" s="51"/>
+      <c r="AB9" s="51"/>
+      <c r="AC9" s="51"/>
+      <c r="AD9" s="51"/>
+      <c r="AE9" s="51"/>
+      <c r="AF9" s="51"/>
+      <c r="AG9" s="51"/>
+      <c r="AH9" s="51"/>
+      <c r="AI9" s="51"/>
+      <c r="AJ9" s="51"/>
+      <c r="AK9" s="51"/>
+      <c r="AL9" s="51"/>
     </row>
     <row r="10" ht="30" customHeight="1" spans="8:38">
-      <c r="H10" s="50" t="s">
+      <c r="H10" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="I10" s="51" t="s">
+      <c r="I10" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="J10" s="50" t="s">
+      <c r="J10" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="K10" s="52" t="s">
+      <c r="K10" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="L10" s="52" t="s">
+      <c r="L10" s="54" t="s">
         <v>21</v>
       </c>
-      <c r="M10" s="52" t="s">
+      <c r="M10" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="N10" s="53" t="s">
+      <c r="N10" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="O10" s="54" t="s">
+      <c r="O10" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="P10" s="54" t="s">
+      <c r="P10" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="Q10" s="54" t="s">
+      <c r="Q10" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="R10" s="54" t="s">
+      <c r="R10" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="S10" s="55" t="s">
+      <c r="S10" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="T10" s="55" t="s">
+      <c r="T10" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="U10" s="56" t="s">
+      <c r="U10" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="V10" s="56" t="s">
+      <c r="V10" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="W10" s="55" t="s">
+      <c r="W10" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="X10" s="57" t="s">
+      <c r="X10" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="Y10" s="58" t="s">
+      <c r="Y10" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="Z10" s="57" t="s">
+      <c r="Z10" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="AA10" s="59" t="s">
+      <c r="AA10" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="AB10" s="60" t="s">
+      <c r="AB10" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="AC10" s="61" t="s">
+      <c r="AC10" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="AD10" s="60" t="s">
+      <c r="AD10" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="AE10" s="60" t="s">
+      <c r="AE10" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="AF10" s="60" t="s">
+      <c r="AF10" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="AG10" s="62" t="s">
+      <c r="AG10" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="AH10" s="62" t="s">
+      <c r="AH10" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="AI10" s="62" t="s">
+      <c r="AI10" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="AJ10" s="62" t="s">
+      <c r="AJ10" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="AK10" s="62" t="s">
+      <c r="AK10" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="AL10" s="63" t="s">
+      <c r="AL10" s="65" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="11" spans="8:38">
-      <c r="H11" s="64">
+      <c r="H11" s="66">
         <v>1</v>
       </c>
-      <c r="I11" s="65" t="s">
+      <c r="I11" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="J11" s="66">
+      <c r="J11" s="68">
         <v>46204</v>
       </c>
-      <c r="K11" s="66"/>
-      <c r="L11" s="66"/>
-      <c r="M11" s="66"/>
-      <c r="N11" s="67"/>
-      <c r="O11" s="67"/>
-      <c r="P11" s="67"/>
-      <c r="Q11" s="67"/>
-      <c r="R11" s="67"/>
-      <c r="S11" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="T11" s="67"/>
-      <c r="U11" s="67"/>
-      <c r="V11" s="67"/>
-      <c r="W11" s="67"/>
-      <c r="X11" s="67"/>
-      <c r="Y11" s="67"/>
-      <c r="Z11" s="67"/>
-      <c r="AA11" s="67"/>
-      <c r="AB11" s="68"/>
-      <c r="AC11" s="68"/>
-      <c r="AD11" s="68"/>
-      <c r="AE11" s="68"/>
-      <c r="AF11" s="68"/>
-      <c r="AG11" s="68"/>
-      <c r="AH11" s="68"/>
-      <c r="AI11" s="68"/>
-      <c r="AJ11" s="68"/>
-      <c r="AK11" s="68"/>
-      <c r="AL11" s="69">
+      <c r="K11" s="68"/>
+      <c r="L11" s="68"/>
+      <c r="M11" s="68"/>
+      <c r="N11" s="69"/>
+      <c r="O11" s="69"/>
+      <c r="P11" s="69"/>
+      <c r="Q11" s="69"/>
+      <c r="R11" s="69"/>
+      <c r="S11" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="T11" s="69"/>
+      <c r="U11" s="69"/>
+      <c r="V11" s="69"/>
+      <c r="W11" s="69"/>
+      <c r="X11" s="69"/>
+      <c r="Y11" s="69"/>
+      <c r="Z11" s="69"/>
+      <c r="AA11" s="69"/>
+      <c r="AB11" s="70"/>
+      <c r="AC11" s="70"/>
+      <c r="AD11" s="70"/>
+      <c r="AE11" s="70"/>
+      <c r="AF11" s="70"/>
+      <c r="AG11" s="70"/>
+      <c r="AH11" s="70"/>
+      <c r="AI11" s="70"/>
+      <c r="AJ11" s="70"/>
+      <c r="AK11" s="70"/>
+      <c r="AL11" s="71">
         <f>COUNTA(K11:AK11)</f>
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="8:38">
-      <c r="H12" s="64">
+      <c r="H12" s="66">
         <v>2</v>
       </c>
-      <c r="I12" s="65" t="s">
+      <c r="I12" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="66">
+      <c r="J12" s="68">
         <v>46205</v>
       </c>
-      <c r="K12" s="66"/>
-      <c r="L12" s="66"/>
-      <c r="M12" s="66"/>
-      <c r="N12" s="67"/>
-      <c r="O12" s="67"/>
-      <c r="P12" s="67"/>
-      <c r="Q12" s="67"/>
-      <c r="R12" s="67"/>
-      <c r="S12" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="T12" s="67"/>
-      <c r="U12" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="V12" s="67"/>
-      <c r="W12" s="67"/>
-      <c r="X12" s="67"/>
-      <c r="Y12" s="67"/>
-      <c r="Z12" s="67"/>
-      <c r="AA12" s="67"/>
-      <c r="AB12" s="67"/>
-      <c r="AC12" s="67"/>
-      <c r="AD12" s="67"/>
-      <c r="AE12" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AF12" s="67"/>
-      <c r="AG12" s="67"/>
-      <c r="AH12" s="67"/>
-      <c r="AI12" s="67"/>
-      <c r="AJ12" s="67"/>
-      <c r="AK12" s="67"/>
-      <c r="AL12" s="69">
+      <c r="K12" s="68"/>
+      <c r="L12" s="68"/>
+      <c r="M12" s="68"/>
+      <c r="N12" s="69"/>
+      <c r="O12" s="69"/>
+      <c r="P12" s="69"/>
+      <c r="Q12" s="69"/>
+      <c r="R12" s="69"/>
+      <c r="S12" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="T12" s="69"/>
+      <c r="U12" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="V12" s="69"/>
+      <c r="W12" s="69"/>
+      <c r="X12" s="69"/>
+      <c r="Y12" s="69"/>
+      <c r="Z12" s="69"/>
+      <c r="AA12" s="69"/>
+      <c r="AB12" s="69"/>
+      <c r="AC12" s="69"/>
+      <c r="AD12" s="69"/>
+      <c r="AE12" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF12" s="69"/>
+      <c r="AG12" s="69"/>
+      <c r="AH12" s="69"/>
+      <c r="AI12" s="69"/>
+      <c r="AJ12" s="69"/>
+      <c r="AK12" s="69"/>
+      <c r="AL12" s="71">
         <f t="shared" ref="AL12:AL41" si="0">COUNTA(K12:AK12)</f>
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="8:38">
-      <c r="H13" s="64">
+      <c r="H13" s="66">
         <v>3</v>
       </c>
-      <c r="I13" s="65" t="s">
+      <c r="I13" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="J13" s="66">
+      <c r="J13" s="68">
         <v>46206</v>
       </c>
-      <c r="K13" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="L13" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="M13" s="70"/>
-      <c r="N13" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="O13" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="P13" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q13" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="R13" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="S13" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="T13" s="67"/>
-      <c r="U13" s="67"/>
-      <c r="V13" s="67"/>
-      <c r="W13" s="67"/>
-      <c r="X13" s="67"/>
-      <c r="Y13" s="67"/>
-      <c r="Z13" s="67"/>
-      <c r="AA13" s="67"/>
-      <c r="AB13" s="67"/>
-      <c r="AC13" s="67"/>
-      <c r="AD13" s="67"/>
-      <c r="AE13" s="67"/>
-      <c r="AF13" s="67"/>
-      <c r="AG13" s="67"/>
-      <c r="AH13" s="67"/>
-      <c r="AI13" s="67"/>
-      <c r="AJ13" s="67"/>
-      <c r="AK13" s="67"/>
-      <c r="AL13" s="69">
+      <c r="K13" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="L13" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="M13" s="72"/>
+      <c r="N13" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="O13" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="P13" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q13" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="R13" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="S13" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="T13" s="69"/>
+      <c r="U13" s="69"/>
+      <c r="V13" s="69"/>
+      <c r="W13" s="69"/>
+      <c r="X13" s="69"/>
+      <c r="Y13" s="69"/>
+      <c r="Z13" s="69"/>
+      <c r="AA13" s="69"/>
+      <c r="AB13" s="69"/>
+      <c r="AC13" s="69"/>
+      <c r="AD13" s="69"/>
+      <c r="AE13" s="69"/>
+      <c r="AF13" s="69"/>
+      <c r="AG13" s="69"/>
+      <c r="AH13" s="69"/>
+      <c r="AI13" s="69"/>
+      <c r="AJ13" s="69"/>
+      <c r="AK13" s="69"/>
+      <c r="AL13" s="71">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
     <row r="14" spans="8:38">
-      <c r="H14" s="64">
+      <c r="H14" s="66">
         <v>4</v>
       </c>
-      <c r="I14" s="65" t="s">
+      <c r="I14" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="J14" s="66">
+      <c r="J14" s="68">
         <v>46207</v>
       </c>
-      <c r="K14" s="70"/>
-      <c r="L14" s="70"/>
-      <c r="M14" s="70"/>
-      <c r="N14" s="67"/>
-      <c r="O14" s="67"/>
-      <c r="P14" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q14" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="R14" s="67"/>
-      <c r="S14" s="67"/>
-      <c r="T14" s="67"/>
-      <c r="U14" s="67"/>
-      <c r="V14" s="67"/>
-      <c r="W14" s="67"/>
-      <c r="X14" s="67"/>
-      <c r="Y14" s="67"/>
-      <c r="Z14" s="67"/>
-      <c r="AA14" s="67"/>
-      <c r="AB14" s="67"/>
-      <c r="AC14" s="67"/>
-      <c r="AD14" s="67"/>
-      <c r="AE14" s="67"/>
-      <c r="AF14" s="67"/>
-      <c r="AG14" s="67"/>
-      <c r="AH14" s="67"/>
-      <c r="AI14" s="67"/>
-      <c r="AJ14" s="67"/>
-      <c r="AK14" s="67"/>
-      <c r="AL14" s="69">
+      <c r="K14" s="72"/>
+      <c r="L14" s="72"/>
+      <c r="M14" s="72"/>
+      <c r="N14" s="69"/>
+      <c r="O14" s="69"/>
+      <c r="P14" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q14" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="R14" s="69"/>
+      <c r="S14" s="69"/>
+      <c r="T14" s="69"/>
+      <c r="U14" s="69"/>
+      <c r="V14" s="69"/>
+      <c r="W14" s="69"/>
+      <c r="X14" s="69"/>
+      <c r="Y14" s="69"/>
+      <c r="Z14" s="69"/>
+      <c r="AA14" s="69"/>
+      <c r="AB14" s="69"/>
+      <c r="AC14" s="69"/>
+      <c r="AD14" s="69"/>
+      <c r="AE14" s="69"/>
+      <c r="AF14" s="69"/>
+      <c r="AG14" s="69"/>
+      <c r="AH14" s="69"/>
+      <c r="AI14" s="69"/>
+      <c r="AJ14" s="69"/>
+      <c r="AK14" s="69"/>
+      <c r="AL14" s="71">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="8:38">
-      <c r="H15" s="64">
+      <c r="H15" s="66">
         <v>5</v>
       </c>
-      <c r="I15" s="65" t="s">
+      <c r="I15" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="J15" s="66">
+      <c r="J15" s="68">
         <v>46208</v>
       </c>
-      <c r="K15" s="70"/>
-      <c r="L15" s="70"/>
-      <c r="M15" s="70"/>
-      <c r="N15" s="67"/>
-      <c r="O15" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="P15" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q15" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="R15" s="67"/>
-      <c r="S15" s="67"/>
-      <c r="T15" s="67"/>
-      <c r="U15" s="67"/>
-      <c r="V15" s="67"/>
-      <c r="W15" s="67"/>
-      <c r="X15" s="67"/>
-      <c r="Y15" s="67"/>
-      <c r="Z15" s="67"/>
-      <c r="AA15" s="67"/>
-      <c r="AB15" s="67"/>
-      <c r="AC15" s="67"/>
-      <c r="AD15" s="67"/>
-      <c r="AE15" s="67"/>
-      <c r="AF15" s="67"/>
-      <c r="AG15" s="67"/>
-      <c r="AH15" s="67"/>
-      <c r="AI15" s="67"/>
-      <c r="AJ15" s="67"/>
-      <c r="AK15" s="67"/>
-      <c r="AL15" s="69">
+      <c r="K15" s="72"/>
+      <c r="L15" s="72"/>
+      <c r="M15" s="72"/>
+      <c r="N15" s="69"/>
+      <c r="O15" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="P15" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q15" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="R15" s="69"/>
+      <c r="S15" s="69"/>
+      <c r="T15" s="69"/>
+      <c r="U15" s="69"/>
+      <c r="V15" s="69"/>
+      <c r="W15" s="69"/>
+      <c r="X15" s="69"/>
+      <c r="Y15" s="69"/>
+      <c r="Z15" s="69"/>
+      <c r="AA15" s="69"/>
+      <c r="AB15" s="69"/>
+      <c r="AC15" s="69"/>
+      <c r="AD15" s="69"/>
+      <c r="AE15" s="69"/>
+      <c r="AF15" s="69"/>
+      <c r="AG15" s="69"/>
+      <c r="AH15" s="69"/>
+      <c r="AI15" s="69"/>
+      <c r="AJ15" s="69"/>
+      <c r="AK15" s="69"/>
+      <c r="AL15" s="71">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="8:38">
-      <c r="H16" s="64">
+      <c r="H16" s="66">
         <v>6</v>
       </c>
-      <c r="I16" s="65" t="s">
+      <c r="I16" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="J16" s="66">
+      <c r="J16" s="68">
         <v>46209</v>
       </c>
-      <c r="K16" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="L16" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="M16" s="70"/>
-      <c r="N16" s="67"/>
-      <c r="O16" s="67"/>
-      <c r="P16" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q16" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="R16" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="S16" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="T16" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="U16" s="67"/>
-      <c r="V16" s="67"/>
-      <c r="W16" s="67"/>
-      <c r="X16" s="67"/>
-      <c r="Y16" s="67"/>
-      <c r="Z16" s="67"/>
-      <c r="AA16" s="67"/>
-      <c r="AB16" s="67"/>
-      <c r="AC16" s="67"/>
-      <c r="AD16" s="67"/>
-      <c r="AE16" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AF16" s="67"/>
-      <c r="AG16" s="67"/>
-      <c r="AH16" s="67"/>
-      <c r="AI16" s="67"/>
-      <c r="AJ16" s="67"/>
-      <c r="AK16" s="67"/>
-      <c r="AL16" s="69">
+      <c r="K16" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="L16" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="M16" s="72"/>
+      <c r="N16" s="69"/>
+      <c r="O16" s="69"/>
+      <c r="P16" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q16" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="R16" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="S16" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="T16" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="U16" s="69"/>
+      <c r="V16" s="69"/>
+      <c r="W16" s="69"/>
+      <c r="X16" s="69"/>
+      <c r="Y16" s="69"/>
+      <c r="Z16" s="69"/>
+      <c r="AA16" s="69"/>
+      <c r="AB16" s="69"/>
+      <c r="AC16" s="69"/>
+      <c r="AD16" s="69"/>
+      <c r="AE16" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF16" s="69"/>
+      <c r="AG16" s="69"/>
+      <c r="AH16" s="69"/>
+      <c r="AI16" s="69"/>
+      <c r="AJ16" s="69"/>
+      <c r="AK16" s="69"/>
+      <c r="AL16" s="71">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
     <row r="17" spans="8:38">
-      <c r="H17" s="64">
+      <c r="H17" s="66">
         <v>7</v>
       </c>
-      <c r="I17" s="65" t="s">
+      <c r="I17" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="J17" s="66">
+      <c r="J17" s="68">
         <v>46210</v>
       </c>
-      <c r="K17" s="70"/>
-      <c r="L17" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="M17" s="70"/>
-      <c r="N17" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="O17" s="67"/>
-      <c r="P17" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q17" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="R17" s="67"/>
-      <c r="S17" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="T17" s="67"/>
-      <c r="U17" s="67"/>
-      <c r="V17" s="67"/>
-      <c r="W17" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="X17" s="67"/>
-      <c r="Y17" s="67"/>
-      <c r="Z17" s="67"/>
-      <c r="AA17" s="67"/>
-      <c r="AB17" s="67"/>
-      <c r="AC17" s="67"/>
-      <c r="AD17" s="67"/>
-      <c r="AE17" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AF17" s="67"/>
-      <c r="AG17" s="67"/>
-      <c r="AH17" s="67"/>
-      <c r="AI17" s="67"/>
-      <c r="AJ17" s="67"/>
-      <c r="AK17" s="67"/>
-      <c r="AL17" s="69">
+      <c r="K17" s="72"/>
+      <c r="L17" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="M17" s="72"/>
+      <c r="N17" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="O17" s="69"/>
+      <c r="P17" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q17" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="R17" s="69"/>
+      <c r="S17" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="T17" s="69"/>
+      <c r="U17" s="69"/>
+      <c r="V17" s="69"/>
+      <c r="W17" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="X17" s="69"/>
+      <c r="Y17" s="69"/>
+      <c r="Z17" s="69"/>
+      <c r="AA17" s="69"/>
+      <c r="AB17" s="69"/>
+      <c r="AC17" s="69"/>
+      <c r="AD17" s="69"/>
+      <c r="AE17" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF17" s="69"/>
+      <c r="AG17" s="69"/>
+      <c r="AH17" s="69"/>
+      <c r="AI17" s="69"/>
+      <c r="AJ17" s="69"/>
+      <c r="AK17" s="69"/>
+      <c r="AL17" s="71">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
     <row r="18" spans="8:38">
-      <c r="H18" s="64">
+      <c r="H18" s="66">
         <v>8</v>
       </c>
-      <c r="I18" s="65" t="s">
+      <c r="I18" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="J18" s="66">
+      <c r="J18" s="68">
         <v>46211</v>
       </c>
-      <c r="K18" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="L18" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="M18" s="70"/>
-      <c r="N18" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="O18" s="67"/>
-      <c r="P18" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q18" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="R18" s="67"/>
-      <c r="S18" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="T18" s="67"/>
-      <c r="U18" s="67"/>
-      <c r="V18" s="67"/>
-      <c r="W18" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="X18" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y18" s="67"/>
-      <c r="Z18" s="67"/>
-      <c r="AA18" s="67"/>
-      <c r="AB18" s="67"/>
-      <c r="AC18" s="67"/>
-      <c r="AD18" s="67"/>
-      <c r="AE18" s="67"/>
-      <c r="AF18" s="67"/>
-      <c r="AG18" s="67"/>
-      <c r="AH18" s="67"/>
-      <c r="AI18" s="67"/>
-      <c r="AJ18" s="67"/>
-      <c r="AK18" s="67"/>
-      <c r="AL18" s="69">
+      <c r="K18" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="L18" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="M18" s="72"/>
+      <c r="N18" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="O18" s="69"/>
+      <c r="P18" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q18" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="R18" s="69"/>
+      <c r="S18" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="T18" s="69"/>
+      <c r="U18" s="69"/>
+      <c r="V18" s="69"/>
+      <c r="W18" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="X18" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y18" s="69"/>
+      <c r="Z18" s="69"/>
+      <c r="AA18" s="69"/>
+      <c r="AB18" s="69"/>
+      <c r="AC18" s="69"/>
+      <c r="AD18" s="69"/>
+      <c r="AE18" s="69"/>
+      <c r="AF18" s="69"/>
+      <c r="AG18" s="69"/>
+      <c r="AH18" s="69"/>
+      <c r="AI18" s="69"/>
+      <c r="AJ18" s="69"/>
+      <c r="AK18" s="69"/>
+      <c r="AL18" s="71">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
     <row r="19" spans="8:38">
-      <c r="H19" s="64">
+      <c r="H19" s="66">
         <v>9</v>
       </c>
-      <c r="I19" s="65" t="s">
+      <c r="I19" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="J19" s="66">
+      <c r="J19" s="68">
         <v>46212</v>
       </c>
-      <c r="K19" s="70"/>
-      <c r="L19" s="70"/>
-      <c r="M19" s="70"/>
-      <c r="N19" s="67"/>
-      <c r="O19" s="67"/>
-      <c r="P19" s="67"/>
-      <c r="Q19" s="67"/>
-      <c r="R19" s="67"/>
-      <c r="S19" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="T19" s="67"/>
-      <c r="U19" s="67"/>
-      <c r="V19" s="67"/>
-      <c r="W19" s="67"/>
-      <c r="X19" s="67"/>
-      <c r="Y19" s="67"/>
-      <c r="Z19" s="67"/>
-      <c r="AA19" s="67"/>
-      <c r="AB19" s="67"/>
-      <c r="AC19" s="67"/>
-      <c r="AD19" s="67"/>
-      <c r="AE19" s="67"/>
-      <c r="AF19" s="67"/>
-      <c r="AG19" s="67"/>
-      <c r="AH19" s="67"/>
-      <c r="AI19" s="67"/>
-      <c r="AJ19" s="67"/>
-      <c r="AK19" s="67"/>
-      <c r="AL19" s="69">
+      <c r="K19" s="72"/>
+      <c r="L19" s="72"/>
+      <c r="M19" s="72"/>
+      <c r="N19" s="69"/>
+      <c r="O19" s="69"/>
+      <c r="P19" s="69"/>
+      <c r="Q19" s="69"/>
+      <c r="R19" s="69"/>
+      <c r="S19" s="73" t="s">
+        <v>12</v>
+      </c>
+      <c r="T19" s="69"/>
+      <c r="U19" s="69"/>
+      <c r="V19" s="69"/>
+      <c r="W19" s="69"/>
+      <c r="X19" s="69"/>
+      <c r="Y19" s="69"/>
+      <c r="Z19" s="69"/>
+      <c r="AA19" s="69"/>
+      <c r="AB19" s="69"/>
+      <c r="AC19" s="69"/>
+      <c r="AD19" s="69"/>
+      <c r="AE19" s="69"/>
+      <c r="AF19" s="69"/>
+      <c r="AG19" s="69"/>
+      <c r="AH19" s="69"/>
+      <c r="AI19" s="69"/>
+      <c r="AJ19" s="69"/>
+      <c r="AK19" s="69"/>
+      <c r="AL19" s="71">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="8:38">
-      <c r="H20" s="64">
+      <c r="H20" s="66">
         <v>10</v>
       </c>
-      <c r="I20" s="65" t="s">
+      <c r="I20" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="J20" s="66">
+      <c r="J20" s="68">
         <v>46213</v>
       </c>
-      <c r="K20" s="70"/>
-      <c r="L20" s="70"/>
-      <c r="M20" s="70"/>
-      <c r="N20" s="67"/>
-      <c r="O20" s="67"/>
-      <c r="P20" s="67"/>
-      <c r="Q20" s="67"/>
-      <c r="R20" s="67"/>
-      <c r="S20" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="T20" s="67"/>
-      <c r="U20" s="67"/>
-      <c r="V20" s="67"/>
-      <c r="W20" s="67"/>
-      <c r="X20" s="67"/>
-      <c r="Y20" s="67"/>
-      <c r="Z20" s="67"/>
-      <c r="AA20" s="67"/>
-      <c r="AB20" s="67"/>
-      <c r="AC20" s="67"/>
-      <c r="AD20" s="67"/>
-      <c r="AE20" s="67"/>
-      <c r="AF20" s="67"/>
-      <c r="AG20" s="67"/>
-      <c r="AH20" s="67"/>
-      <c r="AI20" s="67"/>
-      <c r="AJ20" s="67"/>
-      <c r="AK20" s="67"/>
-      <c r="AL20" s="69">
+      <c r="K20" s="72"/>
+      <c r="L20" s="72"/>
+      <c r="M20" s="72"/>
+      <c r="N20" s="69"/>
+      <c r="O20" s="69"/>
+      <c r="P20" s="69"/>
+      <c r="Q20" s="69"/>
+      <c r="R20" s="69"/>
+      <c r="S20" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="T20" s="69"/>
+      <c r="U20" s="69"/>
+      <c r="V20" s="69"/>
+      <c r="W20" s="69"/>
+      <c r="X20" s="69"/>
+      <c r="Y20" s="69"/>
+      <c r="Z20" s="69"/>
+      <c r="AA20" s="69"/>
+      <c r="AB20" s="69"/>
+      <c r="AC20" s="69"/>
+      <c r="AD20" s="69"/>
+      <c r="AE20" s="69"/>
+      <c r="AF20" s="69"/>
+      <c r="AG20" s="69"/>
+      <c r="AH20" s="69"/>
+      <c r="AI20" s="69"/>
+      <c r="AJ20" s="69"/>
+      <c r="AK20" s="69"/>
+      <c r="AL20" s="71">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="8:38">
-      <c r="H21" s="64">
+      <c r="H21" s="66">
         <v>11</v>
       </c>
-      <c r="I21" s="65" t="s">
+      <c r="I21" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="J21" s="66">
+      <c r="J21" s="68">
         <v>46214</v>
       </c>
-      <c r="K21" s="70"/>
-      <c r="L21" s="70"/>
-      <c r="M21" s="70"/>
-      <c r="N21" s="67"/>
-      <c r="O21" s="67"/>
-      <c r="P21" s="67"/>
-      <c r="Q21" s="67"/>
-      <c r="R21" s="67"/>
-      <c r="S21" s="67"/>
-      <c r="T21" s="67"/>
-      <c r="U21" s="67"/>
-      <c r="V21" s="67"/>
-      <c r="W21" s="67"/>
-      <c r="X21" s="67"/>
-      <c r="Y21" s="67"/>
-      <c r="Z21" s="67"/>
-      <c r="AA21" s="67"/>
-      <c r="AB21" s="67"/>
-      <c r="AC21" s="67"/>
-      <c r="AD21" s="67"/>
-      <c r="AE21" s="67"/>
-      <c r="AF21" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG21" s="67"/>
-      <c r="AH21" s="67"/>
-      <c r="AI21" s="67"/>
-      <c r="AJ21" s="67"/>
-      <c r="AK21" s="67"/>
-      <c r="AL21" s="69">
+      <c r="K21" s="72"/>
+      <c r="L21" s="72"/>
+      <c r="M21" s="72"/>
+      <c r="N21" s="69"/>
+      <c r="O21" s="69"/>
+      <c r="P21" s="69"/>
+      <c r="Q21" s="69"/>
+      <c r="R21" s="69"/>
+      <c r="S21" s="69"/>
+      <c r="T21" s="69"/>
+      <c r="U21" s="69"/>
+      <c r="V21" s="69"/>
+      <c r="W21" s="69"/>
+      <c r="X21" s="69"/>
+      <c r="Y21" s="69"/>
+      <c r="Z21" s="69"/>
+      <c r="AA21" s="69"/>
+      <c r="AB21" s="69"/>
+      <c r="AC21" s="69"/>
+      <c r="AD21" s="69"/>
+      <c r="AE21" s="69"/>
+      <c r="AF21" s="73" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG21" s="69"/>
+      <c r="AH21" s="69"/>
+      <c r="AI21" s="69"/>
+      <c r="AJ21" s="69"/>
+      <c r="AK21" s="69"/>
+      <c r="AL21" s="71">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="8:38">
-      <c r="H22" s="64">
-        <v>12</v>
-      </c>
-      <c r="I22" s="65" t="s">
+      <c r="H22" s="66">
+        <v>12</v>
+      </c>
+      <c r="I22" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="J22" s="66">
+      <c r="J22" s="68">
         <v>46215</v>
       </c>
-      <c r="K22" s="70"/>
-      <c r="L22" s="70"/>
-      <c r="M22" s="70"/>
-      <c r="N22" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="O22" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="P22" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q22" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="R22" s="67"/>
-      <c r="S22" s="67"/>
-      <c r="T22" s="67"/>
-      <c r="U22" s="67"/>
-      <c r="V22" s="67"/>
-      <c r="W22" s="67"/>
-      <c r="X22" s="67"/>
-      <c r="Y22" s="67"/>
-      <c r="Z22" s="67"/>
-      <c r="AA22" s="67"/>
-      <c r="AB22" s="67"/>
-      <c r="AC22" s="67"/>
-      <c r="AD22" s="67"/>
-      <c r="AE22" s="67"/>
-      <c r="AF22" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG22" s="67"/>
-      <c r="AH22" s="67"/>
-      <c r="AI22" s="67"/>
-      <c r="AJ22" s="67"/>
-      <c r="AK22" s="67"/>
-      <c r="AL22" s="69">
+      <c r="K22" s="72"/>
+      <c r="L22" s="72"/>
+      <c r="M22" s="72"/>
+      <c r="N22" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="O22" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="P22" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q22" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="R22" s="69"/>
+      <c r="S22" s="69"/>
+      <c r="T22" s="69"/>
+      <c r="U22" s="69"/>
+      <c r="V22" s="69"/>
+      <c r="W22" s="69"/>
+      <c r="X22" s="69"/>
+      <c r="Y22" s="69"/>
+      <c r="Z22" s="69"/>
+      <c r="AA22" s="69"/>
+      <c r="AB22" s="69"/>
+      <c r="AC22" s="69"/>
+      <c r="AD22" s="69"/>
+      <c r="AE22" s="69"/>
+      <c r="AF22" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG22" s="69"/>
+      <c r="AH22" s="69"/>
+      <c r="AI22" s="69"/>
+      <c r="AJ22" s="69"/>
+      <c r="AK22" s="69"/>
+      <c r="AL22" s="71">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
     <row r="23" spans="8:38">
-      <c r="H23" s="64">
+      <c r="H23" s="66">
         <v>13</v>
       </c>
-      <c r="I23" s="65" t="s">
+      <c r="I23" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="J23" s="66">
+      <c r="J23" s="68">
         <v>46216</v>
       </c>
-      <c r="K23" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="L23" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="M23" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="N23" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="O23" s="67"/>
-      <c r="P23" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q23" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="R23" s="67"/>
-      <c r="S23" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="T23" s="67"/>
-      <c r="U23" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="V23" s="67"/>
-      <c r="W23" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="X23" s="67"/>
-      <c r="Y23" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z23" s="67"/>
-      <c r="AA23" s="67"/>
-      <c r="AB23" s="67"/>
-      <c r="AC23" s="67"/>
-      <c r="AD23" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE23" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AF23" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG23" s="67"/>
-      <c r="AH23" s="67"/>
-      <c r="AI23" s="67"/>
-      <c r="AJ23" s="67"/>
-      <c r="AK23" s="67"/>
-      <c r="AL23" s="69">
+      <c r="K23" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="L23" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="M23" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="N23" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="O23" s="69"/>
+      <c r="P23" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q23" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="R23" s="69"/>
+      <c r="S23" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="T23" s="69"/>
+      <c r="U23" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="V23" s="69"/>
+      <c r="W23" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="X23" s="69"/>
+      <c r="Y23" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z23" s="69"/>
+      <c r="AA23" s="69"/>
+      <c r="AB23" s="69"/>
+      <c r="AC23" s="69"/>
+      <c r="AD23" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE23" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF23" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG23" s="69"/>
+      <c r="AH23" s="69"/>
+      <c r="AI23" s="69"/>
+      <c r="AJ23" s="69"/>
+      <c r="AK23" s="69"/>
+      <c r="AL23" s="71">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
     </row>
     <row r="24" spans="8:38">
-      <c r="H24" s="64">
+      <c r="H24" s="66">
         <v>14</v>
       </c>
-      <c r="I24" s="65" t="s">
+      <c r="I24" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="J24" s="66">
+      <c r="J24" s="68">
         <v>46217</v>
       </c>
-      <c r="K24" s="70"/>
-      <c r="L24" s="70"/>
-      <c r="M24" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="N24" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="O24" s="67"/>
-      <c r="P24" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q24" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="R24" s="67"/>
-      <c r="S24" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="T24" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="U24" s="67"/>
-      <c r="V24" s="67"/>
-      <c r="W24" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="X24" s="67"/>
-      <c r="Y24" s="67"/>
-      <c r="Z24" s="67"/>
-      <c r="AA24" s="67"/>
-      <c r="AB24" s="67"/>
-      <c r="AC24" s="67"/>
-      <c r="AD24" s="67"/>
-      <c r="AE24" s="67"/>
-      <c r="AF24" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG24" s="67"/>
-      <c r="AH24" s="67"/>
-      <c r="AI24" s="67"/>
-      <c r="AJ24" s="67"/>
-      <c r="AK24" s="67"/>
-      <c r="AL24" s="69">
+      <c r="K24" s="72"/>
+      <c r="L24" s="72"/>
+      <c r="M24" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="N24" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="O24" s="69"/>
+      <c r="P24" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q24" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="R24" s="69"/>
+      <c r="S24" s="73" t="s">
+        <v>12</v>
+      </c>
+      <c r="T24" s="73" t="s">
+        <v>12</v>
+      </c>
+      <c r="U24" s="69"/>
+      <c r="V24" s="69"/>
+      <c r="W24" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="X24" s="69"/>
+      <c r="Y24" s="69"/>
+      <c r="Z24" s="69"/>
+      <c r="AA24" s="69"/>
+      <c r="AB24" s="69"/>
+      <c r="AC24" s="69"/>
+      <c r="AD24" s="69"/>
+      <c r="AE24" s="69"/>
+      <c r="AF24" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG24" s="69"/>
+      <c r="AH24" s="69"/>
+      <c r="AI24" s="69"/>
+      <c r="AJ24" s="69"/>
+      <c r="AK24" s="69"/>
+      <c r="AL24" s="71">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
     <row r="25" spans="8:38">
-      <c r="H25" s="64">
+      <c r="H25" s="66">
         <v>15</v>
       </c>
-      <c r="I25" s="65" t="s">
+      <c r="I25" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="J25" s="66">
+      <c r="J25" s="68">
         <v>46218</v>
       </c>
-      <c r="K25" s="70"/>
-      <c r="L25" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="M25" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="N25" s="67"/>
-      <c r="O25" s="67"/>
-      <c r="P25" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q25" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="R25" s="67"/>
-      <c r="S25" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="T25" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="U25" s="67"/>
-      <c r="V25" s="67"/>
-      <c r="W25" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="X25" s="67"/>
-      <c r="Y25" s="67"/>
-      <c r="Z25" s="67"/>
-      <c r="AA25" s="67"/>
-      <c r="AB25" s="67"/>
-      <c r="AC25" s="67"/>
-      <c r="AD25" s="67"/>
-      <c r="AE25" s="67"/>
-      <c r="AF25" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG25" s="67"/>
-      <c r="AH25" s="67"/>
-      <c r="AI25" s="67"/>
-      <c r="AJ25" s="67"/>
-      <c r="AK25" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AL25" s="69">
+      <c r="K25" s="72"/>
+      <c r="L25" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="M25" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="N25" s="69"/>
+      <c r="O25" s="69"/>
+      <c r="P25" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q25" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="R25" s="69"/>
+      <c r="S25" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="T25" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="U25" s="69"/>
+      <c r="V25" s="69"/>
+      <c r="W25" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="X25" s="69"/>
+      <c r="Y25" s="69"/>
+      <c r="Z25" s="69"/>
+      <c r="AA25" s="69"/>
+      <c r="AB25" s="69"/>
+      <c r="AC25" s="69"/>
+      <c r="AD25" s="69"/>
+      <c r="AE25" s="69"/>
+      <c r="AF25" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG25" s="69"/>
+      <c r="AH25" s="69"/>
+      <c r="AI25" s="69"/>
+      <c r="AJ25" s="69"/>
+      <c r="AK25" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL25" s="71">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
     <row r="26" spans="8:38">
-      <c r="H26" s="64">
+      <c r="H26" s="66">
         <v>16</v>
       </c>
-      <c r="I26" s="65" t="s">
+      <c r="I26" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="J26" s="66">
+      <c r="J26" s="68">
         <v>46219</v>
       </c>
-      <c r="K26" s="70"/>
-      <c r="L26" s="70"/>
-      <c r="M26" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="N26" s="67"/>
-      <c r="O26" s="67"/>
-      <c r="P26" s="67"/>
-      <c r="Q26" s="67"/>
-      <c r="R26" s="67"/>
-      <c r="S26" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="T26" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="U26" s="67"/>
-      <c r="V26" s="67"/>
-      <c r="W26" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="X26" s="67"/>
-      <c r="Y26" s="67"/>
-      <c r="Z26" s="67"/>
-      <c r="AA26" s="67"/>
-      <c r="AB26" s="67"/>
-      <c r="AC26" s="67"/>
-      <c r="AD26" s="67"/>
-      <c r="AE26" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AF26" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG26" s="67"/>
-      <c r="AH26" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AI26" s="67"/>
-      <c r="AJ26" s="67"/>
-      <c r="AK26" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AL26" s="69">
+      <c r="K26" s="72"/>
+      <c r="L26" s="72"/>
+      <c r="M26" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="N26" s="69"/>
+      <c r="O26" s="69"/>
+      <c r="P26" s="69"/>
+      <c r="Q26" s="69"/>
+      <c r="R26" s="69"/>
+      <c r="S26" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="T26" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="U26" s="69"/>
+      <c r="V26" s="69"/>
+      <c r="W26" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="X26" s="69"/>
+      <c r="Y26" s="69"/>
+      <c r="Z26" s="69"/>
+      <c r="AA26" s="69"/>
+      <c r="AB26" s="69"/>
+      <c r="AC26" s="69"/>
+      <c r="AD26" s="69"/>
+      <c r="AE26" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF26" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG26" s="69"/>
+      <c r="AH26" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="AI26" s="69"/>
+      <c r="AJ26" s="69"/>
+      <c r="AK26" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL26" s="71">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
     <row r="27" spans="8:38">
-      <c r="H27" s="64">
+      <c r="H27" s="66">
         <v>17</v>
       </c>
-      <c r="I27" s="65" t="s">
+      <c r="I27" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="J27" s="66">
+      <c r="J27" s="68">
         <v>46220</v>
       </c>
-      <c r="K27" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="L27" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="M27" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="N27" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="O27" s="67"/>
-      <c r="P27" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q27" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="R27" s="67"/>
-      <c r="S27" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="T27" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="U27" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="V27" s="67"/>
-      <c r="W27" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="X27" s="67"/>
-      <c r="Y27" s="67"/>
-      <c r="Z27" s="67"/>
-      <c r="AA27" s="67"/>
-      <c r="AB27" s="67"/>
-      <c r="AC27" s="67"/>
-      <c r="AD27" s="67"/>
-      <c r="AE27" s="67"/>
-      <c r="AF27" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG27" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AH27" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AI27" s="67"/>
-      <c r="AJ27" s="67"/>
-      <c r="AK27" s="67"/>
-      <c r="AL27" s="69">
+      <c r="K27" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="L27" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="M27" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="N27" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="O27" s="69"/>
+      <c r="P27" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q27" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="R27" s="69"/>
+      <c r="S27" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="T27" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="U27" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="V27" s="69"/>
+      <c r="W27" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="X27" s="69"/>
+      <c r="Y27" s="69"/>
+      <c r="Z27" s="69"/>
+      <c r="AA27" s="69"/>
+      <c r="AB27" s="69"/>
+      <c r="AC27" s="69"/>
+      <c r="AD27" s="69"/>
+      <c r="AE27" s="69"/>
+      <c r="AF27" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG27" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="AH27" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="AI27" s="69"/>
+      <c r="AJ27" s="69"/>
+      <c r="AK27" s="69"/>
+      <c r="AL27" s="71">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
     </row>
     <row r="28" spans="8:38">
-      <c r="H28" s="64">
+      <c r="H28" s="66">
         <v>18</v>
       </c>
-      <c r="I28" s="65" t="s">
+      <c r="I28" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="J28" s="66">
+      <c r="J28" s="68">
         <v>46221</v>
       </c>
-      <c r="K28" s="70"/>
-      <c r="L28" s="70"/>
-      <c r="M28" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="N28" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="O28" s="67"/>
-      <c r="P28" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q28" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="R28" s="67"/>
-      <c r="S28" s="67"/>
-      <c r="T28" s="67"/>
-      <c r="U28" s="67"/>
-      <c r="V28" s="67"/>
-      <c r="W28" s="67"/>
-      <c r="X28" s="67"/>
-      <c r="Y28" s="67"/>
-      <c r="Z28" s="67"/>
-      <c r="AA28" s="67"/>
-      <c r="AB28" s="67"/>
-      <c r="AC28" s="67"/>
-      <c r="AD28" s="67"/>
-      <c r="AE28" s="67"/>
-      <c r="AF28" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG28" s="67"/>
-      <c r="AH28" s="67"/>
-      <c r="AI28" s="67"/>
-      <c r="AJ28" s="67"/>
-      <c r="AK28" s="67"/>
-      <c r="AL28" s="69">
+      <c r="K28" s="72"/>
+      <c r="L28" s="72"/>
+      <c r="M28" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="N28" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="O28" s="69"/>
+      <c r="P28" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q28" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="R28" s="69"/>
+      <c r="S28" s="69"/>
+      <c r="T28" s="69"/>
+      <c r="U28" s="69"/>
+      <c r="V28" s="69"/>
+      <c r="W28" s="69"/>
+      <c r="X28" s="69"/>
+      <c r="Y28" s="69"/>
+      <c r="Z28" s="69"/>
+      <c r="AA28" s="69"/>
+      <c r="AB28" s="69"/>
+      <c r="AC28" s="69"/>
+      <c r="AD28" s="69"/>
+      <c r="AE28" s="69"/>
+      <c r="AF28" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG28" s="69"/>
+      <c r="AH28" s="69"/>
+      <c r="AI28" s="69"/>
+      <c r="AJ28" s="69"/>
+      <c r="AK28" s="69"/>
+      <c r="AL28" s="71">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
     <row r="29" spans="8:38">
-      <c r="H29" s="64">
+      <c r="H29" s="66">
         <v>19</v>
       </c>
-      <c r="I29" s="65" t="s">
+      <c r="I29" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="J29" s="66">
+      <c r="J29" s="68">
         <v>46222</v>
       </c>
-      <c r="K29" s="70"/>
-      <c r="L29" s="70"/>
-      <c r="M29" s="70"/>
-      <c r="N29" s="67"/>
-      <c r="O29" s="67"/>
-      <c r="P29" s="67"/>
-      <c r="Q29" s="67"/>
-      <c r="R29" s="67"/>
-      <c r="S29" s="67"/>
-      <c r="T29" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="U29" s="67"/>
-      <c r="V29" s="67"/>
-      <c r="W29" s="67"/>
-      <c r="X29" s="67"/>
-      <c r="Y29" s="67"/>
-      <c r="Z29" s="67"/>
-      <c r="AA29" s="67"/>
-      <c r="AB29" s="67"/>
-      <c r="AC29" s="67"/>
-      <c r="AD29" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE29" s="67"/>
-      <c r="AF29" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG29" s="67"/>
-      <c r="AH29" s="67"/>
-      <c r="AI29" s="67"/>
-      <c r="AJ29" s="67"/>
-      <c r="AK29" s="67"/>
-      <c r="AL29" s="69">
+      <c r="K29" s="72"/>
+      <c r="L29" s="72"/>
+      <c r="M29" s="72"/>
+      <c r="N29" s="69"/>
+      <c r="O29" s="69"/>
+      <c r="P29" s="69"/>
+      <c r="Q29" s="69"/>
+      <c r="R29" s="69"/>
+      <c r="S29" s="69"/>
+      <c r="T29" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="U29" s="69"/>
+      <c r="V29" s="69"/>
+      <c r="W29" s="69"/>
+      <c r="X29" s="69"/>
+      <c r="Y29" s="69"/>
+      <c r="Z29" s="69"/>
+      <c r="AA29" s="69"/>
+      <c r="AB29" s="69"/>
+      <c r="AC29" s="69"/>
+      <c r="AD29" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE29" s="69"/>
+      <c r="AF29" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG29" s="69"/>
+      <c r="AH29" s="69"/>
+      <c r="AI29" s="69"/>
+      <c r="AJ29" s="69"/>
+      <c r="AK29" s="69"/>
+      <c r="AL29" s="71">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="30" spans="8:38">
-      <c r="H30" s="64">
+      <c r="H30" s="66">
         <v>20</v>
       </c>
-      <c r="I30" s="65" t="s">
+      <c r="I30" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="J30" s="66">
+      <c r="J30" s="68">
         <v>46223</v>
       </c>
-      <c r="K30" s="70"/>
-      <c r="L30" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="M30" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="N30" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="O30" s="67"/>
-      <c r="P30" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q30" s="67"/>
-      <c r="R30" s="67"/>
-      <c r="S30" s="67"/>
-      <c r="T30" s="67"/>
-      <c r="U30" s="67"/>
-      <c r="V30" s="67"/>
-      <c r="W30" s="67"/>
-      <c r="X30" s="67"/>
-      <c r="Y30" s="67"/>
-      <c r="Z30" s="67"/>
-      <c r="AA30" s="67"/>
-      <c r="AB30" s="67"/>
-      <c r="AC30" s="67"/>
-      <c r="AD30" s="67"/>
-      <c r="AE30" s="67"/>
-      <c r="AF30" s="67"/>
-      <c r="AG30" s="67"/>
-      <c r="AH30" s="67"/>
-      <c r="AI30" s="67"/>
-      <c r="AJ30" s="67"/>
-      <c r="AK30" s="67"/>
-      <c r="AL30" s="69">
+      <c r="K30" s="72"/>
+      <c r="L30" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="M30" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="N30" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="O30" s="69"/>
+      <c r="P30" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q30" s="69"/>
+      <c r="R30" s="69"/>
+      <c r="S30" s="69"/>
+      <c r="T30" s="69"/>
+      <c r="U30" s="69"/>
+      <c r="V30" s="69"/>
+      <c r="W30" s="69"/>
+      <c r="X30" s="69"/>
+      <c r="Y30" s="69"/>
+      <c r="Z30" s="69"/>
+      <c r="AA30" s="69"/>
+      <c r="AB30" s="69"/>
+      <c r="AC30" s="69"/>
+      <c r="AD30" s="69"/>
+      <c r="AE30" s="69"/>
+      <c r="AF30" s="69"/>
+      <c r="AG30" s="69"/>
+      <c r="AH30" s="69"/>
+      <c r="AI30" s="69"/>
+      <c r="AJ30" s="69"/>
+      <c r="AK30" s="69"/>
+      <c r="AL30" s="71">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="31" spans="8:38">
-      <c r="H31" s="64">
+      <c r="H31" s="66">
         <v>21</v>
       </c>
-      <c r="I31" s="65" t="s">
+      <c r="I31" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="J31" s="66">
+      <c r="J31" s="68">
         <v>46224</v>
       </c>
-      <c r="K31" s="70"/>
-      <c r="L31" s="70"/>
-      <c r="M31" s="70"/>
-      <c r="N31" s="67"/>
-      <c r="O31" s="67"/>
-      <c r="P31" s="67"/>
-      <c r="Q31" s="67"/>
-      <c r="R31" s="67"/>
-      <c r="S31" s="67"/>
-      <c r="T31" s="67"/>
-      <c r="U31" s="67"/>
-      <c r="V31" s="67"/>
-      <c r="W31" s="67"/>
-      <c r="X31" s="67"/>
-      <c r="Y31" s="67"/>
-      <c r="Z31" s="67"/>
-      <c r="AA31" s="67"/>
-      <c r="AB31" s="67"/>
-      <c r="AC31" s="67"/>
-      <c r="AD31" s="67"/>
-      <c r="AE31" s="67"/>
-      <c r="AF31" s="67"/>
-      <c r="AG31" s="67"/>
-      <c r="AH31" s="67"/>
-      <c r="AI31" s="67"/>
-      <c r="AJ31" s="67"/>
-      <c r="AK31" s="67"/>
-      <c r="AL31" s="69">
+      <c r="K31" s="72"/>
+      <c r="L31" s="72"/>
+      <c r="M31" s="72"/>
+      <c r="N31" s="69"/>
+      <c r="O31" s="69"/>
+      <c r="P31" s="69"/>
+      <c r="Q31" s="69"/>
+      <c r="R31" s="69"/>
+      <c r="S31" s="69"/>
+      <c r="T31" s="69"/>
+      <c r="U31" s="69"/>
+      <c r="V31" s="69"/>
+      <c r="W31" s="69"/>
+      <c r="X31" s="69"/>
+      <c r="Y31" s="69"/>
+      <c r="Z31" s="69"/>
+      <c r="AA31" s="69"/>
+      <c r="AB31" s="69"/>
+      <c r="AC31" s="69"/>
+      <c r="AD31" s="69"/>
+      <c r="AE31" s="69"/>
+      <c r="AF31" s="69"/>
+      <c r="AG31" s="69"/>
+      <c r="AH31" s="69"/>
+      <c r="AI31" s="69"/>
+      <c r="AJ31" s="69"/>
+      <c r="AK31" s="69"/>
+      <c r="AL31" s="71">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="8:38">
-      <c r="H32" s="64">
+      <c r="H32" s="66">
         <v>22</v>
       </c>
-      <c r="I32" s="65" t="s">
+      <c r="I32" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="J32" s="66">
+      <c r="J32" s="68">
         <v>46225</v>
       </c>
-      <c r="K32" s="70"/>
-      <c r="L32" s="70"/>
-      <c r="M32" s="70"/>
-      <c r="N32" s="67"/>
-      <c r="O32" s="67"/>
-      <c r="P32" s="67"/>
-      <c r="Q32" s="67"/>
-      <c r="R32" s="67"/>
-      <c r="S32" s="67"/>
-      <c r="T32" s="67"/>
-      <c r="U32" s="67"/>
-      <c r="V32" s="67"/>
-      <c r="W32" s="67"/>
-      <c r="X32" s="67"/>
-      <c r="Y32" s="67"/>
-      <c r="Z32" s="67"/>
-      <c r="AA32" s="67"/>
-      <c r="AB32" s="67"/>
-      <c r="AC32" s="67"/>
-      <c r="AD32" s="67"/>
-      <c r="AE32" s="67"/>
-      <c r="AF32" s="67"/>
-      <c r="AG32" s="67"/>
-      <c r="AH32" s="67"/>
-      <c r="AI32" s="67"/>
-      <c r="AJ32" s="67"/>
-      <c r="AK32" s="67"/>
-      <c r="AL32" s="69">
+      <c r="K32" s="72"/>
+      <c r="L32" s="72"/>
+      <c r="M32" s="72"/>
+      <c r="N32" s="69"/>
+      <c r="O32" s="69"/>
+      <c r="P32" s="69"/>
+      <c r="Q32" s="69"/>
+      <c r="R32" s="69"/>
+      <c r="S32" s="69"/>
+      <c r="T32" s="69"/>
+      <c r="U32" s="69"/>
+      <c r="V32" s="69"/>
+      <c r="W32" s="69"/>
+      <c r="X32" s="69"/>
+      <c r="Y32" s="69"/>
+      <c r="Z32" s="69"/>
+      <c r="AA32" s="69"/>
+      <c r="AB32" s="69"/>
+      <c r="AC32" s="69"/>
+      <c r="AD32" s="69"/>
+      <c r="AE32" s="69"/>
+      <c r="AF32" s="69"/>
+      <c r="AG32" s="69"/>
+      <c r="AH32" s="69"/>
+      <c r="AI32" s="69"/>
+      <c r="AJ32" s="69"/>
+      <c r="AK32" s="69"/>
+      <c r="AL32" s="71">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="8:38">
-      <c r="H33" s="64">
+      <c r="H33" s="66">
         <v>23</v>
       </c>
-      <c r="I33" s="65" t="s">
+      <c r="I33" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="J33" s="66">
+      <c r="J33" s="68">
         <v>46226</v>
       </c>
-      <c r="K33" s="70"/>
-      <c r="L33" s="70"/>
-      <c r="M33" s="70"/>
-      <c r="N33" s="67"/>
-      <c r="O33" s="67"/>
-      <c r="P33" s="67"/>
-      <c r="Q33" s="67"/>
-      <c r="R33" s="67"/>
-      <c r="S33" s="67"/>
-      <c r="T33" s="67"/>
-      <c r="U33" s="67"/>
-      <c r="V33" s="67"/>
-      <c r="W33" s="67"/>
-      <c r="X33" s="67"/>
-      <c r="Y33" s="67"/>
-      <c r="Z33" s="67"/>
-      <c r="AA33" s="67"/>
-      <c r="AB33" s="67"/>
-      <c r="AC33" s="67"/>
-      <c r="AD33" s="67"/>
-      <c r="AE33" s="67"/>
-      <c r="AF33" s="67"/>
-      <c r="AG33" s="67"/>
-      <c r="AH33" s="67"/>
-      <c r="AI33" s="67"/>
-      <c r="AJ33" s="67"/>
-      <c r="AK33" s="67"/>
-      <c r="AL33" s="69">
+      <c r="K33" s="72"/>
+      <c r="L33" s="72"/>
+      <c r="M33" s="72"/>
+      <c r="N33" s="69"/>
+      <c r="O33" s="69"/>
+      <c r="P33" s="69"/>
+      <c r="Q33" s="69"/>
+      <c r="R33" s="69"/>
+      <c r="S33" s="69"/>
+      <c r="T33" s="69"/>
+      <c r="U33" s="69"/>
+      <c r="V33" s="69"/>
+      <c r="W33" s="69"/>
+      <c r="X33" s="69"/>
+      <c r="Y33" s="69"/>
+      <c r="Z33" s="69"/>
+      <c r="AA33" s="69"/>
+      <c r="AB33" s="69"/>
+      <c r="AC33" s="69"/>
+      <c r="AD33" s="69"/>
+      <c r="AE33" s="69"/>
+      <c r="AF33" s="69"/>
+      <c r="AG33" s="69"/>
+      <c r="AH33" s="69"/>
+      <c r="AI33" s="69"/>
+      <c r="AJ33" s="69"/>
+      <c r="AK33" s="69"/>
+      <c r="AL33" s="71">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="8:38">
-      <c r="H34" s="64">
+      <c r="H34" s="66">
         <v>24</v>
       </c>
-      <c r="I34" s="65" t="s">
+      <c r="I34" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="J34" s="66">
+      <c r="J34" s="68">
         <v>46227</v>
       </c>
-      <c r="K34" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="L34" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="M34" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="N34" s="67"/>
-      <c r="O34" s="67"/>
-      <c r="P34" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q34" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="R34" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="S34" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="T34" s="67"/>
-      <c r="U34" s="67"/>
-      <c r="V34" s="67"/>
-      <c r="W34" s="67"/>
-      <c r="X34" s="67"/>
-      <c r="Y34" s="67"/>
-      <c r="Z34" s="67"/>
-      <c r="AA34" s="67"/>
-      <c r="AB34" s="67"/>
-      <c r="AC34" s="67"/>
-      <c r="AD34" s="67"/>
-      <c r="AE34" s="67"/>
-      <c r="AF34" s="67"/>
-      <c r="AG34" s="67"/>
-      <c r="AH34" s="67"/>
-      <c r="AI34" s="67"/>
-      <c r="AJ34" s="67"/>
-      <c r="AK34" s="67"/>
-      <c r="AL34" s="69">
+      <c r="K34" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="L34" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="M34" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="N34" s="69"/>
+      <c r="O34" s="69"/>
+      <c r="P34" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q34" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="R34" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="S34" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="T34" s="69"/>
+      <c r="U34" s="69"/>
+      <c r="V34" s="69"/>
+      <c r="W34" s="69"/>
+      <c r="X34" s="69"/>
+      <c r="Y34" s="69"/>
+      <c r="Z34" s="69"/>
+      <c r="AA34" s="69"/>
+      <c r="AB34" s="69"/>
+      <c r="AC34" s="69"/>
+      <c r="AD34" s="69"/>
+      <c r="AE34" s="69"/>
+      <c r="AF34" s="69"/>
+      <c r="AG34" s="69"/>
+      <c r="AH34" s="69"/>
+      <c r="AI34" s="69"/>
+      <c r="AJ34" s="69"/>
+      <c r="AK34" s="69"/>
+      <c r="AL34" s="71">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
     <row r="35" spans="8:38">
-      <c r="H35" s="64">
+      <c r="H35" s="66">
         <v>25</v>
       </c>
-      <c r="I35" s="65" t="s">
+      <c r="I35" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="J35" s="66">
+      <c r="J35" s="68">
         <v>46228</v>
       </c>
-      <c r="K35" s="70"/>
-      <c r="L35" s="70"/>
-      <c r="M35" s="70"/>
-      <c r="N35" s="67"/>
-      <c r="O35" s="67"/>
-      <c r="P35" s="67"/>
-      <c r="Q35" s="67"/>
-      <c r="R35" s="67"/>
-      <c r="S35" s="67"/>
-      <c r="T35" s="67"/>
-      <c r="U35" s="67"/>
-      <c r="V35" s="67"/>
-      <c r="W35" s="67"/>
-      <c r="X35" s="67"/>
-      <c r="Y35" s="67"/>
-      <c r="Z35" s="67"/>
-      <c r="AA35" s="67"/>
-      <c r="AB35" s="67"/>
-      <c r="AC35" s="67"/>
-      <c r="AD35" s="67"/>
-      <c r="AE35" s="67"/>
-      <c r="AF35" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG35" s="67"/>
-      <c r="AH35" s="67"/>
-      <c r="AI35" s="67"/>
-      <c r="AJ35" s="67"/>
-      <c r="AK35" s="67"/>
-      <c r="AL35" s="69">
+      <c r="K35" s="72"/>
+      <c r="L35" s="72"/>
+      <c r="M35" s="72"/>
+      <c r="N35" s="69"/>
+      <c r="O35" s="69"/>
+      <c r="P35" s="69"/>
+      <c r="Q35" s="69"/>
+      <c r="R35" s="69"/>
+      <c r="S35" s="69"/>
+      <c r="T35" s="69"/>
+      <c r="U35" s="69"/>
+      <c r="V35" s="69"/>
+      <c r="W35" s="69"/>
+      <c r="X35" s="69"/>
+      <c r="Y35" s="69"/>
+      <c r="Z35" s="69"/>
+      <c r="AA35" s="69"/>
+      <c r="AB35" s="69"/>
+      <c r="AC35" s="69"/>
+      <c r="AD35" s="69"/>
+      <c r="AE35" s="69"/>
+      <c r="AF35" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG35" s="69"/>
+      <c r="AH35" s="69"/>
+      <c r="AI35" s="69"/>
+      <c r="AJ35" s="69"/>
+      <c r="AK35" s="69"/>
+      <c r="AL35" s="71">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="8:38">
-      <c r="H36" s="64">
+      <c r="H36" s="66">
         <v>26</v>
       </c>
-      <c r="I36" s="65" t="s">
+      <c r="I36" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="J36" s="66">
+      <c r="J36" s="68">
         <v>46229</v>
       </c>
-      <c r="K36" s="70"/>
-      <c r="L36" s="70"/>
-      <c r="M36" s="70"/>
-      <c r="N36" s="67"/>
-      <c r="O36" s="67"/>
-      <c r="P36" s="67"/>
-      <c r="Q36" s="67"/>
-      <c r="R36" s="67"/>
-      <c r="S36" s="67"/>
-      <c r="T36" s="67"/>
-      <c r="U36" s="67"/>
-      <c r="V36" s="67"/>
-      <c r="W36" s="67"/>
-      <c r="X36" s="67"/>
-      <c r="Y36" s="67"/>
-      <c r="Z36" s="67"/>
-      <c r="AA36" s="67"/>
-      <c r="AB36" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AC36" s="67"/>
-      <c r="AD36" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE36" s="67"/>
-      <c r="AF36" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG36" s="67"/>
-      <c r="AH36" s="67"/>
-      <c r="AI36" s="67"/>
-      <c r="AJ36" s="67"/>
-      <c r="AK36" s="67"/>
-      <c r="AL36" s="69">
+      <c r="K36" s="72"/>
+      <c r="L36" s="72"/>
+      <c r="M36" s="72"/>
+      <c r="N36" s="69"/>
+      <c r="O36" s="69"/>
+      <c r="P36" s="69"/>
+      <c r="Q36" s="69"/>
+      <c r="R36" s="69"/>
+      <c r="S36" s="69"/>
+      <c r="T36" s="69"/>
+      <c r="U36" s="69"/>
+      <c r="V36" s="69"/>
+      <c r="W36" s="69"/>
+      <c r="X36" s="69"/>
+      <c r="Y36" s="69"/>
+      <c r="Z36" s="69"/>
+      <c r="AA36" s="69"/>
+      <c r="AB36" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC36" s="69"/>
+      <c r="AD36" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE36" s="69"/>
+      <c r="AF36" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG36" s="69"/>
+      <c r="AH36" s="69"/>
+      <c r="AI36" s="69"/>
+      <c r="AJ36" s="69"/>
+      <c r="AK36" s="69"/>
+      <c r="AL36" s="71">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="37" spans="8:38">
-      <c r="H37" s="64">
+      <c r="H37" s="66">
         <v>27</v>
       </c>
-      <c r="I37" s="65" t="s">
+      <c r="I37" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="J37" s="66">
+      <c r="J37" s="68">
         <v>46230</v>
       </c>
-      <c r="K37" s="70"/>
-      <c r="L37" s="70"/>
-      <c r="M37" s="70"/>
-      <c r="N37" s="67"/>
-      <c r="O37" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="P37" s="67"/>
-      <c r="Q37" s="67"/>
-      <c r="R37" s="67"/>
-      <c r="S37" s="67"/>
-      <c r="T37" s="67"/>
-      <c r="U37" s="67"/>
-      <c r="V37" s="67"/>
-      <c r="W37" s="67"/>
-      <c r="X37" s="67"/>
-      <c r="Y37" s="67"/>
-      <c r="Z37" s="67"/>
-      <c r="AA37" s="67"/>
-      <c r="AB37" s="67"/>
-      <c r="AC37" s="67"/>
-      <c r="AD37" s="67"/>
-      <c r="AE37" s="67"/>
-      <c r="AF37" s="67"/>
-      <c r="AG37" s="67"/>
-      <c r="AH37" s="67"/>
-      <c r="AI37" s="67"/>
-      <c r="AJ37" s="67"/>
-      <c r="AK37" s="67"/>
-      <c r="AL37" s="69">
+      <c r="K37" s="72"/>
+      <c r="L37" s="72"/>
+      <c r="M37" s="72"/>
+      <c r="N37" s="69"/>
+      <c r="O37" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="P37" s="69"/>
+      <c r="Q37" s="69"/>
+      <c r="R37" s="69"/>
+      <c r="S37" s="69"/>
+      <c r="T37" s="69"/>
+      <c r="U37" s="69"/>
+      <c r="V37" s="69"/>
+      <c r="W37" s="69"/>
+      <c r="X37" s="69"/>
+      <c r="Y37" s="69"/>
+      <c r="Z37" s="69"/>
+      <c r="AA37" s="69"/>
+      <c r="AB37" s="69"/>
+      <c r="AC37" s="69"/>
+      <c r="AD37" s="69"/>
+      <c r="AE37" s="69"/>
+      <c r="AF37" s="69"/>
+      <c r="AG37" s="69"/>
+      <c r="AH37" s="69"/>
+      <c r="AI37" s="69"/>
+      <c r="AJ37" s="69"/>
+      <c r="AK37" s="69"/>
+      <c r="AL37" s="71">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="8:38">
-      <c r="H38" s="64">
+      <c r="H38" s="66">
         <v>28</v>
       </c>
-      <c r="I38" s="65" t="s">
+      <c r="I38" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="J38" s="66">
+      <c r="J38" s="68">
         <v>46231</v>
       </c>
-      <c r="K38" s="70"/>
-      <c r="L38" s="70"/>
-      <c r="M38" s="70"/>
-      <c r="N38" s="67"/>
-      <c r="O38" s="67"/>
-      <c r="P38" s="67"/>
-      <c r="Q38" s="67"/>
-      <c r="R38" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="S38" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="T38" s="67"/>
-      <c r="U38" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="V38" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="W38" s="67"/>
-      <c r="X38" s="67"/>
-      <c r="Y38" s="67"/>
-      <c r="Z38" s="67"/>
-      <c r="AA38" s="67"/>
-      <c r="AB38" s="67"/>
-      <c r="AC38" s="67"/>
-      <c r="AD38" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE38" s="67"/>
-      <c r="AF38" s="67"/>
-      <c r="AG38" s="67"/>
-      <c r="AH38" s="67"/>
-      <c r="AI38" s="67"/>
-      <c r="AJ38" s="67"/>
-      <c r="AK38" s="67"/>
-      <c r="AL38" s="69">
+      <c r="K38" s="72"/>
+      <c r="L38" s="72"/>
+      <c r="M38" s="72"/>
+      <c r="N38" s="69"/>
+      <c r="O38" s="69"/>
+      <c r="P38" s="69"/>
+      <c r="Q38" s="69"/>
+      <c r="R38" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="S38" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="T38" s="69"/>
+      <c r="U38" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="V38" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="W38" s="69"/>
+      <c r="X38" s="69"/>
+      <c r="Y38" s="69"/>
+      <c r="Z38" s="69"/>
+      <c r="AA38" s="69"/>
+      <c r="AB38" s="69"/>
+      <c r="AC38" s="69"/>
+      <c r="AD38" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE38" s="69"/>
+      <c r="AF38" s="69"/>
+      <c r="AG38" s="69"/>
+      <c r="AH38" s="69"/>
+      <c r="AI38" s="69"/>
+      <c r="AJ38" s="69"/>
+      <c r="AK38" s="69"/>
+      <c r="AL38" s="71">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
     <row r="39" spans="8:38">
-      <c r="H39" s="64">
+      <c r="H39" s="66">
         <v>29</v>
       </c>
-      <c r="I39" s="65" t="s">
+      <c r="I39" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="J39" s="66">
+      <c r="J39" s="68">
         <v>46232</v>
       </c>
-      <c r="K39" s="70"/>
-      <c r="L39" s="70"/>
-      <c r="M39" s="70"/>
-      <c r="N39" s="67"/>
-      <c r="O39" s="67"/>
-      <c r="P39" s="67"/>
-      <c r="Q39" s="67"/>
-      <c r="R39" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="S39" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="T39" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="U39" s="67"/>
-      <c r="V39" s="67"/>
-      <c r="W39" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="X39" s="67"/>
-      <c r="Y39" s="67"/>
-      <c r="Z39" s="67"/>
-      <c r="AA39" s="67"/>
-      <c r="AB39" s="67"/>
-      <c r="AC39" s="67"/>
-      <c r="AD39" s="67"/>
-      <c r="AE39" s="67"/>
-      <c r="AF39" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG39" s="67"/>
-      <c r="AH39" s="67"/>
-      <c r="AI39" s="67"/>
-      <c r="AJ39" s="67"/>
-      <c r="AK39" s="67"/>
-      <c r="AL39" s="69">
+      <c r="K39" s="72"/>
+      <c r="L39" s="72"/>
+      <c r="M39" s="72"/>
+      <c r="N39" s="69"/>
+      <c r="O39" s="69"/>
+      <c r="P39" s="69"/>
+      <c r="Q39" s="69"/>
+      <c r="R39" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="S39" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="T39" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="U39" s="69"/>
+      <c r="V39" s="69"/>
+      <c r="W39" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="X39" s="69"/>
+      <c r="Y39" s="69"/>
+      <c r="Z39" s="69"/>
+      <c r="AA39" s="69"/>
+      <c r="AB39" s="69"/>
+      <c r="AC39" s="69"/>
+      <c r="AD39" s="69"/>
+      <c r="AE39" s="69"/>
+      <c r="AF39" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG39" s="69"/>
+      <c r="AH39" s="69"/>
+      <c r="AI39" s="69"/>
+      <c r="AJ39" s="69"/>
+      <c r="AK39" s="69"/>
+      <c r="AL39" s="71">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
     <row r="40" spans="8:38">
-      <c r="H40" s="64">
+      <c r="H40" s="66">
         <v>30</v>
       </c>
-      <c r="I40" s="65" t="s">
+      <c r="I40" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="J40" s="66">
+      <c r="J40" s="68">
         <v>46233</v>
       </c>
-      <c r="K40" s="70"/>
-      <c r="L40" s="70"/>
-      <c r="M40" s="70"/>
-      <c r="N40" s="67"/>
-      <c r="O40" s="67"/>
-      <c r="P40" s="67"/>
-      <c r="Q40" s="67"/>
-      <c r="R40" s="67"/>
-      <c r="S40" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="T40" s="67"/>
-      <c r="U40" s="67"/>
-      <c r="V40" s="67"/>
-      <c r="W40" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="X40" s="67"/>
-      <c r="Y40" s="67"/>
-      <c r="Z40" s="67"/>
-      <c r="AA40" s="67"/>
-      <c r="AB40" s="67"/>
-      <c r="AC40" s="67"/>
-      <c r="AD40" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE40" s="67"/>
-      <c r="AF40" s="67"/>
-      <c r="AG40" s="67"/>
-      <c r="AH40" s="67"/>
-      <c r="AI40" s="67"/>
-      <c r="AJ40" s="67"/>
-      <c r="AK40" s="67"/>
-      <c r="AL40" s="69">
+      <c r="K40" s="72"/>
+      <c r="L40" s="72"/>
+      <c r="M40" s="72"/>
+      <c r="N40" s="69"/>
+      <c r="O40" s="69"/>
+      <c r="P40" s="69"/>
+      <c r="Q40" s="69"/>
+      <c r="R40" s="69"/>
+      <c r="S40" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="T40" s="69"/>
+      <c r="U40" s="69"/>
+      <c r="V40" s="69"/>
+      <c r="W40" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="X40" s="69"/>
+      <c r="Y40" s="69"/>
+      <c r="Z40" s="69"/>
+      <c r="AA40" s="69"/>
+      <c r="AB40" s="69"/>
+      <c r="AC40" s="69"/>
+      <c r="AD40" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE40" s="69"/>
+      <c r="AF40" s="69"/>
+      <c r="AG40" s="69"/>
+      <c r="AH40" s="69"/>
+      <c r="AI40" s="69"/>
+      <c r="AJ40" s="69"/>
+      <c r="AK40" s="69"/>
+      <c r="AL40" s="71">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
     <row r="41" spans="8:38">
-      <c r="H41" s="64">
+      <c r="H41" s="66">
         <v>31</v>
       </c>
-      <c r="I41" s="65" t="s">
+      <c r="I41" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="J41" s="66">
+      <c r="J41" s="68">
         <v>46234</v>
       </c>
-      <c r="K41" s="70"/>
-      <c r="L41" s="70"/>
-      <c r="M41" s="70" t="s">
-        <v>12</v>
-      </c>
-      <c r="N41" s="67"/>
-      <c r="O41" s="67"/>
-      <c r="P41" s="67"/>
-      <c r="Q41" s="67"/>
-      <c r="R41" s="67"/>
-      <c r="S41" s="67"/>
-      <c r="T41" s="67"/>
-      <c r="U41" s="67"/>
-      <c r="V41" s="67"/>
-      <c r="W41" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="X41" s="67"/>
-      <c r="Y41" s="67"/>
-      <c r="Z41" s="67"/>
-      <c r="AA41" s="67"/>
-      <c r="AB41" s="67"/>
-      <c r="AC41" s="67"/>
-      <c r="AD41" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE41" s="67"/>
-      <c r="AF41" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG41" s="67"/>
-      <c r="AH41" s="67"/>
-      <c r="AI41" s="67"/>
-      <c r="AJ41" s="67"/>
-      <c r="AK41" s="67"/>
-      <c r="AL41" s="69">
+      <c r="K41" s="72"/>
+      <c r="L41" s="72"/>
+      <c r="M41" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="N41" s="69"/>
+      <c r="O41" s="69"/>
+      <c r="P41" s="69"/>
+      <c r="Q41" s="69"/>
+      <c r="R41" s="69"/>
+      <c r="S41" s="69"/>
+      <c r="T41" s="69"/>
+      <c r="U41" s="69"/>
+      <c r="V41" s="69"/>
+      <c r="W41" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="X41" s="69"/>
+      <c r="Y41" s="69"/>
+      <c r="Z41" s="69"/>
+      <c r="AA41" s="69"/>
+      <c r="AB41" s="69"/>
+      <c r="AC41" s="69"/>
+      <c r="AD41" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE41" s="69"/>
+      <c r="AF41" s="69" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG41" s="69"/>
+      <c r="AH41" s="69"/>
+      <c r="AI41" s="69"/>
+      <c r="AJ41" s="69"/>
+      <c r="AK41" s="69"/>
+      <c r="AL41" s="71">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="42" ht="14.6" spans="8:38">
-      <c r="H42" s="72" t="s">
+      <c r="H42" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="I42" s="72"/>
-      <c r="J42" s="72"/>
-      <c r="K42" s="50">
+      <c r="I42" s="74"/>
+      <c r="J42" s="74"/>
+      <c r="K42" s="52">
         <f>COUNTA(K11:K41)</f>
         <v>6</v>
       </c>
-      <c r="L42" s="50">
+      <c r="L42" s="52">
         <f t="shared" ref="L42:AK42" si="1">COUNTA(L11:L41)</f>
         <v>9</v>
       </c>
-      <c r="M42" s="50">
+      <c r="M42" s="52">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="N42" s="50">
+      <c r="N42" s="52">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="O42" s="50">
+      <c r="O42" s="52">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="P42" s="50">
+      <c r="P42" s="52">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="Q42" s="50">
+      <c r="Q42" s="52">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="R42" s="50">
+      <c r="R42" s="52">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="S42" s="50">
+      <c r="S42" s="52">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="T42" s="50">
+      <c r="T42" s="52">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="U42" s="50">
+      <c r="U42" s="52">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="V42" s="50">
+      <c r="V42" s="52">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="W42" s="50">
+      <c r="W42" s="52">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="X42" s="50">
+      <c r="X42" s="52">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="Y42" s="50">
+      <c r="Y42" s="52">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="Z42" s="50">
+      <c r="Z42" s="52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AA42" s="50">
+      <c r="AA42" s="52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AB42" s="50">
+      <c r="AB42" s="52">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AC42" s="50">
+      <c r="AC42" s="52">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AD42" s="50">
+      <c r="AD42" s="52">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="AE42" s="50">
+      <c r="AE42" s="52">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="AF42" s="50">
+      <c r="AF42" s="52">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="AG42" s="50">
+      <c r="AG42" s="52">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH42" s="50">
+      <c r="AH42" s="52">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="AI42" s="50"/>
-      <c r="AJ42" s="50"/>
-      <c r="AK42" s="50">
+      <c r="AI42" s="52"/>
+      <c r="AJ42" s="52"/>
+      <c r="AK42" s="52">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="AL42" s="73">
+      <c r="AL42" s="75">
         <f t="shared" ref="AL42" si="2">COUNTA(AL11:AL41)</f>
         <v>31</v>
       </c>
@@ -5349,9 +5364,15 @@
       </c>
       <c r="AF3" s="36"/>
       <c r="AG3" s="36"/>
-      <c r="AH3" s="37"/>
-      <c r="AI3" s="37"/>
-      <c r="AJ3" s="37"/>
+      <c r="AH3" s="37">
+        <v>2</v>
+      </c>
+      <c r="AI3" s="37">
+        <v>2</v>
+      </c>
+      <c r="AJ3" s="37">
+        <v>2</v>
+      </c>
       <c r="AK3" s="38"/>
     </row>
     <row r="4" spans="1:37">
@@ -5822,46 +5843,52 @@
       <c r="C11" s="40">
         <v>46211</v>
       </c>
-      <c r="D11" s="46" t="s">
+      <c r="D11" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="J11" s="45"/>
-      <c r="K11" s="45"/>
-      <c r="L11" s="39"/>
-      <c r="M11" s="39"/>
-      <c r="N11" s="39"/>
-      <c r="O11" s="39"/>
-      <c r="P11" s="39"/>
-      <c r="Q11" s="39"/>
-      <c r="R11" s="39"/>
-      <c r="S11" s="39"/>
-      <c r="T11" s="39"/>
-      <c r="U11" s="39"/>
-      <c r="V11" s="39"/>
-      <c r="W11" s="39"/>
-      <c r="X11" s="39"/>
-      <c r="Y11" s="39"/>
-      <c r="Z11" s="39"/>
-      <c r="AA11" s="39"/>
-      <c r="AB11" s="39"/>
-      <c r="AC11" s="39"/>
-      <c r="AD11" s="39"/>
-      <c r="AE11" s="39"/>
-      <c r="AF11" s="39"/>
-      <c r="AG11" s="39"/>
-      <c r="AH11" s="39"/>
-      <c r="AI11" s="39"/>
-      <c r="AJ11" s="39"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="J11" s="46"/>
+      <c r="K11" s="46"/>
+      <c r="L11" s="46"/>
+      <c r="M11" s="46"/>
+      <c r="N11" s="46"/>
+      <c r="O11" s="46"/>
+      <c r="P11" s="46"/>
+      <c r="Q11" s="46"/>
+      <c r="R11" s="46"/>
+      <c r="S11" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="T11" s="47"/>
+      <c r="U11" s="47"/>
+      <c r="V11" s="47"/>
+      <c r="W11" s="47"/>
+      <c r="X11" s="47"/>
+      <c r="Y11" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z11" s="47"/>
+      <c r="AA11" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB11" s="47"/>
+      <c r="AC11" s="47"/>
+      <c r="AD11" s="47"/>
+      <c r="AE11" s="47"/>
+      <c r="AF11" s="47"/>
+      <c r="AG11" s="47"/>
+      <c r="AH11" s="47"/>
+      <c r="AI11" s="47"/>
+      <c r="AJ11" s="47"/>
       <c r="AK11" s="43">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -5874,42 +5901,48 @@
       <c r="C12" s="40">
         <v>46212</v>
       </c>
-      <c r="D12" s="41"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="39"/>
-      <c r="M12" s="39"/>
-      <c r="N12" s="39"/>
-      <c r="O12" s="39"/>
-      <c r="P12" s="39"/>
-      <c r="Q12" s="39"/>
-      <c r="R12" s="39"/>
-      <c r="S12" s="39"/>
-      <c r="T12" s="39"/>
-      <c r="U12" s="39"/>
-      <c r="V12" s="39"/>
-      <c r="W12" s="39"/>
-      <c r="X12" s="39"/>
-      <c r="Y12" s="39"/>
-      <c r="Z12" s="39"/>
-      <c r="AA12" s="39"/>
-      <c r="AB12" s="39"/>
-      <c r="AC12" s="39"/>
-      <c r="AD12" s="39"/>
-      <c r="AE12" s="39"/>
-      <c r="AF12" s="39"/>
-      <c r="AG12" s="39"/>
-      <c r="AH12" s="39"/>
-      <c r="AI12" s="39"/>
-      <c r="AJ12" s="39"/>
+      <c r="D12" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="46"/>
+      <c r="K12" s="46"/>
+      <c r="L12" s="46"/>
+      <c r="M12" s="46"/>
+      <c r="N12" s="46"/>
+      <c r="O12" s="46"/>
+      <c r="P12" s="46"/>
+      <c r="Q12" s="46"/>
+      <c r="R12" s="46"/>
+      <c r="S12" s="46"/>
+      <c r="T12" s="46"/>
+      <c r="U12" s="46"/>
+      <c r="V12" s="46"/>
+      <c r="W12" s="46"/>
+      <c r="X12" s="46"/>
+      <c r="Y12" s="46"/>
+      <c r="Z12" s="46"/>
+      <c r="AA12" s="46"/>
+      <c r="AB12" s="46"/>
+      <c r="AC12" s="46"/>
+      <c r="AD12" s="46"/>
+      <c r="AE12" s="46"/>
+      <c r="AF12" s="46"/>
+      <c r="AG12" s="46"/>
+      <c r="AH12" s="46"/>
+      <c r="AI12" s="46"/>
+      <c r="AJ12" s="46"/>
       <c r="AK12" s="43">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:37">

--- a/Другое/study_chart.xlsx
+++ b/Другое/study_chart.xlsx
@@ -740,8 +740,33 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Собянин Евгений Андреевич (new)</author>
+  </authors>
+  <commentList>
+    <comment ref="AH14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Сделать 60% задач из задачника.
+13 из 22
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="73">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -948,6 +973,18 @@
   </si>
   <si>
     <t>89.4</t>
+  </si>
+  <si>
+    <t>Упражнение Ситуация - Приговор - Факт (с 10.08)</t>
+  </si>
+  <si>
+    <t>89.2</t>
+  </si>
+  <si>
+    <t>Упражнения для голоса (с 11.08)</t>
+  </si>
+  <si>
+    <t>89.3</t>
   </si>
 </sst>
 </file>
@@ -955,9 +992,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="dd\.mmm"/>
+    <numFmt numFmtId="164" formatCode="dd\.mmm"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1184,8 +1221,14 @@
       <name val="Tahoma"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="28">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1345,6 +1388,42 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE6A817"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFD5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECFEF1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1644,7 +1723,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1707,7 +1786,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1779,7 +1858,7 @@
     <xf numFmtId="0" fontId="26" fillId="22" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="26" fillId="22" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="26" fillId="22" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="22" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1789,7 +1868,7 @@
     <xf numFmtId="0" fontId="27" fillId="26" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="26" fillId="22" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="22" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="26" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1808,13 +1887,34 @@
     <xf numFmtId="0" fontId="26" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="26" fillId="22" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="26" fillId="22" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="27" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1842,6 +1942,39 @@
     <xf numFmtId="0" fontId="19" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1861,39 +1994,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1940,16 +2040,16 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFECFEF1"/>
+      <color rgb="FFBCFCCD"/>
+      <color rgb="FFFFEFFF"/>
+      <color rgb="FFFFE1FF"/>
+      <color rgb="FFB1BCC3"/>
+      <color rgb="FFFFFFD5"/>
       <color rgb="FFB6EA86"/>
-      <color rgb="FFBCFCCD"/>
       <color rgb="FFB9FFF2"/>
       <color rgb="FFFDDBF7"/>
       <color rgb="FF3A0000"/>
-      <color rgb="FFF8B2F8"/>
-      <color rgb="FF5C650B"/>
-      <color rgb="FFEFF6A8"/>
-      <color rgb="FFFCF7B2"/>
-      <color rgb="FFBD07B4"/>
     </mruColors>
   </colors>
   <extLst>
@@ -2261,18 +2361,18 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:17" ht="45" customHeight="1">
-      <c r="H9" s="62" t="s">
+      <c r="H9" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="63"/>
-      <c r="J9" s="63"/>
-      <c r="K9" s="63"/>
-      <c r="L9" s="63"/>
-      <c r="M9" s="63"/>
-      <c r="N9" s="63"/>
-      <c r="O9" s="63"/>
-      <c r="P9" s="63"/>
-      <c r="Q9" s="64"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="70"/>
+      <c r="K9" s="70"/>
+      <c r="L9" s="70"/>
+      <c r="M9" s="70"/>
+      <c r="N9" s="70"/>
+      <c r="O9" s="70"/>
+      <c r="P9" s="70"/>
+      <c r="Q9" s="71"/>
     </row>
     <row r="10" spans="8:17" ht="30" customHeight="1">
       <c r="H10" s="55" t="s">
@@ -2541,11 +2641,11 @@
       <c r="Q21" s="60"/>
     </row>
     <row r="22" spans="8:17" ht="15.75">
-      <c r="H22" s="65" t="s">
+      <c r="H22" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="66"/>
-      <c r="J22" s="67"/>
+      <c r="I22" s="73"/>
+      <c r="J22" s="74"/>
       <c r="K22" s="61">
         <f>COUNTA(K11:K21)</f>
         <v>6</v>
@@ -2622,39 +2722,39 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:38" ht="45" customHeight="1">
-      <c r="H9" s="68" t="s">
+      <c r="H9" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="69"/>
-      <c r="J9" s="69"/>
-      <c r="K9" s="69"/>
-      <c r="L9" s="69"/>
-      <c r="M9" s="69"/>
-      <c r="N9" s="69"/>
-      <c r="O9" s="69"/>
-      <c r="P9" s="69"/>
-      <c r="Q9" s="69"/>
-      <c r="R9" s="69"/>
-      <c r="S9" s="69"/>
-      <c r="T9" s="69"/>
-      <c r="U9" s="69"/>
-      <c r="V9" s="69"/>
-      <c r="W9" s="69"/>
-      <c r="X9" s="69"/>
-      <c r="Y9" s="69"/>
-      <c r="Z9" s="69"/>
-      <c r="AA9" s="69"/>
-      <c r="AB9" s="69"/>
-      <c r="AC9" s="69"/>
-      <c r="AD9" s="69"/>
-      <c r="AE9" s="69"/>
-      <c r="AF9" s="69"/>
-      <c r="AG9" s="69"/>
-      <c r="AH9" s="69"/>
-      <c r="AI9" s="69"/>
-      <c r="AJ9" s="69"/>
-      <c r="AK9" s="69"/>
-      <c r="AL9" s="69"/>
+      <c r="I9" s="76"/>
+      <c r="J9" s="76"/>
+      <c r="K9" s="76"/>
+      <c r="L9" s="76"/>
+      <c r="M9" s="76"/>
+      <c r="N9" s="76"/>
+      <c r="O9" s="76"/>
+      <c r="P9" s="76"/>
+      <c r="Q9" s="76"/>
+      <c r="R9" s="76"/>
+      <c r="S9" s="76"/>
+      <c r="T9" s="76"/>
+      <c r="U9" s="76"/>
+      <c r="V9" s="76"/>
+      <c r="W9" s="76"/>
+      <c r="X9" s="76"/>
+      <c r="Y9" s="76"/>
+      <c r="Z9" s="76"/>
+      <c r="AA9" s="76"/>
+      <c r="AB9" s="76"/>
+      <c r="AC9" s="76"/>
+      <c r="AD9" s="76"/>
+      <c r="AE9" s="76"/>
+      <c r="AF9" s="76"/>
+      <c r="AG9" s="76"/>
+      <c r="AH9" s="76"/>
+      <c r="AI9" s="76"/>
+      <c r="AJ9" s="76"/>
+      <c r="AK9" s="76"/>
+      <c r="AL9" s="76"/>
     </row>
     <row r="10" spans="8:38" ht="30" customHeight="1">
       <c r="H10" s="32" t="s">
@@ -4334,11 +4434,11 @@
       </c>
     </row>
     <row r="42" spans="8:38" ht="15.75">
-      <c r="H42" s="70" t="s">
+      <c r="H42" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="I42" s="70"/>
-      <c r="J42" s="70"/>
+      <c r="I42" s="77"/>
+      <c r="J42" s="77"/>
       <c r="K42" s="32">
         <f>COUNTA(K11:K41)</f>
         <v>6</v>
@@ -4494,7 +4594,9 @@
     <col min="29" max="29" width="15.7109375" style="3" customWidth="1"/>
     <col min="30" max="30" width="29.28515625" style="3" customWidth="1"/>
     <col min="31" max="31" width="24.42578125" style="3" customWidth="1"/>
-    <col min="32" max="36" width="15.7109375" style="3" customWidth="1"/>
+    <col min="32" max="32" width="33.7109375" style="3" customWidth="1"/>
+    <col min="33" max="33" width="34.28515625" style="3" customWidth="1"/>
+    <col min="34" max="36" width="15.7109375" style="3" customWidth="1"/>
     <col min="37" max="37" width="24.5703125" style="3" customWidth="1"/>
     <col min="38" max="38" width="20.7109375" style="3" customWidth="1"/>
     <col min="39" max="16384" width="9" style="3"/>
@@ -4507,42 +4609,42 @@
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="71" t="s">
+      <c r="E1" s="89" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
-      <c r="J1" s="71"/>
-      <c r="K1" s="71"/>
-      <c r="L1" s="72" t="s">
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="89"/>
+      <c r="K1" s="89"/>
+      <c r="L1" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="72"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="72"/>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="72"/>
-      <c r="R1" s="72"/>
-      <c r="S1" s="73" t="s">
+      <c r="M1" s="90"/>
+      <c r="N1" s="90"/>
+      <c r="O1" s="90"/>
+      <c r="P1" s="90"/>
+      <c r="Q1" s="90"/>
+      <c r="R1" s="90"/>
+      <c r="S1" s="91" t="s">
         <v>39</v>
       </c>
-      <c r="T1" s="73"/>
-      <c r="U1" s="74" t="s">
+      <c r="T1" s="91"/>
+      <c r="U1" s="92" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="75"/>
-      <c r="W1" s="75"/>
-      <c r="X1" s="75"/>
-      <c r="Y1" s="76"/>
-      <c r="Z1" s="77" t="s">
+      <c r="V1" s="93"/>
+      <c r="W1" s="93"/>
+      <c r="X1" s="93"/>
+      <c r="Y1" s="94"/>
+      <c r="Z1" s="95" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="77"/>
-      <c r="AB1" s="77"/>
-      <c r="AC1" s="77"/>
-      <c r="AD1" s="77"/>
+      <c r="AA1" s="95"/>
+      <c r="AB1" s="95"/>
+      <c r="AC1" s="95"/>
+      <c r="AD1" s="95"/>
       <c r="AE1" s="78" t="s">
         <v>42</v>
       </c>
@@ -4646,10 +4748,10 @@
         <v>61</v>
       </c>
       <c r="AF2" s="11" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="AG2" s="11" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="AH2" s="12"/>
       <c r="AI2" s="12"/>
@@ -4750,8 +4852,12 @@
       <c r="AE3" s="19">
         <v>3</v>
       </c>
-      <c r="AF3" s="19"/>
-      <c r="AG3" s="19"/>
+      <c r="AF3" s="19">
+        <v>2</v>
+      </c>
+      <c r="AG3" s="19">
+        <v>2</v>
+      </c>
       <c r="AH3" s="20">
         <v>2</v>
       </c>
@@ -4774,50 +4880,50 @@
         <v>46204</v>
       </c>
       <c r="D4" s="23"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="K4" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="24"/>
-      <c r="Q4" s="24"/>
-      <c r="R4" s="24"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="64"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
       <c r="S4" s="24"/>
       <c r="T4" s="24"/>
-      <c r="U4" s="24"/>
-      <c r="V4" s="24"/>
-      <c r="W4" s="24"/>
-      <c r="X4" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y4" s="24"/>
-      <c r="Z4" s="24"/>
-      <c r="AA4" s="24"/>
-      <c r="AB4" s="24"/>
-      <c r="AC4" s="24"/>
-      <c r="AD4" s="24"/>
-      <c r="AE4" s="24"/>
-      <c r="AF4" s="24"/>
-      <c r="AG4" s="24"/>
-      <c r="AH4" s="24"/>
-      <c r="AI4" s="24"/>
-      <c r="AJ4" s="24"/>
+      <c r="U4" s="65"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="65"/>
+      <c r="X4" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y4" s="65"/>
+      <c r="Z4" s="66"/>
+      <c r="AA4" s="66"/>
+      <c r="AB4" s="66"/>
+      <c r="AC4" s="66"/>
+      <c r="AD4" s="66"/>
+      <c r="AE4" s="67"/>
+      <c r="AF4" s="67"/>
+      <c r="AG4" s="67"/>
+      <c r="AH4" s="68"/>
+      <c r="AI4" s="68"/>
+      <c r="AJ4" s="68"/>
       <c r="AK4" s="25">
         <f>SUMIF(E4:AJ4,"&lt;&gt;",$E$3:$AJ$3)</f>
         <v>9</v>
@@ -4834,42 +4940,42 @@
         <v>46205</v>
       </c>
       <c r="D5" s="23"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="J5" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="K5" s="24"/>
-      <c r="L5" s="24"/>
-      <c r="M5" s="24"/>
-      <c r="N5" s="24"/>
-      <c r="O5" s="24"/>
-      <c r="P5" s="24"/>
-      <c r="Q5" s="24"/>
-      <c r="R5" s="24"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="62"/>
+      <c r="L5" s="64"/>
+      <c r="M5" s="64"/>
+      <c r="N5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="64"/>
+      <c r="Q5" s="64"/>
+      <c r="R5" s="64"/>
       <c r="S5" s="24"/>
       <c r="T5" s="24"/>
-      <c r="U5" s="24"/>
-      <c r="V5" s="24"/>
-      <c r="W5" s="24"/>
-      <c r="X5" s="24"/>
-      <c r="Y5" s="24"/>
-      <c r="Z5" s="24"/>
-      <c r="AA5" s="24"/>
-      <c r="AB5" s="24"/>
-      <c r="AC5" s="24"/>
-      <c r="AD5" s="24"/>
-      <c r="AE5" s="24"/>
-      <c r="AF5" s="24"/>
-      <c r="AG5" s="24"/>
-      <c r="AH5" s="24"/>
-      <c r="AI5" s="24"/>
-      <c r="AJ5" s="24"/>
+      <c r="U5" s="65"/>
+      <c r="V5" s="65"/>
+      <c r="W5" s="65"/>
+      <c r="X5" s="65"/>
+      <c r="Y5" s="65"/>
+      <c r="Z5" s="66"/>
+      <c r="AA5" s="66"/>
+      <c r="AB5" s="66"/>
+      <c r="AC5" s="66"/>
+      <c r="AD5" s="66"/>
+      <c r="AE5" s="67"/>
+      <c r="AF5" s="67"/>
+      <c r="AG5" s="67"/>
+      <c r="AH5" s="68"/>
+      <c r="AI5" s="68"/>
+      <c r="AJ5" s="68"/>
       <c r="AK5" s="25">
         <f t="shared" ref="AK5:AK34" si="0">SUMIF(E5:AJ5,"&lt;&gt;",$E$3:$AJ$3)</f>
         <v>3</v>
@@ -4886,66 +4992,66 @@
         <v>46206</v>
       </c>
       <c r="D6" s="26"/>
-      <c r="E6" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="N6" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="O6" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="P6" s="24"/>
-      <c r="Q6" s="24"/>
-      <c r="R6" s="24"/>
+      <c r="E6" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="K6" s="62"/>
+      <c r="L6" s="64"/>
+      <c r="M6" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="N6" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="O6" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="P6" s="64"/>
+      <c r="Q6" s="64"/>
+      <c r="R6" s="64"/>
       <c r="S6" s="24"/>
       <c r="T6" s="24"/>
-      <c r="U6" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="V6" s="24"/>
-      <c r="W6" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="X6" s="24"/>
-      <c r="Y6" s="24"/>
-      <c r="Z6" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="AA6" s="24"/>
-      <c r="AB6" s="24"/>
-      <c r="AC6" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD6" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE6" s="24"/>
-      <c r="AF6" s="24"/>
-      <c r="AG6" s="24"/>
-      <c r="AH6" s="24"/>
-      <c r="AI6" s="24"/>
-      <c r="AJ6" s="24"/>
+      <c r="U6" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="V6" s="65"/>
+      <c r="W6" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="X6" s="65"/>
+      <c r="Y6" s="65"/>
+      <c r="Z6" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA6" s="66"/>
+      <c r="AB6" s="66"/>
+      <c r="AC6" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD6" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE6" s="67"/>
+      <c r="AF6" s="67"/>
+      <c r="AG6" s="67"/>
+      <c r="AH6" s="68"/>
+      <c r="AI6" s="68"/>
+      <c r="AJ6" s="68"/>
       <c r="AK6" s="25">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -4964,62 +5070,62 @@
       <c r="D7" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="E7" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="J7" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="N7" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="O7" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="P7" s="24"/>
-      <c r="Q7" s="24"/>
-      <c r="R7" s="24"/>
+      <c r="E7" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="K7" s="62"/>
+      <c r="L7" s="64"/>
+      <c r="M7" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="N7" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="O7" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="P7" s="64"/>
+      <c r="Q7" s="64"/>
+      <c r="R7" s="64"/>
       <c r="S7" s="24"/>
       <c r="T7" s="24"/>
-      <c r="U7" s="24"/>
-      <c r="V7" s="24"/>
-      <c r="W7" s="24"/>
-      <c r="X7" s="24"/>
-      <c r="Y7" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z7" s="24"/>
-      <c r="AA7" s="24"/>
-      <c r="AB7" s="24"/>
-      <c r="AC7" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD7" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE7" s="24"/>
-      <c r="AF7" s="24"/>
-      <c r="AG7" s="24"/>
-      <c r="AH7" s="24"/>
-      <c r="AI7" s="24"/>
-      <c r="AJ7" s="24"/>
+      <c r="U7" s="65"/>
+      <c r="V7" s="65"/>
+      <c r="W7" s="65"/>
+      <c r="X7" s="65"/>
+      <c r="Y7" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z7" s="66"/>
+      <c r="AA7" s="66"/>
+      <c r="AB7" s="66"/>
+      <c r="AC7" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD7" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE7" s="67"/>
+      <c r="AF7" s="67"/>
+      <c r="AG7" s="67"/>
+      <c r="AH7" s="68"/>
+      <c r="AI7" s="68"/>
+      <c r="AJ7" s="68"/>
       <c r="AK7" s="25">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -5038,58 +5144,58 @@
       <c r="D8" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="24"/>
-      <c r="I8" s="24"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="M8" s="24"/>
-      <c r="N8" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="O8" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="P8" s="24"/>
-      <c r="Q8" s="24"/>
-      <c r="R8" s="24"/>
+      <c r="E8" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="62"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="M8" s="64"/>
+      <c r="N8" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="O8" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="P8" s="64"/>
+      <c r="Q8" s="64"/>
+      <c r="R8" s="64"/>
       <c r="S8" s="24"/>
       <c r="T8" s="24"/>
-      <c r="U8" s="24"/>
-      <c r="V8" s="24"/>
-      <c r="W8" s="24"/>
-      <c r="X8" s="24"/>
-      <c r="Y8" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z8" s="24"/>
-      <c r="AA8" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB8" s="24"/>
-      <c r="AC8" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD8" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE8" s="24"/>
-      <c r="AF8" s="24"/>
-      <c r="AG8" s="24"/>
-      <c r="AH8" s="24"/>
-      <c r="AI8" s="24"/>
-      <c r="AJ8" s="24"/>
+      <c r="U8" s="65"/>
+      <c r="V8" s="65"/>
+      <c r="W8" s="65"/>
+      <c r="X8" s="65"/>
+      <c r="Y8" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z8" s="66"/>
+      <c r="AA8" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB8" s="66"/>
+      <c r="AC8" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD8" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE8" s="67"/>
+      <c r="AF8" s="67"/>
+      <c r="AG8" s="67"/>
+      <c r="AH8" s="68"/>
+      <c r="AI8" s="68"/>
+      <c r="AJ8" s="68"/>
       <c r="AK8" s="25">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -5108,56 +5214,56 @@
       <c r="D9" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="E9" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="H9" s="24"/>
-      <c r="I9" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="L9" s="24"/>
-      <c r="M9" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="N9" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="O9" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="P9" s="24"/>
-      <c r="Q9" s="24"/>
-      <c r="R9" s="24"/>
+      <c r="E9" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="62"/>
+      <c r="I9" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" s="62"/>
+      <c r="K9" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="L9" s="64"/>
+      <c r="M9" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="N9" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="O9" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="P9" s="64"/>
+      <c r="Q9" s="64"/>
+      <c r="R9" s="64"/>
       <c r="S9" s="24"/>
       <c r="T9" s="24"/>
-      <c r="U9" s="24"/>
-      <c r="V9" s="24"/>
-      <c r="W9" s="24"/>
-      <c r="X9" s="24"/>
-      <c r="Y9" s="24"/>
-      <c r="Z9" s="24"/>
-      <c r="AA9" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB9" s="24"/>
-      <c r="AC9" s="24"/>
-      <c r="AD9" s="24"/>
-      <c r="AE9" s="24"/>
-      <c r="AF9" s="24"/>
-      <c r="AG9" s="24"/>
-      <c r="AH9" s="24"/>
-      <c r="AI9" s="24"/>
-      <c r="AJ9" s="24"/>
+      <c r="U9" s="65"/>
+      <c r="V9" s="65"/>
+      <c r="W9" s="65"/>
+      <c r="X9" s="65"/>
+      <c r="Y9" s="65"/>
+      <c r="Z9" s="66"/>
+      <c r="AA9" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB9" s="66"/>
+      <c r="AC9" s="66"/>
+      <c r="AD9" s="66"/>
+      <c r="AE9" s="67"/>
+      <c r="AF9" s="67"/>
+      <c r="AG9" s="67"/>
+      <c r="AH9" s="68"/>
+      <c r="AI9" s="68"/>
+      <c r="AJ9" s="68"/>
       <c r="AK9" s="25">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -5176,46 +5282,46 @@
       <c r="D10" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="27"/>
-      <c r="N10" s="27"/>
-      <c r="O10" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="P10" s="27"/>
-      <c r="Q10" s="27"/>
-      <c r="R10" s="27"/>
+      <c r="E10" s="62"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="62"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="62"/>
+      <c r="J10" s="62"/>
+      <c r="K10" s="62"/>
+      <c r="L10" s="64"/>
+      <c r="M10" s="64"/>
+      <c r="N10" s="64"/>
+      <c r="O10" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="P10" s="64"/>
+      <c r="Q10" s="64"/>
+      <c r="R10" s="64"/>
       <c r="S10" s="27"/>
       <c r="T10" s="27"/>
-      <c r="U10" s="27"/>
-      <c r="V10" s="27"/>
-      <c r="W10" s="27"/>
-      <c r="X10" s="27"/>
-      <c r="Y10" s="27"/>
-      <c r="Z10" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="AA10" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB10" s="27"/>
-      <c r="AC10" s="27"/>
-      <c r="AD10" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE10" s="27"/>
-      <c r="AF10" s="27"/>
-      <c r="AG10" s="27"/>
-      <c r="AH10" s="27"/>
-      <c r="AI10" s="27"/>
-      <c r="AJ10" s="27"/>
+      <c r="U10" s="65"/>
+      <c r="V10" s="65"/>
+      <c r="W10" s="65"/>
+      <c r="X10" s="65"/>
+      <c r="Y10" s="65"/>
+      <c r="Z10" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA10" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB10" s="66"/>
+      <c r="AC10" s="66"/>
+      <c r="AD10" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE10" s="67"/>
+      <c r="AF10" s="67"/>
+      <c r="AG10" s="67"/>
+      <c r="AH10" s="68"/>
+      <c r="AI10" s="68"/>
+      <c r="AJ10" s="68"/>
       <c r="AK10" s="25">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -5234,48 +5340,48 @@
       <c r="D11" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="28"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="J11" s="28"/>
-      <c r="K11" s="28"/>
-      <c r="L11" s="28"/>
-      <c r="M11" s="28"/>
-      <c r="N11" s="28"/>
-      <c r="O11" s="28"/>
-      <c r="P11" s="28"/>
-      <c r="Q11" s="28"/>
-      <c r="R11" s="28"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="62"/>
+      <c r="H11" s="62"/>
+      <c r="I11" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="J11" s="62"/>
+      <c r="K11" s="62"/>
+      <c r="L11" s="64"/>
+      <c r="M11" s="64"/>
+      <c r="N11" s="64"/>
+      <c r="O11" s="64"/>
+      <c r="P11" s="64"/>
+      <c r="Q11" s="64"/>
+      <c r="R11" s="64"/>
       <c r="S11" s="29" t="s">
         <v>12</v>
       </c>
       <c r="T11" s="29"/>
-      <c r="U11" s="29"/>
-      <c r="V11" s="29"/>
-      <c r="W11" s="29"/>
-      <c r="X11" s="29"/>
-      <c r="Y11" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z11" s="29"/>
-      <c r="AA11" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB11" s="29"/>
-      <c r="AC11" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD11" s="29"/>
-      <c r="AE11" s="29"/>
-      <c r="AF11" s="29"/>
-      <c r="AG11" s="29"/>
-      <c r="AH11" s="29"/>
-      <c r="AI11" s="29"/>
-      <c r="AJ11" s="29"/>
+      <c r="U11" s="65"/>
+      <c r="V11" s="65"/>
+      <c r="W11" s="65"/>
+      <c r="X11" s="65"/>
+      <c r="Y11" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z11" s="66"/>
+      <c r="AA11" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB11" s="66"/>
+      <c r="AC11" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD11" s="66"/>
+      <c r="AE11" s="67"/>
+      <c r="AF11" s="67"/>
+      <c r="AG11" s="67"/>
+      <c r="AH11" s="68"/>
+      <c r="AI11" s="68"/>
+      <c r="AJ11" s="68"/>
       <c r="AK11" s="25">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -5294,58 +5400,58 @@
       <c r="D12" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="E12" s="28"/>
-      <c r="F12" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="H12" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="I12" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="J12" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="K12" s="28"/>
-      <c r="L12" s="28"/>
-      <c r="M12" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="N12" s="28"/>
-      <c r="O12" s="28"/>
-      <c r="P12" s="28"/>
-      <c r="Q12" s="28"/>
-      <c r="R12" s="28"/>
+      <c r="E12" s="62"/>
+      <c r="F12" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="J12" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="K12" s="62"/>
+      <c r="L12" s="64"/>
+      <c r="M12" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="N12" s="64"/>
+      <c r="O12" s="64"/>
+      <c r="P12" s="64"/>
+      <c r="Q12" s="64"/>
+      <c r="R12" s="64"/>
       <c r="S12" s="28"/>
       <c r="T12" s="28"/>
-      <c r="U12" s="28"/>
-      <c r="V12" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="W12" s="28"/>
-      <c r="X12" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y12" s="28"/>
-      <c r="Z12" s="28"/>
-      <c r="AA12" s="28"/>
-      <c r="AB12" s="28"/>
-      <c r="AC12" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD12" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE12" s="28"/>
-      <c r="AF12" s="28"/>
-      <c r="AG12" s="28"/>
-      <c r="AH12" s="28"/>
-      <c r="AI12" s="28"/>
-      <c r="AJ12" s="28"/>
+      <c r="U12" s="65"/>
+      <c r="V12" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="W12" s="65"/>
+      <c r="X12" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y12" s="65"/>
+      <c r="Z12" s="66"/>
+      <c r="AA12" s="66"/>
+      <c r="AB12" s="66"/>
+      <c r="AC12" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD12" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE12" s="67"/>
+      <c r="AF12" s="67"/>
+      <c r="AG12" s="67"/>
+      <c r="AH12" s="68"/>
+      <c r="AI12" s="68"/>
+      <c r="AJ12" s="68"/>
       <c r="AK12" s="25">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -5364,53 +5470,63 @@
       <c r="D13" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="E13" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="H13" s="29"/>
-      <c r="I13" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="J13" s="29"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="N13" s="29"/>
-      <c r="O13" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="P13" s="29"/>
-      <c r="Q13" s="29"/>
-      <c r="R13" s="29"/>
+      <c r="E13" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="62"/>
+      <c r="I13" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="J13" s="62"/>
+      <c r="K13" s="62"/>
+      <c r="L13" s="64"/>
+      <c r="M13" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="N13" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="O13" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="P13" s="64"/>
+      <c r="Q13" s="64"/>
+      <c r="R13" s="64"/>
       <c r="S13" s="29"/>
       <c r="T13" s="29"/>
-      <c r="U13" s="29"/>
-      <c r="V13" s="29"/>
-      <c r="W13" s="29"/>
-      <c r="X13" s="29"/>
-      <c r="Y13" s="29"/>
-      <c r="Z13" s="29"/>
-      <c r="AA13" s="29"/>
-      <c r="AB13" s="29"/>
-      <c r="AC13" s="29"/>
-      <c r="AD13" s="29"/>
-      <c r="AE13" s="29"/>
-      <c r="AF13" s="29"/>
-      <c r="AG13" s="29"/>
-      <c r="AH13" s="29"/>
-      <c r="AI13" s="29"/>
-      <c r="AJ13" s="29"/>
+      <c r="U13" s="65"/>
+      <c r="V13" s="65"/>
+      <c r="W13" s="65"/>
+      <c r="X13" s="65"/>
+      <c r="Y13" s="65"/>
+      <c r="Z13" s="66"/>
+      <c r="AA13" s="66"/>
+      <c r="AB13" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC13" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD13" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE13" s="67"/>
+      <c r="AF13" s="67" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG13" s="67"/>
+      <c r="AH13" s="68"/>
+      <c r="AI13" s="68"/>
+      <c r="AJ13" s="68"/>
       <c r="AK13" s="25">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -5423,42 +5539,76 @@
       <c r="C14" s="22">
         <v>46214</v>
       </c>
-      <c r="D14" s="23"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
-      <c r="M14" s="21"/>
-      <c r="N14" s="21"/>
-      <c r="O14" s="21"/>
-      <c r="P14" s="21"/>
-      <c r="Q14" s="21"/>
-      <c r="R14" s="21"/>
-      <c r="S14" s="21"/>
-      <c r="T14" s="21"/>
-      <c r="U14" s="21"/>
-      <c r="V14" s="21"/>
-      <c r="W14" s="21"/>
-      <c r="X14" s="21"/>
-      <c r="Y14" s="21"/>
-      <c r="Z14" s="21"/>
-      <c r="AA14" s="21"/>
-      <c r="AB14" s="21"/>
-      <c r="AC14" s="21"/>
-      <c r="AD14" s="21"/>
-      <c r="AE14" s="21"/>
-      <c r="AF14" s="21"/>
-      <c r="AG14" s="21"/>
-      <c r="AH14" s="21"/>
-      <c r="AI14" s="21"/>
-      <c r="AJ14" s="21"/>
+      <c r="D14" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="62"/>
+      <c r="I14" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="J14" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="K14" s="62"/>
+      <c r="L14" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="M14" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="N14" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="O14" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="P14" s="64"/>
+      <c r="Q14" s="64"/>
+      <c r="R14" s="64"/>
+      <c r="S14" s="29"/>
+      <c r="T14" s="29"/>
+      <c r="U14" s="65"/>
+      <c r="V14" s="65"/>
+      <c r="W14" s="65"/>
+      <c r="X14" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y14" s="65"/>
+      <c r="Z14" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA14" s="66"/>
+      <c r="AB14" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC14" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD14" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE14" s="67"/>
+      <c r="AF14" s="67" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG14" s="67" t="s">
+        <v>12</v>
+      </c>
+      <c r="AH14" s="68"/>
+      <c r="AI14" s="68"/>
+      <c r="AJ14" s="68"/>
       <c r="AK14" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -5471,42 +5621,56 @@
       <c r="C15" s="22">
         <v>46215</v>
       </c>
-      <c r="D15" s="23"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="21"/>
-      <c r="N15" s="21"/>
-      <c r="O15" s="21"/>
-      <c r="P15" s="21"/>
-      <c r="Q15" s="21"/>
-      <c r="R15" s="21"/>
-      <c r="S15" s="21"/>
-      <c r="T15" s="21"/>
-      <c r="U15" s="21"/>
-      <c r="V15" s="21"/>
-      <c r="W15" s="21"/>
-      <c r="X15" s="21"/>
-      <c r="Y15" s="21"/>
-      <c r="Z15" s="21"/>
-      <c r="AA15" s="21"/>
-      <c r="AB15" s="21"/>
-      <c r="AC15" s="21"/>
-      <c r="AD15" s="21"/>
-      <c r="AE15" s="21"/>
-      <c r="AF15" s="21"/>
-      <c r="AG15" s="21"/>
-      <c r="AH15" s="21"/>
-      <c r="AI15" s="21"/>
-      <c r="AJ15" s="21"/>
+      <c r="D15" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="M15" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="N15" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="O15" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="P15" s="29"/>
+      <c r="Q15" s="29"/>
+      <c r="R15" s="29"/>
+      <c r="S15" s="29"/>
+      <c r="T15" s="29"/>
+      <c r="U15" s="29"/>
+      <c r="V15" s="29"/>
+      <c r="W15" s="29"/>
+      <c r="X15" s="29"/>
+      <c r="Y15" s="29"/>
+      <c r="Z15" s="29"/>
+      <c r="AA15" s="29"/>
+      <c r="AB15" s="29"/>
+      <c r="AC15" s="29"/>
+      <c r="AD15" s="29"/>
+      <c r="AE15" s="29"/>
+      <c r="AF15" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG15" s="29"/>
+      <c r="AH15" s="29"/>
+      <c r="AI15" s="29"/>
+      <c r="AJ15" s="29"/>
       <c r="AK15" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -5592,7 +5756,7 @@
       <c r="Z17" s="21"/>
       <c r="AA17" s="21"/>
       <c r="AB17" s="21"/>
-      <c r="AC17" s="21"/>
+      <c r="AC17" s="63"/>
       <c r="AD17" s="21"/>
       <c r="AE17" s="21"/>
       <c r="AF17" s="21"/>
@@ -6440,5 +6604,6 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Другое/study_chart.xlsx
+++ b/Другое/study_chart.xlsx
@@ -766,7 +766,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="75">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -985,6 +985,12 @@
   </si>
   <si>
     <t>89.3</t>
+  </si>
+  <si>
+    <t>88.5</t>
+  </si>
+  <si>
+    <t>88.3</t>
   </si>
 </sst>
 </file>
@@ -1428,7 +1434,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -1719,11 +1725,108 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1897,9 +2000,6 @@
     <xf numFmtId="0" fontId="1" fillId="28" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="29" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1994,6 +2094,85 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2041,11 +2220,11 @@
   <colors>
     <mruColors>
       <color rgb="FFECFEF1"/>
+      <color rgb="FFFFEFFF"/>
+      <color rgb="FFFFFFD5"/>
       <color rgb="FFBCFCCD"/>
-      <color rgb="FFFFEFFF"/>
       <color rgb="FFFFE1FF"/>
       <color rgb="FFB1BCC3"/>
-      <color rgb="FFFFFFD5"/>
       <color rgb="FFB6EA86"/>
       <color rgb="FFB9FFF2"/>
       <color rgb="FFFDDBF7"/>
@@ -2361,18 +2540,18 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:17" ht="45" customHeight="1">
-      <c r="H9" s="69" t="s">
+      <c r="H9" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="70"/>
-      <c r="J9" s="70"/>
-      <c r="K9" s="70"/>
-      <c r="L9" s="70"/>
-      <c r="M9" s="70"/>
-      <c r="N9" s="70"/>
-      <c r="O9" s="70"/>
-      <c r="P9" s="70"/>
-      <c r="Q9" s="71"/>
+      <c r="I9" s="69"/>
+      <c r="J9" s="69"/>
+      <c r="K9" s="69"/>
+      <c r="L9" s="69"/>
+      <c r="M9" s="69"/>
+      <c r="N9" s="69"/>
+      <c r="O9" s="69"/>
+      <c r="P9" s="69"/>
+      <c r="Q9" s="70"/>
     </row>
     <row r="10" spans="8:17" ht="30" customHeight="1">
       <c r="H10" s="55" t="s">
@@ -2641,11 +2820,11 @@
       <c r="Q21" s="60"/>
     </row>
     <row r="22" spans="8:17" ht="15.75">
-      <c r="H22" s="72" t="s">
+      <c r="H22" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="73"/>
-      <c r="J22" s="74"/>
+      <c r="I22" s="72"/>
+      <c r="J22" s="73"/>
       <c r="K22" s="61">
         <f>COUNTA(K11:K21)</f>
         <v>6</v>
@@ -2722,39 +2901,39 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:38" ht="45" customHeight="1">
-      <c r="H9" s="75" t="s">
+      <c r="H9" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="76"/>
-      <c r="J9" s="76"/>
-      <c r="K9" s="76"/>
-      <c r="L9" s="76"/>
-      <c r="M9" s="76"/>
-      <c r="N9" s="76"/>
-      <c r="O9" s="76"/>
-      <c r="P9" s="76"/>
-      <c r="Q9" s="76"/>
-      <c r="R9" s="76"/>
-      <c r="S9" s="76"/>
-      <c r="T9" s="76"/>
-      <c r="U9" s="76"/>
-      <c r="V9" s="76"/>
-      <c r="W9" s="76"/>
-      <c r="X9" s="76"/>
-      <c r="Y9" s="76"/>
-      <c r="Z9" s="76"/>
-      <c r="AA9" s="76"/>
-      <c r="AB9" s="76"/>
-      <c r="AC9" s="76"/>
-      <c r="AD9" s="76"/>
-      <c r="AE9" s="76"/>
-      <c r="AF9" s="76"/>
-      <c r="AG9" s="76"/>
-      <c r="AH9" s="76"/>
-      <c r="AI9" s="76"/>
-      <c r="AJ9" s="76"/>
-      <c r="AK9" s="76"/>
-      <c r="AL9" s="76"/>
+      <c r="I9" s="75"/>
+      <c r="J9" s="75"/>
+      <c r="K9" s="75"/>
+      <c r="L9" s="75"/>
+      <c r="M9" s="75"/>
+      <c r="N9" s="75"/>
+      <c r="O9" s="75"/>
+      <c r="P9" s="75"/>
+      <c r="Q9" s="75"/>
+      <c r="R9" s="75"/>
+      <c r="S9" s="75"/>
+      <c r="T9" s="75"/>
+      <c r="U9" s="75"/>
+      <c r="V9" s="75"/>
+      <c r="W9" s="75"/>
+      <c r="X9" s="75"/>
+      <c r="Y9" s="75"/>
+      <c r="Z9" s="75"/>
+      <c r="AA9" s="75"/>
+      <c r="AB9" s="75"/>
+      <c r="AC9" s="75"/>
+      <c r="AD9" s="75"/>
+      <c r="AE9" s="75"/>
+      <c r="AF9" s="75"/>
+      <c r="AG9" s="75"/>
+      <c r="AH9" s="75"/>
+      <c r="AI9" s="75"/>
+      <c r="AJ9" s="75"/>
+      <c r="AK9" s="75"/>
+      <c r="AL9" s="75"/>
     </row>
     <row r="10" spans="8:38" ht="30" customHeight="1">
       <c r="H10" s="32" t="s">
@@ -4434,11 +4613,11 @@
       </c>
     </row>
     <row r="42" spans="8:38" ht="15.75">
-      <c r="H42" s="77" t="s">
+      <c r="H42" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="I42" s="77"/>
-      <c r="J42" s="77"/>
+      <c r="I42" s="76"/>
+      <c r="J42" s="76"/>
       <c r="K42" s="32">
         <f>COUNTA(K11:K41)</f>
         <v>6</v>
@@ -4603,66 +4782,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="83"/>
-      <c r="B1" s="84"/>
-      <c r="C1" s="85"/>
+      <c r="A1" s="82"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="84"/>
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="89" t="s">
+      <c r="E1" s="88" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
-      <c r="H1" s="89"/>
-      <c r="I1" s="89"/>
-      <c r="J1" s="89"/>
-      <c r="K1" s="89"/>
-      <c r="L1" s="90" t="s">
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="89" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="90"/>
-      <c r="N1" s="90"/>
-      <c r="O1" s="90"/>
-      <c r="P1" s="90"/>
-      <c r="Q1" s="90"/>
-      <c r="R1" s="90"/>
-      <c r="S1" s="91" t="s">
+      <c r="M1" s="89"/>
+      <c r="N1" s="89"/>
+      <c r="O1" s="89"/>
+      <c r="P1" s="89"/>
+      <c r="Q1" s="89"/>
+      <c r="R1" s="89"/>
+      <c r="S1" s="90" t="s">
         <v>39</v>
       </c>
-      <c r="T1" s="91"/>
-      <c r="U1" s="92" t="s">
+      <c r="T1" s="90"/>
+      <c r="U1" s="91" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="93"/>
-      <c r="W1" s="93"/>
-      <c r="X1" s="93"/>
-      <c r="Y1" s="94"/>
-      <c r="Z1" s="95" t="s">
+      <c r="V1" s="92"/>
+      <c r="W1" s="92"/>
+      <c r="X1" s="92"/>
+      <c r="Y1" s="93"/>
+      <c r="Z1" s="94" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="95"/>
-      <c r="AB1" s="95"/>
-      <c r="AC1" s="95"/>
-      <c r="AD1" s="95"/>
-      <c r="AE1" s="78" t="s">
+      <c r="AA1" s="94"/>
+      <c r="AB1" s="94"/>
+      <c r="AC1" s="94"/>
+      <c r="AD1" s="94"/>
+      <c r="AE1" s="77" t="s">
         <v>42</v>
       </c>
-      <c r="AF1" s="78"/>
-      <c r="AG1" s="78"/>
-      <c r="AH1" s="79" t="s">
+      <c r="AF1" s="77"/>
+      <c r="AG1" s="77"/>
+      <c r="AH1" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="AI1" s="79"/>
-      <c r="AJ1" s="79"/>
-      <c r="AK1" s="80" t="s">
+      <c r="AI1" s="78"/>
+      <c r="AJ1" s="78"/>
+      <c r="AK1" s="79" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1">
-      <c r="A2" s="86"/>
-      <c r="B2" s="87"/>
-      <c r="C2" s="88"/>
+      <c r="A2" s="85"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="87"/>
       <c r="D2" s="5" t="s">
         <v>44</v>
       </c>
@@ -4756,7 +4935,7 @@
       <c r="AH2" s="12"/>
       <c r="AI2" s="12"/>
       <c r="AJ2" s="12"/>
-      <c r="AK2" s="81"/>
+      <c r="AK2" s="80"/>
     </row>
     <row r="3" spans="1:37">
       <c r="A3" s="13" t="s">
@@ -4867,7 +5046,7 @@
       <c r="AJ3" s="20">
         <v>2</v>
       </c>
-      <c r="AK3" s="82"/>
+      <c r="AK3" s="81"/>
     </row>
     <row r="4" spans="1:37">
       <c r="A4" s="21">
@@ -4897,33 +5076,33 @@
       <c r="K4" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="64"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
+      <c r="L4" s="63"/>
+      <c r="M4" s="63"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="63"/>
+      <c r="P4" s="63"/>
+      <c r="Q4" s="63"/>
+      <c r="R4" s="63"/>
       <c r="S4" s="24"/>
       <c r="T4" s="24"/>
-      <c r="U4" s="65"/>
-      <c r="V4" s="65"/>
-      <c r="W4" s="65"/>
-      <c r="X4" s="65" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y4" s="65"/>
-      <c r="Z4" s="66"/>
-      <c r="AA4" s="66"/>
-      <c r="AB4" s="66"/>
-      <c r="AC4" s="66"/>
-      <c r="AD4" s="66"/>
-      <c r="AE4" s="67"/>
-      <c r="AF4" s="67"/>
-      <c r="AG4" s="67"/>
-      <c r="AH4" s="68"/>
-      <c r="AI4" s="68"/>
-      <c r="AJ4" s="68"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="64"/>
+      <c r="W4" s="64"/>
+      <c r="X4" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y4" s="64"/>
+      <c r="Z4" s="65"/>
+      <c r="AA4" s="65"/>
+      <c r="AB4" s="65"/>
+      <c r="AC4" s="65"/>
+      <c r="AD4" s="65"/>
+      <c r="AE4" s="66"/>
+      <c r="AF4" s="66"/>
+      <c r="AG4" s="66"/>
+      <c r="AH4" s="67"/>
+      <c r="AI4" s="67"/>
+      <c r="AJ4" s="67"/>
       <c r="AK4" s="25">
         <f>SUMIF(E4:AJ4,"&lt;&gt;",$E$3:$AJ$3)</f>
         <v>9</v>
@@ -4951,31 +5130,31 @@
         <v>12</v>
       </c>
       <c r="K5" s="62"/>
-      <c r="L5" s="64"/>
-      <c r="M5" s="64"/>
-      <c r="N5" s="64"/>
-      <c r="O5" s="64"/>
-      <c r="P5" s="64"/>
-      <c r="Q5" s="64"/>
-      <c r="R5" s="64"/>
+      <c r="L5" s="63"/>
+      <c r="M5" s="63"/>
+      <c r="N5" s="63"/>
+      <c r="O5" s="63"/>
+      <c r="P5" s="63"/>
+      <c r="Q5" s="63"/>
+      <c r="R5" s="63"/>
       <c r="S5" s="24"/>
       <c r="T5" s="24"/>
-      <c r="U5" s="65"/>
-      <c r="V5" s="65"/>
-      <c r="W5" s="65"/>
-      <c r="X5" s="65"/>
-      <c r="Y5" s="65"/>
-      <c r="Z5" s="66"/>
-      <c r="AA5" s="66"/>
-      <c r="AB5" s="66"/>
-      <c r="AC5" s="66"/>
-      <c r="AD5" s="66"/>
-      <c r="AE5" s="67"/>
-      <c r="AF5" s="67"/>
-      <c r="AG5" s="67"/>
-      <c r="AH5" s="68"/>
-      <c r="AI5" s="68"/>
-      <c r="AJ5" s="68"/>
+      <c r="U5" s="64"/>
+      <c r="V5" s="64"/>
+      <c r="W5" s="64"/>
+      <c r="X5" s="64"/>
+      <c r="Y5" s="64"/>
+      <c r="Z5" s="65"/>
+      <c r="AA5" s="65"/>
+      <c r="AB5" s="65"/>
+      <c r="AC5" s="65"/>
+      <c r="AD5" s="65"/>
+      <c r="AE5" s="66"/>
+      <c r="AF5" s="66"/>
+      <c r="AG5" s="66"/>
+      <c r="AH5" s="67"/>
+      <c r="AI5" s="67"/>
+      <c r="AJ5" s="67"/>
       <c r="AK5" s="25">
         <f t="shared" ref="AK5:AK34" si="0">SUMIF(E5:AJ5,"&lt;&gt;",$E$3:$AJ$3)</f>
         <v>3</v>
@@ -5011,47 +5190,47 @@
         <v>12</v>
       </c>
       <c r="K6" s="62"/>
-      <c r="L6" s="64"/>
-      <c r="M6" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="N6" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="O6" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="P6" s="64"/>
-      <c r="Q6" s="64"/>
-      <c r="R6" s="64"/>
+      <c r="L6" s="63"/>
+      <c r="M6" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="N6" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="O6" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="P6" s="63"/>
+      <c r="Q6" s="63"/>
+      <c r="R6" s="63"/>
       <c r="S6" s="24"/>
       <c r="T6" s="24"/>
-      <c r="U6" s="65" t="s">
-        <v>12</v>
-      </c>
-      <c r="V6" s="65"/>
-      <c r="W6" s="65" t="s">
-        <v>12</v>
-      </c>
-      <c r="X6" s="65"/>
-      <c r="Y6" s="65"/>
-      <c r="Z6" s="66" t="s">
-        <v>12</v>
-      </c>
-      <c r="AA6" s="66"/>
-      <c r="AB6" s="66"/>
-      <c r="AC6" s="66" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD6" s="66" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE6" s="67"/>
-      <c r="AF6" s="67"/>
-      <c r="AG6" s="67"/>
-      <c r="AH6" s="68"/>
-      <c r="AI6" s="68"/>
-      <c r="AJ6" s="68"/>
+      <c r="U6" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="V6" s="64"/>
+      <c r="W6" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="X6" s="64"/>
+      <c r="Y6" s="64"/>
+      <c r="Z6" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA6" s="65"/>
+      <c r="AB6" s="65"/>
+      <c r="AC6" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD6" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE6" s="66"/>
+      <c r="AF6" s="66"/>
+      <c r="AG6" s="66"/>
+      <c r="AH6" s="67"/>
+      <c r="AI6" s="67"/>
+      <c r="AJ6" s="67"/>
       <c r="AK6" s="25">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -5089,43 +5268,43 @@
         <v>12</v>
       </c>
       <c r="K7" s="62"/>
-      <c r="L7" s="64"/>
-      <c r="M7" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="N7" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="O7" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="P7" s="64"/>
-      <c r="Q7" s="64"/>
-      <c r="R7" s="64"/>
+      <c r="L7" s="63"/>
+      <c r="M7" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="N7" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="O7" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="P7" s="63"/>
+      <c r="Q7" s="63"/>
+      <c r="R7" s="63"/>
       <c r="S7" s="24"/>
       <c r="T7" s="24"/>
-      <c r="U7" s="65"/>
-      <c r="V7" s="65"/>
-      <c r="W7" s="65"/>
-      <c r="X7" s="65"/>
-      <c r="Y7" s="65" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z7" s="66"/>
-      <c r="AA7" s="66"/>
-      <c r="AB7" s="66"/>
-      <c r="AC7" s="66" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD7" s="66" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE7" s="67"/>
-      <c r="AF7" s="67"/>
-      <c r="AG7" s="67"/>
-      <c r="AH7" s="68"/>
-      <c r="AI7" s="68"/>
-      <c r="AJ7" s="68"/>
+      <c r="U7" s="64"/>
+      <c r="V7" s="64"/>
+      <c r="W7" s="64"/>
+      <c r="X7" s="64"/>
+      <c r="Y7" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z7" s="65"/>
+      <c r="AA7" s="65"/>
+      <c r="AB7" s="65"/>
+      <c r="AC7" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD7" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE7" s="66"/>
+      <c r="AF7" s="66"/>
+      <c r="AG7" s="66"/>
+      <c r="AH7" s="67"/>
+      <c r="AI7" s="67"/>
+      <c r="AJ7" s="67"/>
       <c r="AK7" s="25">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -5157,45 +5336,45 @@
       <c r="I8" s="62"/>
       <c r="J8" s="62"/>
       <c r="K8" s="62"/>
-      <c r="L8" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="M8" s="64"/>
-      <c r="N8" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="O8" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="P8" s="64"/>
-      <c r="Q8" s="64"/>
-      <c r="R8" s="64"/>
+      <c r="L8" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="M8" s="63"/>
+      <c r="N8" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="O8" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="P8" s="63"/>
+      <c r="Q8" s="63"/>
+      <c r="R8" s="63"/>
       <c r="S8" s="24"/>
       <c r="T8" s="24"/>
-      <c r="U8" s="65"/>
-      <c r="V8" s="65"/>
-      <c r="W8" s="65"/>
-      <c r="X8" s="65"/>
-      <c r="Y8" s="65" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z8" s="66"/>
-      <c r="AA8" s="66" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB8" s="66"/>
-      <c r="AC8" s="66" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD8" s="66" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE8" s="67"/>
-      <c r="AF8" s="67"/>
-      <c r="AG8" s="67"/>
-      <c r="AH8" s="68"/>
-      <c r="AI8" s="68"/>
-      <c r="AJ8" s="68"/>
+      <c r="U8" s="64"/>
+      <c r="V8" s="64"/>
+      <c r="W8" s="64"/>
+      <c r="X8" s="64"/>
+      <c r="Y8" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z8" s="65"/>
+      <c r="AA8" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB8" s="65"/>
+      <c r="AC8" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD8" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE8" s="66"/>
+      <c r="AF8" s="66"/>
+      <c r="AG8" s="66"/>
+      <c r="AH8" s="67"/>
+      <c r="AI8" s="67"/>
+      <c r="AJ8" s="67"/>
       <c r="AK8" s="25">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -5231,39 +5410,39 @@
       <c r="K9" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="L9" s="64"/>
-      <c r="M9" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="N9" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="O9" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="P9" s="64"/>
-      <c r="Q9" s="64"/>
-      <c r="R9" s="64"/>
+      <c r="L9" s="63"/>
+      <c r="M9" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="N9" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="O9" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="P9" s="63"/>
+      <c r="Q9" s="63"/>
+      <c r="R9" s="63"/>
       <c r="S9" s="24"/>
       <c r="T9" s="24"/>
-      <c r="U9" s="65"/>
-      <c r="V9" s="65"/>
-      <c r="W9" s="65"/>
-      <c r="X9" s="65"/>
-      <c r="Y9" s="65"/>
-      <c r="Z9" s="66"/>
-      <c r="AA9" s="66" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB9" s="66"/>
-      <c r="AC9" s="66"/>
-      <c r="AD9" s="66"/>
-      <c r="AE9" s="67"/>
-      <c r="AF9" s="67"/>
-      <c r="AG9" s="67"/>
-      <c r="AH9" s="68"/>
-      <c r="AI9" s="68"/>
-      <c r="AJ9" s="68"/>
+      <c r="U9" s="64"/>
+      <c r="V9" s="64"/>
+      <c r="W9" s="64"/>
+      <c r="X9" s="64"/>
+      <c r="Y9" s="64"/>
+      <c r="Z9" s="65"/>
+      <c r="AA9" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB9" s="65"/>
+      <c r="AC9" s="65"/>
+      <c r="AD9" s="65"/>
+      <c r="AE9" s="66"/>
+      <c r="AF9" s="66"/>
+      <c r="AG9" s="66"/>
+      <c r="AH9" s="67"/>
+      <c r="AI9" s="67"/>
+      <c r="AJ9" s="67"/>
       <c r="AK9" s="25">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -5289,39 +5468,39 @@
       <c r="I10" s="62"/>
       <c r="J10" s="62"/>
       <c r="K10" s="62"/>
-      <c r="L10" s="64"/>
-      <c r="M10" s="64"/>
-      <c r="N10" s="64"/>
-      <c r="O10" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="P10" s="64"/>
-      <c r="Q10" s="64"/>
-      <c r="R10" s="64"/>
+      <c r="L10" s="63"/>
+      <c r="M10" s="63"/>
+      <c r="N10" s="63"/>
+      <c r="O10" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="P10" s="63"/>
+      <c r="Q10" s="63"/>
+      <c r="R10" s="63"/>
       <c r="S10" s="27"/>
       <c r="T10" s="27"/>
-      <c r="U10" s="65"/>
-      <c r="V10" s="65"/>
-      <c r="W10" s="65"/>
-      <c r="X10" s="65"/>
-      <c r="Y10" s="65"/>
-      <c r="Z10" s="66" t="s">
-        <v>12</v>
-      </c>
-      <c r="AA10" s="66" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB10" s="66"/>
-      <c r="AC10" s="66"/>
-      <c r="AD10" s="66" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE10" s="67"/>
-      <c r="AF10" s="67"/>
-      <c r="AG10" s="67"/>
-      <c r="AH10" s="68"/>
-      <c r="AI10" s="68"/>
-      <c r="AJ10" s="68"/>
+      <c r="U10" s="64"/>
+      <c r="V10" s="64"/>
+      <c r="W10" s="64"/>
+      <c r="X10" s="64"/>
+      <c r="Y10" s="64"/>
+      <c r="Z10" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA10" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB10" s="65"/>
+      <c r="AC10" s="65"/>
+      <c r="AD10" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE10" s="66"/>
+      <c r="AF10" s="66"/>
+      <c r="AG10" s="66"/>
+      <c r="AH10" s="67"/>
+      <c r="AI10" s="67"/>
+      <c r="AJ10" s="67"/>
       <c r="AK10" s="25">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -5349,39 +5528,39 @@
       </c>
       <c r="J11" s="62"/>
       <c r="K11" s="62"/>
-      <c r="L11" s="64"/>
-      <c r="M11" s="64"/>
-      <c r="N11" s="64"/>
-      <c r="O11" s="64"/>
-      <c r="P11" s="64"/>
-      <c r="Q11" s="64"/>
-      <c r="R11" s="64"/>
+      <c r="L11" s="63"/>
+      <c r="M11" s="63"/>
+      <c r="N11" s="63"/>
+      <c r="O11" s="63"/>
+      <c r="P11" s="63"/>
+      <c r="Q11" s="63"/>
+      <c r="R11" s="63"/>
       <c r="S11" s="29" t="s">
         <v>12</v>
       </c>
       <c r="T11" s="29"/>
-      <c r="U11" s="65"/>
-      <c r="V11" s="65"/>
-      <c r="W11" s="65"/>
-      <c r="X11" s="65"/>
-      <c r="Y11" s="65" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z11" s="66"/>
-      <c r="AA11" s="66" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB11" s="66"/>
-      <c r="AC11" s="66" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD11" s="66"/>
-      <c r="AE11" s="67"/>
-      <c r="AF11" s="67"/>
-      <c r="AG11" s="67"/>
-      <c r="AH11" s="68"/>
-      <c r="AI11" s="68"/>
-      <c r="AJ11" s="68"/>
+      <c r="U11" s="64"/>
+      <c r="V11" s="64"/>
+      <c r="W11" s="64"/>
+      <c r="X11" s="64"/>
+      <c r="Y11" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z11" s="65"/>
+      <c r="AA11" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB11" s="65"/>
+      <c r="AC11" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD11" s="65"/>
+      <c r="AE11" s="66"/>
+      <c r="AF11" s="66"/>
+      <c r="AG11" s="66"/>
+      <c r="AH11" s="67"/>
+      <c r="AI11" s="67"/>
+      <c r="AJ11" s="67"/>
       <c r="AK11" s="25">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -5417,41 +5596,41 @@
         <v>12</v>
       </c>
       <c r="K12" s="62"/>
-      <c r="L12" s="64"/>
-      <c r="M12" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="N12" s="64"/>
-      <c r="O12" s="64"/>
-      <c r="P12" s="64"/>
-      <c r="Q12" s="64"/>
-      <c r="R12" s="64"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="N12" s="63"/>
+      <c r="O12" s="63"/>
+      <c r="P12" s="63"/>
+      <c r="Q12" s="63"/>
+      <c r="R12" s="63"/>
       <c r="S12" s="28"/>
       <c r="T12" s="28"/>
-      <c r="U12" s="65"/>
-      <c r="V12" s="65" t="s">
-        <v>12</v>
-      </c>
-      <c r="W12" s="65"/>
-      <c r="X12" s="65" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y12" s="65"/>
-      <c r="Z12" s="66"/>
-      <c r="AA12" s="66"/>
-      <c r="AB12" s="66"/>
-      <c r="AC12" s="66" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD12" s="66" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE12" s="67"/>
-      <c r="AF12" s="67"/>
-      <c r="AG12" s="67"/>
-      <c r="AH12" s="68"/>
-      <c r="AI12" s="68"/>
-      <c r="AJ12" s="68"/>
+      <c r="U12" s="64"/>
+      <c r="V12" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="W12" s="64"/>
+      <c r="X12" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y12" s="64"/>
+      <c r="Z12" s="65"/>
+      <c r="AA12" s="65"/>
+      <c r="AB12" s="65"/>
+      <c r="AC12" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD12" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE12" s="66"/>
+      <c r="AF12" s="66"/>
+      <c r="AG12" s="66"/>
+      <c r="AH12" s="67"/>
+      <c r="AI12" s="67"/>
+      <c r="AJ12" s="67"/>
       <c r="AK12" s="25">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -5485,45 +5664,45 @@
       </c>
       <c r="J13" s="62"/>
       <c r="K13" s="62"/>
-      <c r="L13" s="64"/>
-      <c r="M13" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="N13" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="O13" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="P13" s="64"/>
-      <c r="Q13" s="64"/>
-      <c r="R13" s="64"/>
+      <c r="L13" s="63"/>
+      <c r="M13" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="N13" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="O13" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="P13" s="63"/>
+      <c r="Q13" s="63"/>
+      <c r="R13" s="63"/>
       <c r="S13" s="29"/>
       <c r="T13" s="29"/>
-      <c r="U13" s="65"/>
-      <c r="V13" s="65"/>
-      <c r="W13" s="65"/>
-      <c r="X13" s="65"/>
-      <c r="Y13" s="65"/>
-      <c r="Z13" s="66"/>
-      <c r="AA13" s="66"/>
-      <c r="AB13" s="66" t="s">
-        <v>12</v>
-      </c>
-      <c r="AC13" s="66" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD13" s="66" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE13" s="67"/>
-      <c r="AF13" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG13" s="67"/>
-      <c r="AH13" s="68"/>
-      <c r="AI13" s="68"/>
-      <c r="AJ13" s="68"/>
+      <c r="U13" s="64"/>
+      <c r="V13" s="64"/>
+      <c r="W13" s="64"/>
+      <c r="X13" s="64"/>
+      <c r="Y13" s="64"/>
+      <c r="Z13" s="65"/>
+      <c r="AA13" s="65"/>
+      <c r="AB13" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC13" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD13" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE13" s="66"/>
+      <c r="AF13" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG13" s="66"/>
+      <c r="AH13" s="67"/>
+      <c r="AI13" s="67"/>
+      <c r="AJ13" s="67"/>
       <c r="AK13" s="25">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -5559,53 +5738,53 @@
         <v>12</v>
       </c>
       <c r="K14" s="62"/>
-      <c r="L14" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="M14" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="N14" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="O14" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="P14" s="64"/>
-      <c r="Q14" s="64"/>
-      <c r="R14" s="64"/>
+      <c r="L14" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="M14" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="N14" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="O14" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="P14" s="63"/>
+      <c r="Q14" s="63"/>
+      <c r="R14" s="63"/>
       <c r="S14" s="29"/>
       <c r="T14" s="29"/>
-      <c r="U14" s="65"/>
-      <c r="V14" s="65"/>
-      <c r="W14" s="65"/>
-      <c r="X14" s="65" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y14" s="65"/>
-      <c r="Z14" s="66" t="s">
-        <v>12</v>
-      </c>
-      <c r="AA14" s="66"/>
-      <c r="AB14" s="66" t="s">
-        <v>12</v>
-      </c>
-      <c r="AC14" s="66" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD14" s="66" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE14" s="67"/>
-      <c r="AF14" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG14" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="AH14" s="68"/>
-      <c r="AI14" s="68"/>
-      <c r="AJ14" s="68"/>
+      <c r="U14" s="64"/>
+      <c r="V14" s="64"/>
+      <c r="W14" s="64"/>
+      <c r="X14" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y14" s="64"/>
+      <c r="Z14" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA14" s="65"/>
+      <c r="AB14" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC14" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD14" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE14" s="66"/>
+      <c r="AF14" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG14" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AH14" s="67"/>
+      <c r="AI14" s="67"/>
+      <c r="AJ14" s="67"/>
       <c r="AK14" s="25">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -5624,56 +5803,62 @@
       <c r="D15" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="H15" s="29"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="29"/>
-      <c r="K15" s="29"/>
-      <c r="L15" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="M15" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="N15" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="O15" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="P15" s="29"/>
-      <c r="Q15" s="29"/>
-      <c r="R15" s="29"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="62"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="62"/>
+      <c r="K15" s="62"/>
+      <c r="L15" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="M15" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="N15" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="O15" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="P15" s="63"/>
+      <c r="Q15" s="63"/>
+      <c r="R15" s="63"/>
       <c r="S15" s="29"/>
       <c r="T15" s="29"/>
-      <c r="U15" s="29"/>
-      <c r="V15" s="29"/>
-      <c r="W15" s="29"/>
-      <c r="X15" s="29"/>
-      <c r="Y15" s="29"/>
-      <c r="Z15" s="29"/>
-      <c r="AA15" s="29"/>
-      <c r="AB15" s="29"/>
-      <c r="AC15" s="29"/>
-      <c r="AD15" s="29"/>
-      <c r="AE15" s="29"/>
-      <c r="AF15" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG15" s="29"/>
-      <c r="AH15" s="29"/>
-      <c r="AI15" s="29"/>
-      <c r="AJ15" s="29"/>
+      <c r="U15" s="64"/>
+      <c r="V15" s="64"/>
+      <c r="W15" s="64"/>
+      <c r="X15" s="64"/>
+      <c r="Y15" s="64"/>
+      <c r="Z15" s="65"/>
+      <c r="AA15" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB15" s="65"/>
+      <c r="AC15" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD15" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE15" s="66"/>
+      <c r="AF15" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG15" s="66"/>
+      <c r="AH15" s="67"/>
+      <c r="AI15" s="67"/>
+      <c r="AJ15" s="67"/>
       <c r="AK15" s="25">
         <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:37">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:37" ht="15.75" thickBot="1">
       <c r="A16" s="21">
         <v>13</v>
       </c>
@@ -5683,88 +5868,102 @@
       <c r="C16" s="22">
         <v>46216</v>
       </c>
-      <c r="D16" s="23"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
-      <c r="M16" s="21"/>
-      <c r="N16" s="21"/>
-      <c r="O16" s="21"/>
-      <c r="P16" s="21"/>
-      <c r="Q16" s="21"/>
-      <c r="R16" s="21"/>
-      <c r="S16" s="21"/>
-      <c r="T16" s="21"/>
-      <c r="U16" s="21"/>
-      <c r="V16" s="21"/>
-      <c r="W16" s="21"/>
-      <c r="X16" s="21"/>
-      <c r="Y16" s="21"/>
-      <c r="Z16" s="21"/>
-      <c r="AA16" s="21"/>
-      <c r="AB16" s="21"/>
-      <c r="AC16" s="21"/>
-      <c r="AD16" s="21"/>
-      <c r="AE16" s="21"/>
-      <c r="AF16" s="21"/>
-      <c r="AG16" s="21"/>
-      <c r="AH16" s="21"/>
-      <c r="AI16" s="21"/>
-      <c r="AJ16" s="21"/>
+      <c r="D16" s="97" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" s="98"/>
+      <c r="F16" s="98"/>
+      <c r="G16" s="98" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="98"/>
+      <c r="I16" s="98"/>
+      <c r="J16" s="98"/>
+      <c r="K16" s="98"/>
+      <c r="L16" s="99"/>
+      <c r="M16" s="99" t="s">
+        <v>12</v>
+      </c>
+      <c r="N16" s="99" t="s">
+        <v>12</v>
+      </c>
+      <c r="O16" s="99" t="s">
+        <v>12</v>
+      </c>
+      <c r="P16" s="99"/>
+      <c r="Q16" s="99"/>
+      <c r="R16" s="99"/>
+      <c r="S16" s="100"/>
+      <c r="T16" s="100"/>
+      <c r="U16" s="101"/>
+      <c r="V16" s="101"/>
+      <c r="W16" s="101"/>
+      <c r="X16" s="101"/>
+      <c r="Y16" s="101"/>
+      <c r="Z16" s="102"/>
+      <c r="AA16" s="102"/>
+      <c r="AB16" s="102"/>
+      <c r="AC16" s="102" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD16" s="102"/>
+      <c r="AE16" s="103"/>
+      <c r="AF16" s="103"/>
+      <c r="AG16" s="103"/>
+      <c r="AH16" s="104"/>
+      <c r="AI16" s="104"/>
+      <c r="AJ16" s="104"/>
       <c r="AK16" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:37">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:37" ht="15.75" thickBot="1">
       <c r="A17" s="21">
         <v>14</v>
       </c>
       <c r="B17" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="95">
         <v>46217</v>
       </c>
-      <c r="D17" s="23"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
-      <c r="M17" s="21"/>
-      <c r="N17" s="21"/>
-      <c r="O17" s="21"/>
-      <c r="P17" s="21"/>
-      <c r="Q17" s="21"/>
-      <c r="R17" s="21"/>
-      <c r="S17" s="21"/>
-      <c r="T17" s="21"/>
-      <c r="U17" s="21"/>
-      <c r="V17" s="21"/>
-      <c r="W17" s="21"/>
-      <c r="X17" s="21"/>
-      <c r="Y17" s="21"/>
-      <c r="Z17" s="21"/>
-      <c r="AA17" s="21"/>
-      <c r="AB17" s="21"/>
-      <c r="AC17" s="63"/>
-      <c r="AD17" s="21"/>
-      <c r="AE17" s="21"/>
-      <c r="AF17" s="21"/>
-      <c r="AG17" s="21"/>
-      <c r="AH17" s="21"/>
-      <c r="AI17" s="21"/>
-      <c r="AJ17" s="21"/>
-      <c r="AK17" s="25">
+      <c r="D17" s="113" t="s">
+        <v>74</v>
+      </c>
+      <c r="E17" s="114"/>
+      <c r="F17" s="114"/>
+      <c r="G17" s="114"/>
+      <c r="H17" s="114"/>
+      <c r="I17" s="114"/>
+      <c r="J17" s="114"/>
+      <c r="K17" s="114"/>
+      <c r="L17" s="115"/>
+      <c r="M17" s="115"/>
+      <c r="N17" s="115"/>
+      <c r="O17" s="115"/>
+      <c r="P17" s="115"/>
+      <c r="Q17" s="115"/>
+      <c r="R17" s="115"/>
+      <c r="S17" s="116"/>
+      <c r="T17" s="116"/>
+      <c r="U17" s="117"/>
+      <c r="V17" s="117"/>
+      <c r="W17" s="117"/>
+      <c r="X17" s="117"/>
+      <c r="Y17" s="117"/>
+      <c r="Z17" s="118"/>
+      <c r="AA17" s="118"/>
+      <c r="AB17" s="118"/>
+      <c r="AC17" s="118"/>
+      <c r="AD17" s="118"/>
+      <c r="AE17" s="119"/>
+      <c r="AF17" s="119"/>
+      <c r="AG17" s="119"/>
+      <c r="AH17" s="120"/>
+      <c r="AI17" s="120"/>
+      <c r="AJ17" s="121"/>
+      <c r="AK17" s="96">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5779,39 +5978,39 @@
       <c r="C18" s="22">
         <v>46218</v>
       </c>
-      <c r="D18" s="23"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21"/>
-      <c r="M18" s="21"/>
-      <c r="N18" s="21"/>
-      <c r="O18" s="21"/>
-      <c r="P18" s="21"/>
-      <c r="Q18" s="21"/>
-      <c r="R18" s="21"/>
-      <c r="S18" s="21"/>
-      <c r="T18" s="21"/>
-      <c r="U18" s="21"/>
-      <c r="V18" s="21"/>
-      <c r="W18" s="21"/>
-      <c r="X18" s="21"/>
-      <c r="Y18" s="21"/>
-      <c r="Z18" s="21"/>
-      <c r="AA18" s="21"/>
-      <c r="AB18" s="21"/>
-      <c r="AC18" s="21"/>
-      <c r="AD18" s="21"/>
-      <c r="AE18" s="21"/>
-      <c r="AF18" s="21"/>
-      <c r="AG18" s="21"/>
-      <c r="AH18" s="21"/>
-      <c r="AI18" s="21"/>
-      <c r="AJ18" s="21"/>
+      <c r="D18" s="105"/>
+      <c r="E18" s="106"/>
+      <c r="F18" s="106"/>
+      <c r="G18" s="106"/>
+      <c r="H18" s="106"/>
+      <c r="I18" s="106"/>
+      <c r="J18" s="106"/>
+      <c r="K18" s="106"/>
+      <c r="L18" s="107"/>
+      <c r="M18" s="107"/>
+      <c r="N18" s="107"/>
+      <c r="O18" s="107"/>
+      <c r="P18" s="107"/>
+      <c r="Q18" s="107"/>
+      <c r="R18" s="107"/>
+      <c r="S18" s="108"/>
+      <c r="T18" s="108"/>
+      <c r="U18" s="109"/>
+      <c r="V18" s="109"/>
+      <c r="W18" s="109"/>
+      <c r="X18" s="109"/>
+      <c r="Y18" s="109"/>
+      <c r="Z18" s="110"/>
+      <c r="AA18" s="110"/>
+      <c r="AB18" s="110"/>
+      <c r="AC18" s="110"/>
+      <c r="AD18" s="110"/>
+      <c r="AE18" s="111"/>
+      <c r="AF18" s="111"/>
+      <c r="AG18" s="111"/>
+      <c r="AH18" s="112"/>
+      <c r="AI18" s="112"/>
+      <c r="AJ18" s="112"/>
       <c r="AK18" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5828,38 +6027,38 @@
         <v>46219</v>
       </c>
       <c r="D19" s="23"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="21"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="21"/>
-      <c r="M19" s="21"/>
-      <c r="N19" s="21"/>
-      <c r="O19" s="21"/>
-      <c r="P19" s="21"/>
-      <c r="Q19" s="21"/>
-      <c r="R19" s="21"/>
-      <c r="S19" s="21"/>
-      <c r="T19" s="21"/>
-      <c r="U19" s="21"/>
-      <c r="V19" s="21"/>
-      <c r="W19" s="21"/>
-      <c r="X19" s="21"/>
-      <c r="Y19" s="21"/>
-      <c r="Z19" s="21"/>
-      <c r="AA19" s="21"/>
-      <c r="AB19" s="21"/>
-      <c r="AC19" s="21"/>
-      <c r="AD19" s="21"/>
-      <c r="AE19" s="21"/>
-      <c r="AF19" s="21"/>
-      <c r="AG19" s="21"/>
-      <c r="AH19" s="21"/>
-      <c r="AI19" s="21"/>
-      <c r="AJ19" s="21"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="62"/>
+      <c r="G19" s="62"/>
+      <c r="H19" s="62"/>
+      <c r="I19" s="62"/>
+      <c r="J19" s="62"/>
+      <c r="K19" s="62"/>
+      <c r="L19" s="63"/>
+      <c r="M19" s="63"/>
+      <c r="N19" s="63"/>
+      <c r="O19" s="63"/>
+      <c r="P19" s="63"/>
+      <c r="Q19" s="63"/>
+      <c r="R19" s="63"/>
+      <c r="S19" s="29"/>
+      <c r="T19" s="29"/>
+      <c r="U19" s="64"/>
+      <c r="V19" s="64"/>
+      <c r="W19" s="64"/>
+      <c r="X19" s="64"/>
+      <c r="Y19" s="64"/>
+      <c r="Z19" s="65"/>
+      <c r="AA19" s="65"/>
+      <c r="AB19" s="65"/>
+      <c r="AC19" s="65"/>
+      <c r="AD19" s="65"/>
+      <c r="AE19" s="66"/>
+      <c r="AF19" s="66"/>
+      <c r="AG19" s="66"/>
+      <c r="AH19" s="67"/>
+      <c r="AI19" s="67"/>
+      <c r="AJ19" s="67"/>
       <c r="AK19" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5876,38 +6075,38 @@
         <v>46220</v>
       </c>
       <c r="D20" s="23"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="21"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="21"/>
-      <c r="M20" s="21"/>
-      <c r="N20" s="21"/>
-      <c r="O20" s="21"/>
-      <c r="P20" s="21"/>
-      <c r="Q20" s="21"/>
-      <c r="R20" s="21"/>
-      <c r="S20" s="21"/>
-      <c r="T20" s="21"/>
-      <c r="U20" s="21"/>
-      <c r="V20" s="21"/>
-      <c r="W20" s="21"/>
-      <c r="X20" s="21"/>
-      <c r="Y20" s="21"/>
-      <c r="Z20" s="21"/>
-      <c r="AA20" s="21"/>
-      <c r="AB20" s="21"/>
-      <c r="AC20" s="21"/>
-      <c r="AD20" s="21"/>
-      <c r="AE20" s="21"/>
-      <c r="AF20" s="21"/>
-      <c r="AG20" s="21"/>
-      <c r="AH20" s="21"/>
-      <c r="AI20" s="21"/>
-      <c r="AJ20" s="21"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="62"/>
+      <c r="H20" s="62"/>
+      <c r="I20" s="62"/>
+      <c r="J20" s="62"/>
+      <c r="K20" s="62"/>
+      <c r="L20" s="63"/>
+      <c r="M20" s="63"/>
+      <c r="N20" s="63"/>
+      <c r="O20" s="63"/>
+      <c r="P20" s="63"/>
+      <c r="Q20" s="63"/>
+      <c r="R20" s="63"/>
+      <c r="S20" s="29"/>
+      <c r="T20" s="29"/>
+      <c r="U20" s="64"/>
+      <c r="V20" s="64"/>
+      <c r="W20" s="64"/>
+      <c r="X20" s="64"/>
+      <c r="Y20" s="64"/>
+      <c r="Z20" s="65"/>
+      <c r="AA20" s="65"/>
+      <c r="AB20" s="65"/>
+      <c r="AC20" s="65"/>
+      <c r="AD20" s="65"/>
+      <c r="AE20" s="66"/>
+      <c r="AF20" s="66"/>
+      <c r="AG20" s="66"/>
+      <c r="AH20" s="67"/>
+      <c r="AI20" s="67"/>
+      <c r="AJ20" s="67"/>
       <c r="AK20" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5924,38 +6123,38 @@
         <v>46221</v>
       </c>
       <c r="D21" s="23"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21"/>
-      <c r="M21" s="21"/>
-      <c r="N21" s="21"/>
-      <c r="O21" s="21"/>
-      <c r="P21" s="21"/>
-      <c r="Q21" s="21"/>
-      <c r="R21" s="21"/>
-      <c r="S21" s="21"/>
-      <c r="T21" s="21"/>
-      <c r="U21" s="21"/>
-      <c r="V21" s="21"/>
-      <c r="W21" s="21"/>
-      <c r="X21" s="21"/>
-      <c r="Y21" s="21"/>
-      <c r="Z21" s="21"/>
-      <c r="AA21" s="21"/>
-      <c r="AB21" s="21"/>
-      <c r="AC21" s="21"/>
-      <c r="AD21" s="21"/>
-      <c r="AE21" s="21"/>
-      <c r="AF21" s="21"/>
-      <c r="AG21" s="21"/>
-      <c r="AH21" s="21"/>
-      <c r="AI21" s="21"/>
-      <c r="AJ21" s="21"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="62"/>
+      <c r="H21" s="62"/>
+      <c r="I21" s="62"/>
+      <c r="J21" s="62"/>
+      <c r="K21" s="62"/>
+      <c r="L21" s="63"/>
+      <c r="M21" s="63"/>
+      <c r="N21" s="63"/>
+      <c r="O21" s="63"/>
+      <c r="P21" s="63"/>
+      <c r="Q21" s="63"/>
+      <c r="R21" s="63"/>
+      <c r="S21" s="29"/>
+      <c r="T21" s="29"/>
+      <c r="U21" s="64"/>
+      <c r="V21" s="64"/>
+      <c r="W21" s="64"/>
+      <c r="X21" s="64"/>
+      <c r="Y21" s="64"/>
+      <c r="Z21" s="65"/>
+      <c r="AA21" s="65"/>
+      <c r="AB21" s="65"/>
+      <c r="AC21" s="65"/>
+      <c r="AD21" s="65"/>
+      <c r="AE21" s="66"/>
+      <c r="AF21" s="66"/>
+      <c r="AG21" s="66"/>
+      <c r="AH21" s="67"/>
+      <c r="AI21" s="67"/>
+      <c r="AJ21" s="67"/>
       <c r="AK21" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5972,38 +6171,38 @@
         <v>46222</v>
       </c>
       <c r="D22" s="23"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
-      <c r="L22" s="21"/>
-      <c r="M22" s="21"/>
-      <c r="N22" s="21"/>
-      <c r="O22" s="21"/>
-      <c r="P22" s="21"/>
-      <c r="Q22" s="21"/>
-      <c r="R22" s="21"/>
-      <c r="S22" s="21"/>
-      <c r="T22" s="21"/>
-      <c r="U22" s="21"/>
-      <c r="V22" s="21"/>
-      <c r="W22" s="21"/>
-      <c r="X22" s="21"/>
-      <c r="Y22" s="21"/>
-      <c r="Z22" s="21"/>
-      <c r="AA22" s="21"/>
-      <c r="AB22" s="21"/>
-      <c r="AC22" s="21"/>
-      <c r="AD22" s="21"/>
-      <c r="AE22" s="21"/>
-      <c r="AF22" s="21"/>
-      <c r="AG22" s="21"/>
-      <c r="AH22" s="21"/>
-      <c r="AI22" s="21"/>
-      <c r="AJ22" s="21"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="62"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="63"/>
+      <c r="M22" s="63"/>
+      <c r="N22" s="63"/>
+      <c r="O22" s="63"/>
+      <c r="P22" s="63"/>
+      <c r="Q22" s="63"/>
+      <c r="R22" s="63"/>
+      <c r="S22" s="29"/>
+      <c r="T22" s="29"/>
+      <c r="U22" s="64"/>
+      <c r="V22" s="64"/>
+      <c r="W22" s="64"/>
+      <c r="X22" s="64"/>
+      <c r="Y22" s="64"/>
+      <c r="Z22" s="65"/>
+      <c r="AA22" s="65"/>
+      <c r="AB22" s="65"/>
+      <c r="AC22" s="65"/>
+      <c r="AD22" s="65"/>
+      <c r="AE22" s="66"/>
+      <c r="AF22" s="66"/>
+      <c r="AG22" s="66"/>
+      <c r="AH22" s="67"/>
+      <c r="AI22" s="67"/>
+      <c r="AJ22" s="67"/>
       <c r="AK22" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6020,38 +6219,38 @@
         <v>46223</v>
       </c>
       <c r="D23" s="23"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="21"/>
-      <c r="M23" s="21"/>
-      <c r="N23" s="21"/>
-      <c r="O23" s="21"/>
-      <c r="P23" s="21"/>
-      <c r="Q23" s="21"/>
-      <c r="R23" s="21"/>
-      <c r="S23" s="21"/>
-      <c r="T23" s="21"/>
-      <c r="U23" s="21"/>
-      <c r="V23" s="21"/>
-      <c r="W23" s="21"/>
-      <c r="X23" s="21"/>
-      <c r="Y23" s="21"/>
-      <c r="Z23" s="21"/>
-      <c r="AA23" s="21"/>
-      <c r="AB23" s="21"/>
-      <c r="AC23" s="21"/>
-      <c r="AD23" s="21"/>
-      <c r="AE23" s="21"/>
-      <c r="AF23" s="21"/>
-      <c r="AG23" s="21"/>
-      <c r="AH23" s="21"/>
-      <c r="AI23" s="21"/>
-      <c r="AJ23" s="21"/>
+      <c r="E23" s="62"/>
+      <c r="F23" s="62"/>
+      <c r="G23" s="62"/>
+      <c r="H23" s="62"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="62"/>
+      <c r="K23" s="62"/>
+      <c r="L23" s="63"/>
+      <c r="M23" s="63"/>
+      <c r="N23" s="63"/>
+      <c r="O23" s="63"/>
+      <c r="P23" s="63"/>
+      <c r="Q23" s="63"/>
+      <c r="R23" s="63"/>
+      <c r="S23" s="29"/>
+      <c r="T23" s="29"/>
+      <c r="U23" s="64"/>
+      <c r="V23" s="64"/>
+      <c r="W23" s="64"/>
+      <c r="X23" s="64"/>
+      <c r="Y23" s="64"/>
+      <c r="Z23" s="65"/>
+      <c r="AA23" s="65"/>
+      <c r="AB23" s="65"/>
+      <c r="AC23" s="65"/>
+      <c r="AD23" s="65"/>
+      <c r="AE23" s="66"/>
+      <c r="AF23" s="66"/>
+      <c r="AG23" s="66"/>
+      <c r="AH23" s="67"/>
+      <c r="AI23" s="67"/>
+      <c r="AJ23" s="67"/>
       <c r="AK23" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6068,38 +6267,38 @@
         <v>46224</v>
       </c>
       <c r="D24" s="23"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="21"/>
-      <c r="K24" s="21"/>
-      <c r="L24" s="21"/>
-      <c r="M24" s="21"/>
-      <c r="N24" s="21"/>
-      <c r="O24" s="21"/>
-      <c r="P24" s="21"/>
-      <c r="Q24" s="21"/>
-      <c r="R24" s="21"/>
-      <c r="S24" s="21"/>
-      <c r="T24" s="21"/>
-      <c r="U24" s="21"/>
-      <c r="V24" s="21"/>
-      <c r="W24" s="21"/>
-      <c r="X24" s="21"/>
-      <c r="Y24" s="21"/>
-      <c r="Z24" s="21"/>
-      <c r="AA24" s="21"/>
-      <c r="AB24" s="21"/>
-      <c r="AC24" s="21"/>
-      <c r="AD24" s="21"/>
-      <c r="AE24" s="21"/>
-      <c r="AF24" s="21"/>
-      <c r="AG24" s="21"/>
-      <c r="AH24" s="21"/>
-      <c r="AI24" s="21"/>
-      <c r="AJ24" s="21"/>
+      <c r="E24" s="62"/>
+      <c r="F24" s="62"/>
+      <c r="G24" s="62"/>
+      <c r="H24" s="62"/>
+      <c r="I24" s="62"/>
+      <c r="J24" s="62"/>
+      <c r="K24" s="62"/>
+      <c r="L24" s="63"/>
+      <c r="M24" s="63"/>
+      <c r="N24" s="63"/>
+      <c r="O24" s="63"/>
+      <c r="P24" s="63"/>
+      <c r="Q24" s="63"/>
+      <c r="R24" s="63"/>
+      <c r="S24" s="29"/>
+      <c r="T24" s="29"/>
+      <c r="U24" s="64"/>
+      <c r="V24" s="64"/>
+      <c r="W24" s="64"/>
+      <c r="X24" s="64"/>
+      <c r="Y24" s="64"/>
+      <c r="Z24" s="65"/>
+      <c r="AA24" s="65"/>
+      <c r="AB24" s="65"/>
+      <c r="AC24" s="65"/>
+      <c r="AD24" s="65"/>
+      <c r="AE24" s="66"/>
+      <c r="AF24" s="66"/>
+      <c r="AG24" s="66"/>
+      <c r="AH24" s="67"/>
+      <c r="AI24" s="67"/>
+      <c r="AJ24" s="67"/>
       <c r="AK24" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6116,38 +6315,38 @@
         <v>46225</v>
       </c>
       <c r="D25" s="23"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="21"/>
-      <c r="K25" s="21"/>
-      <c r="L25" s="21"/>
-      <c r="M25" s="21"/>
-      <c r="N25" s="21"/>
-      <c r="O25" s="21"/>
-      <c r="P25" s="21"/>
-      <c r="Q25" s="21"/>
-      <c r="R25" s="21"/>
-      <c r="S25" s="21"/>
-      <c r="T25" s="21"/>
-      <c r="U25" s="21"/>
-      <c r="V25" s="21"/>
-      <c r="W25" s="21"/>
-      <c r="X25" s="21"/>
-      <c r="Y25" s="21"/>
-      <c r="Z25" s="21"/>
-      <c r="AA25" s="21"/>
-      <c r="AB25" s="21"/>
-      <c r="AC25" s="21"/>
-      <c r="AD25" s="21"/>
-      <c r="AE25" s="21"/>
-      <c r="AF25" s="21"/>
-      <c r="AG25" s="21"/>
-      <c r="AH25" s="21"/>
-      <c r="AI25" s="21"/>
-      <c r="AJ25" s="21"/>
+      <c r="E25" s="62"/>
+      <c r="F25" s="62"/>
+      <c r="G25" s="62"/>
+      <c r="H25" s="62"/>
+      <c r="I25" s="62"/>
+      <c r="J25" s="62"/>
+      <c r="K25" s="62"/>
+      <c r="L25" s="63"/>
+      <c r="M25" s="63"/>
+      <c r="N25" s="63"/>
+      <c r="O25" s="63"/>
+      <c r="P25" s="63"/>
+      <c r="Q25" s="63"/>
+      <c r="R25" s="63"/>
+      <c r="S25" s="29"/>
+      <c r="T25" s="29"/>
+      <c r="U25" s="64"/>
+      <c r="V25" s="64"/>
+      <c r="W25" s="64"/>
+      <c r="X25" s="64"/>
+      <c r="Y25" s="64"/>
+      <c r="Z25" s="65"/>
+      <c r="AA25" s="65"/>
+      <c r="AB25" s="65"/>
+      <c r="AC25" s="65"/>
+      <c r="AD25" s="65"/>
+      <c r="AE25" s="66"/>
+      <c r="AF25" s="66"/>
+      <c r="AG25" s="66"/>
+      <c r="AH25" s="67"/>
+      <c r="AI25" s="67"/>
+      <c r="AJ25" s="67"/>
       <c r="AK25" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6164,38 +6363,38 @@
         <v>46226</v>
       </c>
       <c r="D26" s="23"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="21"/>
-      <c r="K26" s="21"/>
-      <c r="L26" s="21"/>
-      <c r="M26" s="21"/>
-      <c r="N26" s="21"/>
-      <c r="O26" s="21"/>
-      <c r="P26" s="21"/>
-      <c r="Q26" s="21"/>
-      <c r="R26" s="21"/>
-      <c r="S26" s="21"/>
-      <c r="T26" s="21"/>
-      <c r="U26" s="21"/>
-      <c r="V26" s="21"/>
-      <c r="W26" s="21"/>
-      <c r="X26" s="21"/>
-      <c r="Y26" s="21"/>
-      <c r="Z26" s="21"/>
-      <c r="AA26" s="21"/>
-      <c r="AB26" s="21"/>
-      <c r="AC26" s="21"/>
-      <c r="AD26" s="21"/>
-      <c r="AE26" s="21"/>
-      <c r="AF26" s="21"/>
-      <c r="AG26" s="21"/>
-      <c r="AH26" s="21"/>
-      <c r="AI26" s="21"/>
-      <c r="AJ26" s="21"/>
+      <c r="E26" s="62"/>
+      <c r="F26" s="62"/>
+      <c r="G26" s="62"/>
+      <c r="H26" s="62"/>
+      <c r="I26" s="62"/>
+      <c r="J26" s="62"/>
+      <c r="K26" s="62"/>
+      <c r="L26" s="63"/>
+      <c r="M26" s="63"/>
+      <c r="N26" s="63"/>
+      <c r="O26" s="63"/>
+      <c r="P26" s="63"/>
+      <c r="Q26" s="63"/>
+      <c r="R26" s="63"/>
+      <c r="S26" s="29"/>
+      <c r="T26" s="29"/>
+      <c r="U26" s="64"/>
+      <c r="V26" s="64"/>
+      <c r="W26" s="64"/>
+      <c r="X26" s="64"/>
+      <c r="Y26" s="64"/>
+      <c r="Z26" s="65"/>
+      <c r="AA26" s="65"/>
+      <c r="AB26" s="65"/>
+      <c r="AC26" s="65"/>
+      <c r="AD26" s="65"/>
+      <c r="AE26" s="66"/>
+      <c r="AF26" s="66"/>
+      <c r="AG26" s="66"/>
+      <c r="AH26" s="67"/>
+      <c r="AI26" s="67"/>
+      <c r="AJ26" s="67"/>
       <c r="AK26" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6212,38 +6411,38 @@
         <v>46227</v>
       </c>
       <c r="D27" s="23"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
-      <c r="I27" s="21"/>
-      <c r="J27" s="21"/>
-      <c r="K27" s="21"/>
-      <c r="L27" s="21"/>
-      <c r="M27" s="21"/>
-      <c r="N27" s="21"/>
-      <c r="O27" s="21"/>
-      <c r="P27" s="21"/>
-      <c r="Q27" s="21"/>
-      <c r="R27" s="21"/>
-      <c r="S27" s="21"/>
-      <c r="T27" s="21"/>
-      <c r="U27" s="21"/>
-      <c r="V27" s="21"/>
-      <c r="W27" s="21"/>
-      <c r="X27" s="21"/>
-      <c r="Y27" s="21"/>
-      <c r="Z27" s="21"/>
-      <c r="AA27" s="21"/>
-      <c r="AB27" s="21"/>
-      <c r="AC27" s="21"/>
-      <c r="AD27" s="21"/>
-      <c r="AE27" s="21"/>
-      <c r="AF27" s="21"/>
-      <c r="AG27" s="21"/>
-      <c r="AH27" s="21"/>
-      <c r="AI27" s="21"/>
-      <c r="AJ27" s="21"/>
+      <c r="E27" s="62"/>
+      <c r="F27" s="62"/>
+      <c r="G27" s="62"/>
+      <c r="H27" s="62"/>
+      <c r="I27" s="62"/>
+      <c r="J27" s="62"/>
+      <c r="K27" s="62"/>
+      <c r="L27" s="63"/>
+      <c r="M27" s="63"/>
+      <c r="N27" s="63"/>
+      <c r="O27" s="63"/>
+      <c r="P27" s="63"/>
+      <c r="Q27" s="63"/>
+      <c r="R27" s="63"/>
+      <c r="S27" s="29"/>
+      <c r="T27" s="29"/>
+      <c r="U27" s="64"/>
+      <c r="V27" s="64"/>
+      <c r="W27" s="64"/>
+      <c r="X27" s="64"/>
+      <c r="Y27" s="64"/>
+      <c r="Z27" s="65"/>
+      <c r="AA27" s="65"/>
+      <c r="AB27" s="65"/>
+      <c r="AC27" s="65"/>
+      <c r="AD27" s="65"/>
+      <c r="AE27" s="66"/>
+      <c r="AF27" s="66"/>
+      <c r="AG27" s="66"/>
+      <c r="AH27" s="67"/>
+      <c r="AI27" s="67"/>
+      <c r="AJ27" s="67"/>
       <c r="AK27" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6260,38 +6459,38 @@
         <v>46228</v>
       </c>
       <c r="D28" s="23"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="21"/>
-      <c r="K28" s="21"/>
-      <c r="L28" s="21"/>
-      <c r="M28" s="21"/>
-      <c r="N28" s="21"/>
-      <c r="O28" s="21"/>
-      <c r="P28" s="21"/>
-      <c r="Q28" s="21"/>
-      <c r="R28" s="21"/>
-      <c r="S28" s="21"/>
-      <c r="T28" s="21"/>
-      <c r="U28" s="21"/>
-      <c r="V28" s="21"/>
-      <c r="W28" s="21"/>
-      <c r="X28" s="21"/>
-      <c r="Y28" s="21"/>
-      <c r="Z28" s="21"/>
-      <c r="AA28" s="21"/>
-      <c r="AB28" s="21"/>
-      <c r="AC28" s="21"/>
-      <c r="AD28" s="21"/>
-      <c r="AE28" s="21"/>
-      <c r="AF28" s="21"/>
-      <c r="AG28" s="21"/>
-      <c r="AH28" s="21"/>
-      <c r="AI28" s="21"/>
-      <c r="AJ28" s="21"/>
+      <c r="E28" s="62"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="62"/>
+      <c r="H28" s="62"/>
+      <c r="I28" s="62"/>
+      <c r="J28" s="62"/>
+      <c r="K28" s="62"/>
+      <c r="L28" s="63"/>
+      <c r="M28" s="63"/>
+      <c r="N28" s="63"/>
+      <c r="O28" s="63"/>
+      <c r="P28" s="63"/>
+      <c r="Q28" s="63"/>
+      <c r="R28" s="63"/>
+      <c r="S28" s="29"/>
+      <c r="T28" s="29"/>
+      <c r="U28" s="64"/>
+      <c r="V28" s="64"/>
+      <c r="W28" s="64"/>
+      <c r="X28" s="64"/>
+      <c r="Y28" s="64"/>
+      <c r="Z28" s="65"/>
+      <c r="AA28" s="65"/>
+      <c r="AB28" s="65"/>
+      <c r="AC28" s="65"/>
+      <c r="AD28" s="65"/>
+      <c r="AE28" s="66"/>
+      <c r="AF28" s="66"/>
+      <c r="AG28" s="66"/>
+      <c r="AH28" s="67"/>
+      <c r="AI28" s="67"/>
+      <c r="AJ28" s="67"/>
       <c r="AK28" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6308,38 +6507,38 @@
         <v>46229</v>
       </c>
       <c r="D29" s="23"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="21"/>
-      <c r="J29" s="21"/>
-      <c r="K29" s="21"/>
-      <c r="L29" s="21"/>
-      <c r="M29" s="21"/>
-      <c r="N29" s="21"/>
-      <c r="O29" s="21"/>
-      <c r="P29" s="21"/>
-      <c r="Q29" s="21"/>
-      <c r="R29" s="21"/>
-      <c r="S29" s="21"/>
-      <c r="T29" s="21"/>
-      <c r="U29" s="21"/>
-      <c r="V29" s="21"/>
-      <c r="W29" s="21"/>
-      <c r="X29" s="21"/>
-      <c r="Y29" s="21"/>
-      <c r="Z29" s="21"/>
-      <c r="AA29" s="21"/>
-      <c r="AB29" s="21"/>
-      <c r="AC29" s="21"/>
-      <c r="AD29" s="21"/>
-      <c r="AE29" s="21"/>
-      <c r="AF29" s="21"/>
-      <c r="AG29" s="21"/>
-      <c r="AH29" s="21"/>
-      <c r="AI29" s="21"/>
-      <c r="AJ29" s="21"/>
+      <c r="E29" s="62"/>
+      <c r="F29" s="62"/>
+      <c r="G29" s="62"/>
+      <c r="H29" s="62"/>
+      <c r="I29" s="62"/>
+      <c r="J29" s="62"/>
+      <c r="K29" s="62"/>
+      <c r="L29" s="63"/>
+      <c r="M29" s="63"/>
+      <c r="N29" s="63"/>
+      <c r="O29" s="63"/>
+      <c r="P29" s="63"/>
+      <c r="Q29" s="63"/>
+      <c r="R29" s="63"/>
+      <c r="S29" s="29"/>
+      <c r="T29" s="29"/>
+      <c r="U29" s="64"/>
+      <c r="V29" s="64"/>
+      <c r="W29" s="64"/>
+      <c r="X29" s="64"/>
+      <c r="Y29" s="64"/>
+      <c r="Z29" s="65"/>
+      <c r="AA29" s="65"/>
+      <c r="AB29" s="65"/>
+      <c r="AC29" s="65"/>
+      <c r="AD29" s="65"/>
+      <c r="AE29" s="66"/>
+      <c r="AF29" s="66"/>
+      <c r="AG29" s="66"/>
+      <c r="AH29" s="67"/>
+      <c r="AI29" s="67"/>
+      <c r="AJ29" s="67"/>
       <c r="AK29" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6356,38 +6555,38 @@
         <v>46230</v>
       </c>
       <c r="D30" s="23"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="21"/>
-      <c r="K30" s="21"/>
-      <c r="L30" s="21"/>
-      <c r="M30" s="21"/>
-      <c r="N30" s="21"/>
-      <c r="O30" s="21"/>
-      <c r="P30" s="21"/>
-      <c r="Q30" s="21"/>
-      <c r="R30" s="21"/>
-      <c r="S30" s="21"/>
-      <c r="T30" s="21"/>
-      <c r="U30" s="21"/>
-      <c r="V30" s="21"/>
-      <c r="W30" s="21"/>
-      <c r="X30" s="21"/>
-      <c r="Y30" s="21"/>
-      <c r="Z30" s="21"/>
-      <c r="AA30" s="21"/>
-      <c r="AB30" s="21"/>
-      <c r="AC30" s="21"/>
-      <c r="AD30" s="21"/>
-      <c r="AE30" s="21"/>
-      <c r="AF30" s="21"/>
-      <c r="AG30" s="21"/>
-      <c r="AH30" s="21"/>
-      <c r="AI30" s="21"/>
-      <c r="AJ30" s="21"/>
+      <c r="E30" s="62"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="62"/>
+      <c r="H30" s="62"/>
+      <c r="I30" s="62"/>
+      <c r="J30" s="62"/>
+      <c r="K30" s="62"/>
+      <c r="L30" s="63"/>
+      <c r="M30" s="63"/>
+      <c r="N30" s="63"/>
+      <c r="O30" s="63"/>
+      <c r="P30" s="63"/>
+      <c r="Q30" s="63"/>
+      <c r="R30" s="63"/>
+      <c r="S30" s="29"/>
+      <c r="T30" s="29"/>
+      <c r="U30" s="64"/>
+      <c r="V30" s="64"/>
+      <c r="W30" s="64"/>
+      <c r="X30" s="64"/>
+      <c r="Y30" s="64"/>
+      <c r="Z30" s="65"/>
+      <c r="AA30" s="65"/>
+      <c r="AB30" s="65"/>
+      <c r="AC30" s="65"/>
+      <c r="AD30" s="65"/>
+      <c r="AE30" s="66"/>
+      <c r="AF30" s="66"/>
+      <c r="AG30" s="66"/>
+      <c r="AH30" s="67"/>
+      <c r="AI30" s="67"/>
+      <c r="AJ30" s="67"/>
       <c r="AK30" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6404,38 +6603,38 @@
         <v>46231</v>
       </c>
       <c r="D31" s="23"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="21"/>
-      <c r="I31" s="21"/>
-      <c r="J31" s="21"/>
-      <c r="K31" s="21"/>
-      <c r="L31" s="21"/>
-      <c r="M31" s="21"/>
-      <c r="N31" s="21"/>
-      <c r="O31" s="21"/>
-      <c r="P31" s="21"/>
-      <c r="Q31" s="21"/>
-      <c r="R31" s="21"/>
-      <c r="S31" s="21"/>
-      <c r="T31" s="21"/>
-      <c r="U31" s="21"/>
-      <c r="V31" s="21"/>
-      <c r="W31" s="21"/>
-      <c r="X31" s="21"/>
-      <c r="Y31" s="21"/>
-      <c r="Z31" s="21"/>
-      <c r="AA31" s="21"/>
-      <c r="AB31" s="21"/>
-      <c r="AC31" s="21"/>
-      <c r="AD31" s="21"/>
-      <c r="AE31" s="21"/>
-      <c r="AF31" s="21"/>
-      <c r="AG31" s="21"/>
-      <c r="AH31" s="21"/>
-      <c r="AI31" s="21"/>
-      <c r="AJ31" s="21"/>
+      <c r="E31" s="62"/>
+      <c r="F31" s="62"/>
+      <c r="G31" s="62"/>
+      <c r="H31" s="62"/>
+      <c r="I31" s="62"/>
+      <c r="J31" s="62"/>
+      <c r="K31" s="62"/>
+      <c r="L31" s="63"/>
+      <c r="M31" s="63"/>
+      <c r="N31" s="63"/>
+      <c r="O31" s="63"/>
+      <c r="P31" s="63"/>
+      <c r="Q31" s="63"/>
+      <c r="R31" s="63"/>
+      <c r="S31" s="29"/>
+      <c r="T31" s="29"/>
+      <c r="U31" s="64"/>
+      <c r="V31" s="64"/>
+      <c r="W31" s="64"/>
+      <c r="X31" s="64"/>
+      <c r="Y31" s="64"/>
+      <c r="Z31" s="65"/>
+      <c r="AA31" s="65"/>
+      <c r="AB31" s="65"/>
+      <c r="AC31" s="65"/>
+      <c r="AD31" s="65"/>
+      <c r="AE31" s="66"/>
+      <c r="AF31" s="66"/>
+      <c r="AG31" s="66"/>
+      <c r="AH31" s="67"/>
+      <c r="AI31" s="67"/>
+      <c r="AJ31" s="67"/>
       <c r="AK31" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6452,38 +6651,38 @@
         <v>46232</v>
       </c>
       <c r="D32" s="23"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="21"/>
-      <c r="I32" s="21"/>
-      <c r="J32" s="21"/>
-      <c r="K32" s="21"/>
-      <c r="L32" s="21"/>
-      <c r="M32" s="21"/>
-      <c r="N32" s="21"/>
-      <c r="O32" s="21"/>
-      <c r="P32" s="21"/>
-      <c r="Q32" s="21"/>
-      <c r="R32" s="21"/>
-      <c r="S32" s="21"/>
-      <c r="T32" s="21"/>
-      <c r="U32" s="21"/>
-      <c r="V32" s="21"/>
-      <c r="W32" s="21"/>
-      <c r="X32" s="21"/>
-      <c r="Y32" s="21"/>
-      <c r="Z32" s="21"/>
-      <c r="AA32" s="21"/>
-      <c r="AB32" s="21"/>
-      <c r="AC32" s="21"/>
-      <c r="AD32" s="21"/>
-      <c r="AE32" s="21"/>
-      <c r="AF32" s="21"/>
-      <c r="AG32" s="21"/>
-      <c r="AH32" s="21"/>
-      <c r="AI32" s="21"/>
-      <c r="AJ32" s="21"/>
+      <c r="E32" s="62"/>
+      <c r="F32" s="62"/>
+      <c r="G32" s="62"/>
+      <c r="H32" s="62"/>
+      <c r="I32" s="62"/>
+      <c r="J32" s="62"/>
+      <c r="K32" s="62"/>
+      <c r="L32" s="63"/>
+      <c r="M32" s="63"/>
+      <c r="N32" s="63"/>
+      <c r="O32" s="63"/>
+      <c r="P32" s="63"/>
+      <c r="Q32" s="63"/>
+      <c r="R32" s="63"/>
+      <c r="S32" s="29"/>
+      <c r="T32" s="29"/>
+      <c r="U32" s="64"/>
+      <c r="V32" s="64"/>
+      <c r="W32" s="64"/>
+      <c r="X32" s="64"/>
+      <c r="Y32" s="64"/>
+      <c r="Z32" s="65"/>
+      <c r="AA32" s="65"/>
+      <c r="AB32" s="65"/>
+      <c r="AC32" s="65"/>
+      <c r="AD32" s="65"/>
+      <c r="AE32" s="66"/>
+      <c r="AF32" s="66"/>
+      <c r="AG32" s="66"/>
+      <c r="AH32" s="67"/>
+      <c r="AI32" s="67"/>
+      <c r="AJ32" s="67"/>
       <c r="AK32" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6500,38 +6699,38 @@
         <v>46233</v>
       </c>
       <c r="D33" s="23"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="21"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
-      <c r="M33" s="21"/>
-      <c r="N33" s="21"/>
-      <c r="O33" s="21"/>
-      <c r="P33" s="21"/>
-      <c r="Q33" s="21"/>
-      <c r="R33" s="21"/>
-      <c r="S33" s="21"/>
-      <c r="T33" s="21"/>
-      <c r="U33" s="21"/>
-      <c r="V33" s="21"/>
-      <c r="W33" s="21"/>
-      <c r="X33" s="21"/>
-      <c r="Y33" s="21"/>
-      <c r="Z33" s="21"/>
-      <c r="AA33" s="21"/>
-      <c r="AB33" s="21"/>
-      <c r="AC33" s="21"/>
-      <c r="AD33" s="21"/>
-      <c r="AE33" s="21"/>
-      <c r="AF33" s="21"/>
-      <c r="AG33" s="21"/>
-      <c r="AH33" s="21"/>
-      <c r="AI33" s="21"/>
-      <c r="AJ33" s="21"/>
+      <c r="E33" s="62"/>
+      <c r="F33" s="62"/>
+      <c r="G33" s="62"/>
+      <c r="H33" s="62"/>
+      <c r="I33" s="62"/>
+      <c r="J33" s="62"/>
+      <c r="K33" s="62"/>
+      <c r="L33" s="63"/>
+      <c r="M33" s="63"/>
+      <c r="N33" s="63"/>
+      <c r="O33" s="63"/>
+      <c r="P33" s="63"/>
+      <c r="Q33" s="63"/>
+      <c r="R33" s="63"/>
+      <c r="S33" s="29"/>
+      <c r="T33" s="29"/>
+      <c r="U33" s="64"/>
+      <c r="V33" s="64"/>
+      <c r="W33" s="64"/>
+      <c r="X33" s="64"/>
+      <c r="Y33" s="64"/>
+      <c r="Z33" s="65"/>
+      <c r="AA33" s="65"/>
+      <c r="AB33" s="65"/>
+      <c r="AC33" s="65"/>
+      <c r="AD33" s="65"/>
+      <c r="AE33" s="66"/>
+      <c r="AF33" s="66"/>
+      <c r="AG33" s="66"/>
+      <c r="AH33" s="67"/>
+      <c r="AI33" s="67"/>
+      <c r="AJ33" s="67"/>
       <c r="AK33" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -6548,38 +6747,38 @@
         <v>46234</v>
       </c>
       <c r="D34" s="23"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
-      <c r="G34" s="21"/>
-      <c r="H34" s="21"/>
-      <c r="I34" s="21"/>
-      <c r="J34" s="21"/>
-      <c r="K34" s="21"/>
-      <c r="L34" s="21"/>
-      <c r="M34" s="21"/>
-      <c r="N34" s="21"/>
-      <c r="O34" s="21"/>
-      <c r="P34" s="21"/>
-      <c r="Q34" s="21"/>
-      <c r="R34" s="21"/>
-      <c r="S34" s="21"/>
-      <c r="T34" s="21"/>
-      <c r="U34" s="21"/>
-      <c r="V34" s="21"/>
-      <c r="W34" s="21"/>
-      <c r="X34" s="21"/>
-      <c r="Y34" s="21"/>
-      <c r="Z34" s="21"/>
-      <c r="AA34" s="21"/>
-      <c r="AB34" s="21"/>
-      <c r="AC34" s="21"/>
-      <c r="AD34" s="21"/>
-      <c r="AE34" s="21"/>
-      <c r="AF34" s="21"/>
-      <c r="AG34" s="21"/>
-      <c r="AH34" s="21"/>
-      <c r="AI34" s="21"/>
-      <c r="AJ34" s="21"/>
+      <c r="E34" s="62"/>
+      <c r="F34" s="62"/>
+      <c r="G34" s="62"/>
+      <c r="H34" s="62"/>
+      <c r="I34" s="62"/>
+      <c r="J34" s="62"/>
+      <c r="K34" s="62"/>
+      <c r="L34" s="63"/>
+      <c r="M34" s="63"/>
+      <c r="N34" s="63"/>
+      <c r="O34" s="63"/>
+      <c r="P34" s="63"/>
+      <c r="Q34" s="63"/>
+      <c r="R34" s="63"/>
+      <c r="S34" s="29"/>
+      <c r="T34" s="29"/>
+      <c r="U34" s="64"/>
+      <c r="V34" s="64"/>
+      <c r="W34" s="64"/>
+      <c r="X34" s="64"/>
+      <c r="Y34" s="64"/>
+      <c r="Z34" s="65"/>
+      <c r="AA34" s="65"/>
+      <c r="AB34" s="65"/>
+      <c r="AC34" s="65"/>
+      <c r="AD34" s="65"/>
+      <c r="AE34" s="66"/>
+      <c r="AF34" s="66"/>
+      <c r="AG34" s="66"/>
+      <c r="AH34" s="67"/>
+      <c r="AI34" s="67"/>
+      <c r="AJ34" s="67"/>
       <c r="AK34" s="25">
         <f t="shared" si="0"/>
         <v>0</v>

--- a/Другое/study_chart.xlsx
+++ b/Другое/study_chart.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROG\Git\Repository_1\Другое\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10380" activeTab="2"/>
   </bookViews>
@@ -11,7 +16,7 @@
     <sheet name="Июль" sheetId="4" r:id="rId2"/>
     <sheet name="Август" sheetId="5" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +39,7 @@
     <author>Собянин Евгений Андреевич (new)</author>
   </authors>
   <commentList>
-    <comment ref="AF21" authorId="0">
+    <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -57,7 +62,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF22" authorId="0">
+    <comment ref="AF22" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -81,7 +86,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF23" authorId="0">
+    <comment ref="AF23" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -107,7 +112,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF24" authorId="0">
+    <comment ref="AF24" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -131,7 +136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG24" authorId="0">
+    <comment ref="AG24" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -153,7 +158,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH24" authorId="0">
+    <comment ref="AH24" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -175,7 +180,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF25" authorId="0">
+    <comment ref="AF25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -201,7 +206,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG25" authorId="0">
+    <comment ref="AG25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -223,7 +228,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH25" authorId="0">
+    <comment ref="AH25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -245,7 +250,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AI25" authorId="0">
+    <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -267,7 +272,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AJ25" authorId="0">
+    <comment ref="AJ25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -289,7 +294,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AK25" authorId="0">
+    <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -311,7 +316,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF26" authorId="0">
+    <comment ref="AF26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -333,7 +338,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG26" authorId="0">
+    <comment ref="AG26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -355,7 +360,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH26" authorId="0">
+    <comment ref="AH26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -377,7 +382,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AI26" authorId="0">
+    <comment ref="AI26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -399,7 +404,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AJ26" authorId="0">
+    <comment ref="AJ26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -421,7 +426,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AK26" authorId="0">
+    <comment ref="AK26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -443,7 +448,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF27" authorId="0">
+    <comment ref="AF27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -465,7 +470,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG27" authorId="0">
+    <comment ref="AG27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -487,7 +492,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH27" authorId="0">
+    <comment ref="AH27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -509,7 +514,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF28" authorId="0">
+    <comment ref="AF28" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -531,7 +536,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF29" authorId="0">
+    <comment ref="AF29" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -554,7 +559,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF30" authorId="0">
+    <comment ref="AF30" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -578,7 +583,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF31" authorId="0">
+    <comment ref="AF31" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -601,7 +606,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF32" authorId="0">
+    <comment ref="AF32" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -625,7 +630,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF33" authorId="0">
+    <comment ref="AF33" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -648,7 +653,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF35" authorId="0">
+    <comment ref="AF35" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -670,7 +675,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF36" authorId="0">
+    <comment ref="AF36" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -692,7 +697,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF37" authorId="0">
+    <comment ref="AF37" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -714,7 +719,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF38" authorId="0">
+    <comment ref="AF38" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -746,7 +751,7 @@
     <author>Собянин Евгений Андреевич (new)</author>
   </authors>
   <commentList>
-    <comment ref="AH14" authorId="0">
+    <comment ref="AH14" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -766,7 +771,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="76">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -991,12 +996,15 @@
   </si>
   <si>
     <t>88.3</t>
+  </si>
+  <si>
+    <t>88.4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mmm"/>
   </numFmts>
@@ -1434,7 +1442,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -1777,56 +1785,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2015,6 +1978,60 @@
     <xf numFmtId="0" fontId="1" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="27" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2094,85 +2111,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="33" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="33" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="33" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="33" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2235,6 +2173,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -2282,7 +2223,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2314,9 +2255,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2348,6 +2290,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -2523,7 +2466,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="H9:Q22"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -2540,18 +2483,18 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:17" ht="45" customHeight="1">
-      <c r="H9" s="68" t="s">
+      <c r="H9" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="69"/>
-      <c r="J9" s="69"/>
-      <c r="K9" s="69"/>
-      <c r="L9" s="69"/>
-      <c r="M9" s="69"/>
-      <c r="N9" s="69"/>
-      <c r="O9" s="69"/>
-      <c r="P9" s="69"/>
-      <c r="Q9" s="70"/>
+      <c r="I9" s="87"/>
+      <c r="J9" s="87"/>
+      <c r="K9" s="87"/>
+      <c r="L9" s="87"/>
+      <c r="M9" s="87"/>
+      <c r="N9" s="87"/>
+      <c r="O9" s="87"/>
+      <c r="P9" s="87"/>
+      <c r="Q9" s="88"/>
     </row>
     <row r="10" spans="8:17" ht="30" customHeight="1">
       <c r="H10" s="55" t="s">
@@ -2820,11 +2763,11 @@
       <c r="Q21" s="60"/>
     </row>
     <row r="22" spans="8:17" ht="15.75">
-      <c r="H22" s="71" t="s">
+      <c r="H22" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="72"/>
-      <c r="J22" s="73"/>
+      <c r="I22" s="90"/>
+      <c r="J22" s="91"/>
       <c r="K22" s="61">
         <f>COUNTA(K11:K21)</f>
         <v>6</v>
@@ -2875,7 +2818,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="H9:AL42"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -2901,39 +2844,39 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:38" ht="45" customHeight="1">
-      <c r="H9" s="74" t="s">
+      <c r="H9" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="75"/>
-      <c r="J9" s="75"/>
-      <c r="K9" s="75"/>
-      <c r="L9" s="75"/>
-      <c r="M9" s="75"/>
-      <c r="N9" s="75"/>
-      <c r="O9" s="75"/>
-      <c r="P9" s="75"/>
-      <c r="Q9" s="75"/>
-      <c r="R9" s="75"/>
-      <c r="S9" s="75"/>
-      <c r="T9" s="75"/>
-      <c r="U9" s="75"/>
-      <c r="V9" s="75"/>
-      <c r="W9" s="75"/>
-      <c r="X9" s="75"/>
-      <c r="Y9" s="75"/>
-      <c r="Z9" s="75"/>
-      <c r="AA9" s="75"/>
-      <c r="AB9" s="75"/>
-      <c r="AC9" s="75"/>
-      <c r="AD9" s="75"/>
-      <c r="AE9" s="75"/>
-      <c r="AF9" s="75"/>
-      <c r="AG9" s="75"/>
-      <c r="AH9" s="75"/>
-      <c r="AI9" s="75"/>
-      <c r="AJ9" s="75"/>
-      <c r="AK9" s="75"/>
-      <c r="AL9" s="75"/>
+      <c r="I9" s="93"/>
+      <c r="J9" s="93"/>
+      <c r="K9" s="93"/>
+      <c r="L9" s="93"/>
+      <c r="M9" s="93"/>
+      <c r="N9" s="93"/>
+      <c r="O9" s="93"/>
+      <c r="P9" s="93"/>
+      <c r="Q9" s="93"/>
+      <c r="R9" s="93"/>
+      <c r="S9" s="93"/>
+      <c r="T9" s="93"/>
+      <c r="U9" s="93"/>
+      <c r="V9" s="93"/>
+      <c r="W9" s="93"/>
+      <c r="X9" s="93"/>
+      <c r="Y9" s="93"/>
+      <c r="Z9" s="93"/>
+      <c r="AA9" s="93"/>
+      <c r="AB9" s="93"/>
+      <c r="AC9" s="93"/>
+      <c r="AD9" s="93"/>
+      <c r="AE9" s="93"/>
+      <c r="AF9" s="93"/>
+      <c r="AG9" s="93"/>
+      <c r="AH9" s="93"/>
+      <c r="AI9" s="93"/>
+      <c r="AJ9" s="93"/>
+      <c r="AK9" s="93"/>
+      <c r="AL9" s="93"/>
     </row>
     <row r="10" spans="8:38" ht="30" customHeight="1">
       <c r="H10" s="32" t="s">
@@ -4613,11 +4556,11 @@
       </c>
     </row>
     <row r="42" spans="8:38" ht="15.75">
-      <c r="H42" s="76" t="s">
+      <c r="H42" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="I42" s="76"/>
-      <c r="J42" s="76"/>
+      <c r="I42" s="94"/>
+      <c r="J42" s="94"/>
       <c r="K42" s="32">
         <f>COUNTA(K11:K41)</f>
         <v>6</v>
@@ -4747,7 +4690,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AK34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -4782,66 +4725,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="82"/>
-      <c r="B1" s="83"/>
-      <c r="C1" s="84"/>
+      <c r="A1" s="100"/>
+      <c r="B1" s="101"/>
+      <c r="C1" s="102"/>
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="88" t="s">
+      <c r="E1" s="106" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="89" t="s">
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
+      <c r="I1" s="106"/>
+      <c r="J1" s="106"/>
+      <c r="K1" s="106"/>
+      <c r="L1" s="107" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="89"/>
-      <c r="N1" s="89"/>
-      <c r="O1" s="89"/>
-      <c r="P1" s="89"/>
-      <c r="Q1" s="89"/>
-      <c r="R1" s="89"/>
-      <c r="S1" s="90" t="s">
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="107"/>
+      <c r="S1" s="108" t="s">
         <v>39</v>
       </c>
-      <c r="T1" s="90"/>
-      <c r="U1" s="91" t="s">
+      <c r="T1" s="108"/>
+      <c r="U1" s="109" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="92"/>
-      <c r="W1" s="92"/>
-      <c r="X1" s="92"/>
-      <c r="Y1" s="93"/>
-      <c r="Z1" s="94" t="s">
+      <c r="V1" s="110"/>
+      <c r="W1" s="110"/>
+      <c r="X1" s="110"/>
+      <c r="Y1" s="111"/>
+      <c r="Z1" s="112" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="94"/>
-      <c r="AB1" s="94"/>
-      <c r="AC1" s="94"/>
-      <c r="AD1" s="94"/>
-      <c r="AE1" s="77" t="s">
+      <c r="AA1" s="112"/>
+      <c r="AB1" s="112"/>
+      <c r="AC1" s="112"/>
+      <c r="AD1" s="112"/>
+      <c r="AE1" s="95" t="s">
         <v>42</v>
       </c>
-      <c r="AF1" s="77"/>
-      <c r="AG1" s="77"/>
-      <c r="AH1" s="78" t="s">
+      <c r="AF1" s="95"/>
+      <c r="AG1" s="95"/>
+      <c r="AH1" s="96" t="s">
         <v>43</v>
       </c>
-      <c r="AI1" s="78"/>
-      <c r="AJ1" s="78"/>
-      <c r="AK1" s="79" t="s">
+      <c r="AI1" s="96"/>
+      <c r="AJ1" s="96"/>
+      <c r="AK1" s="97" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1">
-      <c r="A2" s="85"/>
-      <c r="B2" s="86"/>
-      <c r="C2" s="87"/>
+      <c r="A2" s="103"/>
+      <c r="B2" s="104"/>
+      <c r="C2" s="105"/>
       <c r="D2" s="5" t="s">
         <v>44</v>
       </c>
@@ -4935,7 +4878,7 @@
       <c r="AH2" s="12"/>
       <c r="AI2" s="12"/>
       <c r="AJ2" s="12"/>
-      <c r="AK2" s="80"/>
+      <c r="AK2" s="98"/>
     </row>
     <row r="3" spans="1:37">
       <c r="A3" s="13" t="s">
@@ -5046,7 +4989,7 @@
       <c r="AJ3" s="20">
         <v>2</v>
       </c>
-      <c r="AK3" s="81"/>
+      <c r="AK3" s="99"/>
     </row>
     <row r="4" spans="1:37">
       <c r="A4" s="21">
@@ -5858,7 +5801,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:37" ht="15.75" thickBot="1">
+    <row r="16" spans="1:37">
       <c r="A16" s="21">
         <v>13</v>
       </c>
@@ -5868,104 +5811,112 @@
       <c r="C16" s="22">
         <v>46216</v>
       </c>
-      <c r="D16" s="97" t="s">
+      <c r="D16" s="70" t="s">
         <v>73</v>
       </c>
-      <c r="E16" s="98"/>
-      <c r="F16" s="98"/>
-      <c r="G16" s="98" t="s">
-        <v>12</v>
-      </c>
-      <c r="H16" s="98"/>
-      <c r="I16" s="98"/>
-      <c r="J16" s="98"/>
-      <c r="K16" s="98"/>
-      <c r="L16" s="99"/>
-      <c r="M16" s="99" t="s">
-        <v>12</v>
-      </c>
-      <c r="N16" s="99" t="s">
-        <v>12</v>
-      </c>
-      <c r="O16" s="99" t="s">
-        <v>12</v>
-      </c>
-      <c r="P16" s="99"/>
-      <c r="Q16" s="99"/>
-      <c r="R16" s="99"/>
-      <c r="S16" s="100"/>
-      <c r="T16" s="100"/>
-      <c r="U16" s="101"/>
-      <c r="V16" s="101"/>
-      <c r="W16" s="101"/>
-      <c r="X16" s="101"/>
-      <c r="Y16" s="101"/>
-      <c r="Z16" s="102"/>
-      <c r="AA16" s="102"/>
-      <c r="AB16" s="102"/>
-      <c r="AC16" s="102" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD16" s="102"/>
-      <c r="AE16" s="103"/>
-      <c r="AF16" s="103"/>
-      <c r="AG16" s="103"/>
-      <c r="AH16" s="104"/>
-      <c r="AI16" s="104"/>
-      <c r="AJ16" s="104"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="71"/>
+      <c r="L16" s="72"/>
+      <c r="M16" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="N16" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="O16" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="73"/>
+      <c r="T16" s="73"/>
+      <c r="U16" s="74"/>
+      <c r="V16" s="74"/>
+      <c r="W16" s="74"/>
+      <c r="X16" s="74"/>
+      <c r="Y16" s="74"/>
+      <c r="Z16" s="75"/>
+      <c r="AA16" s="75"/>
+      <c r="AB16" s="75"/>
+      <c r="AC16" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD16" s="75"/>
+      <c r="AE16" s="76"/>
+      <c r="AF16" s="76"/>
+      <c r="AG16" s="76"/>
+      <c r="AH16" s="77"/>
+      <c r="AI16" s="77"/>
+      <c r="AJ16" s="77"/>
       <c r="AK16" s="25">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:37" ht="15.75" thickBot="1">
+    <row r="17" spans="1:37">
       <c r="A17" s="21">
         <v>14</v>
       </c>
       <c r="B17" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="95">
+      <c r="C17" s="68">
         <v>46217</v>
       </c>
-      <c r="D17" s="113" t="s">
+      <c r="D17" s="70" t="s">
         <v>74</v>
       </c>
-      <c r="E17" s="114"/>
-      <c r="F17" s="114"/>
-      <c r="G17" s="114"/>
-      <c r="H17" s="114"/>
-      <c r="I17" s="114"/>
-      <c r="J17" s="114"/>
-      <c r="K17" s="114"/>
-      <c r="L17" s="115"/>
-      <c r="M17" s="115"/>
-      <c r="N17" s="115"/>
-      <c r="O17" s="115"/>
-      <c r="P17" s="115"/>
-      <c r="Q17" s="115"/>
-      <c r="R17" s="115"/>
-      <c r="S17" s="116"/>
-      <c r="T17" s="116"/>
-      <c r="U17" s="117"/>
-      <c r="V17" s="117"/>
-      <c r="W17" s="117"/>
-      <c r="X17" s="117"/>
-      <c r="Y17" s="117"/>
-      <c r="Z17" s="118"/>
-      <c r="AA17" s="118"/>
-      <c r="AB17" s="118"/>
-      <c r="AC17" s="118"/>
-      <c r="AD17" s="118"/>
-      <c r="AE17" s="119"/>
-      <c r="AF17" s="119"/>
-      <c r="AG17" s="119"/>
-      <c r="AH17" s="120"/>
-      <c r="AI17" s="120"/>
-      <c r="AJ17" s="121"/>
-      <c r="AK17" s="96">
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="71"/>
+      <c r="L17" s="72"/>
+      <c r="M17" s="72"/>
+      <c r="N17" s="72"/>
+      <c r="O17" s="72"/>
+      <c r="P17" s="72"/>
+      <c r="Q17" s="72"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="73"/>
+      <c r="T17" s="73"/>
+      <c r="U17" s="74"/>
+      <c r="V17" s="74"/>
+      <c r="W17" s="74"/>
+      <c r="X17" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y17" s="74"/>
+      <c r="Z17" s="75"/>
+      <c r="AA17" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB17" s="75"/>
+      <c r="AC17" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD17" s="75"/>
+      <c r="AE17" s="76"/>
+      <c r="AF17" s="76"/>
+      <c r="AG17" s="76" t="s">
+        <v>12</v>
+      </c>
+      <c r="AH17" s="77"/>
+      <c r="AI17" s="77"/>
+      <c r="AJ17" s="77"/>
+      <c r="AK17" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -5975,45 +5926,55 @@
       <c r="B18" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="22">
+      <c r="C18" s="68">
         <v>46218</v>
       </c>
-      <c r="D18" s="105"/>
-      <c r="E18" s="106"/>
-      <c r="F18" s="106"/>
-      <c r="G18" s="106"/>
-      <c r="H18" s="106"/>
-      <c r="I18" s="106"/>
-      <c r="J18" s="106"/>
-      <c r="K18" s="106"/>
-      <c r="L18" s="107"/>
-      <c r="M18" s="107"/>
-      <c r="N18" s="107"/>
-      <c r="O18" s="107"/>
-      <c r="P18" s="107"/>
-      <c r="Q18" s="107"/>
-      <c r="R18" s="107"/>
-      <c r="S18" s="108"/>
-      <c r="T18" s="108"/>
-      <c r="U18" s="109"/>
-      <c r="V18" s="109"/>
-      <c r="W18" s="109"/>
-      <c r="X18" s="109"/>
-      <c r="Y18" s="109"/>
-      <c r="Z18" s="110"/>
-      <c r="AA18" s="110"/>
-      <c r="AB18" s="110"/>
-      <c r="AC18" s="110"/>
-      <c r="AD18" s="110"/>
-      <c r="AE18" s="111"/>
-      <c r="AF18" s="111"/>
-      <c r="AG18" s="111"/>
-      <c r="AH18" s="112"/>
-      <c r="AI18" s="112"/>
-      <c r="AJ18" s="112"/>
-      <c r="AK18" s="25">
+      <c r="D18" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="62"/>
+      <c r="F18" s="62"/>
+      <c r="G18" s="62"/>
+      <c r="H18" s="62"/>
+      <c r="I18" s="62"/>
+      <c r="J18" s="62"/>
+      <c r="K18" s="62"/>
+      <c r="L18" s="63"/>
+      <c r="M18" s="63"/>
+      <c r="N18" s="63"/>
+      <c r="O18" s="63"/>
+      <c r="P18" s="63"/>
+      <c r="Q18" s="63"/>
+      <c r="R18" s="63"/>
+      <c r="S18" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="T18" s="29"/>
+      <c r="U18" s="64"/>
+      <c r="V18" s="64"/>
+      <c r="W18" s="64"/>
+      <c r="X18" s="64"/>
+      <c r="Y18" s="64"/>
+      <c r="Z18" s="65"/>
+      <c r="AA18" s="65"/>
+      <c r="AB18" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC18" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD18" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE18" s="66"/>
+      <c r="AF18" s="66"/>
+      <c r="AG18" s="66"/>
+      <c r="AH18" s="67"/>
+      <c r="AI18" s="67"/>
+      <c r="AJ18" s="67"/>
+      <c r="AK18" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -6026,42 +5987,54 @@
       <c r="C19" s="22">
         <v>46219</v>
       </c>
-      <c r="D19" s="23"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="62"/>
-      <c r="J19" s="62"/>
-      <c r="K19" s="62"/>
-      <c r="L19" s="63"/>
-      <c r="M19" s="63"/>
-      <c r="N19" s="63"/>
-      <c r="O19" s="63"/>
-      <c r="P19" s="63"/>
-      <c r="Q19" s="63"/>
-      <c r="R19" s="63"/>
-      <c r="S19" s="29"/>
-      <c r="T19" s="29"/>
-      <c r="U19" s="64"/>
-      <c r="V19" s="64"/>
-      <c r="W19" s="64"/>
-      <c r="X19" s="64"/>
-      <c r="Y19" s="64"/>
-      <c r="Z19" s="65"/>
-      <c r="AA19" s="65"/>
-      <c r="AB19" s="65"/>
-      <c r="AC19" s="65"/>
-      <c r="AD19" s="65"/>
-      <c r="AE19" s="66"/>
-      <c r="AF19" s="66"/>
-      <c r="AG19" s="66"/>
-      <c r="AH19" s="67"/>
-      <c r="AI19" s="67"/>
-      <c r="AJ19" s="67"/>
+      <c r="D19" s="85" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" s="78"/>
+      <c r="F19" s="78"/>
+      <c r="G19" s="78" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="78"/>
+      <c r="I19" s="78"/>
+      <c r="J19" s="78"/>
+      <c r="K19" s="78"/>
+      <c r="L19" s="79"/>
+      <c r="M19" s="79"/>
+      <c r="N19" s="79"/>
+      <c r="O19" s="79"/>
+      <c r="P19" s="79"/>
+      <c r="Q19" s="79"/>
+      <c r="R19" s="79"/>
+      <c r="S19" s="80" t="s">
+        <v>12</v>
+      </c>
+      <c r="T19" s="80"/>
+      <c r="U19" s="81"/>
+      <c r="V19" s="81"/>
+      <c r="W19" s="81"/>
+      <c r="X19" s="81"/>
+      <c r="Y19" s="81"/>
+      <c r="Z19" s="82"/>
+      <c r="AA19" s="82" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB19" s="82"/>
+      <c r="AC19" s="82" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD19" s="82" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE19" s="83"/>
+      <c r="AF19" s="83"/>
+      <c r="AG19" s="83"/>
+      <c r="AH19" s="84"/>
+      <c r="AI19" s="84"/>
+      <c r="AJ19" s="84"/>
       <c r="AK19" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -6074,7 +6047,7 @@
       <c r="C20" s="22">
         <v>46220</v>
       </c>
-      <c r="D20" s="23"/>
+      <c r="D20" s="30"/>
       <c r="E20" s="62"/>
       <c r="F20" s="62"/>
       <c r="G20" s="62"/>
@@ -6122,7 +6095,7 @@
       <c r="C21" s="22">
         <v>46221</v>
       </c>
-      <c r="D21" s="23"/>
+      <c r="D21" s="30"/>
       <c r="E21" s="62"/>
       <c r="F21" s="62"/>
       <c r="G21" s="62"/>
@@ -6170,7 +6143,7 @@
       <c r="C22" s="22">
         <v>46222</v>
       </c>
-      <c r="D22" s="23"/>
+      <c r="D22" s="30"/>
       <c r="E22" s="62"/>
       <c r="F22" s="62"/>
       <c r="G22" s="62"/>
@@ -6218,7 +6191,7 @@
       <c r="C23" s="22">
         <v>46223</v>
       </c>
-      <c r="D23" s="23"/>
+      <c r="D23" s="30"/>
       <c r="E23" s="62"/>
       <c r="F23" s="62"/>
       <c r="G23" s="62"/>
@@ -6266,7 +6239,7 @@
       <c r="C24" s="22">
         <v>46224</v>
       </c>
-      <c r="D24" s="23"/>
+      <c r="D24" s="30"/>
       <c r="E24" s="62"/>
       <c r="F24" s="62"/>
       <c r="G24" s="62"/>
@@ -6314,7 +6287,7 @@
       <c r="C25" s="22">
         <v>46225</v>
       </c>
-      <c r="D25" s="23"/>
+      <c r="D25" s="30"/>
       <c r="E25" s="62"/>
       <c r="F25" s="62"/>
       <c r="G25" s="62"/>
@@ -6362,7 +6335,7 @@
       <c r="C26" s="22">
         <v>46226</v>
       </c>
-      <c r="D26" s="23"/>
+      <c r="D26" s="30"/>
       <c r="E26" s="62"/>
       <c r="F26" s="62"/>
       <c r="G26" s="62"/>
@@ -6410,7 +6383,7 @@
       <c r="C27" s="22">
         <v>46227</v>
       </c>
-      <c r="D27" s="23"/>
+      <c r="D27" s="30"/>
       <c r="E27" s="62"/>
       <c r="F27" s="62"/>
       <c r="G27" s="62"/>
@@ -6458,7 +6431,7 @@
       <c r="C28" s="22">
         <v>46228</v>
       </c>
-      <c r="D28" s="23"/>
+      <c r="D28" s="30"/>
       <c r="E28" s="62"/>
       <c r="F28" s="62"/>
       <c r="G28" s="62"/>
@@ -6506,7 +6479,7 @@
       <c r="C29" s="22">
         <v>46229</v>
       </c>
-      <c r="D29" s="23"/>
+      <c r="D29" s="30"/>
       <c r="E29" s="62"/>
       <c r="F29" s="62"/>
       <c r="G29" s="62"/>
@@ -6554,7 +6527,7 @@
       <c r="C30" s="22">
         <v>46230</v>
       </c>
-      <c r="D30" s="23"/>
+      <c r="D30" s="30"/>
       <c r="E30" s="62"/>
       <c r="F30" s="62"/>
       <c r="G30" s="62"/>
@@ -6602,7 +6575,7 @@
       <c r="C31" s="22">
         <v>46231</v>
       </c>
-      <c r="D31" s="23"/>
+      <c r="D31" s="30"/>
       <c r="E31" s="62"/>
       <c r="F31" s="62"/>
       <c r="G31" s="62"/>
@@ -6650,7 +6623,7 @@
       <c r="C32" s="22">
         <v>46232</v>
       </c>
-      <c r="D32" s="23"/>
+      <c r="D32" s="30"/>
       <c r="E32" s="62"/>
       <c r="F32" s="62"/>
       <c r="G32" s="62"/>
@@ -6698,7 +6671,7 @@
       <c r="C33" s="22">
         <v>46233</v>
       </c>
-      <c r="D33" s="23"/>
+      <c r="D33" s="30"/>
       <c r="E33" s="62"/>
       <c r="F33" s="62"/>
       <c r="G33" s="62"/>
@@ -6746,7 +6719,7 @@
       <c r="C34" s="22">
         <v>46234</v>
       </c>
-      <c r="D34" s="23"/>
+      <c r="D34" s="30"/>
       <c r="E34" s="62"/>
       <c r="F34" s="62"/>
       <c r="G34" s="62"/>

--- a/Другое/study_chart.xlsx
+++ b/Другое/study_chart.xlsx
@@ -1,13 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROG\Git\Repository_1\Другое\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10380" activeTab="2"/>
   </bookViews>
@@ -16,7 +11,7 @@
     <sheet name="Июль" sheetId="4" r:id="rId2"/>
     <sheet name="Август" sheetId="5" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="125725"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +34,7 @@
     <author>Собянин Евгений Андреевич (new)</author>
   </authors>
   <commentList>
-    <comment ref="AF21" authorId="0" shapeId="0">
+    <comment ref="AF21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -62,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF22" authorId="0" shapeId="0">
+    <comment ref="AF22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -86,7 +81,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF23" authorId="0" shapeId="0">
+    <comment ref="AF23" authorId="0">
       <text>
         <r>
           <rPr>
@@ -112,7 +107,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF24" authorId="0" shapeId="0">
+    <comment ref="AF24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -136,7 +131,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG24" authorId="0" shapeId="0">
+    <comment ref="AG24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -158,7 +153,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH24" authorId="0" shapeId="0">
+    <comment ref="AH24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -180,7 +175,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF25" authorId="0" shapeId="0">
+    <comment ref="AF25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -206,7 +201,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG25" authorId="0" shapeId="0">
+    <comment ref="AG25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -228,7 +223,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH25" authorId="0" shapeId="0">
+    <comment ref="AH25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -250,7 +245,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AI25" authorId="0" shapeId="0">
+    <comment ref="AI25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -272,7 +267,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AJ25" authorId="0" shapeId="0">
+    <comment ref="AJ25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -294,7 +289,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AK25" authorId="0" shapeId="0">
+    <comment ref="AK25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -316,7 +311,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF26" authorId="0" shapeId="0">
+    <comment ref="AF26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -338,7 +333,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG26" authorId="0" shapeId="0">
+    <comment ref="AG26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -360,7 +355,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH26" authorId="0" shapeId="0">
+    <comment ref="AH26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -382,7 +377,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AI26" authorId="0" shapeId="0">
+    <comment ref="AI26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -404,7 +399,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AJ26" authorId="0" shapeId="0">
+    <comment ref="AJ26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -426,7 +421,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AK26" authorId="0" shapeId="0">
+    <comment ref="AK26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -448,7 +443,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF27" authorId="0" shapeId="0">
+    <comment ref="AF27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -470,7 +465,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG27" authorId="0" shapeId="0">
+    <comment ref="AG27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -492,7 +487,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH27" authorId="0" shapeId="0">
+    <comment ref="AH27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -514,7 +509,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF28" authorId="0" shapeId="0">
+    <comment ref="AF28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -536,7 +531,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF29" authorId="0" shapeId="0">
+    <comment ref="AF29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -559,7 +554,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF30" authorId="0" shapeId="0">
+    <comment ref="AF30" authorId="0">
       <text>
         <r>
           <rPr>
@@ -583,7 +578,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF31" authorId="0" shapeId="0">
+    <comment ref="AF31" authorId="0">
       <text>
         <r>
           <rPr>
@@ -606,7 +601,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF32" authorId="0" shapeId="0">
+    <comment ref="AF32" authorId="0">
       <text>
         <r>
           <rPr>
@@ -630,7 +625,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF33" authorId="0" shapeId="0">
+    <comment ref="AF33" authorId="0">
       <text>
         <r>
           <rPr>
@@ -653,7 +648,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF35" authorId="0" shapeId="0">
+    <comment ref="AF35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -675,7 +670,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF36" authorId="0" shapeId="0">
+    <comment ref="AF36" authorId="0">
       <text>
         <r>
           <rPr>
@@ -697,7 +692,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF37" authorId="0" shapeId="0">
+    <comment ref="AF37" authorId="0">
       <text>
         <r>
           <rPr>
@@ -719,7 +714,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF38" authorId="0" shapeId="0">
+    <comment ref="AF38" authorId="0">
       <text>
         <r>
           <rPr>
@@ -751,7 +746,7 @@
     <author>Собянин Евгений Андреевич (new)</author>
   </authors>
   <commentList>
-    <comment ref="AH14" authorId="0" shapeId="0">
+    <comment ref="AH14" authorId="0">
       <text>
         <r>
           <rPr>
@@ -771,7 +766,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="77">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -999,12 +994,15 @@
   </si>
   <si>
     <t>88.4</t>
+  </si>
+  <si>
+    <t>88.9</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mmm"/>
   </numFmts>
@@ -1442,7 +1440,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="35">
     <border>
       <left/>
       <right/>
@@ -1785,11 +1783,104 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2032,6 +2123,42 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="27" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2111,6 +2238,69 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2223,7 +2413,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2255,10 +2445,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2290,7 +2479,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -2466,7 +2654,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="H9:Q22"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -2483,18 +2671,18 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:17" ht="45" customHeight="1">
-      <c r="H9" s="86" t="s">
+      <c r="H9" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="87"/>
-      <c r="J9" s="87"/>
-      <c r="K9" s="87"/>
-      <c r="L9" s="87"/>
-      <c r="M9" s="87"/>
-      <c r="N9" s="87"/>
-      <c r="O9" s="87"/>
-      <c r="P9" s="87"/>
-      <c r="Q9" s="88"/>
+      <c r="I9" s="99"/>
+      <c r="J9" s="99"/>
+      <c r="K9" s="99"/>
+      <c r="L9" s="99"/>
+      <c r="M9" s="99"/>
+      <c r="N9" s="99"/>
+      <c r="O9" s="99"/>
+      <c r="P9" s="99"/>
+      <c r="Q9" s="100"/>
     </row>
     <row r="10" spans="8:17" ht="30" customHeight="1">
       <c r="H10" s="55" t="s">
@@ -2763,11 +2951,11 @@
       <c r="Q21" s="60"/>
     </row>
     <row r="22" spans="8:17" ht="15.75">
-      <c r="H22" s="89" t="s">
+      <c r="H22" s="101" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="90"/>
-      <c r="J22" s="91"/>
+      <c r="I22" s="102"/>
+      <c r="J22" s="103"/>
       <c r="K22" s="61">
         <f>COUNTA(K11:K21)</f>
         <v>6</v>
@@ -2818,7 +3006,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="H9:AL42"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -2844,39 +3032,39 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:38" ht="45" customHeight="1">
-      <c r="H9" s="92" t="s">
+      <c r="H9" s="104" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="93"/>
-      <c r="J9" s="93"/>
-      <c r="K9" s="93"/>
-      <c r="L9" s="93"/>
-      <c r="M9" s="93"/>
-      <c r="N9" s="93"/>
-      <c r="O9" s="93"/>
-      <c r="P9" s="93"/>
-      <c r="Q9" s="93"/>
-      <c r="R9" s="93"/>
-      <c r="S9" s="93"/>
-      <c r="T9" s="93"/>
-      <c r="U9" s="93"/>
-      <c r="V9" s="93"/>
-      <c r="W9" s="93"/>
-      <c r="X9" s="93"/>
-      <c r="Y9" s="93"/>
-      <c r="Z9" s="93"/>
-      <c r="AA9" s="93"/>
-      <c r="AB9" s="93"/>
-      <c r="AC9" s="93"/>
-      <c r="AD9" s="93"/>
-      <c r="AE9" s="93"/>
-      <c r="AF9" s="93"/>
-      <c r="AG9" s="93"/>
-      <c r="AH9" s="93"/>
-      <c r="AI9" s="93"/>
-      <c r="AJ9" s="93"/>
-      <c r="AK9" s="93"/>
-      <c r="AL9" s="93"/>
+      <c r="I9" s="105"/>
+      <c r="J9" s="105"/>
+      <c r="K9" s="105"/>
+      <c r="L9" s="105"/>
+      <c r="M9" s="105"/>
+      <c r="N9" s="105"/>
+      <c r="O9" s="105"/>
+      <c r="P9" s="105"/>
+      <c r="Q9" s="105"/>
+      <c r="R9" s="105"/>
+      <c r="S9" s="105"/>
+      <c r="T9" s="105"/>
+      <c r="U9" s="105"/>
+      <c r="V9" s="105"/>
+      <c r="W9" s="105"/>
+      <c r="X9" s="105"/>
+      <c r="Y9" s="105"/>
+      <c r="Z9" s="105"/>
+      <c r="AA9" s="105"/>
+      <c r="AB9" s="105"/>
+      <c r="AC9" s="105"/>
+      <c r="AD9" s="105"/>
+      <c r="AE9" s="105"/>
+      <c r="AF9" s="105"/>
+      <c r="AG9" s="105"/>
+      <c r="AH9" s="105"/>
+      <c r="AI9" s="105"/>
+      <c r="AJ9" s="105"/>
+      <c r="AK9" s="105"/>
+      <c r="AL9" s="105"/>
     </row>
     <row r="10" spans="8:38" ht="30" customHeight="1">
       <c r="H10" s="32" t="s">
@@ -4556,11 +4744,11 @@
       </c>
     </row>
     <row r="42" spans="8:38" ht="15.75">
-      <c r="H42" s="94" t="s">
+      <c r="H42" s="106" t="s">
         <v>19</v>
       </c>
-      <c r="I42" s="94"/>
-      <c r="J42" s="94"/>
+      <c r="I42" s="106"/>
+      <c r="J42" s="106"/>
       <c r="K42" s="32">
         <f>COUNTA(K11:K41)</f>
         <v>6</v>
@@ -4690,7 +4878,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AK34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -4725,66 +4913,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="100"/>
-      <c r="B1" s="101"/>
-      <c r="C1" s="102"/>
+      <c r="A1" s="112"/>
+      <c r="B1" s="113"/>
+      <c r="C1" s="114"/>
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="106" t="s">
+      <c r="E1" s="118" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="107" t="s">
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
+      <c r="H1" s="118"/>
+      <c r="I1" s="118"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="119" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="108" t="s">
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="120" t="s">
         <v>39</v>
       </c>
-      <c r="T1" s="108"/>
-      <c r="U1" s="109" t="s">
+      <c r="T1" s="120"/>
+      <c r="U1" s="121" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="110"/>
-      <c r="W1" s="110"/>
-      <c r="X1" s="110"/>
-      <c r="Y1" s="111"/>
-      <c r="Z1" s="112" t="s">
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="123"/>
+      <c r="Z1" s="124" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="112"/>
-      <c r="AB1" s="112"/>
-      <c r="AC1" s="112"/>
-      <c r="AD1" s="112"/>
-      <c r="AE1" s="95" t="s">
+      <c r="AA1" s="124"/>
+      <c r="AB1" s="124"/>
+      <c r="AC1" s="124"/>
+      <c r="AD1" s="124"/>
+      <c r="AE1" s="107" t="s">
         <v>42</v>
       </c>
-      <c r="AF1" s="95"/>
-      <c r="AG1" s="95"/>
-      <c r="AH1" s="96" t="s">
+      <c r="AF1" s="107"/>
+      <c r="AG1" s="107"/>
+      <c r="AH1" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="AI1" s="96"/>
-      <c r="AJ1" s="96"/>
-      <c r="AK1" s="97" t="s">
+      <c r="AI1" s="108"/>
+      <c r="AJ1" s="108"/>
+      <c r="AK1" s="109" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1">
-      <c r="A2" s="103"/>
-      <c r="B2" s="104"/>
-      <c r="C2" s="105"/>
+      <c r="A2" s="115"/>
+      <c r="B2" s="116"/>
+      <c r="C2" s="117"/>
       <c r="D2" s="5" t="s">
         <v>44</v>
       </c>
@@ -4878,7 +5066,7 @@
       <c r="AH2" s="12"/>
       <c r="AI2" s="12"/>
       <c r="AJ2" s="12"/>
-      <c r="AK2" s="98"/>
+      <c r="AK2" s="110"/>
     </row>
     <row r="3" spans="1:37">
       <c r="A3" s="13" t="s">
@@ -4989,7 +5177,7 @@
       <c r="AJ3" s="20">
         <v>2</v>
       </c>
-      <c r="AK3" s="99"/>
+      <c r="AK3" s="111"/>
     </row>
     <row r="4" spans="1:37">
       <c r="A4" s="21">
@@ -5978,181 +6166,257 @@
       </c>
     </row>
     <row r="19" spans="1:37">
-      <c r="A19" s="21">
+      <c r="A19" s="70">
         <v>16</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="22">
+      <c r="C19" s="86">
         <v>46219</v>
       </c>
-      <c r="D19" s="85" t="s">
+      <c r="D19" s="87" t="s">
         <v>62</v>
       </c>
-      <c r="E19" s="78"/>
-      <c r="F19" s="78"/>
-      <c r="G19" s="78" t="s">
-        <v>12</v>
-      </c>
-      <c r="H19" s="78"/>
-      <c r="I19" s="78"/>
-      <c r="J19" s="78"/>
-      <c r="K19" s="78"/>
-      <c r="L19" s="79"/>
-      <c r="M19" s="79"/>
-      <c r="N19" s="79"/>
-      <c r="O19" s="79"/>
-      <c r="P19" s="79"/>
-      <c r="Q19" s="79"/>
-      <c r="R19" s="79"/>
-      <c r="S19" s="80" t="s">
-        <v>12</v>
-      </c>
-      <c r="T19" s="80"/>
-      <c r="U19" s="81"/>
-      <c r="V19" s="81"/>
-      <c r="W19" s="81"/>
-      <c r="X19" s="81"/>
-      <c r="Y19" s="81"/>
-      <c r="Z19" s="82"/>
-      <c r="AA19" s="82" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB19" s="82"/>
-      <c r="AC19" s="82" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD19" s="82" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE19" s="83"/>
-      <c r="AF19" s="83"/>
-      <c r="AG19" s="83"/>
-      <c r="AH19" s="84"/>
-      <c r="AI19" s="84"/>
-      <c r="AJ19" s="84"/>
-      <c r="AK19" s="25">
+      <c r="E19" s="88"/>
+      <c r="F19" s="88"/>
+      <c r="G19" s="88" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="88"/>
+      <c r="I19" s="88"/>
+      <c r="J19" s="88" t="s">
+        <v>12</v>
+      </c>
+      <c r="K19" s="88"/>
+      <c r="L19" s="89"/>
+      <c r="M19" s="89"/>
+      <c r="N19" s="89"/>
+      <c r="O19" s="89"/>
+      <c r="P19" s="89"/>
+      <c r="Q19" s="89"/>
+      <c r="R19" s="89"/>
+      <c r="S19" s="90" t="s">
+        <v>12</v>
+      </c>
+      <c r="T19" s="90"/>
+      <c r="U19" s="91"/>
+      <c r="V19" s="91"/>
+      <c r="W19" s="91"/>
+      <c r="X19" s="91"/>
+      <c r="Y19" s="91"/>
+      <c r="Z19" s="92"/>
+      <c r="AA19" s="92" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB19" s="92"/>
+      <c r="AC19" s="92" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD19" s="92" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE19" s="93"/>
+      <c r="AF19" s="93"/>
+      <c r="AG19" s="93"/>
+      <c r="AH19" s="94"/>
+      <c r="AI19" s="94"/>
+      <c r="AJ19" s="94"/>
+      <c r="AK19" s="95">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:37">
-      <c r="A20" s="21">
+      <c r="A20" s="70">
         <v>17</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="22">
+      <c r="C20" s="86">
         <v>46220</v>
       </c>
-      <c r="D20" s="30"/>
-      <c r="E20" s="62"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="62"/>
-      <c r="J20" s="62"/>
-      <c r="K20" s="62"/>
-      <c r="L20" s="63"/>
-      <c r="M20" s="63"/>
-      <c r="N20" s="63"/>
-      <c r="O20" s="63"/>
-      <c r="P20" s="63"/>
-      <c r="Q20" s="63"/>
-      <c r="R20" s="63"/>
-      <c r="S20" s="29"/>
-      <c r="T20" s="29"/>
-      <c r="U20" s="64"/>
-      <c r="V20" s="64"/>
-      <c r="W20" s="64"/>
-      <c r="X20" s="64"/>
-      <c r="Y20" s="64"/>
-      <c r="Z20" s="65"/>
-      <c r="AA20" s="65"/>
-      <c r="AB20" s="65"/>
-      <c r="AC20" s="65"/>
-      <c r="AD20" s="65"/>
-      <c r="AE20" s="66"/>
-      <c r="AF20" s="66"/>
-      <c r="AG20" s="66"/>
-      <c r="AH20" s="67"/>
-      <c r="AI20" s="67"/>
-      <c r="AJ20" s="67"/>
-      <c r="AK20" s="25">
+      <c r="D20" s="70" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="I20" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="J20" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="K20" s="71"/>
+      <c r="L20" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="M20" s="72"/>
+      <c r="N20" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="O20" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="P20" s="72"/>
+      <c r="Q20" s="72"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="73"/>
+      <c r="T20" s="73"/>
+      <c r="U20" s="74"/>
+      <c r="V20" s="74"/>
+      <c r="W20" s="74"/>
+      <c r="X20" s="74"/>
+      <c r="Y20" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z20" s="75"/>
+      <c r="AA20" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB20" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC20" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD20" s="75"/>
+      <c r="AE20" s="76"/>
+      <c r="AF20" s="76" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG20" s="76"/>
+      <c r="AH20" s="77"/>
+      <c r="AI20" s="77"/>
+      <c r="AJ20" s="77"/>
+      <c r="AK20" s="95">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:37">
-      <c r="A21" s="21">
+      <c r="A21" s="70">
         <v>18</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="70" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="22">
+      <c r="C21" s="86">
         <v>46221</v>
       </c>
-      <c r="D21" s="30"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="62"/>
-      <c r="H21" s="62"/>
-      <c r="I21" s="62"/>
-      <c r="J21" s="62"/>
-      <c r="K21" s="62"/>
-      <c r="L21" s="63"/>
-      <c r="M21" s="63"/>
-      <c r="N21" s="63"/>
-      <c r="O21" s="63"/>
-      <c r="P21" s="63"/>
-      <c r="Q21" s="63"/>
-      <c r="R21" s="63"/>
-      <c r="S21" s="29"/>
-      <c r="T21" s="29"/>
-      <c r="U21" s="64"/>
-      <c r="V21" s="64"/>
-      <c r="W21" s="64"/>
-      <c r="X21" s="64"/>
-      <c r="Y21" s="64"/>
-      <c r="Z21" s="65"/>
-      <c r="AA21" s="65"/>
-      <c r="AB21" s="65"/>
-      <c r="AC21" s="65"/>
-      <c r="AD21" s="65"/>
-      <c r="AE21" s="66"/>
-      <c r="AF21" s="66"/>
-      <c r="AG21" s="66"/>
-      <c r="AH21" s="67"/>
-      <c r="AI21" s="67"/>
-      <c r="AJ21" s="67"/>
-      <c r="AK21" s="25">
+      <c r="D21" s="70" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="H21" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="I21" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="J21" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="K21" s="71"/>
+      <c r="L21" s="72"/>
+      <c r="M21" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="N21" s="72"/>
+      <c r="O21" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="P21" s="72"/>
+      <c r="Q21" s="72"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="73"/>
+      <c r="T21" s="73"/>
+      <c r="U21" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="V21" s="74"/>
+      <c r="W21" s="74"/>
+      <c r="X21" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y21" s="74"/>
+      <c r="Z21" s="75"/>
+      <c r="AA21" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB21" s="75"/>
+      <c r="AC21" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD21" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE21" s="76"/>
+      <c r="AF21" s="76" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG21" s="76" t="s">
+        <v>12</v>
+      </c>
+      <c r="AH21" s="77"/>
+      <c r="AI21" s="77"/>
+      <c r="AJ21" s="77"/>
+      <c r="AK21" s="95">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:37">
-      <c r="A22" s="21">
+      <c r="A22" s="30">
         <v>19</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="30" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="22">
         <v>46222</v>
       </c>
-      <c r="D22" s="30"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="62"/>
+      <c r="D22" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="62" t="s">
+        <v>12</v>
+      </c>
       <c r="H22" s="62"/>
-      <c r="I22" s="62"/>
+      <c r="I22" s="62" t="s">
+        <v>12</v>
+      </c>
       <c r="J22" s="62"/>
       <c r="K22" s="62"/>
       <c r="L22" s="63"/>
-      <c r="M22" s="63"/>
+      <c r="M22" s="63" t="s">
+        <v>12</v>
+      </c>
       <c r="N22" s="63"/>
       <c r="O22" s="63"/>
       <c r="P22" s="63"/>
@@ -6166,7 +6430,9 @@
       <c r="X22" s="64"/>
       <c r="Y22" s="64"/>
       <c r="Z22" s="65"/>
-      <c r="AA22" s="65"/>
+      <c r="AA22" s="65" t="s">
+        <v>12</v>
+      </c>
       <c r="AB22" s="65"/>
       <c r="AC22" s="65"/>
       <c r="AD22" s="65"/>
@@ -6178,151 +6444,197 @@
       <c r="AJ22" s="67"/>
       <c r="AK22" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:37">
-      <c r="A23" s="21">
+      <c r="A23" s="85">
         <v>20</v>
       </c>
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="22">
+      <c r="C23" s="96">
         <v>46223</v>
       </c>
-      <c r="D23" s="30"/>
-      <c r="E23" s="62"/>
-      <c r="F23" s="62"/>
-      <c r="G23" s="62"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="62"/>
-      <c r="K23" s="62"/>
-      <c r="L23" s="63"/>
-      <c r="M23" s="63"/>
-      <c r="N23" s="63"/>
-      <c r="O23" s="63"/>
-      <c r="P23" s="63"/>
-      <c r="Q23" s="63"/>
-      <c r="R23" s="63"/>
-      <c r="S23" s="29"/>
-      <c r="T23" s="29"/>
-      <c r="U23" s="64"/>
-      <c r="V23" s="64"/>
-      <c r="W23" s="64"/>
-      <c r="X23" s="64"/>
-      <c r="Y23" s="64"/>
-      <c r="Z23" s="65"/>
-      <c r="AA23" s="65"/>
-      <c r="AB23" s="65"/>
-      <c r="AC23" s="65"/>
-      <c r="AD23" s="65"/>
-      <c r="AE23" s="66"/>
-      <c r="AF23" s="66"/>
-      <c r="AG23" s="66"/>
-      <c r="AH23" s="67"/>
-      <c r="AI23" s="67"/>
-      <c r="AJ23" s="67"/>
-      <c r="AK23" s="25">
+      <c r="D23" s="87" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23" s="88"/>
+      <c r="F23" s="88"/>
+      <c r="G23" s="88"/>
+      <c r="H23" s="88"/>
+      <c r="I23" s="88"/>
+      <c r="J23" s="88"/>
+      <c r="K23" s="88"/>
+      <c r="L23" s="89"/>
+      <c r="M23" s="89" t="s">
+        <v>12</v>
+      </c>
+      <c r="N23" s="89" t="s">
+        <v>12</v>
+      </c>
+      <c r="O23" s="89" t="s">
+        <v>12</v>
+      </c>
+      <c r="P23" s="89"/>
+      <c r="Q23" s="89"/>
+      <c r="R23" s="89"/>
+      <c r="S23" s="90"/>
+      <c r="T23" s="90"/>
+      <c r="U23" s="91"/>
+      <c r="V23" s="91"/>
+      <c r="W23" s="91"/>
+      <c r="X23" s="91"/>
+      <c r="Y23" s="91"/>
+      <c r="Z23" s="92"/>
+      <c r="AA23" s="92" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB23" s="92"/>
+      <c r="AC23" s="92" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD23" s="92" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE23" s="93"/>
+      <c r="AF23" s="93"/>
+      <c r="AG23" s="93"/>
+      <c r="AH23" s="94"/>
+      <c r="AI23" s="94"/>
+      <c r="AJ23" s="94"/>
+      <c r="AK23" s="125">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:37">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:37" ht="15.75" thickBot="1">
       <c r="A24" s="21">
         <v>21</v>
       </c>
       <c r="B24" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="22">
+      <c r="C24" s="68">
         <v>46224</v>
       </c>
-      <c r="D24" s="30"/>
-      <c r="E24" s="62"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="62"/>
-      <c r="H24" s="62"/>
-      <c r="I24" s="62"/>
-      <c r="J24" s="62"/>
-      <c r="K24" s="62"/>
-      <c r="L24" s="63"/>
-      <c r="M24" s="63"/>
-      <c r="N24" s="63"/>
-      <c r="O24" s="63"/>
-      <c r="P24" s="63"/>
-      <c r="Q24" s="63"/>
-      <c r="R24" s="63"/>
-      <c r="S24" s="29"/>
-      <c r="T24" s="29"/>
-      <c r="U24" s="64"/>
-      <c r="V24" s="64"/>
-      <c r="W24" s="64"/>
-      <c r="X24" s="64"/>
-      <c r="Y24" s="64"/>
-      <c r="Z24" s="65"/>
-      <c r="AA24" s="65"/>
-      <c r="AB24" s="65"/>
-      <c r="AC24" s="65"/>
-      <c r="AD24" s="65"/>
-      <c r="AE24" s="66"/>
-      <c r="AF24" s="66"/>
-      <c r="AG24" s="66"/>
-      <c r="AH24" s="67"/>
-      <c r="AI24" s="67"/>
-      <c r="AJ24" s="67"/>
-      <c r="AK24" s="25">
+      <c r="D24" s="126" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" s="127" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="127" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" s="127" t="s">
+        <v>12</v>
+      </c>
+      <c r="H24" s="127"/>
+      <c r="I24" s="127"/>
+      <c r="J24" s="127"/>
+      <c r="K24" s="127"/>
+      <c r="L24" s="128" t="s">
+        <v>12</v>
+      </c>
+      <c r="M24" s="128" t="s">
+        <v>12</v>
+      </c>
+      <c r="N24" s="128" t="s">
+        <v>12</v>
+      </c>
+      <c r="O24" s="128" t="s">
+        <v>12</v>
+      </c>
+      <c r="P24" s="128"/>
+      <c r="Q24" s="128"/>
+      <c r="R24" s="128"/>
+      <c r="S24" s="129"/>
+      <c r="T24" s="129"/>
+      <c r="U24" s="130" t="s">
+        <v>12</v>
+      </c>
+      <c r="V24" s="130"/>
+      <c r="W24" s="130"/>
+      <c r="X24" s="130"/>
+      <c r="Y24" s="130"/>
+      <c r="Z24" s="131"/>
+      <c r="AA24" s="131"/>
+      <c r="AB24" s="131"/>
+      <c r="AC24" s="131" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD24" s="131" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE24" s="132"/>
+      <c r="AF24" s="132"/>
+      <c r="AG24" s="132"/>
+      <c r="AH24" s="133"/>
+      <c r="AI24" s="133"/>
+      <c r="AJ24" s="133"/>
+      <c r="AK24" s="134">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:37">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:37" ht="15.75" thickBot="1">
       <c r="A25" s="21">
         <v>22</v>
       </c>
       <c r="B25" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="22">
+      <c r="C25" s="68">
         <v>46225</v>
       </c>
-      <c r="D25" s="30"/>
-      <c r="E25" s="62"/>
-      <c r="F25" s="62"/>
-      <c r="G25" s="62"/>
-      <c r="H25" s="62"/>
-      <c r="I25" s="62"/>
-      <c r="J25" s="62"/>
-      <c r="K25" s="62"/>
-      <c r="L25" s="63"/>
-      <c r="M25" s="63"/>
-      <c r="N25" s="63"/>
-      <c r="O25" s="63"/>
-      <c r="P25" s="63"/>
-      <c r="Q25" s="63"/>
-      <c r="R25" s="63"/>
-      <c r="S25" s="29"/>
-      <c r="T25" s="29"/>
-      <c r="U25" s="64"/>
-      <c r="V25" s="64"/>
-      <c r="W25" s="64"/>
-      <c r="X25" s="64"/>
-      <c r="Y25" s="64"/>
-      <c r="Z25" s="65"/>
-      <c r="AA25" s="65"/>
-      <c r="AB25" s="65"/>
-      <c r="AC25" s="65"/>
-      <c r="AD25" s="65"/>
-      <c r="AE25" s="66"/>
-      <c r="AF25" s="66"/>
-      <c r="AG25" s="66"/>
-      <c r="AH25" s="67"/>
-      <c r="AI25" s="67"/>
-      <c r="AJ25" s="67"/>
-      <c r="AK25" s="25">
+      <c r="D25" s="137" t="s">
+        <v>62</v>
+      </c>
+      <c r="E25" s="138"/>
+      <c r="F25" s="138" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="138"/>
+      <c r="H25" s="138"/>
+      <c r="I25" s="138"/>
+      <c r="J25" s="138"/>
+      <c r="K25" s="138" t="s">
+        <v>12</v>
+      </c>
+      <c r="L25" s="139" t="s">
+        <v>12</v>
+      </c>
+      <c r="M25" s="139" t="s">
+        <v>12</v>
+      </c>
+      <c r="N25" s="139"/>
+      <c r="O25" s="139"/>
+      <c r="P25" s="139"/>
+      <c r="Q25" s="139"/>
+      <c r="R25" s="139"/>
+      <c r="S25" s="140"/>
+      <c r="T25" s="140"/>
+      <c r="U25" s="141"/>
+      <c r="V25" s="141"/>
+      <c r="W25" s="141"/>
+      <c r="X25" s="141"/>
+      <c r="Y25" s="141"/>
+      <c r="Z25" s="142"/>
+      <c r="AA25" s="142"/>
+      <c r="AB25" s="142"/>
+      <c r="AC25" s="142"/>
+      <c r="AD25" s="142"/>
+      <c r="AE25" s="143"/>
+      <c r="AF25" s="143"/>
+      <c r="AG25" s="143"/>
+      <c r="AH25" s="144"/>
+      <c r="AI25" s="144"/>
+      <c r="AJ25" s="144"/>
+      <c r="AK25" s="145">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:37">
@@ -6332,43 +6644,43 @@
       <c r="B26" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="22">
+      <c r="C26" s="68">
         <v>46226</v>
       </c>
-      <c r="D26" s="30"/>
-      <c r="E26" s="62"/>
-      <c r="F26" s="62"/>
-      <c r="G26" s="62"/>
-      <c r="H26" s="62"/>
-      <c r="I26" s="62"/>
-      <c r="J26" s="62"/>
-      <c r="K26" s="62"/>
-      <c r="L26" s="63"/>
-      <c r="M26" s="63"/>
-      <c r="N26" s="63"/>
-      <c r="O26" s="63"/>
-      <c r="P26" s="63"/>
-      <c r="Q26" s="63"/>
-      <c r="R26" s="63"/>
-      <c r="S26" s="29"/>
-      <c r="T26" s="29"/>
-      <c r="U26" s="64"/>
-      <c r="V26" s="64"/>
-      <c r="W26" s="64"/>
-      <c r="X26" s="64"/>
-      <c r="Y26" s="64"/>
-      <c r="Z26" s="65"/>
-      <c r="AA26" s="65"/>
-      <c r="AB26" s="65"/>
-      <c r="AC26" s="65"/>
-      <c r="AD26" s="65"/>
-      <c r="AE26" s="66"/>
-      <c r="AF26" s="66"/>
-      <c r="AG26" s="66"/>
-      <c r="AH26" s="67"/>
-      <c r="AI26" s="67"/>
-      <c r="AJ26" s="67"/>
-      <c r="AK26" s="25">
+      <c r="D26" s="135"/>
+      <c r="E26" s="136"/>
+      <c r="F26" s="78"/>
+      <c r="G26" s="78"/>
+      <c r="H26" s="78"/>
+      <c r="I26" s="78"/>
+      <c r="J26" s="78"/>
+      <c r="K26" s="78"/>
+      <c r="L26" s="79"/>
+      <c r="M26" s="79"/>
+      <c r="N26" s="79"/>
+      <c r="O26" s="79"/>
+      <c r="P26" s="79"/>
+      <c r="Q26" s="79"/>
+      <c r="R26" s="79"/>
+      <c r="S26" s="80"/>
+      <c r="T26" s="80"/>
+      <c r="U26" s="81"/>
+      <c r="V26" s="81"/>
+      <c r="W26" s="81"/>
+      <c r="X26" s="81"/>
+      <c r="Y26" s="81"/>
+      <c r="Z26" s="82"/>
+      <c r="AA26" s="82"/>
+      <c r="AB26" s="82"/>
+      <c r="AC26" s="82"/>
+      <c r="AD26" s="82"/>
+      <c r="AE26" s="83"/>
+      <c r="AF26" s="83"/>
+      <c r="AG26" s="83"/>
+      <c r="AH26" s="84"/>
+      <c r="AI26" s="84"/>
+      <c r="AJ26" s="84"/>
+      <c r="AK26" s="97">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6383,7 +6695,7 @@
       <c r="C27" s="22">
         <v>46227</v>
       </c>
-      <c r="D27" s="30"/>
+      <c r="D27" s="85"/>
       <c r="E27" s="62"/>
       <c r="F27" s="62"/>
       <c r="G27" s="62"/>

--- a/Другое/study_chart.xlsx
+++ b/Другое/study_chart.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROG\Git\Repository_1\Другое\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10380" activeTab="2"/>
   </bookViews>
@@ -11,7 +16,7 @@
     <sheet name="Июль" sheetId="4" r:id="rId2"/>
     <sheet name="Август" sheetId="5" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +39,7 @@
     <author>Собянин Евгений Андреевич (new)</author>
   </authors>
   <commentList>
-    <comment ref="AF21" authorId="0">
+    <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -57,7 +62,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF22" authorId="0">
+    <comment ref="AF22" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -81,7 +86,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF23" authorId="0">
+    <comment ref="AF23" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -107,7 +112,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF24" authorId="0">
+    <comment ref="AF24" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -131,7 +136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG24" authorId="0">
+    <comment ref="AG24" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -153,7 +158,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH24" authorId="0">
+    <comment ref="AH24" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -175,7 +180,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF25" authorId="0">
+    <comment ref="AF25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -201,7 +206,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG25" authorId="0">
+    <comment ref="AG25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -223,7 +228,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH25" authorId="0">
+    <comment ref="AH25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -245,7 +250,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AI25" authorId="0">
+    <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -267,7 +272,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AJ25" authorId="0">
+    <comment ref="AJ25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -289,7 +294,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AK25" authorId="0">
+    <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -311,7 +316,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF26" authorId="0">
+    <comment ref="AF26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -333,7 +338,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG26" authorId="0">
+    <comment ref="AG26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -355,7 +360,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH26" authorId="0">
+    <comment ref="AH26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -377,7 +382,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AI26" authorId="0">
+    <comment ref="AI26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -399,7 +404,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AJ26" authorId="0">
+    <comment ref="AJ26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -421,7 +426,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AK26" authorId="0">
+    <comment ref="AK26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -443,7 +448,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF27" authorId="0">
+    <comment ref="AF27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -465,7 +470,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG27" authorId="0">
+    <comment ref="AG27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -487,7 +492,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH27" authorId="0">
+    <comment ref="AH27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -509,7 +514,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF28" authorId="0">
+    <comment ref="AF28" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -531,7 +536,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF29" authorId="0">
+    <comment ref="AF29" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -554,7 +559,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF30" authorId="0">
+    <comment ref="AF30" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -578,7 +583,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF31" authorId="0">
+    <comment ref="AF31" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -601,7 +606,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF32" authorId="0">
+    <comment ref="AF32" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -625,7 +630,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF33" authorId="0">
+    <comment ref="AF33" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -648,7 +653,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF35" authorId="0">
+    <comment ref="AF35" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -670,7 +675,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF36" authorId="0">
+    <comment ref="AF36" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -692,7 +697,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF37" authorId="0">
+    <comment ref="AF37" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -714,7 +719,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF38" authorId="0">
+    <comment ref="AF38" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -746,7 +751,7 @@
     <author>Собянин Евгений Андреевич (new)</author>
   </authors>
   <commentList>
-    <comment ref="AH14" authorId="0">
+    <comment ref="AH14" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -766,7 +771,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="77">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -1002,7 +1007,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mmm"/>
   </numFmts>
@@ -1440,7 +1445,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="35">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -1808,15 +1813,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="0" tint="-0.34998626667073579"/>
+      <left style="medium">
+        <color theme="0" tint="-0.249977111117893"/>
       </left>
       <right style="thin">
         <color theme="0" tint="-0.34998626667073579"/>
       </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="0" tint="-0.34998626667073579"/>
+      <top style="medium">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.249977111117893"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1825,24 +1832,11 @@
       <right style="thin">
         <color theme="0" tint="-0.249977111117893"/>
       </right>
-      <top/>
-      <bottom style="thin">
+      <top style="medium">
         <color theme="0" tint="-0.249977111117893"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </right>
-      <top style="medium">
-        <color theme="0" tint="-0.34998626667073579"/>
       </top>
       <bottom style="medium">
-        <color theme="0" tint="-0.34998626667073579"/>
+        <color theme="0" tint="-0.249977111117893"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1854,10 +1848,10 @@
         <color theme="0" tint="-0.249977111117893"/>
       </right>
       <top style="medium">
-        <color theme="0" tint="-0.34998626667073579"/>
+        <color theme="0" tint="-0.249977111117893"/>
       </top>
       <bottom style="medium">
-        <color theme="0" tint="-0.34998626667073579"/>
+        <color theme="0" tint="-0.249977111117893"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1866,13 +1860,13 @@
         <color theme="0" tint="-0.249977111117893"/>
       </left>
       <right style="medium">
-        <color theme="0" tint="-0.34998626667073579"/>
+        <color theme="0" tint="-0.249977111117893"/>
       </right>
       <top style="medium">
-        <color theme="0" tint="-0.34998626667073579"/>
+        <color theme="0" tint="-0.249977111117893"/>
       </top>
       <bottom style="medium">
-        <color theme="0" tint="-0.34998626667073579"/>
+        <color theme="0" tint="-0.249977111117893"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1880,7 +1874,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2159,6 +2153,36 @@
     <xf numFmtId="0" fontId="17" fillId="12" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="27" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2240,67 +2264,34 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="33" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="28" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="33" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2413,7 +2404,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2445,9 +2436,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2479,6 +2471,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -2654,7 +2647,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="H9:Q22"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -2671,18 +2664,18 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:17" ht="45" customHeight="1">
-      <c r="H9" s="98" t="s">
+      <c r="H9" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="99"/>
-      <c r="J9" s="99"/>
-      <c r="K9" s="99"/>
-      <c r="L9" s="99"/>
-      <c r="M9" s="99"/>
-      <c r="N9" s="99"/>
-      <c r="O9" s="99"/>
-      <c r="P9" s="99"/>
-      <c r="Q9" s="100"/>
+      <c r="I9" s="109"/>
+      <c r="J9" s="109"/>
+      <c r="K9" s="109"/>
+      <c r="L9" s="109"/>
+      <c r="M9" s="109"/>
+      <c r="N9" s="109"/>
+      <c r="O9" s="109"/>
+      <c r="P9" s="109"/>
+      <c r="Q9" s="110"/>
     </row>
     <row r="10" spans="8:17" ht="30" customHeight="1">
       <c r="H10" s="55" t="s">
@@ -2951,11 +2944,11 @@
       <c r="Q21" s="60"/>
     </row>
     <row r="22" spans="8:17" ht="15.75">
-      <c r="H22" s="101" t="s">
+      <c r="H22" s="111" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="102"/>
-      <c r="J22" s="103"/>
+      <c r="I22" s="112"/>
+      <c r="J22" s="113"/>
       <c r="K22" s="61">
         <f>COUNTA(K11:K21)</f>
         <v>6</v>
@@ -3006,7 +2999,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="H9:AL42"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -3032,39 +3025,39 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:38" ht="45" customHeight="1">
-      <c r="H9" s="104" t="s">
+      <c r="H9" s="114" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="105"/>
-      <c r="J9" s="105"/>
-      <c r="K9" s="105"/>
-      <c r="L9" s="105"/>
-      <c r="M9" s="105"/>
-      <c r="N9" s="105"/>
-      <c r="O9" s="105"/>
-      <c r="P9" s="105"/>
-      <c r="Q9" s="105"/>
-      <c r="R9" s="105"/>
-      <c r="S9" s="105"/>
-      <c r="T9" s="105"/>
-      <c r="U9" s="105"/>
-      <c r="V9" s="105"/>
-      <c r="W9" s="105"/>
-      <c r="X9" s="105"/>
-      <c r="Y9" s="105"/>
-      <c r="Z9" s="105"/>
-      <c r="AA9" s="105"/>
-      <c r="AB9" s="105"/>
-      <c r="AC9" s="105"/>
-      <c r="AD9" s="105"/>
-      <c r="AE9" s="105"/>
-      <c r="AF9" s="105"/>
-      <c r="AG9" s="105"/>
-      <c r="AH9" s="105"/>
-      <c r="AI9" s="105"/>
-      <c r="AJ9" s="105"/>
-      <c r="AK9" s="105"/>
-      <c r="AL9" s="105"/>
+      <c r="I9" s="115"/>
+      <c r="J9" s="115"/>
+      <c r="K9" s="115"/>
+      <c r="L9" s="115"/>
+      <c r="M9" s="115"/>
+      <c r="N9" s="115"/>
+      <c r="O9" s="115"/>
+      <c r="P9" s="115"/>
+      <c r="Q9" s="115"/>
+      <c r="R9" s="115"/>
+      <c r="S9" s="115"/>
+      <c r="T9" s="115"/>
+      <c r="U9" s="115"/>
+      <c r="V9" s="115"/>
+      <c r="W9" s="115"/>
+      <c r="X9" s="115"/>
+      <c r="Y9" s="115"/>
+      <c r="Z9" s="115"/>
+      <c r="AA9" s="115"/>
+      <c r="AB9" s="115"/>
+      <c r="AC9" s="115"/>
+      <c r="AD9" s="115"/>
+      <c r="AE9" s="115"/>
+      <c r="AF9" s="115"/>
+      <c r="AG9" s="115"/>
+      <c r="AH9" s="115"/>
+      <c r="AI9" s="115"/>
+      <c r="AJ9" s="115"/>
+      <c r="AK9" s="115"/>
+      <c r="AL9" s="115"/>
     </row>
     <row r="10" spans="8:38" ht="30" customHeight="1">
       <c r="H10" s="32" t="s">
@@ -4744,11 +4737,11 @@
       </c>
     </row>
     <row r="42" spans="8:38" ht="15.75">
-      <c r="H42" s="106" t="s">
+      <c r="H42" s="116" t="s">
         <v>19</v>
       </c>
-      <c r="I42" s="106"/>
-      <c r="J42" s="106"/>
+      <c r="I42" s="116"/>
+      <c r="J42" s="116"/>
       <c r="K42" s="32">
         <f>COUNTA(K11:K41)</f>
         <v>6</v>
@@ -4878,7 +4871,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AK34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -4913,66 +4906,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="112"/>
-      <c r="B1" s="113"/>
-      <c r="C1" s="114"/>
+      <c r="A1" s="122"/>
+      <c r="B1" s="123"/>
+      <c r="C1" s="124"/>
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="118" t="s">
+      <c r="E1" s="128" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="118"/>
-      <c r="G1" s="118"/>
-      <c r="H1" s="118"/>
-      <c r="I1" s="118"/>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="119" t="s">
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="128"/>
+      <c r="K1" s="128"/>
+      <c r="L1" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="120" t="s">
+      <c r="M1" s="129"/>
+      <c r="N1" s="129"/>
+      <c r="O1" s="129"/>
+      <c r="P1" s="129"/>
+      <c r="Q1" s="129"/>
+      <c r="R1" s="129"/>
+      <c r="S1" s="130" t="s">
         <v>39</v>
       </c>
-      <c r="T1" s="120"/>
-      <c r="U1" s="121" t="s">
+      <c r="T1" s="130"/>
+      <c r="U1" s="131" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="123"/>
-      <c r="Z1" s="124" t="s">
+      <c r="V1" s="132"/>
+      <c r="W1" s="132"/>
+      <c r="X1" s="132"/>
+      <c r="Y1" s="133"/>
+      <c r="Z1" s="134" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="124"/>
-      <c r="AB1" s="124"/>
-      <c r="AC1" s="124"/>
-      <c r="AD1" s="124"/>
-      <c r="AE1" s="107" t="s">
+      <c r="AA1" s="134"/>
+      <c r="AB1" s="134"/>
+      <c r="AC1" s="134"/>
+      <c r="AD1" s="134"/>
+      <c r="AE1" s="117" t="s">
         <v>42</v>
       </c>
-      <c r="AF1" s="107"/>
-      <c r="AG1" s="107"/>
-      <c r="AH1" s="108" t="s">
+      <c r="AF1" s="117"/>
+      <c r="AG1" s="117"/>
+      <c r="AH1" s="118" t="s">
         <v>43</v>
       </c>
-      <c r="AI1" s="108"/>
-      <c r="AJ1" s="108"/>
-      <c r="AK1" s="109" t="s">
+      <c r="AI1" s="118"/>
+      <c r="AJ1" s="118"/>
+      <c r="AK1" s="119" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1">
-      <c r="A2" s="115"/>
-      <c r="B2" s="116"/>
-      <c r="C2" s="117"/>
+      <c r="A2" s="125"/>
+      <c r="B2" s="126"/>
+      <c r="C2" s="127"/>
       <c r="D2" s="5" t="s">
         <v>44</v>
       </c>
@@ -5066,7 +5059,7 @@
       <c r="AH2" s="12"/>
       <c r="AI2" s="12"/>
       <c r="AJ2" s="12"/>
-      <c r="AK2" s="110"/>
+      <c r="AK2" s="120"/>
     </row>
     <row r="3" spans="1:37">
       <c r="A3" s="13" t="s">
@@ -5177,7 +5170,7 @@
       <c r="AJ3" s="20">
         <v>2</v>
       </c>
-      <c r="AK3" s="111"/>
+      <c r="AK3" s="121"/>
     </row>
     <row r="4" spans="1:37">
       <c r="A4" s="21">
@@ -6504,12 +6497,12 @@
       <c r="AH23" s="94"/>
       <c r="AI23" s="94"/>
       <c r="AJ23" s="94"/>
-      <c r="AK23" s="125">
+      <c r="AK23" s="98">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:37" ht="15.75" thickBot="1">
+    <row r="24" spans="1:37">
       <c r="A24" s="21">
         <v>21</v>
       </c>
@@ -6519,62 +6512,62 @@
       <c r="C24" s="68">
         <v>46224</v>
       </c>
-      <c r="D24" s="126" t="s">
+      <c r="D24" s="99" t="s">
         <v>62</v>
       </c>
-      <c r="E24" s="127" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="127" t="s">
-        <v>12</v>
-      </c>
-      <c r="G24" s="127" t="s">
-        <v>12</v>
-      </c>
-      <c r="H24" s="127"/>
-      <c r="I24" s="127"/>
-      <c r="J24" s="127"/>
-      <c r="K24" s="127"/>
-      <c r="L24" s="128" t="s">
-        <v>12</v>
-      </c>
-      <c r="M24" s="128" t="s">
-        <v>12</v>
-      </c>
-      <c r="N24" s="128" t="s">
-        <v>12</v>
-      </c>
-      <c r="O24" s="128" t="s">
-        <v>12</v>
-      </c>
-      <c r="P24" s="128"/>
-      <c r="Q24" s="128"/>
-      <c r="R24" s="128"/>
-      <c r="S24" s="129"/>
-      <c r="T24" s="129"/>
-      <c r="U24" s="130" t="s">
-        <v>12</v>
-      </c>
-      <c r="V24" s="130"/>
-      <c r="W24" s="130"/>
-      <c r="X24" s="130"/>
-      <c r="Y24" s="130"/>
-      <c r="Z24" s="131"/>
-      <c r="AA24" s="131"/>
-      <c r="AB24" s="131"/>
-      <c r="AC24" s="131" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD24" s="131" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE24" s="132"/>
-      <c r="AF24" s="132"/>
-      <c r="AG24" s="132"/>
-      <c r="AH24" s="133"/>
-      <c r="AI24" s="133"/>
-      <c r="AJ24" s="133"/>
-      <c r="AK24" s="134">
+      <c r="E24" s="100" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="100" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" s="100" t="s">
+        <v>12</v>
+      </c>
+      <c r="H24" s="100"/>
+      <c r="I24" s="100"/>
+      <c r="J24" s="100"/>
+      <c r="K24" s="100"/>
+      <c r="L24" s="101" t="s">
+        <v>12</v>
+      </c>
+      <c r="M24" s="101" t="s">
+        <v>12</v>
+      </c>
+      <c r="N24" s="101" t="s">
+        <v>12</v>
+      </c>
+      <c r="O24" s="101" t="s">
+        <v>12</v>
+      </c>
+      <c r="P24" s="101"/>
+      <c r="Q24" s="101"/>
+      <c r="R24" s="101"/>
+      <c r="S24" s="102"/>
+      <c r="T24" s="102"/>
+      <c r="U24" s="103" t="s">
+        <v>12</v>
+      </c>
+      <c r="V24" s="103"/>
+      <c r="W24" s="103"/>
+      <c r="X24" s="103"/>
+      <c r="Y24" s="103"/>
+      <c r="Z24" s="104"/>
+      <c r="AA24" s="104"/>
+      <c r="AB24" s="104"/>
+      <c r="AC24" s="104" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD24" s="104" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE24" s="105"/>
+      <c r="AF24" s="105"/>
+      <c r="AG24" s="105"/>
+      <c r="AH24" s="106"/>
+      <c r="AI24" s="106"/>
+      <c r="AJ24" s="106"/>
+      <c r="AK24" s="107">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -6589,55 +6582,65 @@
       <c r="C25" s="68">
         <v>46225</v>
       </c>
-      <c r="D25" s="137" t="s">
+      <c r="D25" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="E25" s="138"/>
-      <c r="F25" s="138" t="s">
-        <v>12</v>
-      </c>
-      <c r="G25" s="138"/>
-      <c r="H25" s="138"/>
-      <c r="I25" s="138"/>
-      <c r="J25" s="138"/>
-      <c r="K25" s="138" t="s">
-        <v>12</v>
-      </c>
-      <c r="L25" s="139" t="s">
-        <v>12</v>
-      </c>
-      <c r="M25" s="139" t="s">
-        <v>12</v>
-      </c>
-      <c r="N25" s="139"/>
-      <c r="O25" s="139"/>
-      <c r="P25" s="139"/>
-      <c r="Q25" s="139"/>
-      <c r="R25" s="139"/>
-      <c r="S25" s="140"/>
-      <c r="T25" s="140"/>
-      <c r="U25" s="141"/>
-      <c r="V25" s="141"/>
-      <c r="W25" s="141"/>
-      <c r="X25" s="141"/>
-      <c r="Y25" s="141"/>
-      <c r="Z25" s="142"/>
-      <c r="AA25" s="142"/>
-      <c r="AB25" s="142"/>
-      <c r="AC25" s="142"/>
-      <c r="AD25" s="142"/>
-      <c r="AE25" s="143"/>
-      <c r="AF25" s="143"/>
-      <c r="AG25" s="143"/>
-      <c r="AH25" s="144"/>
-      <c r="AI25" s="144"/>
-      <c r="AJ25" s="144"/>
-      <c r="AK25" s="145">
+      <c r="E25" s="71"/>
+      <c r="F25" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="71"/>
+      <c r="K25" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="L25" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="M25" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="N25" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="O25" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="P25" s="72"/>
+      <c r="Q25" s="72"/>
+      <c r="R25" s="72"/>
+      <c r="S25" s="73"/>
+      <c r="T25" s="73"/>
+      <c r="U25" s="74"/>
+      <c r="V25" s="74"/>
+      <c r="W25" s="74"/>
+      <c r="X25" s="74"/>
+      <c r="Y25" s="74"/>
+      <c r="Z25" s="75"/>
+      <c r="AA25" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB25" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC25" s="75"/>
+      <c r="AD25" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE25" s="76"/>
+      <c r="AF25" s="76"/>
+      <c r="AG25" s="76"/>
+      <c r="AH25" s="77"/>
+      <c r="AI25" s="77"/>
+      <c r="AJ25" s="77"/>
+      <c r="AK25" s="95">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:37">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:37" ht="15.75" thickBot="1">
       <c r="A26" s="21">
         <v>23</v>
       </c>
@@ -6649,40 +6652,44 @@
       </c>
       <c r="D26" s="135"/>
       <c r="E26" s="136"/>
-      <c r="F26" s="78"/>
-      <c r="G26" s="78"/>
-      <c r="H26" s="78"/>
-      <c r="I26" s="78"/>
-      <c r="J26" s="78"/>
-      <c r="K26" s="78"/>
-      <c r="L26" s="79"/>
-      <c r="M26" s="79"/>
-      <c r="N26" s="79"/>
-      <c r="O26" s="79"/>
-      <c r="P26" s="79"/>
-      <c r="Q26" s="79"/>
-      <c r="R26" s="79"/>
-      <c r="S26" s="80"/>
-      <c r="T26" s="80"/>
-      <c r="U26" s="81"/>
-      <c r="V26" s="81"/>
-      <c r="W26" s="81"/>
-      <c r="X26" s="81"/>
-      <c r="Y26" s="81"/>
-      <c r="Z26" s="82"/>
-      <c r="AA26" s="82"/>
-      <c r="AB26" s="82"/>
-      <c r="AC26" s="82"/>
-      <c r="AD26" s="82"/>
-      <c r="AE26" s="83"/>
-      <c r="AF26" s="83"/>
-      <c r="AG26" s="83"/>
-      <c r="AH26" s="84"/>
-      <c r="AI26" s="84"/>
-      <c r="AJ26" s="84"/>
-      <c r="AK26" s="97">
+      <c r="F26" s="137"/>
+      <c r="G26" s="137" t="s">
+        <v>12</v>
+      </c>
+      <c r="H26" s="137"/>
+      <c r="I26" s="137"/>
+      <c r="J26" s="137"/>
+      <c r="K26" s="137" t="s">
+        <v>12</v>
+      </c>
+      <c r="L26" s="138"/>
+      <c r="M26" s="138"/>
+      <c r="N26" s="138"/>
+      <c r="O26" s="138"/>
+      <c r="P26" s="138"/>
+      <c r="Q26" s="138"/>
+      <c r="R26" s="138"/>
+      <c r="S26" s="139"/>
+      <c r="T26" s="139"/>
+      <c r="U26" s="140"/>
+      <c r="V26" s="140"/>
+      <c r="W26" s="140"/>
+      <c r="X26" s="140"/>
+      <c r="Y26" s="140"/>
+      <c r="Z26" s="141"/>
+      <c r="AA26" s="141"/>
+      <c r="AB26" s="141"/>
+      <c r="AC26" s="141"/>
+      <c r="AD26" s="141"/>
+      <c r="AE26" s="142"/>
+      <c r="AF26" s="142"/>
+      <c r="AG26" s="142"/>
+      <c r="AH26" s="143"/>
+      <c r="AI26" s="143"/>
+      <c r="AJ26" s="143"/>
+      <c r="AK26" s="144">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:37">
@@ -6696,39 +6703,39 @@
         <v>46227</v>
       </c>
       <c r="D27" s="85"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="62"/>
-      <c r="K27" s="62"/>
-      <c r="L27" s="63"/>
-      <c r="M27" s="63"/>
-      <c r="N27" s="63"/>
-      <c r="O27" s="63"/>
-      <c r="P27" s="63"/>
-      <c r="Q27" s="63"/>
-      <c r="R27" s="63"/>
-      <c r="S27" s="29"/>
-      <c r="T27" s="29"/>
-      <c r="U27" s="64"/>
-      <c r="V27" s="64"/>
-      <c r="W27" s="64"/>
-      <c r="X27" s="64"/>
-      <c r="Y27" s="64"/>
-      <c r="Z27" s="65"/>
-      <c r="AA27" s="65"/>
-      <c r="AB27" s="65"/>
-      <c r="AC27" s="65"/>
-      <c r="AD27" s="65"/>
-      <c r="AE27" s="66"/>
-      <c r="AF27" s="66"/>
-      <c r="AG27" s="66"/>
-      <c r="AH27" s="67"/>
-      <c r="AI27" s="67"/>
-      <c r="AJ27" s="67"/>
-      <c r="AK27" s="25">
+      <c r="E27" s="78"/>
+      <c r="F27" s="78"/>
+      <c r="G27" s="78"/>
+      <c r="H27" s="78"/>
+      <c r="I27" s="78"/>
+      <c r="J27" s="78"/>
+      <c r="K27" s="78"/>
+      <c r="L27" s="79"/>
+      <c r="M27" s="79"/>
+      <c r="N27" s="79"/>
+      <c r="O27" s="79"/>
+      <c r="P27" s="79"/>
+      <c r="Q27" s="79"/>
+      <c r="R27" s="79"/>
+      <c r="S27" s="80"/>
+      <c r="T27" s="80"/>
+      <c r="U27" s="81"/>
+      <c r="V27" s="81"/>
+      <c r="W27" s="81"/>
+      <c r="X27" s="81"/>
+      <c r="Y27" s="81"/>
+      <c r="Z27" s="82"/>
+      <c r="AA27" s="82"/>
+      <c r="AB27" s="82"/>
+      <c r="AC27" s="82"/>
+      <c r="AD27" s="82"/>
+      <c r="AE27" s="83"/>
+      <c r="AF27" s="83"/>
+      <c r="AG27" s="83"/>
+      <c r="AH27" s="84"/>
+      <c r="AI27" s="84"/>
+      <c r="AJ27" s="84"/>
+      <c r="AK27" s="97">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>

--- a/Другое/study_chart.xlsx
+++ b/Другое/study_chart.xlsx
@@ -1,13 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROG\Git\Repository_1\Другое\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10380" activeTab="2"/>
   </bookViews>
@@ -16,7 +11,7 @@
     <sheet name="Июль" sheetId="4" r:id="rId2"/>
     <sheet name="Август" sheetId="5" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="125725"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +34,7 @@
     <author>Собянин Евгений Андреевич (new)</author>
   </authors>
   <commentList>
-    <comment ref="AF21" authorId="0" shapeId="0">
+    <comment ref="AF21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -62,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF22" authorId="0" shapeId="0">
+    <comment ref="AF22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -86,7 +81,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF23" authorId="0" shapeId="0">
+    <comment ref="AF23" authorId="0">
       <text>
         <r>
           <rPr>
@@ -112,7 +107,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF24" authorId="0" shapeId="0">
+    <comment ref="AF24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -136,7 +131,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG24" authorId="0" shapeId="0">
+    <comment ref="AG24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -158,7 +153,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH24" authorId="0" shapeId="0">
+    <comment ref="AH24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -180,7 +175,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF25" authorId="0" shapeId="0">
+    <comment ref="AF25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -206,7 +201,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG25" authorId="0" shapeId="0">
+    <comment ref="AG25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -228,7 +223,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH25" authorId="0" shapeId="0">
+    <comment ref="AH25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -250,7 +245,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AI25" authorId="0" shapeId="0">
+    <comment ref="AI25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -272,7 +267,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AJ25" authorId="0" shapeId="0">
+    <comment ref="AJ25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -294,7 +289,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AK25" authorId="0" shapeId="0">
+    <comment ref="AK25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -316,7 +311,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF26" authorId="0" shapeId="0">
+    <comment ref="AF26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -338,7 +333,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG26" authorId="0" shapeId="0">
+    <comment ref="AG26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -360,7 +355,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH26" authorId="0" shapeId="0">
+    <comment ref="AH26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -382,7 +377,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AI26" authorId="0" shapeId="0">
+    <comment ref="AI26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -404,7 +399,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AJ26" authorId="0" shapeId="0">
+    <comment ref="AJ26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -426,7 +421,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AK26" authorId="0" shapeId="0">
+    <comment ref="AK26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -448,7 +443,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF27" authorId="0" shapeId="0">
+    <comment ref="AF27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -470,7 +465,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG27" authorId="0" shapeId="0">
+    <comment ref="AG27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -492,7 +487,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH27" authorId="0" shapeId="0">
+    <comment ref="AH27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -514,7 +509,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF28" authorId="0" shapeId="0">
+    <comment ref="AF28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -536,7 +531,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF29" authorId="0" shapeId="0">
+    <comment ref="AF29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -559,7 +554,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF30" authorId="0" shapeId="0">
+    <comment ref="AF30" authorId="0">
       <text>
         <r>
           <rPr>
@@ -583,7 +578,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF31" authorId="0" shapeId="0">
+    <comment ref="AF31" authorId="0">
       <text>
         <r>
           <rPr>
@@ -606,7 +601,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF32" authorId="0" shapeId="0">
+    <comment ref="AF32" authorId="0">
       <text>
         <r>
           <rPr>
@@ -630,7 +625,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF33" authorId="0" shapeId="0">
+    <comment ref="AF33" authorId="0">
       <text>
         <r>
           <rPr>
@@ -653,7 +648,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF35" authorId="0" shapeId="0">
+    <comment ref="AF35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -675,7 +670,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF36" authorId="0" shapeId="0">
+    <comment ref="AF36" authorId="0">
       <text>
         <r>
           <rPr>
@@ -697,7 +692,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF37" authorId="0" shapeId="0">
+    <comment ref="AF37" authorId="0">
       <text>
         <r>
           <rPr>
@@ -719,7 +714,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF38" authorId="0" shapeId="0">
+    <comment ref="AF38" authorId="0">
       <text>
         <r>
           <rPr>
@@ -751,7 +746,7 @@
     <author>Собянин Евгений Андреевич (new)</author>
   </authors>
   <commentList>
-    <comment ref="AH14" authorId="0" shapeId="0">
+    <comment ref="AH14" authorId="0">
       <text>
         <r>
           <rPr>
@@ -771,7 +766,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="77">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -1007,7 +1002,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mmm"/>
   </numFmts>
@@ -1813,34 +1808,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color theme="0" tint="-0.249977111117893"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </right>
-      <top style="medium">
-        <color theme="0" tint="-0.249977111117893"/>
-      </top>
-      <bottom style="medium">
-        <color theme="0" tint="-0.249977111117893"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </right>
-      <top style="medium">
-        <color theme="0" tint="-0.249977111117893"/>
-      </top>
-      <bottom style="medium">
-        <color theme="0" tint="-0.249977111117893"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color theme="0" tint="-0.249977111117893"/>
       </left>
@@ -1870,11 +1837,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="medium">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2183,6 +2176,39 @@
     <xf numFmtId="0" fontId="17" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="27" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2264,34 +2290,7 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="33" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2404,7 +2403,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2436,10 +2435,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2471,7 +2469,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -2647,7 +2644,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="H9:Q22"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -2664,18 +2661,18 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:17" ht="45" customHeight="1">
-      <c r="H9" s="108" t="s">
+      <c r="H9" s="119" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="109"/>
-      <c r="J9" s="109"/>
-      <c r="K9" s="109"/>
-      <c r="L9" s="109"/>
-      <c r="M9" s="109"/>
-      <c r="N9" s="109"/>
-      <c r="O9" s="109"/>
-      <c r="P9" s="109"/>
-      <c r="Q9" s="110"/>
+      <c r="I9" s="120"/>
+      <c r="J9" s="120"/>
+      <c r="K9" s="120"/>
+      <c r="L9" s="120"/>
+      <c r="M9" s="120"/>
+      <c r="N9" s="120"/>
+      <c r="O9" s="120"/>
+      <c r="P9" s="120"/>
+      <c r="Q9" s="121"/>
     </row>
     <row r="10" spans="8:17" ht="30" customHeight="1">
       <c r="H10" s="55" t="s">
@@ -2944,11 +2941,11 @@
       <c r="Q21" s="60"/>
     </row>
     <row r="22" spans="8:17" ht="15.75">
-      <c r="H22" s="111" t="s">
+      <c r="H22" s="122" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="112"/>
-      <c r="J22" s="113"/>
+      <c r="I22" s="123"/>
+      <c r="J22" s="124"/>
       <c r="K22" s="61">
         <f>COUNTA(K11:K21)</f>
         <v>6</v>
@@ -2999,7 +2996,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="H9:AL42"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
@@ -3025,39 +3022,39 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:38" ht="45" customHeight="1">
-      <c r="H9" s="114" t="s">
+      <c r="H9" s="125" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="115"/>
-      <c r="J9" s="115"/>
-      <c r="K9" s="115"/>
-      <c r="L9" s="115"/>
-      <c r="M9" s="115"/>
-      <c r="N9" s="115"/>
-      <c r="O9" s="115"/>
-      <c r="P9" s="115"/>
-      <c r="Q9" s="115"/>
-      <c r="R9" s="115"/>
-      <c r="S9" s="115"/>
-      <c r="T9" s="115"/>
-      <c r="U9" s="115"/>
-      <c r="V9" s="115"/>
-      <c r="W9" s="115"/>
-      <c r="X9" s="115"/>
-      <c r="Y9" s="115"/>
-      <c r="Z9" s="115"/>
-      <c r="AA9" s="115"/>
-      <c r="AB9" s="115"/>
-      <c r="AC9" s="115"/>
-      <c r="AD9" s="115"/>
-      <c r="AE9" s="115"/>
-      <c r="AF9" s="115"/>
-      <c r="AG9" s="115"/>
-      <c r="AH9" s="115"/>
-      <c r="AI9" s="115"/>
-      <c r="AJ9" s="115"/>
-      <c r="AK9" s="115"/>
-      <c r="AL9" s="115"/>
+      <c r="I9" s="126"/>
+      <c r="J9" s="126"/>
+      <c r="K9" s="126"/>
+      <c r="L9" s="126"/>
+      <c r="M9" s="126"/>
+      <c r="N9" s="126"/>
+      <c r="O9" s="126"/>
+      <c r="P9" s="126"/>
+      <c r="Q9" s="126"/>
+      <c r="R9" s="126"/>
+      <c r="S9" s="126"/>
+      <c r="T9" s="126"/>
+      <c r="U9" s="126"/>
+      <c r="V9" s="126"/>
+      <c r="W9" s="126"/>
+      <c r="X9" s="126"/>
+      <c r="Y9" s="126"/>
+      <c r="Z9" s="126"/>
+      <c r="AA9" s="126"/>
+      <c r="AB9" s="126"/>
+      <c r="AC9" s="126"/>
+      <c r="AD9" s="126"/>
+      <c r="AE9" s="126"/>
+      <c r="AF9" s="126"/>
+      <c r="AG9" s="126"/>
+      <c r="AH9" s="126"/>
+      <c r="AI9" s="126"/>
+      <c r="AJ9" s="126"/>
+      <c r="AK9" s="126"/>
+      <c r="AL9" s="126"/>
     </row>
     <row r="10" spans="8:38" ht="30" customHeight="1">
       <c r="H10" s="32" t="s">
@@ -4737,11 +4734,11 @@
       </c>
     </row>
     <row r="42" spans="8:38" ht="15.75">
-      <c r="H42" s="116" t="s">
+      <c r="H42" s="127" t="s">
         <v>19</v>
       </c>
-      <c r="I42" s="116"/>
-      <c r="J42" s="116"/>
+      <c r="I42" s="127"/>
+      <c r="J42" s="127"/>
       <c r="K42" s="32">
         <f>COUNTA(K11:K41)</f>
         <v>6</v>
@@ -4871,7 +4868,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AK34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -4906,66 +4903,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="122"/>
-      <c r="B1" s="123"/>
-      <c r="C1" s="124"/>
+      <c r="A1" s="133"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="135"/>
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="128" t="s">
+      <c r="E1" s="139" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="128"/>
-      <c r="G1" s="128"/>
-      <c r="H1" s="128"/>
-      <c r="I1" s="128"/>
-      <c r="J1" s="128"/>
-      <c r="K1" s="128"/>
-      <c r="L1" s="129" t="s">
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="139"/>
+      <c r="L1" s="140" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="129"/>
-      <c r="N1" s="129"/>
-      <c r="O1" s="129"/>
-      <c r="P1" s="129"/>
-      <c r="Q1" s="129"/>
-      <c r="R1" s="129"/>
-      <c r="S1" s="130" t="s">
+      <c r="M1" s="140"/>
+      <c r="N1" s="140"/>
+      <c r="O1" s="140"/>
+      <c r="P1" s="140"/>
+      <c r="Q1" s="140"/>
+      <c r="R1" s="140"/>
+      <c r="S1" s="141" t="s">
         <v>39</v>
       </c>
-      <c r="T1" s="130"/>
-      <c r="U1" s="131" t="s">
+      <c r="T1" s="141"/>
+      <c r="U1" s="142" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="132"/>
-      <c r="W1" s="132"/>
-      <c r="X1" s="132"/>
-      <c r="Y1" s="133"/>
-      <c r="Z1" s="134" t="s">
+      <c r="V1" s="143"/>
+      <c r="W1" s="143"/>
+      <c r="X1" s="143"/>
+      <c r="Y1" s="144"/>
+      <c r="Z1" s="145" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="134"/>
-      <c r="AB1" s="134"/>
-      <c r="AC1" s="134"/>
-      <c r="AD1" s="134"/>
-      <c r="AE1" s="117" t="s">
+      <c r="AA1" s="145"/>
+      <c r="AB1" s="145"/>
+      <c r="AC1" s="145"/>
+      <c r="AD1" s="145"/>
+      <c r="AE1" s="128" t="s">
         <v>42</v>
       </c>
-      <c r="AF1" s="117"/>
-      <c r="AG1" s="117"/>
-      <c r="AH1" s="118" t="s">
+      <c r="AF1" s="128"/>
+      <c r="AG1" s="128"/>
+      <c r="AH1" s="129" t="s">
         <v>43</v>
       </c>
-      <c r="AI1" s="118"/>
-      <c r="AJ1" s="118"/>
-      <c r="AK1" s="119" t="s">
+      <c r="AI1" s="129"/>
+      <c r="AJ1" s="129"/>
+      <c r="AK1" s="130" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1">
-      <c r="A2" s="125"/>
-      <c r="B2" s="126"/>
-      <c r="C2" s="127"/>
+      <c r="A2" s="136"/>
+      <c r="B2" s="137"/>
+      <c r="C2" s="138"/>
       <c r="D2" s="5" t="s">
         <v>44</v>
       </c>
@@ -5059,7 +5056,7 @@
       <c r="AH2" s="12"/>
       <c r="AI2" s="12"/>
       <c r="AJ2" s="12"/>
-      <c r="AK2" s="120"/>
+      <c r="AK2" s="131"/>
     </row>
     <row r="3" spans="1:37">
       <c r="A3" s="13" t="s">
@@ -5170,7 +5167,7 @@
       <c r="AJ3" s="20">
         <v>2</v>
       </c>
-      <c r="AK3" s="121"/>
+      <c r="AK3" s="132"/>
     </row>
     <row r="4" spans="1:37">
       <c r="A4" s="21">
@@ -6572,7 +6569,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:37" ht="15.75" thickBot="1">
+    <row r="25" spans="1:37">
       <c r="A25" s="21">
         <v>22</v>
       </c>
@@ -6640,198 +6637,252 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:37" ht="15.75" thickBot="1">
-      <c r="A26" s="21">
+    <row r="26" spans="1:37">
+      <c r="A26" s="70">
         <v>23</v>
       </c>
-      <c r="B26" s="21" t="s">
+      <c r="B26" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="68">
+      <c r="C26" s="116">
         <v>46226</v>
       </c>
-      <c r="D26" s="135"/>
-      <c r="E26" s="136"/>
-      <c r="F26" s="137"/>
-      <c r="G26" s="137" t="s">
-        <v>12</v>
-      </c>
-      <c r="H26" s="137"/>
-      <c r="I26" s="137"/>
-      <c r="J26" s="137"/>
-      <c r="K26" s="137" t="s">
-        <v>12</v>
-      </c>
-      <c r="L26" s="138"/>
-      <c r="M26" s="138"/>
-      <c r="N26" s="138"/>
-      <c r="O26" s="138"/>
-      <c r="P26" s="138"/>
-      <c r="Q26" s="138"/>
-      <c r="R26" s="138"/>
-      <c r="S26" s="139"/>
-      <c r="T26" s="139"/>
-      <c r="U26" s="140"/>
-      <c r="V26" s="140"/>
-      <c r="W26" s="140"/>
-      <c r="X26" s="140"/>
-      <c r="Y26" s="140"/>
-      <c r="Z26" s="141"/>
-      <c r="AA26" s="141"/>
-      <c r="AB26" s="141"/>
-      <c r="AC26" s="141"/>
-      <c r="AD26" s="141"/>
-      <c r="AE26" s="142"/>
-      <c r="AF26" s="142"/>
-      <c r="AG26" s="142"/>
-      <c r="AH26" s="143"/>
-      <c r="AI26" s="143"/>
-      <c r="AJ26" s="143"/>
-      <c r="AK26" s="144">
+      <c r="D26" s="70" t="s">
+        <v>62</v>
+      </c>
+      <c r="E26" s="71"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="H26" s="71"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="L26" s="72"/>
+      <c r="M26" s="72"/>
+      <c r="N26" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="O26" s="72"/>
+      <c r="P26" s="72"/>
+      <c r="Q26" s="72"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="73" t="s">
+        <v>12</v>
+      </c>
+      <c r="T26" s="73"/>
+      <c r="U26" s="74"/>
+      <c r="V26" s="74"/>
+      <c r="W26" s="74"/>
+      <c r="X26" s="74"/>
+      <c r="Y26" s="74"/>
+      <c r="Z26" s="75"/>
+      <c r="AA26" s="75"/>
+      <c r="AB26" s="75"/>
+      <c r="AC26" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD26" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE26" s="76"/>
+      <c r="AF26" s="76"/>
+      <c r="AG26" s="76"/>
+      <c r="AH26" s="77"/>
+      <c r="AI26" s="77"/>
+      <c r="AJ26" s="77"/>
+      <c r="AK26" s="95">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:37">
-      <c r="A27" s="21">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:37" ht="15.75" thickBot="1">
+      <c r="A27" s="70">
         <v>24</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="22">
+      <c r="C27" s="86">
         <v>46227</v>
       </c>
-      <c r="D27" s="85"/>
-      <c r="E27" s="78"/>
-      <c r="F27" s="78"/>
-      <c r="G27" s="78"/>
-      <c r="H27" s="78"/>
-      <c r="I27" s="78"/>
-      <c r="J27" s="78"/>
-      <c r="K27" s="78"/>
-      <c r="L27" s="79"/>
-      <c r="M27" s="79"/>
-      <c r="N27" s="79"/>
-      <c r="O27" s="79"/>
-      <c r="P27" s="79"/>
-      <c r="Q27" s="79"/>
-      <c r="R27" s="79"/>
-      <c r="S27" s="80"/>
-      <c r="T27" s="80"/>
-      <c r="U27" s="81"/>
-      <c r="V27" s="81"/>
-      <c r="W27" s="81"/>
-      <c r="X27" s="81"/>
-      <c r="Y27" s="81"/>
-      <c r="Z27" s="82"/>
-      <c r="AA27" s="82"/>
-      <c r="AB27" s="82"/>
-      <c r="AC27" s="82"/>
-      <c r="AD27" s="82"/>
-      <c r="AE27" s="83"/>
-      <c r="AF27" s="83"/>
-      <c r="AG27" s="83"/>
-      <c r="AH27" s="84"/>
-      <c r="AI27" s="84"/>
-      <c r="AJ27" s="84"/>
-      <c r="AK27" s="97">
+      <c r="D27" s="70" t="s">
+        <v>67</v>
+      </c>
+      <c r="E27" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="H27" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="I27" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="J27" s="71"/>
+      <c r="K27" s="71"/>
+      <c r="L27" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="M27" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="N27" s="72"/>
+      <c r="O27" s="72"/>
+      <c r="P27" s="72"/>
+      <c r="Q27" s="72"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="73"/>
+      <c r="T27" s="73"/>
+      <c r="U27" s="74"/>
+      <c r="V27" s="74"/>
+      <c r="W27" s="74"/>
+      <c r="X27" s="74"/>
+      <c r="Y27" s="74"/>
+      <c r="Z27" s="75"/>
+      <c r="AA27" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB27" s="75"/>
+      <c r="AC27" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD27" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE27" s="76" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF27" s="76" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG27" s="76"/>
+      <c r="AH27" s="77"/>
+      <c r="AI27" s="77"/>
+      <c r="AJ27" s="77"/>
+      <c r="AK27" s="95">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:37">
-      <c r="A28" s="21">
         <v>25</v>
       </c>
-      <c r="B28" s="21" t="s">
+    </row>
+    <row r="28" spans="1:37" ht="15.75" thickBot="1">
+      <c r="A28" s="117">
+        <v>25</v>
+      </c>
+      <c r="B28" s="118" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="22">
+      <c r="C28" s="146">
         <v>46228</v>
       </c>
-      <c r="D28" s="30"/>
-      <c r="E28" s="62"/>
-      <c r="F28" s="62"/>
-      <c r="G28" s="62"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="62"/>
-      <c r="J28" s="62"/>
-      <c r="K28" s="62"/>
-      <c r="L28" s="63"/>
-      <c r="M28" s="63"/>
-      <c r="N28" s="63"/>
-      <c r="O28" s="63"/>
-      <c r="P28" s="63"/>
-      <c r="Q28" s="63"/>
-      <c r="R28" s="63"/>
-      <c r="S28" s="29"/>
-      <c r="T28" s="29"/>
-      <c r="U28" s="64"/>
-      <c r="V28" s="64"/>
-      <c r="W28" s="64"/>
-      <c r="X28" s="64"/>
-      <c r="Y28" s="64"/>
-      <c r="Z28" s="65"/>
-      <c r="AA28" s="65"/>
-      <c r="AB28" s="65"/>
-      <c r="AC28" s="65"/>
-      <c r="AD28" s="65"/>
-      <c r="AE28" s="66"/>
-      <c r="AF28" s="66"/>
-      <c r="AG28" s="66"/>
-      <c r="AH28" s="67"/>
-      <c r="AI28" s="67"/>
-      <c r="AJ28" s="67"/>
-      <c r="AK28" s="25">
+      <c r="D28" s="118" t="s">
+        <v>62</v>
+      </c>
+      <c r="E28" s="108" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="108" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" s="108" t="s">
+        <v>12</v>
+      </c>
+      <c r="H28" s="108"/>
+      <c r="I28" s="108" t="s">
+        <v>12</v>
+      </c>
+      <c r="J28" s="108" t="s">
+        <v>12</v>
+      </c>
+      <c r="K28" s="108"/>
+      <c r="L28" s="109"/>
+      <c r="M28" s="109" t="s">
+        <v>12</v>
+      </c>
+      <c r="N28" s="109" t="s">
+        <v>12</v>
+      </c>
+      <c r="O28" s="109"/>
+      <c r="P28" s="109"/>
+      <c r="Q28" s="109"/>
+      <c r="R28" s="109"/>
+      <c r="S28" s="110"/>
+      <c r="T28" s="110"/>
+      <c r="U28" s="111" t="s">
+        <v>12</v>
+      </c>
+      <c r="V28" s="111"/>
+      <c r="W28" s="111"/>
+      <c r="X28" s="111"/>
+      <c r="Y28" s="111"/>
+      <c r="Z28" s="112"/>
+      <c r="AA28" s="112"/>
+      <c r="AB28" s="112"/>
+      <c r="AC28" s="112"/>
+      <c r="AD28" s="112"/>
+      <c r="AE28" s="113"/>
+      <c r="AF28" s="113" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG28" s="113"/>
+      <c r="AH28" s="114"/>
+      <c r="AI28" s="114"/>
+      <c r="AJ28" s="114"/>
+      <c r="AK28" s="115">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:37">
-      <c r="A29" s="21">
+      <c r="A29" s="85">
         <v>26</v>
       </c>
-      <c r="B29" s="21" t="s">
+      <c r="B29" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="C29" s="22">
+      <c r="C29" s="96">
         <v>46229</v>
       </c>
-      <c r="D29" s="30"/>
-      <c r="E29" s="62"/>
-      <c r="F29" s="62"/>
-      <c r="G29" s="62"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="62"/>
-      <c r="J29" s="62"/>
-      <c r="K29" s="62"/>
-      <c r="L29" s="63"/>
-      <c r="M29" s="63"/>
-      <c r="N29" s="63"/>
-      <c r="O29" s="63"/>
-      <c r="P29" s="63"/>
-      <c r="Q29" s="63"/>
-      <c r="R29" s="63"/>
-      <c r="S29" s="29"/>
-      <c r="T29" s="29"/>
-      <c r="U29" s="64"/>
-      <c r="V29" s="64"/>
-      <c r="W29" s="64"/>
-      <c r="X29" s="64"/>
-      <c r="Y29" s="64"/>
-      <c r="Z29" s="65"/>
-      <c r="AA29" s="65"/>
-      <c r="AB29" s="65"/>
-      <c r="AC29" s="65"/>
-      <c r="AD29" s="65"/>
-      <c r="AE29" s="66"/>
-      <c r="AF29" s="66"/>
-      <c r="AG29" s="66"/>
-      <c r="AH29" s="67"/>
-      <c r="AI29" s="67"/>
-      <c r="AJ29" s="67"/>
-      <c r="AK29" s="25">
+      <c r="D29" s="85"/>
+      <c r="E29" s="78"/>
+      <c r="F29" s="78"/>
+      <c r="G29" s="78"/>
+      <c r="H29" s="78"/>
+      <c r="I29" s="78"/>
+      <c r="J29" s="78"/>
+      <c r="K29" s="78"/>
+      <c r="L29" s="79"/>
+      <c r="M29" s="79"/>
+      <c r="N29" s="79"/>
+      <c r="O29" s="79"/>
+      <c r="P29" s="79"/>
+      <c r="Q29" s="79"/>
+      <c r="R29" s="79"/>
+      <c r="S29" s="80"/>
+      <c r="T29" s="80"/>
+      <c r="U29" s="81"/>
+      <c r="V29" s="81"/>
+      <c r="W29" s="81"/>
+      <c r="X29" s="81"/>
+      <c r="Y29" s="81"/>
+      <c r="Z29" s="82"/>
+      <c r="AA29" s="82"/>
+      <c r="AB29" s="82"/>
+      <c r="AC29" s="82"/>
+      <c r="AD29" s="82"/>
+      <c r="AE29" s="83"/>
+      <c r="AF29" s="83"/>
+      <c r="AG29" s="83"/>
+      <c r="AH29" s="84"/>
+      <c r="AI29" s="84"/>
+      <c r="AJ29" s="84"/>
+      <c r="AK29" s="97">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>

--- a/Другое/study_chart.xlsx
+++ b/Другое/study_chart.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10380" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10380" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Июнь" sheetId="1" r:id="rId1"/>
     <sheet name="Июль" sheetId="4" r:id="rId2"/>
     <sheet name="Август" sheetId="5" r:id="rId3"/>
+    <sheet name="Сентябрь" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="125725"/>
   <extLst>
@@ -41,6 +42,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
             <charset val="204"/>
           </rPr>
           <t>Собянин Евгений Андреевич (new):</t>
@@ -49,6 +51,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
             <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
@@ -64,6 +67,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
             <charset val="204"/>
           </rPr>
           <t>Собянин Евгений Андреевич (new):</t>
@@ -72,6 +76,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
             <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
@@ -88,7 +93,8 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Собянин Евгений Андреевич (new):</t>
         </r>
@@ -96,7 +102,8 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Контроль уже не 100%,
@@ -114,7 +121,8 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Собянин Евгений Андреевич (new):</t>
         </r>
@@ -122,7 +130,8 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Контроль 80%
@@ -138,7 +147,8 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Собянин Евгений Андреевич (new):</t>
         </r>
@@ -146,7 +156,8 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Найти квартиру для поездки в МСК</t>
@@ -160,7 +171,8 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Собянин Евгений Андреевич (new):</t>
         </r>
@@ -168,7 +180,8 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Определиться с подарком Кулику</t>
@@ -182,7 +195,8 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Собянин Евгений Андреевич (new):</t>
         </r>
@@ -190,7 +204,8 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Контроль 80%
@@ -208,7 +223,8 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Собянин Евгений Андреевич (new):</t>
         </r>
@@ -216,7 +232,8 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Найти квартиру для поездки в МСК</t>
@@ -230,7 +247,8 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Собянин Евгений Андреевич (new):</t>
         </r>
@@ -238,7 +256,8 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Определиться с подарком Кулику</t>
@@ -252,6 +271,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
             <charset val="204"/>
           </rPr>
           <t>Собянин Евгений Андреевич (new):</t>
@@ -260,6 +280,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
             <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
@@ -274,6 +295,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
             <charset val="204"/>
           </rPr>
           <t>Собянин Евгений Андреевич (new):</t>
@@ -282,6 +304,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
             <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
@@ -296,7 +319,8 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">Собянин Евгений Андреевич (new):
 </t>
@@ -305,6 +329,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
             <charset val="204"/>
           </rPr>
           <t>Записаться в парикмахерскую</t>
@@ -318,7 +343,8 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Собянин Евгений Андреевич (new):</t>
         </r>
@@ -326,7 +352,8 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -340,7 +367,8 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Собянин Евгений Андреевич (new):</t>
         </r>
@@ -348,7 +376,8 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Найти квартиру для поездки в МСК</t>
@@ -362,7 +391,8 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Собянин Евгений Андреевич (new):</t>
         </r>
@@ -370,7 +400,8 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Определиться с подарком Кулику</t>
@@ -384,6 +415,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
             <charset val="204"/>
           </rPr>
           <t>Собянин Евгений Андреевич (new):</t>
@@ -392,6 +424,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
             <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
@@ -406,6 +439,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
             <charset val="204"/>
           </rPr>
           <t>Собянин Евгений Андреевич (new):</t>
@@ -414,6 +448,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
             <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
@@ -428,7 +463,8 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Собянин Евгений Андреевич (new):</t>
         </r>
@@ -436,7 +472,8 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Сходить в парикмахерскую</t>
@@ -450,7 +487,8 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Собянин Евгений Андреевич (new):</t>
         </r>
@@ -458,7 +496,8 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Проблем с контрлем не возникало!</t>
@@ -472,7 +511,8 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Собянин Евгений Андреевич (new):</t>
         </r>
@@ -480,7 +520,8 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Найти квартиру для поездки в МСК</t>
@@ -494,6 +535,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
             <charset val="204"/>
           </rPr>
           <t>Собянин Евгений Андреевич (new):</t>
@@ -502,6 +544,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
+            <family val="2"/>
             <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
@@ -516,7 +559,8 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Собянин Евгений Андреевич (new):</t>
         </r>
@@ -524,7 +568,8 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 В субботу было много дел и было не до этого,так что контрль был хороший</t>
@@ -538,7 +583,8 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Собянин Евгений Андреевич (new):</t>
         </r>
@@ -546,7 +592,8 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 После выпитых в субботу нескольких стопок виски утром появились мысли о том чтобы сорваться, я даже зашел в инсту и хотел кому-нибудь написать
@@ -561,7 +608,8 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Собянин Евгений Андреевич (new):</t>
         </r>
@@ -569,7 +617,8 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Контроль значительно просел, посещают мысли об инстаграмме и о том "кто как поживает".
@@ -585,7 +634,8 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Собянин Евгений Андреевич (new):</t>
         </r>
@@ -593,7 +643,8 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Абсолютный провал.
@@ -608,7 +659,8 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Собянин Евгений Андреевич (new):</t>
         </r>
@@ -616,7 +668,8 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Абсолютный провал.
@@ -632,7 +685,8 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Собянин Евгений Андреевич (new):</t>
         </r>
@@ -640,7 +694,8 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Абсолютный провал на фоне недосыпа, ссор с Аней и негативного морального фона.
@@ -655,7 +710,8 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Собянин Евгений Андреевич (new):</t>
         </r>
@@ -663,7 +719,8 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Просто не дали закончить, а так, я практически это сделал</t>
@@ -677,7 +734,8 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Собянин Евгений Андреевич (new):</t>
         </r>
@@ -685,7 +743,8 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Контроля не было вообще, но и возможности тоже не было, по этому получилось сдержаться</t>
@@ -699,7 +758,8 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Собянин Евгений Андреевич (new):</t>
         </r>
@@ -707,7 +767,8 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Контроль был потярян из-за соц.сетей и телефона</t>
@@ -721,7 +782,8 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Собянин Евгений Андреевич (new):</t>
         </r>
@@ -729,7 +791,8 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Было 3 срыва, контроль был потерян из-за соц.сетей и телефона</t>
@@ -753,7 +816,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">Сделать 60% задач из задачника.
 13 из 22
@@ -766,7 +830,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="87">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -998,6 +1062,36 @@
   <si>
     <t>88.9</t>
   </si>
+  <si>
+    <t>Итоги за месяц</t>
+  </si>
+  <si>
+    <t>Среднее значение</t>
+  </si>
+  <si>
+    <t>Наибольшее значение</t>
+  </si>
+  <si>
+    <t>Наименьшее значение</t>
+  </si>
+  <si>
+    <t>Количество дней больше среднего значения</t>
+  </si>
+  <si>
+    <t>Количество дней меньше среднего значения</t>
+  </si>
+  <si>
+    <t>Количество дней больше 20ти</t>
+  </si>
+  <si>
+    <t>Количество дней меньше 20ти</t>
+  </si>
+  <si>
+    <t>Руководство по смете.ру / разбор смет / разбор сметной программы</t>
+  </si>
+  <si>
+    <t>Курс по Figma</t>
+  </si>
 </sst>
 </file>
 
@@ -1006,7 +1100,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mmm"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1018,7 +1112,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Tw Cen MT Condensed Extra Bold"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1026,7 +1120,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Tw Cen MT Condensed Extra Bold"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1034,7 +1128,7 @@
       <sz val="14"/>
       <color rgb="FF5C650B"/>
       <name val="Tw Cen MT Condensed Extra Bold"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1042,7 +1136,7 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Tw Cen MT Condensed Extra Bold"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1050,7 +1144,7 @@
       <sz val="14"/>
       <color rgb="FFBD07B4"/>
       <name val="Tw Cen MT Condensed Extra Bold"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1058,7 +1152,7 @@
       <sz val="14"/>
       <color rgb="FF05254B"/>
       <name val="Tw Cen MT Condensed Extra Bold"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1066,7 +1160,7 @@
       <sz val="14"/>
       <color rgb="FF3A0000"/>
       <name val="Tw Cen MT Condensed Extra Bold"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1075,7 +1169,7 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Tw Cen MT Condensed Extra Bold"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1083,7 +1177,7 @@
       <sz val="11"/>
       <color rgb="FF5C650B"/>
       <name val="Tw Cen MT Condensed Extra Bold"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1091,7 +1185,7 @@
       <sz val="11"/>
       <color rgb="FFBD07B4"/>
       <name val="Tw Cen MT Condensed Extra Bold"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1099,7 +1193,7 @@
       <sz val="11"/>
       <color rgb="FF05254B"/>
       <name val="Tw Cen MT Condensed Extra Bold"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1107,42 +1201,43 @@
       <sz val="11"/>
       <color rgb="FF3A0000"/>
       <name val="Tw Cen MT Condensed Extra Bold"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF5C650B"/>
       <name val="Tw Cen MT Condensed Extra Bold"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFBD07B4"/>
       <name val="Tw Cen MT Condensed Extra Bold"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF05254B"/>
       <name val="Tw Cen MT Condensed Extra Bold"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3A0000"/>
       <name val="Tw Cen MT Condensed Extra Bold"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Tw Cen MT Condensed Extra Bold"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="20"/>
       <color theme="1" tint="0.34998626667073579"/>
       <name val="Impact"/>
+      <family val="2"/>
       <charset val="204"/>
     </font>
     <font>
@@ -1150,6 +1245,7 @@
       <sz val="11"/>
       <color rgb="FF1C1917"/>
       <name val="Courier New"/>
+      <family val="3"/>
       <charset val="204"/>
     </font>
     <font>
@@ -1157,6 +1253,7 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Courier New"/>
+      <family val="3"/>
       <charset val="204"/>
     </font>
     <font>
@@ -1164,6 +1261,7 @@
       <sz val="11"/>
       <color rgb="FFFFFF00"/>
       <name val="Courier New"/>
+      <family val="3"/>
       <charset val="204"/>
     </font>
     <font>
@@ -1171,6 +1269,7 @@
       <sz val="11"/>
       <color theme="1" tint="0.14993743705557422"/>
       <name val="Courier New"/>
+      <family val="3"/>
       <charset val="204"/>
     </font>
     <font>
@@ -1178,6 +1277,7 @@
       <sz val="11"/>
       <color rgb="FF680000"/>
       <name val="Courier New"/>
+      <family val="3"/>
       <charset val="204"/>
     </font>
     <font>
@@ -1185,23 +1285,27 @@
       <sz val="11"/>
       <color rgb="FFF4EFEA"/>
       <name val="Courier New"/>
+      <family val="3"/>
       <charset val="204"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Impact"/>
+      <family val="2"/>
       <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1C1917"/>
       <name val="Courier New"/>
+      <family val="3"/>
       <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF1C1917"/>
       <name val="Impact"/>
+      <family val="2"/>
       <charset val="204"/>
     </font>
     <font>
@@ -1209,38 +1313,54 @@
       <sz val="20"/>
       <color rgb="FF1C1917"/>
       <name val="Impact"/>
+      <family val="2"/>
       <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
+      <family val="2"/>
       <charset val="204"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
+      <family val="2"/>
       <charset val="204"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Tw Cen MT Condensed Extra Bold"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Tw Cen MT"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1439,8 +1559,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="34">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -1732,19 +1864,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color theme="0" tint="-0.249977111117893"/>
@@ -1811,54 +1930,22 @@
       <left style="thin">
         <color theme="0" tint="-0.249977111117893"/>
       </left>
-      <right style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </right>
-      <top style="medium">
+      <right/>
+      <top style="thin">
         <color theme="0" tint="-0.249977111117893"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color theme="0" tint="-0.249977111117893"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </left>
-      <right style="medium">
-        <color theme="0" tint="-0.249977111117893"/>
-      </right>
-      <top style="medium">
-        <color theme="0" tint="-0.249977111117893"/>
-      </top>
-      <bottom style="medium">
-        <color theme="0" tint="-0.249977111117893"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </left>
+      <left/>
       <right/>
       <top style="thin">
         <color theme="0" tint="-0.249977111117893"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="0" tint="-0.249977111117893"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </right>
-      <top style="medium">
-        <color theme="0" tint="-0.249977111117893"/>
-      </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color theme="0" tint="-0.249977111117893"/>
       </bottom>
       <diagonal/>
@@ -2056,61 +2143,88 @@
     <xf numFmtId="0" fontId="1" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="33" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="33" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2137,76 +2251,22 @@
     <xf numFmtId="0" fontId="1" fillId="33" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="33" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="33" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="28" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="27" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2236,6 +2296,24 @@
     <xf numFmtId="0" fontId="19" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2290,14 +2368,114 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="18">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFB6EA86"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFB6EA86"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFB6EA86"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFB6EA86"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFB6EA86"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFB6EA86"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFB6EA86"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFB6EA86"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFB6EA86"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFB6EA86"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFB6EA86"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFB6EA86"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFB6EA86"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2661,18 +2839,18 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:17" ht="45" customHeight="1">
-      <c r="H9" s="119" t="s">
+      <c r="H9" s="110" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="120"/>
-      <c r="J9" s="120"/>
-      <c r="K9" s="120"/>
-      <c r="L9" s="120"/>
-      <c r="M9" s="120"/>
-      <c r="N9" s="120"/>
-      <c r="O9" s="120"/>
-      <c r="P9" s="120"/>
-      <c r="Q9" s="121"/>
+      <c r="I9" s="111"/>
+      <c r="J9" s="111"/>
+      <c r="K9" s="111"/>
+      <c r="L9" s="111"/>
+      <c r="M9" s="111"/>
+      <c r="N9" s="111"/>
+      <c r="O9" s="111"/>
+      <c r="P9" s="111"/>
+      <c r="Q9" s="112"/>
     </row>
     <row r="10" spans="8:17" ht="30" customHeight="1">
       <c r="H10" s="55" t="s">
@@ -2941,11 +3119,11 @@
       <c r="Q21" s="60"/>
     </row>
     <row r="22" spans="8:17" ht="15.75">
-      <c r="H22" s="122" t="s">
+      <c r="H22" s="113" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="123"/>
-      <c r="J22" s="124"/>
+      <c r="I22" s="114"/>
+      <c r="J22" s="115"/>
       <c r="K22" s="61">
         <f>COUNTA(K11:K21)</f>
         <v>6</v>
@@ -2981,12 +3159,12 @@
     <mergeCell ref="H22:J22"/>
   </mergeCells>
   <conditionalFormatting sqref="K22:Q22">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>Q22="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11:Q21">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="16" priority="2">
       <formula>Q11="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3022,39 +3200,39 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:38" ht="45" customHeight="1">
-      <c r="H9" s="125" t="s">
+      <c r="H9" s="116" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="126"/>
-      <c r="J9" s="126"/>
-      <c r="K9" s="126"/>
-      <c r="L9" s="126"/>
-      <c r="M9" s="126"/>
-      <c r="N9" s="126"/>
-      <c r="O9" s="126"/>
-      <c r="P9" s="126"/>
-      <c r="Q9" s="126"/>
-      <c r="R9" s="126"/>
-      <c r="S9" s="126"/>
-      <c r="T9" s="126"/>
-      <c r="U9" s="126"/>
-      <c r="V9" s="126"/>
-      <c r="W9" s="126"/>
-      <c r="X9" s="126"/>
-      <c r="Y9" s="126"/>
-      <c r="Z9" s="126"/>
-      <c r="AA9" s="126"/>
-      <c r="AB9" s="126"/>
-      <c r="AC9" s="126"/>
-      <c r="AD9" s="126"/>
-      <c r="AE9" s="126"/>
-      <c r="AF9" s="126"/>
-      <c r="AG9" s="126"/>
-      <c r="AH9" s="126"/>
-      <c r="AI9" s="126"/>
-      <c r="AJ9" s="126"/>
-      <c r="AK9" s="126"/>
-      <c r="AL9" s="126"/>
+      <c r="I9" s="117"/>
+      <c r="J9" s="117"/>
+      <c r="K9" s="117"/>
+      <c r="L9" s="117"/>
+      <c r="M9" s="117"/>
+      <c r="N9" s="117"/>
+      <c r="O9" s="117"/>
+      <c r="P9" s="117"/>
+      <c r="Q9" s="117"/>
+      <c r="R9" s="117"/>
+      <c r="S9" s="117"/>
+      <c r="T9" s="117"/>
+      <c r="U9" s="117"/>
+      <c r="V9" s="117"/>
+      <c r="W9" s="117"/>
+      <c r="X9" s="117"/>
+      <c r="Y9" s="117"/>
+      <c r="Z9" s="117"/>
+      <c r="AA9" s="117"/>
+      <c r="AB9" s="117"/>
+      <c r="AC9" s="117"/>
+      <c r="AD9" s="117"/>
+      <c r="AE9" s="117"/>
+      <c r="AF9" s="117"/>
+      <c r="AG9" s="117"/>
+      <c r="AH9" s="117"/>
+      <c r="AI9" s="117"/>
+      <c r="AJ9" s="117"/>
+      <c r="AK9" s="117"/>
+      <c r="AL9" s="117"/>
     </row>
     <row r="10" spans="8:38" ht="30" customHeight="1">
       <c r="H10" s="32" t="s">
@@ -4734,11 +4912,11 @@
       </c>
     </row>
     <row r="42" spans="8:38" ht="15.75">
-      <c r="H42" s="127" t="s">
+      <c r="H42" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="I42" s="127"/>
-      <c r="J42" s="127"/>
+      <c r="I42" s="118"/>
+      <c r="J42" s="118"/>
       <c r="K42" s="32">
         <f>COUNTA(K11:K41)</f>
         <v>6</v>
@@ -4852,12 +5030,12 @@
     <mergeCell ref="H42:J42"/>
   </mergeCells>
   <conditionalFormatting sqref="AL42">
-    <cfRule type="expression" dxfId="2" priority="10">
+    <cfRule type="expression" dxfId="15" priority="10">
       <formula>AU42="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11:AK41">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>K11&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4869,7 +5047,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK34"/>
+  <dimension ref="A1:AK45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="15.7109375" style="3" customWidth="1"/>
@@ -4903,66 +5081,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="133"/>
-      <c r="B1" s="134"/>
-      <c r="C1" s="135"/>
+      <c r="A1" s="130"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="132"/>
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="139" t="s">
+      <c r="E1" s="136" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="140" t="s">
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
+      <c r="L1" s="137" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
-      <c r="O1" s="140"/>
-      <c r="P1" s="140"/>
-      <c r="Q1" s="140"/>
-      <c r="R1" s="140"/>
-      <c r="S1" s="141" t="s">
+      <c r="M1" s="137"/>
+      <c r="N1" s="137"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="138" t="s">
         <v>39</v>
       </c>
-      <c r="T1" s="141"/>
-      <c r="U1" s="142" t="s">
+      <c r="T1" s="138"/>
+      <c r="U1" s="139" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="143"/>
-      <c r="W1" s="143"/>
-      <c r="X1" s="143"/>
-      <c r="Y1" s="144"/>
-      <c r="Z1" s="145" t="s">
+      <c r="V1" s="140"/>
+      <c r="W1" s="140"/>
+      <c r="X1" s="140"/>
+      <c r="Y1" s="141"/>
+      <c r="Z1" s="142" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="145"/>
-      <c r="AB1" s="145"/>
-      <c r="AC1" s="145"/>
-      <c r="AD1" s="145"/>
-      <c r="AE1" s="128" t="s">
+      <c r="AA1" s="142"/>
+      <c r="AB1" s="142"/>
+      <c r="AC1" s="142"/>
+      <c r="AD1" s="142"/>
+      <c r="AE1" s="125" t="s">
         <v>42</v>
       </c>
-      <c r="AF1" s="128"/>
-      <c r="AG1" s="128"/>
-      <c r="AH1" s="129" t="s">
+      <c r="AF1" s="125"/>
+      <c r="AG1" s="125"/>
+      <c r="AH1" s="126" t="s">
         <v>43</v>
       </c>
-      <c r="AI1" s="129"/>
-      <c r="AJ1" s="129"/>
-      <c r="AK1" s="130" t="s">
+      <c r="AI1" s="126"/>
+      <c r="AJ1" s="126"/>
+      <c r="AK1" s="127" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1">
-      <c r="A2" s="136"/>
-      <c r="B2" s="137"/>
-      <c r="C2" s="138"/>
+      <c r="A2" s="133"/>
+      <c r="B2" s="134"/>
+      <c r="C2" s="135"/>
       <c r="D2" s="5" t="s">
         <v>44</v>
       </c>
@@ -5056,7 +5234,7 @@
       <c r="AH2" s="12"/>
       <c r="AI2" s="12"/>
       <c r="AJ2" s="12"/>
-      <c r="AK2" s="131"/>
+      <c r="AK2" s="128"/>
     </row>
     <row r="3" spans="1:37">
       <c r="A3" s="13" t="s">
@@ -5167,7 +5345,7 @@
       <c r="AJ3" s="20">
         <v>2</v>
       </c>
-      <c r="AK3" s="132"/>
+      <c r="AK3" s="129"/>
     </row>
     <row r="4" spans="1:37">
       <c r="A4" s="21">
@@ -5177,7 +5355,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="22">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="D4" s="23"/>
       <c r="E4" s="62"/>
@@ -5237,7 +5415,7 @@
         <v>13</v>
       </c>
       <c r="C5" s="22">
-        <v>46205</v>
+        <v>46236</v>
       </c>
       <c r="D5" s="23"/>
       <c r="E5" s="62"/>
@@ -5276,7 +5454,7 @@
       <c r="AH5" s="67"/>
       <c r="AI5" s="67"/>
       <c r="AJ5" s="67"/>
-      <c r="AK5" s="25">
+      <c r="AK5" s="109">
         <f t="shared" ref="AK5:AK34" si="0">SUMIF(E5:AJ5,"&lt;&gt;",$E$3:$AJ$3)</f>
         <v>3</v>
       </c>
@@ -5289,7 +5467,7 @@
         <v>14</v>
       </c>
       <c r="C6" s="22">
-        <v>46206</v>
+        <v>46237</v>
       </c>
       <c r="D6" s="26"/>
       <c r="E6" s="62" t="s">
@@ -5365,7 +5543,7 @@
         <v>15</v>
       </c>
       <c r="C7" s="22">
-        <v>46207</v>
+        <v>46238</v>
       </c>
       <c r="D7" s="21" t="s">
         <v>64</v>
@@ -5439,7 +5617,7 @@
         <v>16</v>
       </c>
       <c r="C8" s="22">
-        <v>46208</v>
+        <v>46239</v>
       </c>
       <c r="D8" s="21" t="s">
         <v>62</v>
@@ -5509,7 +5687,7 @@
         <v>17</v>
       </c>
       <c r="C9" s="22">
-        <v>46209</v>
+        <v>46240</v>
       </c>
       <c r="D9" s="21" t="s">
         <v>65</v>
@@ -5577,7 +5755,7 @@
         <v>18</v>
       </c>
       <c r="C10" s="22">
-        <v>46210</v>
+        <v>46241</v>
       </c>
       <c r="D10" s="26" t="s">
         <v>62</v>
@@ -5635,7 +5813,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="22">
-        <v>46211</v>
+        <v>46242</v>
       </c>
       <c r="D11" s="21" t="s">
         <v>66</v>
@@ -5695,7 +5873,7 @@
         <v>13</v>
       </c>
       <c r="C12" s="22">
-        <v>46212</v>
+        <v>46243</v>
       </c>
       <c r="D12" s="30" t="s">
         <v>67</v>
@@ -5765,7 +5943,7 @@
         <v>14</v>
       </c>
       <c r="C13" s="22">
-        <v>46213</v>
+        <v>46244</v>
       </c>
       <c r="D13" s="30" t="s">
         <v>68</v>
@@ -5837,7 +6015,7 @@
         <v>15</v>
       </c>
       <c r="C14" s="22">
-        <v>46214</v>
+        <v>46245</v>
       </c>
       <c r="D14" s="30" t="s">
         <v>70</v>
@@ -5906,7 +6084,7 @@
       <c r="AH14" s="67"/>
       <c r="AI14" s="67"/>
       <c r="AJ14" s="67"/>
-      <c r="AK14" s="25">
+      <c r="AK14" s="108">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
@@ -5919,7 +6097,7 @@
         <v>16</v>
       </c>
       <c r="C15" s="22">
-        <v>46215</v>
+        <v>46246</v>
       </c>
       <c r="D15" s="30" t="s">
         <v>72</v>
@@ -5987,53 +6165,53 @@
         <v>17</v>
       </c>
       <c r="C16" s="22">
-        <v>46216</v>
-      </c>
-      <c r="D16" s="70" t="s">
+        <v>46247</v>
+      </c>
+      <c r="D16" s="69" t="s">
         <v>73</v>
       </c>
-      <c r="E16" s="71"/>
-      <c r="F16" s="71"/>
-      <c r="G16" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="H16" s="71"/>
-      <c r="I16" s="71"/>
-      <c r="J16" s="71"/>
-      <c r="K16" s="71"/>
-      <c r="L16" s="72"/>
-      <c r="M16" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="N16" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="O16" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="P16" s="72"/>
-      <c r="Q16" s="72"/>
-      <c r="R16" s="72"/>
-      <c r="S16" s="73"/>
-      <c r="T16" s="73"/>
-      <c r="U16" s="74"/>
-      <c r="V16" s="74"/>
-      <c r="W16" s="74"/>
-      <c r="X16" s="74"/>
-      <c r="Y16" s="74"/>
-      <c r="Z16" s="75"/>
-      <c r="AA16" s="75"/>
-      <c r="AB16" s="75"/>
-      <c r="AC16" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD16" s="75"/>
-      <c r="AE16" s="76"/>
-      <c r="AF16" s="76"/>
-      <c r="AG16" s="76"/>
-      <c r="AH16" s="77"/>
-      <c r="AI16" s="77"/>
-      <c r="AJ16" s="77"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="70"/>
+      <c r="K16" s="70"/>
+      <c r="L16" s="71"/>
+      <c r="M16" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="N16" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="O16" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="71"/>
+      <c r="S16" s="72"/>
+      <c r="T16" s="72"/>
+      <c r="U16" s="73"/>
+      <c r="V16" s="73"/>
+      <c r="W16" s="73"/>
+      <c r="X16" s="73"/>
+      <c r="Y16" s="73"/>
+      <c r="Z16" s="74"/>
+      <c r="AA16" s="74"/>
+      <c r="AB16" s="74"/>
+      <c r="AC16" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD16" s="74"/>
+      <c r="AE16" s="75"/>
+      <c r="AF16" s="75"/>
+      <c r="AG16" s="75"/>
+      <c r="AH16" s="76"/>
+      <c r="AI16" s="76"/>
+      <c r="AJ16" s="76"/>
       <c r="AK16" s="25">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -6046,53 +6224,53 @@
       <c r="B17" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="68">
-        <v>46217</v>
-      </c>
-      <c r="D17" s="70" t="s">
+      <c r="C17" s="22">
+        <v>46248</v>
+      </c>
+      <c r="D17" s="69" t="s">
         <v>74</v>
       </c>
-      <c r="E17" s="71"/>
-      <c r="F17" s="71"/>
-      <c r="G17" s="71"/>
-      <c r="H17" s="71"/>
-      <c r="I17" s="71"/>
-      <c r="J17" s="71"/>
-      <c r="K17" s="71"/>
-      <c r="L17" s="72"/>
-      <c r="M17" s="72"/>
-      <c r="N17" s="72"/>
-      <c r="O17" s="72"/>
-      <c r="P17" s="72"/>
-      <c r="Q17" s="72"/>
-      <c r="R17" s="72"/>
-      <c r="S17" s="73"/>
-      <c r="T17" s="73"/>
-      <c r="U17" s="74"/>
-      <c r="V17" s="74"/>
-      <c r="W17" s="74"/>
-      <c r="X17" s="74" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y17" s="74"/>
-      <c r="Z17" s="75"/>
-      <c r="AA17" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB17" s="75"/>
-      <c r="AC17" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD17" s="75"/>
-      <c r="AE17" s="76"/>
-      <c r="AF17" s="76"/>
-      <c r="AG17" s="76" t="s">
-        <v>12</v>
-      </c>
-      <c r="AH17" s="77"/>
-      <c r="AI17" s="77"/>
-      <c r="AJ17" s="77"/>
-      <c r="AK17" s="69">
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70"/>
+      <c r="I17" s="70"/>
+      <c r="J17" s="70"/>
+      <c r="K17" s="70"/>
+      <c r="L17" s="71"/>
+      <c r="M17" s="71"/>
+      <c r="N17" s="71"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="71"/>
+      <c r="S17" s="72"/>
+      <c r="T17" s="72"/>
+      <c r="U17" s="73"/>
+      <c r="V17" s="73"/>
+      <c r="W17" s="73"/>
+      <c r="X17" s="73" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y17" s="73"/>
+      <c r="Z17" s="74"/>
+      <c r="AA17" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB17" s="74"/>
+      <c r="AC17" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD17" s="74"/>
+      <c r="AE17" s="75"/>
+      <c r="AF17" s="75"/>
+      <c r="AG17" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="AH17" s="76"/>
+      <c r="AI17" s="76"/>
+      <c r="AJ17" s="76"/>
+      <c r="AK17" s="68">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -6104,8 +6282,8 @@
       <c r="B18" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="68">
-        <v>46218</v>
+      <c r="C18" s="22">
+        <v>46249</v>
       </c>
       <c r="D18" s="30" t="s">
         <v>75</v>
@@ -6150,227 +6328,227 @@
       <c r="AH18" s="67"/>
       <c r="AI18" s="67"/>
       <c r="AJ18" s="67"/>
-      <c r="AK18" s="69">
+      <c r="AK18" s="68">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:37">
-      <c r="A19" s="70">
+      <c r="A19" s="69">
         <v>16</v>
       </c>
-      <c r="B19" s="70" t="s">
+      <c r="B19" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="86">
-        <v>46219</v>
-      </c>
-      <c r="D19" s="87" t="s">
+      <c r="C19" s="22">
+        <v>46250</v>
+      </c>
+      <c r="D19" s="85" t="s">
         <v>62</v>
       </c>
-      <c r="E19" s="88"/>
-      <c r="F19" s="88"/>
-      <c r="G19" s="88" t="s">
-        <v>12</v>
-      </c>
-      <c r="H19" s="88"/>
-      <c r="I19" s="88"/>
-      <c r="J19" s="88" t="s">
-        <v>12</v>
-      </c>
-      <c r="K19" s="88"/>
-      <c r="L19" s="89"/>
-      <c r="M19" s="89"/>
-      <c r="N19" s="89"/>
-      <c r="O19" s="89"/>
-      <c r="P19" s="89"/>
-      <c r="Q19" s="89"/>
-      <c r="R19" s="89"/>
-      <c r="S19" s="90" t="s">
-        <v>12</v>
-      </c>
-      <c r="T19" s="90"/>
-      <c r="U19" s="91"/>
-      <c r="V19" s="91"/>
-      <c r="W19" s="91"/>
-      <c r="X19" s="91"/>
-      <c r="Y19" s="91"/>
-      <c r="Z19" s="92"/>
-      <c r="AA19" s="92" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB19" s="92"/>
-      <c r="AC19" s="92" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD19" s="92" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE19" s="93"/>
-      <c r="AF19" s="93"/>
-      <c r="AG19" s="93"/>
-      <c r="AH19" s="94"/>
-      <c r="AI19" s="94"/>
-      <c r="AJ19" s="94"/>
-      <c r="AK19" s="95">
+      <c r="E19" s="86"/>
+      <c r="F19" s="86"/>
+      <c r="G19" s="86" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="86"/>
+      <c r="I19" s="86"/>
+      <c r="J19" s="86" t="s">
+        <v>12</v>
+      </c>
+      <c r="K19" s="86"/>
+      <c r="L19" s="87"/>
+      <c r="M19" s="87"/>
+      <c r="N19" s="87"/>
+      <c r="O19" s="87"/>
+      <c r="P19" s="87"/>
+      <c r="Q19" s="87"/>
+      <c r="R19" s="87"/>
+      <c r="S19" s="88" t="s">
+        <v>12</v>
+      </c>
+      <c r="T19" s="88"/>
+      <c r="U19" s="89"/>
+      <c r="V19" s="89"/>
+      <c r="W19" s="89"/>
+      <c r="X19" s="89"/>
+      <c r="Y19" s="89"/>
+      <c r="Z19" s="90"/>
+      <c r="AA19" s="90" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB19" s="90"/>
+      <c r="AC19" s="90" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD19" s="90" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE19" s="91"/>
+      <c r="AF19" s="91"/>
+      <c r="AG19" s="91"/>
+      <c r="AH19" s="92"/>
+      <c r="AI19" s="92"/>
+      <c r="AJ19" s="92"/>
+      <c r="AK19" s="93">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:37">
-      <c r="A20" s="70">
+      <c r="A20" s="69">
         <v>17</v>
       </c>
-      <c r="B20" s="70" t="s">
+      <c r="B20" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="86">
-        <v>46220</v>
-      </c>
-      <c r="D20" s="70" t="s">
+      <c r="C20" s="22">
+        <v>46251</v>
+      </c>
+      <c r="D20" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="E20" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="H20" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="I20" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="J20" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="K20" s="71"/>
-      <c r="L20" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="M20" s="72"/>
-      <c r="N20" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="O20" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="P20" s="72"/>
-      <c r="Q20" s="72"/>
-      <c r="R20" s="72"/>
-      <c r="S20" s="73"/>
-      <c r="T20" s="73"/>
-      <c r="U20" s="74"/>
-      <c r="V20" s="74"/>
-      <c r="W20" s="74"/>
-      <c r="X20" s="74"/>
-      <c r="Y20" s="74" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z20" s="75"/>
-      <c r="AA20" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB20" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="AC20" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD20" s="75"/>
-      <c r="AE20" s="76"/>
-      <c r="AF20" s="76" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG20" s="76"/>
-      <c r="AH20" s="77"/>
-      <c r="AI20" s="77"/>
-      <c r="AJ20" s="77"/>
-      <c r="AK20" s="95">
+      <c r="E20" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="I20" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="J20" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="K20" s="70"/>
+      <c r="L20" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="M20" s="71"/>
+      <c r="N20" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="O20" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="71"/>
+      <c r="S20" s="72"/>
+      <c r="T20" s="72"/>
+      <c r="U20" s="73"/>
+      <c r="V20" s="73"/>
+      <c r="W20" s="73"/>
+      <c r="X20" s="73"/>
+      <c r="Y20" s="73" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z20" s="74"/>
+      <c r="AA20" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB20" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC20" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD20" s="74"/>
+      <c r="AE20" s="75"/>
+      <c r="AF20" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG20" s="75"/>
+      <c r="AH20" s="76"/>
+      <c r="AI20" s="76"/>
+      <c r="AJ20" s="76"/>
+      <c r="AK20" s="93">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:37">
-      <c r="A21" s="70">
+      <c r="A21" s="69">
         <v>18</v>
       </c>
-      <c r="B21" s="70" t="s">
+      <c r="B21" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="86">
-        <v>46221</v>
-      </c>
-      <c r="D21" s="70" t="s">
+      <c r="C21" s="22">
+        <v>46252</v>
+      </c>
+      <c r="D21" s="69" t="s">
         <v>76</v>
       </c>
-      <c r="E21" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="H21" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="I21" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="J21" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="K21" s="71"/>
-      <c r="L21" s="72"/>
-      <c r="M21" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="N21" s="72"/>
-      <c r="O21" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="P21" s="72"/>
-      <c r="Q21" s="72"/>
-      <c r="R21" s="72"/>
-      <c r="S21" s="73"/>
-      <c r="T21" s="73"/>
-      <c r="U21" s="74" t="s">
-        <v>12</v>
-      </c>
-      <c r="V21" s="74"/>
-      <c r="W21" s="74"/>
-      <c r="X21" s="74" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y21" s="74"/>
-      <c r="Z21" s="75"/>
-      <c r="AA21" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB21" s="75"/>
-      <c r="AC21" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD21" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE21" s="76"/>
-      <c r="AF21" s="76" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG21" s="76" t="s">
-        <v>12</v>
-      </c>
-      <c r="AH21" s="77"/>
-      <c r="AI21" s="77"/>
-      <c r="AJ21" s="77"/>
-      <c r="AK21" s="95">
+      <c r="E21" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="H21" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="I21" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="J21" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="K21" s="70"/>
+      <c r="L21" s="71"/>
+      <c r="M21" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="N21" s="71"/>
+      <c r="O21" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="71"/>
+      <c r="S21" s="72"/>
+      <c r="T21" s="72"/>
+      <c r="U21" s="73" t="s">
+        <v>12</v>
+      </c>
+      <c r="V21" s="73"/>
+      <c r="W21" s="73"/>
+      <c r="X21" s="73" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y21" s="73"/>
+      <c r="Z21" s="74"/>
+      <c r="AA21" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB21" s="74"/>
+      <c r="AC21" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD21" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE21" s="75"/>
+      <c r="AF21" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG21" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="AH21" s="76"/>
+      <c r="AI21" s="76"/>
+      <c r="AJ21" s="76"/>
+      <c r="AK21" s="93">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
@@ -6383,7 +6561,7 @@
         <v>16</v>
       </c>
       <c r="C22" s="22">
-        <v>46222</v>
+        <v>46253</v>
       </c>
       <c r="D22" s="30" t="s">
         <v>62</v>
@@ -6438,63 +6616,63 @@
       </c>
     </row>
     <row r="23" spans="1:37">
-      <c r="A23" s="85">
+      <c r="A23" s="84">
         <v>20</v>
       </c>
-      <c r="B23" s="85" t="s">
+      <c r="B23" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="96">
-        <v>46223</v>
-      </c>
-      <c r="D23" s="87" t="s">
+      <c r="C23" s="22">
+        <v>46254</v>
+      </c>
+      <c r="D23" s="85" t="s">
         <v>62</v>
       </c>
-      <c r="E23" s="88"/>
-      <c r="F23" s="88"/>
-      <c r="G23" s="88"/>
-      <c r="H23" s="88"/>
-      <c r="I23" s="88"/>
-      <c r="J23" s="88"/>
-      <c r="K23" s="88"/>
-      <c r="L23" s="89"/>
-      <c r="M23" s="89" t="s">
-        <v>12</v>
-      </c>
-      <c r="N23" s="89" t="s">
-        <v>12</v>
-      </c>
-      <c r="O23" s="89" t="s">
-        <v>12</v>
-      </c>
-      <c r="P23" s="89"/>
-      <c r="Q23" s="89"/>
-      <c r="R23" s="89"/>
-      <c r="S23" s="90"/>
-      <c r="T23" s="90"/>
-      <c r="U23" s="91"/>
-      <c r="V23" s="91"/>
-      <c r="W23" s="91"/>
-      <c r="X23" s="91"/>
-      <c r="Y23" s="91"/>
-      <c r="Z23" s="92"/>
-      <c r="AA23" s="92" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB23" s="92"/>
-      <c r="AC23" s="92" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD23" s="92" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE23" s="93"/>
-      <c r="AF23" s="93"/>
-      <c r="AG23" s="93"/>
-      <c r="AH23" s="94"/>
-      <c r="AI23" s="94"/>
-      <c r="AJ23" s="94"/>
-      <c r="AK23" s="98">
+      <c r="E23" s="86"/>
+      <c r="F23" s="86"/>
+      <c r="G23" s="86"/>
+      <c r="H23" s="86"/>
+      <c r="I23" s="86"/>
+      <c r="J23" s="86"/>
+      <c r="K23" s="86"/>
+      <c r="L23" s="87"/>
+      <c r="M23" s="87" t="s">
+        <v>12</v>
+      </c>
+      <c r="N23" s="87" t="s">
+        <v>12</v>
+      </c>
+      <c r="O23" s="87" t="s">
+        <v>12</v>
+      </c>
+      <c r="P23" s="87"/>
+      <c r="Q23" s="87"/>
+      <c r="R23" s="87"/>
+      <c r="S23" s="88"/>
+      <c r="T23" s="88"/>
+      <c r="U23" s="89"/>
+      <c r="V23" s="89"/>
+      <c r="W23" s="89"/>
+      <c r="X23" s="89"/>
+      <c r="Y23" s="89"/>
+      <c r="Z23" s="90"/>
+      <c r="AA23" s="90" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB23" s="90"/>
+      <c r="AC23" s="90" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD23" s="90" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE23" s="91"/>
+      <c r="AF23" s="91"/>
+      <c r="AG23" s="91"/>
+      <c r="AH23" s="92"/>
+      <c r="AI23" s="92"/>
+      <c r="AJ23" s="92"/>
+      <c r="AK23" s="95">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -6506,65 +6684,65 @@
       <c r="B24" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="68">
-        <v>46224</v>
-      </c>
-      <c r="D24" s="99" t="s">
+      <c r="C24" s="22">
+        <v>46255</v>
+      </c>
+      <c r="D24" s="96" t="s">
         <v>62</v>
       </c>
-      <c r="E24" s="100" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="100" t="s">
-        <v>12</v>
-      </c>
-      <c r="G24" s="100" t="s">
-        <v>12</v>
-      </c>
-      <c r="H24" s="100"/>
-      <c r="I24" s="100"/>
-      <c r="J24" s="100"/>
-      <c r="K24" s="100"/>
-      <c r="L24" s="101" t="s">
-        <v>12</v>
-      </c>
-      <c r="M24" s="101" t="s">
-        <v>12</v>
-      </c>
-      <c r="N24" s="101" t="s">
-        <v>12</v>
-      </c>
-      <c r="O24" s="101" t="s">
-        <v>12</v>
-      </c>
-      <c r="P24" s="101"/>
-      <c r="Q24" s="101"/>
-      <c r="R24" s="101"/>
-      <c r="S24" s="102"/>
-      <c r="T24" s="102"/>
-      <c r="U24" s="103" t="s">
-        <v>12</v>
-      </c>
-      <c r="V24" s="103"/>
-      <c r="W24" s="103"/>
-      <c r="X24" s="103"/>
-      <c r="Y24" s="103"/>
-      <c r="Z24" s="104"/>
-      <c r="AA24" s="104"/>
-      <c r="AB24" s="104"/>
-      <c r="AC24" s="104" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD24" s="104" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE24" s="105"/>
-      <c r="AF24" s="105"/>
-      <c r="AG24" s="105"/>
-      <c r="AH24" s="106"/>
-      <c r="AI24" s="106"/>
-      <c r="AJ24" s="106"/>
-      <c r="AK24" s="107">
+      <c r="E24" s="97" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="97" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" s="97" t="s">
+        <v>12</v>
+      </c>
+      <c r="H24" s="97"/>
+      <c r="I24" s="97"/>
+      <c r="J24" s="97"/>
+      <c r="K24" s="97"/>
+      <c r="L24" s="98" t="s">
+        <v>12</v>
+      </c>
+      <c r="M24" s="98" t="s">
+        <v>12</v>
+      </c>
+      <c r="N24" s="98" t="s">
+        <v>12</v>
+      </c>
+      <c r="O24" s="98" t="s">
+        <v>12</v>
+      </c>
+      <c r="P24" s="98"/>
+      <c r="Q24" s="98"/>
+      <c r="R24" s="98"/>
+      <c r="S24" s="99"/>
+      <c r="T24" s="99"/>
+      <c r="U24" s="100" t="s">
+        <v>12</v>
+      </c>
+      <c r="V24" s="100"/>
+      <c r="W24" s="100"/>
+      <c r="X24" s="100"/>
+      <c r="Y24" s="100"/>
+      <c r="Z24" s="101"/>
+      <c r="AA24" s="101"/>
+      <c r="AB24" s="101"/>
+      <c r="AC24" s="101" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD24" s="101" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE24" s="102"/>
+      <c r="AF24" s="102"/>
+      <c r="AG24" s="102"/>
+      <c r="AH24" s="103"/>
+      <c r="AI24" s="103"/>
+      <c r="AJ24" s="103"/>
+      <c r="AK24" s="104">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -6576,337 +6754,379 @@
       <c r="B25" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="68">
-        <v>46225</v>
-      </c>
-      <c r="D25" s="70" t="s">
+      <c r="C25" s="22">
+        <v>46256</v>
+      </c>
+      <c r="D25" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="E25" s="71"/>
-      <c r="F25" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="G25" s="71"/>
-      <c r="H25" s="71"/>
-      <c r="I25" s="71"/>
-      <c r="J25" s="71"/>
-      <c r="K25" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="L25" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="M25" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="N25" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="O25" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="P25" s="72"/>
-      <c r="Q25" s="72"/>
-      <c r="R25" s="72"/>
-      <c r="S25" s="73"/>
-      <c r="T25" s="73"/>
-      <c r="U25" s="74"/>
-      <c r="V25" s="74"/>
-      <c r="W25" s="74"/>
-      <c r="X25" s="74"/>
-      <c r="Y25" s="74"/>
-      <c r="Z25" s="75"/>
-      <c r="AA25" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB25" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="AC25" s="75"/>
-      <c r="AD25" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE25" s="76"/>
-      <c r="AF25" s="76"/>
-      <c r="AG25" s="76"/>
-      <c r="AH25" s="77"/>
-      <c r="AI25" s="77"/>
-      <c r="AJ25" s="77"/>
-      <c r="AK25" s="95">
+      <c r="E25" s="70"/>
+      <c r="F25" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="70"/>
+      <c r="K25" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="L25" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="M25" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="N25" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="O25" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71"/>
+      <c r="R25" s="71"/>
+      <c r="S25" s="72"/>
+      <c r="T25" s="72"/>
+      <c r="U25" s="73"/>
+      <c r="V25" s="73"/>
+      <c r="W25" s="73"/>
+      <c r="X25" s="73"/>
+      <c r="Y25" s="73"/>
+      <c r="Z25" s="74"/>
+      <c r="AA25" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB25" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC25" s="74"/>
+      <c r="AD25" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE25" s="75"/>
+      <c r="AF25" s="75"/>
+      <c r="AG25" s="75"/>
+      <c r="AH25" s="76"/>
+      <c r="AI25" s="76"/>
+      <c r="AJ25" s="76"/>
+      <c r="AK25" s="93">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:37">
-      <c r="A26" s="70">
+      <c r="A26" s="69">
         <v>23</v>
       </c>
-      <c r="B26" s="70" t="s">
+      <c r="B26" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="116">
-        <v>46226</v>
-      </c>
-      <c r="D26" s="70" t="s">
+      <c r="C26" s="22">
+        <v>46257</v>
+      </c>
+      <c r="D26" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="E26" s="71"/>
-      <c r="F26" s="71"/>
-      <c r="G26" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="H26" s="71"/>
-      <c r="I26" s="71"/>
-      <c r="J26" s="71"/>
-      <c r="K26" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="L26" s="72"/>
-      <c r="M26" s="72"/>
-      <c r="N26" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="O26" s="72"/>
-      <c r="P26" s="72"/>
-      <c r="Q26" s="72"/>
-      <c r="R26" s="72"/>
-      <c r="S26" s="73" t="s">
-        <v>12</v>
-      </c>
-      <c r="T26" s="73"/>
-      <c r="U26" s="74"/>
-      <c r="V26" s="74"/>
-      <c r="W26" s="74"/>
-      <c r="X26" s="74"/>
-      <c r="Y26" s="74"/>
-      <c r="Z26" s="75"/>
-      <c r="AA26" s="75"/>
-      <c r="AB26" s="75"/>
-      <c r="AC26" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD26" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE26" s="76"/>
-      <c r="AF26" s="76"/>
-      <c r="AG26" s="76"/>
-      <c r="AH26" s="77"/>
-      <c r="AI26" s="77"/>
-      <c r="AJ26" s="77"/>
-      <c r="AK26" s="95">
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="70"/>
+      <c r="K26" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="L26" s="71"/>
+      <c r="M26" s="71"/>
+      <c r="N26" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="O26" s="71"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="71"/>
+      <c r="S26" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="T26" s="72"/>
+      <c r="U26" s="73"/>
+      <c r="V26" s="73"/>
+      <c r="W26" s="73"/>
+      <c r="X26" s="73"/>
+      <c r="Y26" s="73"/>
+      <c r="Z26" s="74"/>
+      <c r="AA26" s="74"/>
+      <c r="AB26" s="74"/>
+      <c r="AC26" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD26" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE26" s="75"/>
+      <c r="AF26" s="75"/>
+      <c r="AG26" s="75"/>
+      <c r="AH26" s="76"/>
+      <c r="AI26" s="76"/>
+      <c r="AJ26" s="76"/>
+      <c r="AK26" s="93">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:37" ht="15.75" thickBot="1">
-      <c r="A27" s="70">
+    <row r="27" spans="1:37">
+      <c r="A27" s="69">
         <v>24</v>
       </c>
-      <c r="B27" s="70" t="s">
+      <c r="B27" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="86">
-        <v>46227</v>
-      </c>
-      <c r="D27" s="70" t="s">
+      <c r="C27" s="22">
+        <v>46258</v>
+      </c>
+      <c r="D27" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="E27" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="F27" s="71"/>
-      <c r="G27" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="H27" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="I27" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="J27" s="71"/>
-      <c r="K27" s="71"/>
-      <c r="L27" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="M27" s="72" t="s">
-        <v>12</v>
-      </c>
-      <c r="N27" s="72"/>
-      <c r="O27" s="72"/>
-      <c r="P27" s="72"/>
-      <c r="Q27" s="72"/>
-      <c r="R27" s="72"/>
-      <c r="S27" s="73"/>
-      <c r="T27" s="73"/>
-      <c r="U27" s="74"/>
-      <c r="V27" s="74"/>
-      <c r="W27" s="74"/>
-      <c r="X27" s="74"/>
-      <c r="Y27" s="74"/>
-      <c r="Z27" s="75"/>
-      <c r="AA27" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="AB27" s="75"/>
-      <c r="AC27" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD27" s="75" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE27" s="76" t="s">
-        <v>12</v>
-      </c>
-      <c r="AF27" s="76" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG27" s="76"/>
-      <c r="AH27" s="77"/>
-      <c r="AI27" s="77"/>
-      <c r="AJ27" s="77"/>
-      <c r="AK27" s="95">
+      <c r="E27" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="H27" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="I27" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="J27" s="70"/>
+      <c r="K27" s="70"/>
+      <c r="L27" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="M27" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="N27" s="71"/>
+      <c r="O27" s="71"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="71"/>
+      <c r="S27" s="72"/>
+      <c r="T27" s="72"/>
+      <c r="U27" s="73"/>
+      <c r="V27" s="73"/>
+      <c r="W27" s="73"/>
+      <c r="X27" s="73"/>
+      <c r="Y27" s="73"/>
+      <c r="Z27" s="74"/>
+      <c r="AA27" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB27" s="74"/>
+      <c r="AC27" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD27" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE27" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF27" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG27" s="75"/>
+      <c r="AH27" s="76"/>
+      <c r="AI27" s="76"/>
+      <c r="AJ27" s="76"/>
+      <c r="AK27" s="93">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:37" ht="15.75" thickBot="1">
-      <c r="A28" s="117">
+    <row r="28" spans="1:37">
+      <c r="A28" s="69">
         <v>25</v>
       </c>
-      <c r="B28" s="118" t="s">
+      <c r="B28" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="146">
-        <v>46228</v>
-      </c>
-      <c r="D28" s="118" t="s">
+      <c r="C28" s="22">
+        <v>46259</v>
+      </c>
+      <c r="D28" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="E28" s="108" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" s="108" t="s">
-        <v>12</v>
-      </c>
-      <c r="G28" s="108" t="s">
-        <v>12</v>
-      </c>
-      <c r="H28" s="108"/>
-      <c r="I28" s="108" t="s">
-        <v>12</v>
-      </c>
-      <c r="J28" s="108" t="s">
-        <v>12</v>
-      </c>
-      <c r="K28" s="108"/>
-      <c r="L28" s="109"/>
-      <c r="M28" s="109" t="s">
-        <v>12</v>
-      </c>
-      <c r="N28" s="109" t="s">
-        <v>12</v>
-      </c>
-      <c r="O28" s="109"/>
-      <c r="P28" s="109"/>
-      <c r="Q28" s="109"/>
-      <c r="R28" s="109"/>
-      <c r="S28" s="110"/>
-      <c r="T28" s="110"/>
-      <c r="U28" s="111" t="s">
-        <v>12</v>
-      </c>
-      <c r="V28" s="111"/>
-      <c r="W28" s="111"/>
-      <c r="X28" s="111"/>
-      <c r="Y28" s="111"/>
-      <c r="Z28" s="112"/>
-      <c r="AA28" s="112"/>
-      <c r="AB28" s="112"/>
-      <c r="AC28" s="112"/>
-      <c r="AD28" s="112"/>
-      <c r="AE28" s="113"/>
-      <c r="AF28" s="113" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG28" s="113"/>
-      <c r="AH28" s="114"/>
-      <c r="AI28" s="114"/>
-      <c r="AJ28" s="114"/>
-      <c r="AK28" s="115">
+      <c r="E28" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="J28" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="K28" s="70"/>
+      <c r="L28" s="71"/>
+      <c r="M28" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="N28" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="O28" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71"/>
+      <c r="R28" s="71"/>
+      <c r="S28" s="72"/>
+      <c r="T28" s="72"/>
+      <c r="U28" s="73" t="s">
+        <v>12</v>
+      </c>
+      <c r="V28" s="73"/>
+      <c r="W28" s="73"/>
+      <c r="X28" s="73" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y28" s="73"/>
+      <c r="Z28" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA28" s="74"/>
+      <c r="AB28" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC28" s="74"/>
+      <c r="AD28" s="74"/>
+      <c r="AE28" s="75"/>
+      <c r="AF28" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG28" s="75"/>
+      <c r="AH28" s="76"/>
+      <c r="AI28" s="76"/>
+      <c r="AJ28" s="76"/>
+      <c r="AK28" s="93">
         <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:37">
+      <c r="A29" s="30">
+        <v>26</v>
+      </c>
+      <c r="B29" s="30" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="29" spans="1:37">
-      <c r="A29" s="85">
-        <v>26</v>
-      </c>
-      <c r="B29" s="85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" s="96">
-        <v>46229</v>
-      </c>
-      <c r="D29" s="85"/>
-      <c r="E29" s="78"/>
-      <c r="F29" s="78"/>
-      <c r="G29" s="78"/>
-      <c r="H29" s="78"/>
-      <c r="I29" s="78"/>
-      <c r="J29" s="78"/>
-      <c r="K29" s="78"/>
-      <c r="L29" s="79"/>
-      <c r="M29" s="79"/>
-      <c r="N29" s="79"/>
-      <c r="O29" s="79"/>
-      <c r="P29" s="79"/>
-      <c r="Q29" s="79"/>
-      <c r="R29" s="79"/>
-      <c r="S29" s="80"/>
-      <c r="T29" s="80"/>
-      <c r="U29" s="81"/>
-      <c r="V29" s="81"/>
-      <c r="W29" s="81"/>
-      <c r="X29" s="81"/>
-      <c r="Y29" s="81"/>
-      <c r="Z29" s="82"/>
-      <c r="AA29" s="82"/>
-      <c r="AB29" s="82"/>
-      <c r="AC29" s="82"/>
-      <c r="AD29" s="82"/>
-      <c r="AE29" s="83"/>
-      <c r="AF29" s="83"/>
-      <c r="AG29" s="83"/>
-      <c r="AH29" s="84"/>
-      <c r="AI29" s="84"/>
-      <c r="AJ29" s="84"/>
-      <c r="AK29" s="97">
+      <c r="C29" s="22">
+        <v>46260</v>
+      </c>
+      <c r="D29" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="E29" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="J29" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="K29" s="70"/>
+      <c r="L29" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="M29" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="N29" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="O29" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="71"/>
+      <c r="S29" s="72"/>
+      <c r="T29" s="72"/>
+      <c r="U29" s="73"/>
+      <c r="V29" s="73"/>
+      <c r="W29" s="73"/>
+      <c r="X29" s="73" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y29" s="73"/>
+      <c r="Z29" s="74"/>
+      <c r="AA29" s="74"/>
+      <c r="AB29" s="74"/>
+      <c r="AC29" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD29" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE29" s="75"/>
+      <c r="AF29" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG29" s="75"/>
+      <c r="AH29" s="76"/>
+      <c r="AI29" s="76"/>
+      <c r="AJ29" s="76"/>
+      <c r="AK29" s="93">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:37">
-      <c r="A30" s="21">
+      <c r="A30" s="84">
         <v>27</v>
       </c>
-      <c r="B30" s="21" t="s">
+      <c r="B30" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="C30" s="22">
-        <v>46230</v>
-      </c>
-      <c r="D30" s="30"/>
+      <c r="C30" s="105">
+        <v>46261</v>
+      </c>
+      <c r="D30" s="30" t="s">
+        <v>62</v>
+      </c>
       <c r="E30" s="62"/>
       <c r="F30" s="62"/>
-      <c r="G30" s="62"/>
+      <c r="G30" s="62" t="s">
+        <v>12</v>
+      </c>
       <c r="H30" s="62"/>
       <c r="I30" s="62"/>
       <c r="J30" s="62"/>
       <c r="K30" s="62"/>
-      <c r="L30" s="63"/>
-      <c r="M30" s="63"/>
+      <c r="L30" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="M30" s="63" t="s">
+        <v>12</v>
+      </c>
       <c r="N30" s="63"/>
       <c r="O30" s="63"/>
       <c r="P30" s="63"/>
@@ -6922,7 +7142,9 @@
       <c r="Z30" s="65"/>
       <c r="AA30" s="65"/>
       <c r="AB30" s="65"/>
-      <c r="AC30" s="65"/>
+      <c r="AC30" s="65" t="s">
+        <v>12</v>
+      </c>
       <c r="AD30" s="65"/>
       <c r="AE30" s="66"/>
       <c r="AF30" s="66"/>
@@ -6932,7 +7154,7 @@
       <c r="AJ30" s="67"/>
       <c r="AK30" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:37">
@@ -6943,44 +7165,62 @@
         <v>18</v>
       </c>
       <c r="C31" s="22">
-        <v>46231</v>
-      </c>
-      <c r="D31" s="30"/>
-      <c r="E31" s="62"/>
-      <c r="F31" s="62"/>
-      <c r="G31" s="62"/>
-      <c r="H31" s="62"/>
-      <c r="I31" s="62"/>
-      <c r="J31" s="62"/>
-      <c r="K31" s="62"/>
-      <c r="L31" s="63"/>
-      <c r="M31" s="63"/>
-      <c r="N31" s="63"/>
-      <c r="O31" s="63"/>
-      <c r="P31" s="63"/>
-      <c r="Q31" s="63"/>
-      <c r="R31" s="63"/>
-      <c r="S31" s="29"/>
-      <c r="T31" s="29"/>
-      <c r="U31" s="64"/>
-      <c r="V31" s="64"/>
-      <c r="W31" s="64"/>
-      <c r="X31" s="64"/>
-      <c r="Y31" s="64"/>
-      <c r="Z31" s="65"/>
-      <c r="AA31" s="65"/>
-      <c r="AB31" s="65"/>
-      <c r="AC31" s="65"/>
-      <c r="AD31" s="65"/>
-      <c r="AE31" s="66"/>
-      <c r="AF31" s="66"/>
-      <c r="AG31" s="66"/>
-      <c r="AH31" s="67"/>
-      <c r="AI31" s="67"/>
-      <c r="AJ31" s="67"/>
-      <c r="AK31" s="25">
+        <v>46262</v>
+      </c>
+      <c r="D31" s="84" t="s">
+        <v>62</v>
+      </c>
+      <c r="E31" s="77" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="77" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" s="77" t="s">
+        <v>12</v>
+      </c>
+      <c r="H31" s="77"/>
+      <c r="I31" s="77"/>
+      <c r="J31" s="77"/>
+      <c r="K31" s="77"/>
+      <c r="L31" s="78"/>
+      <c r="M31" s="78" t="s">
+        <v>12</v>
+      </c>
+      <c r="N31" s="78" t="s">
+        <v>12</v>
+      </c>
+      <c r="O31" s="78" t="s">
+        <v>12</v>
+      </c>
+      <c r="P31" s="78"/>
+      <c r="Q31" s="78"/>
+      <c r="R31" s="78"/>
+      <c r="S31" s="79"/>
+      <c r="T31" s="79"/>
+      <c r="U31" s="80"/>
+      <c r="V31" s="80"/>
+      <c r="W31" s="80"/>
+      <c r="X31" s="80"/>
+      <c r="Y31" s="80"/>
+      <c r="Z31" s="81"/>
+      <c r="AA31" s="81"/>
+      <c r="AB31" s="81"/>
+      <c r="AC31" s="81" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD31" s="81" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE31" s="82"/>
+      <c r="AF31" s="82"/>
+      <c r="AG31" s="82"/>
+      <c r="AH31" s="83"/>
+      <c r="AI31" s="83"/>
+      <c r="AJ31" s="83"/>
+      <c r="AK31" s="94">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:37">
@@ -6991,15 +7231,23 @@
         <v>11</v>
       </c>
       <c r="C32" s="22">
-        <v>46232</v>
-      </c>
-      <c r="D32" s="30"/>
+        <v>46263</v>
+      </c>
+      <c r="D32" s="30" t="s">
+        <v>62</v>
+      </c>
       <c r="E32" s="62"/>
       <c r="F32" s="62"/>
-      <c r="G32" s="62"/>
+      <c r="G32" s="62" t="s">
+        <v>12</v>
+      </c>
       <c r="H32" s="62"/>
-      <c r="I32" s="62"/>
-      <c r="J32" s="62"/>
+      <c r="I32" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="J32" s="62" t="s">
+        <v>12</v>
+      </c>
       <c r="K32" s="62"/>
       <c r="L32" s="63"/>
       <c r="M32" s="63"/>
@@ -7015,11 +7263,17 @@
       <c r="W32" s="64"/>
       <c r="X32" s="64"/>
       <c r="Y32" s="64"/>
-      <c r="Z32" s="65"/>
+      <c r="Z32" s="65" t="s">
+        <v>12</v>
+      </c>
       <c r="AA32" s="65"/>
       <c r="AB32" s="65"/>
-      <c r="AC32" s="65"/>
-      <c r="AD32" s="65"/>
+      <c r="AC32" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD32" s="65" t="s">
+        <v>12</v>
+      </c>
       <c r="AE32" s="66"/>
       <c r="AF32" s="66"/>
       <c r="AG32" s="66"/>
@@ -7028,7 +7282,7 @@
       <c r="AJ32" s="67"/>
       <c r="AK32" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:37">
@@ -7039,16 +7293,22 @@
         <v>13</v>
       </c>
       <c r="C33" s="22">
-        <v>46233</v>
-      </c>
-      <c r="D33" s="30"/>
+        <v>46264</v>
+      </c>
+      <c r="D33" s="30" t="s">
+        <v>62</v>
+      </c>
       <c r="E33" s="62"/>
       <c r="F33" s="62"/>
-      <c r="G33" s="62"/>
+      <c r="G33" s="62" t="s">
+        <v>12</v>
+      </c>
       <c r="H33" s="62"/>
       <c r="I33" s="62"/>
       <c r="J33" s="62"/>
-      <c r="K33" s="62"/>
+      <c r="K33" s="62" t="s">
+        <v>12</v>
+      </c>
       <c r="L33" s="63"/>
       <c r="M33" s="63"/>
       <c r="N33" s="63"/>
@@ -7074,9 +7334,9 @@
       <c r="AH33" s="67"/>
       <c r="AI33" s="67"/>
       <c r="AJ33" s="67"/>
-      <c r="AK33" s="25">
+      <c r="AK33" s="109">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:37">
@@ -7087,9 +7347,11 @@
         <v>14</v>
       </c>
       <c r="C34" s="22">
-        <v>46234</v>
-      </c>
-      <c r="D34" s="30"/>
+        <v>46265</v>
+      </c>
+      <c r="D34" s="30" t="s">
+        <v>62</v>
+      </c>
       <c r="E34" s="62"/>
       <c r="F34" s="62"/>
       <c r="G34" s="62"/>
@@ -7097,9 +7359,13 @@
       <c r="I34" s="62"/>
       <c r="J34" s="62"/>
       <c r="K34" s="62"/>
-      <c r="L34" s="63"/>
+      <c r="L34" s="63" t="s">
+        <v>12</v>
+      </c>
       <c r="M34" s="63"/>
-      <c r="N34" s="63"/>
+      <c r="N34" s="63" t="s">
+        <v>12</v>
+      </c>
       <c r="O34" s="63"/>
       <c r="P34" s="63"/>
       <c r="Q34" s="63"/>
@@ -7115,7 +7381,9 @@
       <c r="AA34" s="65"/>
       <c r="AB34" s="65"/>
       <c r="AC34" s="65"/>
-      <c r="AD34" s="65"/>
+      <c r="AD34" s="65" t="s">
+        <v>12</v>
+      </c>
       <c r="AE34" s="66"/>
       <c r="AF34" s="66"/>
       <c r="AG34" s="66"/>
@@ -7124,11 +7392,235 @@
       <c r="AJ34" s="67"/>
       <c r="AK34" s="25">
         <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:37" ht="30" customHeight="1">
+      <c r="A35" s="122" t="s">
+        <v>77</v>
+      </c>
+      <c r="B35" s="123"/>
+      <c r="C35" s="123"/>
+      <c r="D35" s="124"/>
+      <c r="E35" s="106">
+        <f>COUNTA(E4:E34)</f>
+        <v>14</v>
+      </c>
+      <c r="F35" s="106">
+        <f t="shared" ref="F35:AJ35" si="1">COUNTA(F4:F34)</f>
+        <v>15</v>
+      </c>
+      <c r="G35" s="106">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="H35" s="106">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="I35" s="106">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="J35" s="106">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="K35" s="106">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="L35" s="63">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="M35" s="63">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="N35" s="63">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="O35" s="63">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+      <c r="P35" s="63">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
+      <c r="Q35" s="63">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R35" s="63">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S35" s="29">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="T35" s="29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U35" s="64">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="V35" s="64">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="W35" s="64">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="X35" s="64">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="Y35" s="64">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="Z35" s="65">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="AA35" s="65">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="AB35" s="65">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="AC35" s="65">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="AD35" s="65">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="AE35" s="66">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AF35" s="66">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="AG35" s="66">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AH35" s="67">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AI35" s="67">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AJ35" s="67">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AK35" s="25"/>
+    </row>
+    <row r="36" spans="1:37" ht="30" customHeight="1">
+      <c r="AG36" s="119" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH36" s="120"/>
+      <c r="AI36" s="120"/>
+      <c r="AJ36" s="121"/>
+      <c r="AK36" s="107">
+        <f>ROUND(AVERAGE(AK4:AK34),0)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:37" ht="30" customHeight="1">
+      <c r="AG37" s="119" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH37" s="120"/>
+      <c r="AI37" s="120"/>
+      <c r="AJ37" s="121"/>
+      <c r="AK37" s="107">
+        <f>MAX(AK4:AK34)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:37" ht="30" customHeight="1">
+      <c r="AG38" s="119" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH38" s="120"/>
+      <c r="AI38" s="120"/>
+      <c r="AJ38" s="121"/>
+      <c r="AK38" s="107">
+        <f>MIN(AK4:AK34)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:37" ht="30" customHeight="1">
+      <c r="AG39" s="119" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH39" s="120"/>
+      <c r="AI39" s="120"/>
+      <c r="AJ39" s="121"/>
+      <c r="AK39" s="107">
+        <f>COUNTIF(AK4:AK34, "&gt;"&amp;AK36)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:37" ht="30" customHeight="1">
+      <c r="AG40" s="119" t="s">
+        <v>82</v>
+      </c>
+      <c r="AH40" s="120"/>
+      <c r="AI40" s="120"/>
+      <c r="AJ40" s="121"/>
+      <c r="AK40" s="107">
+        <f>COUNTIF(AK4:AK34, "&lt;"&amp;AK36)</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:37" ht="30" customHeight="1">
+      <c r="AG41" s="119" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH41" s="120"/>
+      <c r="AI41" s="120"/>
+      <c r="AJ41" s="121"/>
+      <c r="AK41" s="107">
+        <f>COUNTIF(AK4:AK34, "&gt;"&amp;20)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:37" ht="30" customHeight="1">
+      <c r="AG42" s="119" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH42" s="120"/>
+      <c r="AI42" s="120"/>
+      <c r="AJ42" s="121"/>
+      <c r="AK42" s="107">
+        <f>COUNTIF(AK4:AK34, "&lt;"&amp;20)</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43" spans="1:37" ht="30" customHeight="1"/>
+    <row r="44" spans="1:37" ht="30" customHeight="1"/>
+    <row r="45" spans="1:37" ht="30" customHeight="1"/>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="17">
     <mergeCell ref="AE1:AG1"/>
     <mergeCell ref="AH1:AJ1"/>
     <mergeCell ref="AK1:AK3"/>
@@ -7138,14 +7630,2086 @@
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="U1:Y1"/>
     <mergeCell ref="Z1:AD1"/>
+    <mergeCell ref="AG40:AJ40"/>
+    <mergeCell ref="AG41:AJ41"/>
+    <mergeCell ref="AG42:AJ42"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="AG36:AJ36"/>
+    <mergeCell ref="AG37:AJ37"/>
+    <mergeCell ref="AG38:AJ38"/>
+    <mergeCell ref="AG39:AJ39"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:AJ34">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="13" priority="7">
       <formula>E4="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L35:R35">
+    <cfRule type="expression" dxfId="12" priority="6">
+      <formula>L35="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S35:T35">
+    <cfRule type="expression" dxfId="11" priority="5">
+      <formula>S35="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U35:Y35">
+    <cfRule type="expression" dxfId="10" priority="4">
+      <formula>U35="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z35:AD35">
+    <cfRule type="expression" dxfId="9" priority="3">
+      <formula>Z35="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE35:AG35">
+    <cfRule type="expression" dxfId="8" priority="2">
+      <formula>AE35="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH35:AJ35">
+    <cfRule type="expression" dxfId="7" priority="1">
+      <formula>AH35="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AK44"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="3" width="15.7109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="26" style="3" customWidth="1"/>
+    <col min="5" max="6" width="15.7109375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="21.140625" style="3" customWidth="1"/>
+    <col min="8" max="11" width="15.7109375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="20.28515625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="20.42578125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="33.42578125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="26.7109375" style="3" customWidth="1"/>
+    <col min="16" max="16" width="25.85546875" style="3" customWidth="1"/>
+    <col min="17" max="17" width="21.140625" style="3" customWidth="1"/>
+    <col min="18" max="20" width="15.7109375" style="3" customWidth="1"/>
+    <col min="21" max="21" width="23.7109375" style="3" customWidth="1"/>
+    <col min="22" max="22" width="21.5703125" style="3" customWidth="1"/>
+    <col min="23" max="25" width="15.7109375" style="3" customWidth="1"/>
+    <col min="26" max="26" width="21.42578125" style="3" customWidth="1"/>
+    <col min="27" max="27" width="15.7109375" style="3" customWidth="1"/>
+    <col min="28" max="28" width="27.140625" style="3" customWidth="1"/>
+    <col min="29" max="29" width="15.7109375" style="3" customWidth="1"/>
+    <col min="30" max="30" width="29.28515625" style="3" customWidth="1"/>
+    <col min="31" max="31" width="24.42578125" style="3" customWidth="1"/>
+    <col min="32" max="32" width="33.7109375" style="3" customWidth="1"/>
+    <col min="33" max="33" width="34.28515625" style="3" customWidth="1"/>
+    <col min="34" max="36" width="15.7109375" style="3" customWidth="1"/>
+    <col min="37" max="37" width="24.5703125" style="3" customWidth="1"/>
+    <col min="38" max="38" width="20.7109375" style="3" customWidth="1"/>
+    <col min="39" max="16384" width="9" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
+      <c r="A1" s="130"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="136" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
+      <c r="L1" s="137" t="s">
+        <v>38</v>
+      </c>
+      <c r="M1" s="137"/>
+      <c r="N1" s="137"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="144" t="s">
+        <v>39</v>
+      </c>
+      <c r="S1" s="146"/>
+      <c r="T1" s="145"/>
+      <c r="U1" s="139" t="s">
+        <v>40</v>
+      </c>
+      <c r="V1" s="140"/>
+      <c r="W1" s="140"/>
+      <c r="X1" s="140"/>
+      <c r="Y1" s="141"/>
+      <c r="Z1" s="142" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA1" s="142"/>
+      <c r="AB1" s="142"/>
+      <c r="AC1" s="142"/>
+      <c r="AD1" s="142"/>
+      <c r="AE1" s="125" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF1" s="125"/>
+      <c r="AG1" s="125"/>
+      <c r="AH1" s="126" t="s">
+        <v>43</v>
+      </c>
+      <c r="AI1" s="126"/>
+      <c r="AJ1" s="126"/>
+      <c r="AK1" s="127" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37" s="2" customFormat="1" ht="45" customHeight="1">
+      <c r="A2" s="133"/>
+      <c r="B2" s="134"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="T2" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="U2" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="V2" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="W2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="X2" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y2" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z2" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA2" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB2" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC2" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD2" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE2" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="AF2" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG2" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="AH2" s="12"/>
+      <c r="AI2" s="12"/>
+      <c r="AJ2" s="12"/>
+      <c r="AK2" s="128"/>
+    </row>
+    <row r="3" spans="1:37">
+      <c r="A3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="14">
+        <v>2</v>
+      </c>
+      <c r="F3" s="14">
+        <v>1</v>
+      </c>
+      <c r="G3" s="14">
+        <v>1</v>
+      </c>
+      <c r="H3" s="14">
+        <v>2</v>
+      </c>
+      <c r="I3" s="14">
+        <v>1</v>
+      </c>
+      <c r="J3" s="14">
+        <v>2</v>
+      </c>
+      <c r="K3" s="14">
+        <v>1</v>
+      </c>
+      <c r="L3" s="15">
+        <v>3</v>
+      </c>
+      <c r="M3" s="15">
+        <v>1</v>
+      </c>
+      <c r="N3" s="15">
+        <v>2</v>
+      </c>
+      <c r="O3" s="15">
+        <v>1</v>
+      </c>
+      <c r="P3" s="15">
+        <v>3</v>
+      </c>
+      <c r="Q3" s="15">
+        <v>3</v>
+      </c>
+      <c r="R3" s="16">
+        <v>3</v>
+      </c>
+      <c r="S3" s="16">
+        <v>3</v>
+      </c>
+      <c r="T3" s="16">
+        <v>3</v>
+      </c>
+      <c r="U3" s="17">
+        <v>2</v>
+      </c>
+      <c r="V3" s="17">
+        <v>2</v>
+      </c>
+      <c r="W3" s="17">
+        <v>2</v>
+      </c>
+      <c r="X3" s="17">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="17">
+        <v>2</v>
+      </c>
+      <c r="Z3" s="18">
+        <v>3</v>
+      </c>
+      <c r="AA3" s="18">
+        <v>2</v>
+      </c>
+      <c r="AB3" s="18">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="18">
+        <v>2</v>
+      </c>
+      <c r="AD3" s="18">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="19">
+        <v>3</v>
+      </c>
+      <c r="AF3" s="19">
+        <v>2</v>
+      </c>
+      <c r="AG3" s="19">
+        <v>3</v>
+      </c>
+      <c r="AH3" s="20">
+        <v>2</v>
+      </c>
+      <c r="AI3" s="20">
+        <v>2</v>
+      </c>
+      <c r="AJ3" s="20">
+        <v>1</v>
+      </c>
+      <c r="AK3" s="129"/>
+    </row>
+    <row r="4" spans="1:37">
+      <c r="A4" s="30">
+        <v>1</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="22">
+        <v>46266</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="62"/>
+      <c r="L4" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="M4" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="N4" s="63"/>
+      <c r="O4" s="63"/>
+      <c r="P4" s="63"/>
+      <c r="Q4" s="63"/>
+      <c r="R4" s="24"/>
+      <c r="S4" s="24"/>
+      <c r="T4" s="24"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="64"/>
+      <c r="W4" s="64"/>
+      <c r="X4" s="64"/>
+      <c r="Y4" s="64"/>
+      <c r="Z4" s="65"/>
+      <c r="AA4" s="65"/>
+      <c r="AB4" s="65"/>
+      <c r="AC4" s="65"/>
+      <c r="AD4" s="65"/>
+      <c r="AE4" s="66"/>
+      <c r="AF4" s="66"/>
+      <c r="AG4" s="66"/>
+      <c r="AH4" s="67"/>
+      <c r="AI4" s="67"/>
+      <c r="AJ4" s="67"/>
+      <c r="AK4" s="25">
+        <f>SUMIF(E4:AJ4,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37">
+      <c r="A5" s="30">
+        <v>2</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="22">
+        <v>46267</v>
+      </c>
+      <c r="D5" s="30"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="62"/>
+      <c r="L5" s="63"/>
+      <c r="M5" s="63"/>
+      <c r="N5" s="63"/>
+      <c r="O5" s="63"/>
+      <c r="P5" s="63"/>
+      <c r="Q5" s="63"/>
+      <c r="R5" s="24"/>
+      <c r="S5" s="24"/>
+      <c r="T5" s="24"/>
+      <c r="U5" s="64"/>
+      <c r="V5" s="64"/>
+      <c r="W5" s="64"/>
+      <c r="X5" s="64"/>
+      <c r="Y5" s="64"/>
+      <c r="Z5" s="65"/>
+      <c r="AA5" s="65"/>
+      <c r="AB5" s="65"/>
+      <c r="AC5" s="65"/>
+      <c r="AD5" s="65"/>
+      <c r="AE5" s="66"/>
+      <c r="AF5" s="66"/>
+      <c r="AG5" s="66"/>
+      <c r="AH5" s="67"/>
+      <c r="AI5" s="67"/>
+      <c r="AJ5" s="67"/>
+      <c r="AK5" s="25">
+        <f>SUMIF(E5:AJ5,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37">
+      <c r="A6" s="30">
+        <v>3</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="22">
+        <v>46268</v>
+      </c>
+      <c r="D6" s="30"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="63"/>
+      <c r="M6" s="63"/>
+      <c r="N6" s="63"/>
+      <c r="O6" s="63"/>
+      <c r="P6" s="63"/>
+      <c r="Q6" s="63"/>
+      <c r="R6" s="24"/>
+      <c r="S6" s="24"/>
+      <c r="T6" s="24"/>
+      <c r="U6" s="64"/>
+      <c r="V6" s="64"/>
+      <c r="W6" s="64"/>
+      <c r="X6" s="64"/>
+      <c r="Y6" s="64"/>
+      <c r="Z6" s="65"/>
+      <c r="AA6" s="65"/>
+      <c r="AB6" s="65"/>
+      <c r="AC6" s="65"/>
+      <c r="AD6" s="65"/>
+      <c r="AE6" s="66"/>
+      <c r="AF6" s="66"/>
+      <c r="AG6" s="66"/>
+      <c r="AH6" s="67"/>
+      <c r="AI6" s="67"/>
+      <c r="AJ6" s="67"/>
+      <c r="AK6" s="25">
+        <f>SUMIF(E6:AJ6,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37">
+      <c r="A7" s="30">
+        <v>4</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="22">
+        <v>46269</v>
+      </c>
+      <c r="D7" s="30"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="62"/>
+      <c r="J7" s="62"/>
+      <c r="K7" s="62"/>
+      <c r="L7" s="63"/>
+      <c r="M7" s="63"/>
+      <c r="N7" s="63"/>
+      <c r="O7" s="63"/>
+      <c r="P7" s="63"/>
+      <c r="Q7" s="63"/>
+      <c r="R7" s="24"/>
+      <c r="S7" s="24"/>
+      <c r="T7" s="24"/>
+      <c r="U7" s="64"/>
+      <c r="V7" s="64"/>
+      <c r="W7" s="64"/>
+      <c r="X7" s="64"/>
+      <c r="Y7" s="64"/>
+      <c r="Z7" s="65"/>
+      <c r="AA7" s="65"/>
+      <c r="AB7" s="65"/>
+      <c r="AC7" s="65"/>
+      <c r="AD7" s="65"/>
+      <c r="AE7" s="66"/>
+      <c r="AF7" s="66"/>
+      <c r="AG7" s="66"/>
+      <c r="AH7" s="67"/>
+      <c r="AI7" s="67"/>
+      <c r="AJ7" s="67"/>
+      <c r="AK7" s="25">
+        <f>SUMIF(E7:AJ7,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37">
+      <c r="A8" s="30">
+        <v>5</v>
+      </c>
+      <c r="B8" s="143" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="22">
+        <v>46270</v>
+      </c>
+      <c r="D8" s="30"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
+      <c r="J8" s="62"/>
+      <c r="K8" s="62"/>
+      <c r="L8" s="63"/>
+      <c r="M8" s="63"/>
+      <c r="N8" s="63"/>
+      <c r="O8" s="63"/>
+      <c r="P8" s="63"/>
+      <c r="Q8" s="63"/>
+      <c r="R8" s="24"/>
+      <c r="S8" s="24"/>
+      <c r="T8" s="24"/>
+      <c r="U8" s="64"/>
+      <c r="V8" s="64"/>
+      <c r="W8" s="64"/>
+      <c r="X8" s="64"/>
+      <c r="Y8" s="64"/>
+      <c r="Z8" s="65"/>
+      <c r="AA8" s="65"/>
+      <c r="AB8" s="65"/>
+      <c r="AC8" s="65"/>
+      <c r="AD8" s="65"/>
+      <c r="AE8" s="66"/>
+      <c r="AF8" s="66"/>
+      <c r="AG8" s="66"/>
+      <c r="AH8" s="67"/>
+      <c r="AI8" s="67"/>
+      <c r="AJ8" s="67"/>
+      <c r="AK8" s="25">
+        <f>SUMIF(E8:AJ8,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37">
+      <c r="A9" s="30">
+        <v>6</v>
+      </c>
+      <c r="B9" s="143" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="22">
+        <v>46271</v>
+      </c>
+      <c r="D9" s="30"/>
+      <c r="E9" s="62"/>
+      <c r="F9" s="62"/>
+      <c r="G9" s="62"/>
+      <c r="H9" s="62"/>
+      <c r="I9" s="62"/>
+      <c r="J9" s="62"/>
+      <c r="K9" s="62"/>
+      <c r="L9" s="63"/>
+      <c r="M9" s="63"/>
+      <c r="N9" s="63"/>
+      <c r="O9" s="63"/>
+      <c r="P9" s="63"/>
+      <c r="Q9" s="63"/>
+      <c r="R9" s="24"/>
+      <c r="S9" s="24"/>
+      <c r="T9" s="24"/>
+      <c r="U9" s="64"/>
+      <c r="V9" s="64"/>
+      <c r="W9" s="64"/>
+      <c r="X9" s="64"/>
+      <c r="Y9" s="64"/>
+      <c r="Z9" s="65"/>
+      <c r="AA9" s="65"/>
+      <c r="AB9" s="65"/>
+      <c r="AC9" s="65"/>
+      <c r="AD9" s="65"/>
+      <c r="AE9" s="66"/>
+      <c r="AF9" s="66"/>
+      <c r="AG9" s="66"/>
+      <c r="AH9" s="67"/>
+      <c r="AI9" s="67"/>
+      <c r="AJ9" s="67"/>
+      <c r="AK9" s="25">
+        <f>SUMIF(E9:AJ9,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37">
+      <c r="A10" s="30">
+        <v>7</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="22">
+        <v>46272</v>
+      </c>
+      <c r="D10" s="30"/>
+      <c r="E10" s="62"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="62"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="62"/>
+      <c r="J10" s="62"/>
+      <c r="K10" s="62"/>
+      <c r="L10" s="63"/>
+      <c r="M10" s="63"/>
+      <c r="N10" s="63"/>
+      <c r="O10" s="63"/>
+      <c r="P10" s="63"/>
+      <c r="Q10" s="63"/>
+      <c r="R10" s="27"/>
+      <c r="S10" s="27"/>
+      <c r="T10" s="27"/>
+      <c r="U10" s="64"/>
+      <c r="V10" s="64"/>
+      <c r="W10" s="64"/>
+      <c r="X10" s="64"/>
+      <c r="Y10" s="64"/>
+      <c r="Z10" s="65"/>
+      <c r="AA10" s="65"/>
+      <c r="AB10" s="65"/>
+      <c r="AC10" s="65"/>
+      <c r="AD10" s="65"/>
+      <c r="AE10" s="66"/>
+      <c r="AF10" s="66"/>
+      <c r="AG10" s="66"/>
+      <c r="AH10" s="67"/>
+      <c r="AI10" s="67"/>
+      <c r="AJ10" s="67"/>
+      <c r="AK10" s="25">
+        <f>SUMIF(E10:AJ10,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37">
+      <c r="A11" s="30">
+        <v>8</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="22">
+        <v>46273</v>
+      </c>
+      <c r="D11" s="30"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="62"/>
+      <c r="H11" s="62"/>
+      <c r="I11" s="62"/>
+      <c r="J11" s="62"/>
+      <c r="K11" s="62"/>
+      <c r="L11" s="63"/>
+      <c r="M11" s="63"/>
+      <c r="N11" s="63"/>
+      <c r="O11" s="63"/>
+      <c r="P11" s="63"/>
+      <c r="Q11" s="63"/>
+      <c r="R11" s="29"/>
+      <c r="S11" s="29"/>
+      <c r="T11" s="29"/>
+      <c r="U11" s="64"/>
+      <c r="V11" s="64"/>
+      <c r="W11" s="64"/>
+      <c r="X11" s="64"/>
+      <c r="Y11" s="64"/>
+      <c r="Z11" s="65"/>
+      <c r="AA11" s="65"/>
+      <c r="AB11" s="65"/>
+      <c r="AC11" s="65"/>
+      <c r="AD11" s="65"/>
+      <c r="AE11" s="66"/>
+      <c r="AF11" s="66"/>
+      <c r="AG11" s="66"/>
+      <c r="AH11" s="67"/>
+      <c r="AI11" s="67"/>
+      <c r="AJ11" s="67"/>
+      <c r="AK11" s="25">
+        <f>SUMIF(E11:AJ11,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37">
+      <c r="A12" s="30">
+        <v>9</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="22">
+        <v>46274</v>
+      </c>
+      <c r="D12" s="30"/>
+      <c r="E12" s="62"/>
+      <c r="F12" s="62"/>
+      <c r="G12" s="62"/>
+      <c r="H12" s="62"/>
+      <c r="I12" s="62"/>
+      <c r="J12" s="62"/>
+      <c r="K12" s="62"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="63"/>
+      <c r="N12" s="63"/>
+      <c r="O12" s="63"/>
+      <c r="P12" s="63"/>
+      <c r="Q12" s="63"/>
+      <c r="R12" s="28"/>
+      <c r="S12" s="28"/>
+      <c r="T12" s="28"/>
+      <c r="U12" s="64"/>
+      <c r="V12" s="64"/>
+      <c r="W12" s="64"/>
+      <c r="X12" s="64"/>
+      <c r="Y12" s="64"/>
+      <c r="Z12" s="65"/>
+      <c r="AA12" s="65"/>
+      <c r="AB12" s="65"/>
+      <c r="AC12" s="65"/>
+      <c r="AD12" s="65"/>
+      <c r="AE12" s="66"/>
+      <c r="AF12" s="66"/>
+      <c r="AG12" s="66"/>
+      <c r="AH12" s="67"/>
+      <c r="AI12" s="67"/>
+      <c r="AJ12" s="67"/>
+      <c r="AK12" s="25">
+        <f>SUMIF(E12:AJ12,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37">
+      <c r="A13" s="30">
+        <v>10</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="22">
+        <v>46275</v>
+      </c>
+      <c r="D13" s="30"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="62"/>
+      <c r="G13" s="62"/>
+      <c r="H13" s="62"/>
+      <c r="I13" s="62"/>
+      <c r="J13" s="62"/>
+      <c r="K13" s="62"/>
+      <c r="L13" s="63"/>
+      <c r="M13" s="63"/>
+      <c r="N13" s="63"/>
+      <c r="O13" s="63"/>
+      <c r="P13" s="63"/>
+      <c r="Q13" s="63"/>
+      <c r="R13" s="29"/>
+      <c r="S13" s="29"/>
+      <c r="T13" s="29"/>
+      <c r="U13" s="64"/>
+      <c r="V13" s="64"/>
+      <c r="W13" s="64"/>
+      <c r="X13" s="64"/>
+      <c r="Y13" s="64"/>
+      <c r="Z13" s="65"/>
+      <c r="AA13" s="65"/>
+      <c r="AB13" s="65"/>
+      <c r="AC13" s="65"/>
+      <c r="AD13" s="65"/>
+      <c r="AE13" s="66"/>
+      <c r="AF13" s="66"/>
+      <c r="AG13" s="66"/>
+      <c r="AH13" s="67"/>
+      <c r="AI13" s="67"/>
+      <c r="AJ13" s="67"/>
+      <c r="AK13" s="25">
+        <f>SUMIF(E13:AJ13,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37">
+      <c r="A14" s="30">
+        <v>11</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="22">
+        <v>46276</v>
+      </c>
+      <c r="D14" s="30"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="62"/>
+      <c r="J14" s="62"/>
+      <c r="K14" s="62"/>
+      <c r="L14" s="63"/>
+      <c r="M14" s="63"/>
+      <c r="N14" s="63"/>
+      <c r="O14" s="63"/>
+      <c r="P14" s="63"/>
+      <c r="Q14" s="63"/>
+      <c r="R14" s="29"/>
+      <c r="S14" s="29"/>
+      <c r="T14" s="29"/>
+      <c r="U14" s="64"/>
+      <c r="V14" s="64"/>
+      <c r="W14" s="64"/>
+      <c r="X14" s="64"/>
+      <c r="Y14" s="64"/>
+      <c r="Z14" s="65"/>
+      <c r="AA14" s="65"/>
+      <c r="AB14" s="65"/>
+      <c r="AC14" s="65"/>
+      <c r="AD14" s="65"/>
+      <c r="AE14" s="66"/>
+      <c r="AF14" s="66"/>
+      <c r="AG14" s="66"/>
+      <c r="AH14" s="67"/>
+      <c r="AI14" s="67"/>
+      <c r="AJ14" s="67"/>
+      <c r="AK14" s="25">
+        <f>SUMIF(E14:AJ14,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37">
+      <c r="A15" s="30">
+        <v>12</v>
+      </c>
+      <c r="B15" s="143" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="22">
+        <v>46277</v>
+      </c>
+      <c r="D15" s="30"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="62"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="62"/>
+      <c r="K15" s="62"/>
+      <c r="L15" s="63"/>
+      <c r="M15" s="63"/>
+      <c r="N15" s="63"/>
+      <c r="O15" s="63"/>
+      <c r="P15" s="63"/>
+      <c r="Q15" s="63"/>
+      <c r="R15" s="29"/>
+      <c r="S15" s="29"/>
+      <c r="T15" s="29"/>
+      <c r="U15" s="64"/>
+      <c r="V15" s="64"/>
+      <c r="W15" s="64"/>
+      <c r="X15" s="64"/>
+      <c r="Y15" s="64"/>
+      <c r="Z15" s="65"/>
+      <c r="AA15" s="65"/>
+      <c r="AB15" s="65"/>
+      <c r="AC15" s="65"/>
+      <c r="AD15" s="65"/>
+      <c r="AE15" s="66"/>
+      <c r="AF15" s="66"/>
+      <c r="AG15" s="66"/>
+      <c r="AH15" s="67"/>
+      <c r="AI15" s="67"/>
+      <c r="AJ15" s="67"/>
+      <c r="AK15" s="25">
+        <f>SUMIF(E15:AJ15,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:37">
+      <c r="A16" s="30">
+        <v>13</v>
+      </c>
+      <c r="B16" s="143" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="22">
+        <v>46278</v>
+      </c>
+      <c r="D16" s="69"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="70"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="70"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="70"/>
+      <c r="K16" s="70"/>
+      <c r="L16" s="71"/>
+      <c r="M16" s="71"/>
+      <c r="N16" s="71"/>
+      <c r="O16" s="71"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="72"/>
+      <c r="T16" s="72"/>
+      <c r="U16" s="73"/>
+      <c r="V16" s="73"/>
+      <c r="W16" s="73"/>
+      <c r="X16" s="73"/>
+      <c r="Y16" s="73"/>
+      <c r="Z16" s="74"/>
+      <c r="AA16" s="74"/>
+      <c r="AB16" s="74"/>
+      <c r="AC16" s="74"/>
+      <c r="AD16" s="74"/>
+      <c r="AE16" s="75"/>
+      <c r="AF16" s="75"/>
+      <c r="AG16" s="75"/>
+      <c r="AH16" s="76"/>
+      <c r="AI16" s="76"/>
+      <c r="AJ16" s="76"/>
+      <c r="AK16" s="25">
+        <f>SUMIF(E16:AJ16,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:37">
+      <c r="A17" s="30">
+        <v>14</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="22">
+        <v>46279</v>
+      </c>
+      <c r="D17" s="69"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="70"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="70"/>
+      <c r="I17" s="70"/>
+      <c r="J17" s="70"/>
+      <c r="K17" s="70"/>
+      <c r="L17" s="71"/>
+      <c r="M17" s="71"/>
+      <c r="N17" s="71"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="72"/>
+      <c r="S17" s="72"/>
+      <c r="T17" s="72"/>
+      <c r="U17" s="73"/>
+      <c r="V17" s="73"/>
+      <c r="W17" s="73"/>
+      <c r="X17" s="73"/>
+      <c r="Y17" s="73"/>
+      <c r="Z17" s="74"/>
+      <c r="AA17" s="74"/>
+      <c r="AB17" s="74"/>
+      <c r="AC17" s="74"/>
+      <c r="AD17" s="74"/>
+      <c r="AE17" s="75"/>
+      <c r="AF17" s="75"/>
+      <c r="AG17" s="75"/>
+      <c r="AH17" s="76"/>
+      <c r="AI17" s="76"/>
+      <c r="AJ17" s="76"/>
+      <c r="AK17" s="68">
+        <f>SUMIF(E17:AJ17,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:37">
+      <c r="A18" s="30">
+        <v>15</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="22">
+        <v>46280</v>
+      </c>
+      <c r="D18" s="30"/>
+      <c r="E18" s="62"/>
+      <c r="F18" s="62"/>
+      <c r="G18" s="62"/>
+      <c r="H18" s="62"/>
+      <c r="I18" s="62"/>
+      <c r="J18" s="62"/>
+      <c r="K18" s="62"/>
+      <c r="L18" s="63"/>
+      <c r="M18" s="63"/>
+      <c r="N18" s="63"/>
+      <c r="O18" s="63"/>
+      <c r="P18" s="63"/>
+      <c r="Q18" s="63"/>
+      <c r="R18" s="29"/>
+      <c r="S18" s="29"/>
+      <c r="T18" s="29"/>
+      <c r="U18" s="64"/>
+      <c r="V18" s="64"/>
+      <c r="W18" s="64"/>
+      <c r="X18" s="64"/>
+      <c r="Y18" s="64"/>
+      <c r="Z18" s="65"/>
+      <c r="AA18" s="65"/>
+      <c r="AB18" s="65"/>
+      <c r="AC18" s="65"/>
+      <c r="AD18" s="65"/>
+      <c r="AE18" s="66"/>
+      <c r="AF18" s="66"/>
+      <c r="AG18" s="66"/>
+      <c r="AH18" s="67"/>
+      <c r="AI18" s="67"/>
+      <c r="AJ18" s="67"/>
+      <c r="AK18" s="68">
+        <f>SUMIF(E18:AJ18,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:37">
+      <c r="A19" s="69">
+        <v>16</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="22">
+        <v>46281</v>
+      </c>
+      <c r="D19" s="85"/>
+      <c r="E19" s="86"/>
+      <c r="F19" s="86"/>
+      <c r="G19" s="86"/>
+      <c r="H19" s="86"/>
+      <c r="I19" s="86"/>
+      <c r="J19" s="86"/>
+      <c r="K19" s="86"/>
+      <c r="L19" s="87"/>
+      <c r="M19" s="87"/>
+      <c r="N19" s="87"/>
+      <c r="O19" s="87"/>
+      <c r="P19" s="87"/>
+      <c r="Q19" s="87"/>
+      <c r="R19" s="88"/>
+      <c r="S19" s="88"/>
+      <c r="T19" s="88"/>
+      <c r="U19" s="89"/>
+      <c r="V19" s="89"/>
+      <c r="W19" s="89"/>
+      <c r="X19" s="89"/>
+      <c r="Y19" s="89"/>
+      <c r="Z19" s="90"/>
+      <c r="AA19" s="90"/>
+      <c r="AB19" s="90"/>
+      <c r="AC19" s="90"/>
+      <c r="AD19" s="90"/>
+      <c r="AE19" s="91"/>
+      <c r="AF19" s="91"/>
+      <c r="AG19" s="91"/>
+      <c r="AH19" s="92"/>
+      <c r="AI19" s="92"/>
+      <c r="AJ19" s="92"/>
+      <c r="AK19" s="93">
+        <f>SUMIF(E19:AJ19,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:37">
+      <c r="A20" s="69">
+        <v>17</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="22">
+        <v>46282</v>
+      </c>
+      <c r="D20" s="69"/>
+      <c r="E20" s="70"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="70"/>
+      <c r="K20" s="70"/>
+      <c r="L20" s="71"/>
+      <c r="M20" s="71"/>
+      <c r="N20" s="71"/>
+      <c r="O20" s="71"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="72"/>
+      <c r="S20" s="72"/>
+      <c r="T20" s="72"/>
+      <c r="U20" s="73"/>
+      <c r="V20" s="73"/>
+      <c r="W20" s="73"/>
+      <c r="X20" s="73"/>
+      <c r="Y20" s="73"/>
+      <c r="Z20" s="74"/>
+      <c r="AA20" s="74"/>
+      <c r="AB20" s="74"/>
+      <c r="AC20" s="74"/>
+      <c r="AD20" s="74"/>
+      <c r="AE20" s="75"/>
+      <c r="AF20" s="75"/>
+      <c r="AG20" s="75"/>
+      <c r="AH20" s="76"/>
+      <c r="AI20" s="76"/>
+      <c r="AJ20" s="76"/>
+      <c r="AK20" s="93">
+        <f>SUMIF(E20:AJ20,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:37">
+      <c r="A21" s="69">
+        <v>18</v>
+      </c>
+      <c r="B21" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="22">
+        <v>46283</v>
+      </c>
+      <c r="D21" s="69"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70"/>
+      <c r="I21" s="70"/>
+      <c r="J21" s="70"/>
+      <c r="K21" s="70"/>
+      <c r="L21" s="71"/>
+      <c r="M21" s="71"/>
+      <c r="N21" s="71"/>
+      <c r="O21" s="71"/>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71"/>
+      <c r="R21" s="72"/>
+      <c r="S21" s="72"/>
+      <c r="T21" s="72"/>
+      <c r="U21" s="73"/>
+      <c r="V21" s="73"/>
+      <c r="W21" s="73"/>
+      <c r="X21" s="73"/>
+      <c r="Y21" s="73"/>
+      <c r="Z21" s="74"/>
+      <c r="AA21" s="74"/>
+      <c r="AB21" s="74"/>
+      <c r="AC21" s="74"/>
+      <c r="AD21" s="74"/>
+      <c r="AE21" s="75"/>
+      <c r="AF21" s="75"/>
+      <c r="AG21" s="75"/>
+      <c r="AH21" s="76"/>
+      <c r="AI21" s="76"/>
+      <c r="AJ21" s="76"/>
+      <c r="AK21" s="93">
+        <f>SUMIF(E21:AJ21,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:37">
+      <c r="A22" s="30">
+        <v>19</v>
+      </c>
+      <c r="B22" s="143" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="22">
+        <v>46284</v>
+      </c>
+      <c r="D22" s="30"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="62"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="63"/>
+      <c r="M22" s="63"/>
+      <c r="N22" s="63"/>
+      <c r="O22" s="63"/>
+      <c r="P22" s="63"/>
+      <c r="Q22" s="63"/>
+      <c r="R22" s="29"/>
+      <c r="S22" s="29"/>
+      <c r="T22" s="29"/>
+      <c r="U22" s="64"/>
+      <c r="V22" s="64"/>
+      <c r="W22" s="64"/>
+      <c r="X22" s="64"/>
+      <c r="Y22" s="64"/>
+      <c r="Z22" s="65"/>
+      <c r="AA22" s="65"/>
+      <c r="AB22" s="65"/>
+      <c r="AC22" s="65"/>
+      <c r="AD22" s="65"/>
+      <c r="AE22" s="66"/>
+      <c r="AF22" s="66"/>
+      <c r="AG22" s="66"/>
+      <c r="AH22" s="67"/>
+      <c r="AI22" s="67"/>
+      <c r="AJ22" s="67"/>
+      <c r="AK22" s="25">
+        <f>SUMIF(E22:AJ22,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:37">
+      <c r="A23" s="84">
+        <v>20</v>
+      </c>
+      <c r="B23" s="143" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="22">
+        <v>46285</v>
+      </c>
+      <c r="D23" s="85"/>
+      <c r="E23" s="86"/>
+      <c r="F23" s="86"/>
+      <c r="G23" s="86"/>
+      <c r="H23" s="86"/>
+      <c r="I23" s="86"/>
+      <c r="J23" s="86"/>
+      <c r="K23" s="86"/>
+      <c r="L23" s="87"/>
+      <c r="M23" s="87"/>
+      <c r="N23" s="87"/>
+      <c r="O23" s="87"/>
+      <c r="P23" s="87"/>
+      <c r="Q23" s="87"/>
+      <c r="R23" s="88"/>
+      <c r="S23" s="88"/>
+      <c r="T23" s="88"/>
+      <c r="U23" s="89"/>
+      <c r="V23" s="89"/>
+      <c r="W23" s="89"/>
+      <c r="X23" s="89"/>
+      <c r="Y23" s="89"/>
+      <c r="Z23" s="90"/>
+      <c r="AA23" s="90"/>
+      <c r="AB23" s="90"/>
+      <c r="AC23" s="90"/>
+      <c r="AD23" s="90"/>
+      <c r="AE23" s="91"/>
+      <c r="AF23" s="91"/>
+      <c r="AG23" s="91"/>
+      <c r="AH23" s="92"/>
+      <c r="AI23" s="92"/>
+      <c r="AJ23" s="92"/>
+      <c r="AK23" s="95">
+        <f>SUMIF(E23:AJ23,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:37">
+      <c r="A24" s="30">
+        <v>21</v>
+      </c>
+      <c r="B24" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="22">
+        <v>46286</v>
+      </c>
+      <c r="D24" s="96"/>
+      <c r="E24" s="97"/>
+      <c r="F24" s="97"/>
+      <c r="G24" s="97"/>
+      <c r="H24" s="97"/>
+      <c r="I24" s="97"/>
+      <c r="J24" s="97"/>
+      <c r="K24" s="97"/>
+      <c r="L24" s="98"/>
+      <c r="M24" s="98"/>
+      <c r="N24" s="98"/>
+      <c r="O24" s="98"/>
+      <c r="P24" s="98"/>
+      <c r="Q24" s="98"/>
+      <c r="R24" s="99"/>
+      <c r="S24" s="99"/>
+      <c r="T24" s="99"/>
+      <c r="U24" s="100"/>
+      <c r="V24" s="100"/>
+      <c r="W24" s="100"/>
+      <c r="X24" s="100"/>
+      <c r="Y24" s="100"/>
+      <c r="Z24" s="101"/>
+      <c r="AA24" s="101"/>
+      <c r="AB24" s="101"/>
+      <c r="AC24" s="101"/>
+      <c r="AD24" s="101"/>
+      <c r="AE24" s="102"/>
+      <c r="AF24" s="102"/>
+      <c r="AG24" s="102"/>
+      <c r="AH24" s="103"/>
+      <c r="AI24" s="103"/>
+      <c r="AJ24" s="103"/>
+      <c r="AK24" s="104">
+        <f>SUMIF(E24:AJ24,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:37">
+      <c r="A25" s="30">
+        <v>22</v>
+      </c>
+      <c r="B25" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="22">
+        <v>46287</v>
+      </c>
+      <c r="D25" s="69"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="70"/>
+      <c r="K25" s="70"/>
+      <c r="L25" s="71"/>
+      <c r="M25" s="71"/>
+      <c r="N25" s="71"/>
+      <c r="O25" s="71"/>
+      <c r="P25" s="71"/>
+      <c r="Q25" s="71"/>
+      <c r="R25" s="72"/>
+      <c r="S25" s="72"/>
+      <c r="T25" s="72"/>
+      <c r="U25" s="73"/>
+      <c r="V25" s="73"/>
+      <c r="W25" s="73"/>
+      <c r="X25" s="73"/>
+      <c r="Y25" s="73"/>
+      <c r="Z25" s="74"/>
+      <c r="AA25" s="74"/>
+      <c r="AB25" s="74"/>
+      <c r="AC25" s="74"/>
+      <c r="AD25" s="74"/>
+      <c r="AE25" s="75"/>
+      <c r="AF25" s="75"/>
+      <c r="AG25" s="75"/>
+      <c r="AH25" s="76"/>
+      <c r="AI25" s="76"/>
+      <c r="AJ25" s="76"/>
+      <c r="AK25" s="93">
+        <f>SUMIF(E25:AJ25,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:37">
+      <c r="A26" s="69">
+        <v>23</v>
+      </c>
+      <c r="B26" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="22">
+        <v>46288</v>
+      </c>
+      <c r="D26" s="69"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="70"/>
+      <c r="K26" s="70"/>
+      <c r="L26" s="71"/>
+      <c r="M26" s="71"/>
+      <c r="N26" s="71"/>
+      <c r="O26" s="71"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="72"/>
+      <c r="T26" s="72"/>
+      <c r="U26" s="73"/>
+      <c r="V26" s="73"/>
+      <c r="W26" s="73"/>
+      <c r="X26" s="73"/>
+      <c r="Y26" s="73"/>
+      <c r="Z26" s="74"/>
+      <c r="AA26" s="74"/>
+      <c r="AB26" s="74"/>
+      <c r="AC26" s="74"/>
+      <c r="AD26" s="74"/>
+      <c r="AE26" s="75"/>
+      <c r="AF26" s="75"/>
+      <c r="AG26" s="75"/>
+      <c r="AH26" s="76"/>
+      <c r="AI26" s="76"/>
+      <c r="AJ26" s="76"/>
+      <c r="AK26" s="93">
+        <f>SUMIF(E26:AJ26,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:37">
+      <c r="A27" s="69">
+        <v>24</v>
+      </c>
+      <c r="B27" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="22">
+        <v>46289</v>
+      </c>
+      <c r="D27" s="69"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="70"/>
+      <c r="K27" s="70"/>
+      <c r="L27" s="71"/>
+      <c r="M27" s="71"/>
+      <c r="N27" s="71"/>
+      <c r="O27" s="71"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+      <c r="S27" s="72"/>
+      <c r="T27" s="72"/>
+      <c r="U27" s="73"/>
+      <c r="V27" s="73"/>
+      <c r="W27" s="73"/>
+      <c r="X27" s="73"/>
+      <c r="Y27" s="73"/>
+      <c r="Z27" s="74"/>
+      <c r="AA27" s="74"/>
+      <c r="AB27" s="74"/>
+      <c r="AC27" s="74"/>
+      <c r="AD27" s="74"/>
+      <c r="AE27" s="75"/>
+      <c r="AF27" s="75"/>
+      <c r="AG27" s="75"/>
+      <c r="AH27" s="76"/>
+      <c r="AI27" s="76"/>
+      <c r="AJ27" s="76"/>
+      <c r="AK27" s="93">
+        <f>SUMIF(E27:AJ27,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:37">
+      <c r="A28" s="69">
+        <v>25</v>
+      </c>
+      <c r="B28" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="22">
+        <v>46290</v>
+      </c>
+      <c r="D28" s="69"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="70"/>
+      <c r="K28" s="70"/>
+      <c r="L28" s="71"/>
+      <c r="M28" s="71"/>
+      <c r="N28" s="71"/>
+      <c r="O28" s="71"/>
+      <c r="P28" s="71"/>
+      <c r="Q28" s="71"/>
+      <c r="R28" s="72"/>
+      <c r="S28" s="72"/>
+      <c r="T28" s="72"/>
+      <c r="U28" s="73"/>
+      <c r="V28" s="73"/>
+      <c r="W28" s="73"/>
+      <c r="X28" s="73"/>
+      <c r="Y28" s="73"/>
+      <c r="Z28" s="74"/>
+      <c r="AA28" s="74"/>
+      <c r="AB28" s="74"/>
+      <c r="AC28" s="74"/>
+      <c r="AD28" s="74"/>
+      <c r="AE28" s="75"/>
+      <c r="AF28" s="75"/>
+      <c r="AG28" s="75"/>
+      <c r="AH28" s="76"/>
+      <c r="AI28" s="76"/>
+      <c r="AJ28" s="76"/>
+      <c r="AK28" s="93">
+        <f>SUMIF(E28:AJ28,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:37">
+      <c r="A29" s="30">
+        <v>26</v>
+      </c>
+      <c r="B29" s="143" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="22">
+        <v>46291</v>
+      </c>
+      <c r="D29" s="69"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70"/>
+      <c r="J29" s="70"/>
+      <c r="K29" s="70"/>
+      <c r="L29" s="71"/>
+      <c r="M29" s="71"/>
+      <c r="N29" s="71"/>
+      <c r="O29" s="71"/>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
+      <c r="R29" s="72"/>
+      <c r="S29" s="72"/>
+      <c r="T29" s="72"/>
+      <c r="U29" s="73"/>
+      <c r="V29" s="73"/>
+      <c r="W29" s="73"/>
+      <c r="X29" s="73"/>
+      <c r="Y29" s="73"/>
+      <c r="Z29" s="74"/>
+      <c r="AA29" s="74"/>
+      <c r="AB29" s="74"/>
+      <c r="AC29" s="74"/>
+      <c r="AD29" s="74"/>
+      <c r="AE29" s="75"/>
+      <c r="AF29" s="75"/>
+      <c r="AG29" s="75"/>
+      <c r="AH29" s="76"/>
+      <c r="AI29" s="76"/>
+      <c r="AJ29" s="76"/>
+      <c r="AK29" s="93">
+        <f>SUMIF(E29:AJ29,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:37">
+      <c r="A30" s="84">
+        <v>27</v>
+      </c>
+      <c r="B30" s="143" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" s="22">
+        <v>46292</v>
+      </c>
+      <c r="D30" s="30"/>
+      <c r="E30" s="62"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="62"/>
+      <c r="H30" s="62"/>
+      <c r="I30" s="62"/>
+      <c r="J30" s="62"/>
+      <c r="K30" s="62"/>
+      <c r="L30" s="63"/>
+      <c r="M30" s="63"/>
+      <c r="N30" s="63"/>
+      <c r="O30" s="63"/>
+      <c r="P30" s="63"/>
+      <c r="Q30" s="63"/>
+      <c r="R30" s="29"/>
+      <c r="S30" s="29"/>
+      <c r="T30" s="29"/>
+      <c r="U30" s="64"/>
+      <c r="V30" s="64"/>
+      <c r="W30" s="64"/>
+      <c r="X30" s="64"/>
+      <c r="Y30" s="64"/>
+      <c r="Z30" s="65"/>
+      <c r="AA30" s="65"/>
+      <c r="AB30" s="65"/>
+      <c r="AC30" s="65"/>
+      <c r="AD30" s="65"/>
+      <c r="AE30" s="66"/>
+      <c r="AF30" s="66"/>
+      <c r="AG30" s="66"/>
+      <c r="AH30" s="67"/>
+      <c r="AI30" s="67"/>
+      <c r="AJ30" s="67"/>
+      <c r="AK30" s="25">
+        <f>SUMIF(E30:AJ30,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:37">
+      <c r="A31" s="30">
+        <v>28</v>
+      </c>
+      <c r="B31" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" s="22">
+        <v>46293</v>
+      </c>
+      <c r="D31" s="84"/>
+      <c r="E31" s="77"/>
+      <c r="F31" s="77"/>
+      <c r="G31" s="77"/>
+      <c r="H31" s="77"/>
+      <c r="I31" s="77"/>
+      <c r="J31" s="77"/>
+      <c r="K31" s="77"/>
+      <c r="L31" s="78"/>
+      <c r="M31" s="78"/>
+      <c r="N31" s="78"/>
+      <c r="O31" s="78"/>
+      <c r="P31" s="78"/>
+      <c r="Q31" s="78"/>
+      <c r="R31" s="79"/>
+      <c r="S31" s="79"/>
+      <c r="T31" s="79"/>
+      <c r="U31" s="80"/>
+      <c r="V31" s="80"/>
+      <c r="W31" s="80"/>
+      <c r="X31" s="80"/>
+      <c r="Y31" s="80"/>
+      <c r="Z31" s="81"/>
+      <c r="AA31" s="81"/>
+      <c r="AB31" s="81"/>
+      <c r="AC31" s="81"/>
+      <c r="AD31" s="81"/>
+      <c r="AE31" s="82"/>
+      <c r="AF31" s="82"/>
+      <c r="AG31" s="82"/>
+      <c r="AH31" s="83"/>
+      <c r="AI31" s="83"/>
+      <c r="AJ31" s="83"/>
+      <c r="AK31" s="94">
+        <f>SUMIF(E31:AJ31,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:37">
+      <c r="A32" s="30">
+        <v>29</v>
+      </c>
+      <c r="B32" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="22">
+        <v>46294</v>
+      </c>
+      <c r="D32" s="30"/>
+      <c r="E32" s="62"/>
+      <c r="F32" s="62"/>
+      <c r="G32" s="62"/>
+      <c r="H32" s="62"/>
+      <c r="I32" s="62"/>
+      <c r="J32" s="62"/>
+      <c r="K32" s="62"/>
+      <c r="L32" s="63"/>
+      <c r="M32" s="63"/>
+      <c r="N32" s="63"/>
+      <c r="O32" s="63"/>
+      <c r="P32" s="63"/>
+      <c r="Q32" s="63"/>
+      <c r="R32" s="29"/>
+      <c r="S32" s="29"/>
+      <c r="T32" s="29"/>
+      <c r="U32" s="64"/>
+      <c r="V32" s="64"/>
+      <c r="W32" s="64"/>
+      <c r="X32" s="64"/>
+      <c r="Y32" s="64"/>
+      <c r="Z32" s="65"/>
+      <c r="AA32" s="65"/>
+      <c r="AB32" s="65"/>
+      <c r="AC32" s="65"/>
+      <c r="AD32" s="65"/>
+      <c r="AE32" s="66"/>
+      <c r="AF32" s="66"/>
+      <c r="AG32" s="66"/>
+      <c r="AH32" s="67"/>
+      <c r="AI32" s="67"/>
+      <c r="AJ32" s="67"/>
+      <c r="AK32" s="25">
+        <f>SUMIF(E32:AJ32,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:37">
+      <c r="A33" s="30">
+        <v>30</v>
+      </c>
+      <c r="B33" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="22">
+        <v>46295</v>
+      </c>
+      <c r="D33" s="30"/>
+      <c r="E33" s="62"/>
+      <c r="F33" s="62"/>
+      <c r="G33" s="62"/>
+      <c r="H33" s="62"/>
+      <c r="I33" s="62"/>
+      <c r="J33" s="62"/>
+      <c r="K33" s="62"/>
+      <c r="L33" s="63"/>
+      <c r="M33" s="63"/>
+      <c r="N33" s="63"/>
+      <c r="O33" s="63"/>
+      <c r="P33" s="63"/>
+      <c r="Q33" s="63"/>
+      <c r="R33" s="29"/>
+      <c r="S33" s="29"/>
+      <c r="T33" s="29"/>
+      <c r="U33" s="64"/>
+      <c r="V33" s="64"/>
+      <c r="W33" s="64"/>
+      <c r="X33" s="64"/>
+      <c r="Y33" s="64"/>
+      <c r="Z33" s="65"/>
+      <c r="AA33" s="65"/>
+      <c r="AB33" s="65"/>
+      <c r="AC33" s="65"/>
+      <c r="AD33" s="65"/>
+      <c r="AE33" s="66"/>
+      <c r="AF33" s="66"/>
+      <c r="AG33" s="66"/>
+      <c r="AH33" s="67"/>
+      <c r="AI33" s="67"/>
+      <c r="AJ33" s="67"/>
+      <c r="AK33" s="25">
+        <f>SUMIF(E33:AJ33,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:37" ht="30" customHeight="1">
+      <c r="A34" s="122" t="s">
+        <v>77</v>
+      </c>
+      <c r="B34" s="123"/>
+      <c r="C34" s="123"/>
+      <c r="D34" s="124"/>
+      <c r="E34" s="106">
+        <f>COUNTA(E4:E33)</f>
+        <v>1</v>
+      </c>
+      <c r="F34" s="106">
+        <f>COUNTA(F4:F33)</f>
+        <v>1</v>
+      </c>
+      <c r="G34" s="106">
+        <f>COUNTA(G4:G33)</f>
+        <v>1</v>
+      </c>
+      <c r="H34" s="106">
+        <f>COUNTA(H4:H33)</f>
+        <v>1</v>
+      </c>
+      <c r="I34" s="106">
+        <f>COUNTA(I4:I33)</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="106">
+        <f>COUNTA(J4:J33)</f>
+        <v>0</v>
+      </c>
+      <c r="K34" s="106">
+        <f>COUNTA(K4:K33)</f>
+        <v>0</v>
+      </c>
+      <c r="L34" s="63">
+        <f>COUNTA(L4:L33)</f>
+        <v>1</v>
+      </c>
+      <c r="M34" s="63">
+        <f>COUNTA(M4:M33)</f>
+        <v>1</v>
+      </c>
+      <c r="N34" s="63">
+        <f>COUNTA(N4:N33)</f>
+        <v>0</v>
+      </c>
+      <c r="O34" s="63">
+        <f>COUNTA(O4:O33)</f>
+        <v>0</v>
+      </c>
+      <c r="P34" s="63">
+        <f>COUNTA(P4:P33)</f>
+        <v>0</v>
+      </c>
+      <c r="Q34" s="63">
+        <f>COUNTA(Q4:Q33)</f>
+        <v>0</v>
+      </c>
+      <c r="R34" s="29">
+        <f>COUNTA(R4:R33)</f>
+        <v>0</v>
+      </c>
+      <c r="S34" s="29">
+        <f>COUNTA(S4:S33)</f>
+        <v>0</v>
+      </c>
+      <c r="T34" s="29">
+        <f>COUNTA(T4:T33)</f>
+        <v>0</v>
+      </c>
+      <c r="U34" s="64">
+        <f>COUNTA(U4:U33)</f>
+        <v>0</v>
+      </c>
+      <c r="V34" s="64">
+        <f>COUNTA(V4:V33)</f>
+        <v>0</v>
+      </c>
+      <c r="W34" s="64">
+        <f>COUNTA(W4:W33)</f>
+        <v>0</v>
+      </c>
+      <c r="X34" s="64">
+        <f>COUNTA(X4:X33)</f>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="64">
+        <f>COUNTA(Y4:Y33)</f>
+        <v>0</v>
+      </c>
+      <c r="Z34" s="65">
+        <f>COUNTA(Z4:Z33)</f>
+        <v>0</v>
+      </c>
+      <c r="AA34" s="65">
+        <f>COUNTA(AA4:AA33)</f>
+        <v>0</v>
+      </c>
+      <c r="AB34" s="65">
+        <f>COUNTA(AB4:AB33)</f>
+        <v>0</v>
+      </c>
+      <c r="AC34" s="65">
+        <f>COUNTA(AC4:AC33)</f>
+        <v>0</v>
+      </c>
+      <c r="AD34" s="65">
+        <f>COUNTA(AD4:AD33)</f>
+        <v>0</v>
+      </c>
+      <c r="AE34" s="66">
+        <f>COUNTA(AE4:AE33)</f>
+        <v>0</v>
+      </c>
+      <c r="AF34" s="66">
+        <f>COUNTA(AF4:AF33)</f>
+        <v>0</v>
+      </c>
+      <c r="AG34" s="66">
+        <f>COUNTA(AG4:AG33)</f>
+        <v>0</v>
+      </c>
+      <c r="AH34" s="67">
+        <f>COUNTA(AH4:AH33)</f>
+        <v>0</v>
+      </c>
+      <c r="AI34" s="67">
+        <f>COUNTA(AI4:AI33)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="67">
+        <f>COUNTA(AJ4:AJ33)</f>
+        <v>0</v>
+      </c>
+      <c r="AK34" s="25"/>
+    </row>
+    <row r="35" spans="1:37" ht="30" customHeight="1">
+      <c r="AG35" s="119" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH35" s="120"/>
+      <c r="AI35" s="120"/>
+      <c r="AJ35" s="121"/>
+      <c r="AK35" s="107">
+        <f>ROUND(AVERAGE(AK4:AK33),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:37" ht="30" customHeight="1">
+      <c r="AG36" s="119" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH36" s="120"/>
+      <c r="AI36" s="120"/>
+      <c r="AJ36" s="121"/>
+      <c r="AK36" s="107">
+        <f>MAX(AK4:AK33)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:37" ht="30" customHeight="1">
+      <c r="AG37" s="119" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH37" s="120"/>
+      <c r="AI37" s="120"/>
+      <c r="AJ37" s="121"/>
+      <c r="AK37" s="107">
+        <f>MIN(AK4:AK33)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:37" ht="30" customHeight="1">
+      <c r="AG38" s="119" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH38" s="120"/>
+      <c r="AI38" s="120"/>
+      <c r="AJ38" s="121"/>
+      <c r="AK38" s="107">
+        <f>COUNTIF(AK4:AK33, "&gt;"&amp;AK35)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:37" ht="30" customHeight="1">
+      <c r="AG39" s="119" t="s">
+        <v>82</v>
+      </c>
+      <c r="AH39" s="120"/>
+      <c r="AI39" s="120"/>
+      <c r="AJ39" s="121"/>
+      <c r="AK39" s="107">
+        <f>COUNTIF(AK4:AK33, "&lt;"&amp;AK35)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:37" ht="30" customHeight="1">
+      <c r="AG40" s="119" t="s">
+        <v>83</v>
+      </c>
+      <c r="AH40" s="120"/>
+      <c r="AI40" s="120"/>
+      <c r="AJ40" s="121"/>
+      <c r="AK40" s="107">
+        <f>COUNTIF(AK4:AK33, "&gt;"&amp;20)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:37" ht="30" customHeight="1">
+      <c r="AG41" s="119" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH41" s="120"/>
+      <c r="AI41" s="120"/>
+      <c r="AJ41" s="121"/>
+      <c r="AK41" s="107">
+        <f>COUNTIF(AK4:AK33, "&lt;"&amp;20)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="1:37" ht="30" customHeight="1"/>
+    <row r="43" spans="1:37" ht="30" customHeight="1"/>
+    <row r="44" spans="1:37" ht="30" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="AG37:AJ37"/>
+    <mergeCell ref="AG38:AJ38"/>
+    <mergeCell ref="AG39:AJ39"/>
+    <mergeCell ref="AG40:AJ40"/>
+    <mergeCell ref="AG41:AJ41"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="AE1:AG1"/>
+    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="AK1:AK3"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="AG35:AJ35"/>
+    <mergeCell ref="AG36:AJ36"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="E1:K1"/>
+    <mergeCell ref="L1:Q1"/>
+    <mergeCell ref="U1:Y1"/>
+    <mergeCell ref="Z1:AD1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E4:AJ33 L34:Q34">
+    <cfRule type="expression" dxfId="6" priority="7">
+      <formula>E4="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R34:T34">
+    <cfRule type="expression" dxfId="5" priority="5">
+      <formula>R34="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U34:Y34">
+    <cfRule type="expression" dxfId="4" priority="4">
+      <formula>U34="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z34:AD34">
+    <cfRule type="expression" dxfId="3" priority="3">
+      <formula>Z34="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE34:AG34">
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>AE34="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH34:AJ34">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>AH34="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+</worksheet>
 </file>
--- a/Другое/study_chart.xlsx
+++ b/Другое/study_chart.xlsx
@@ -829,8 +829,46 @@
 </comments>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Собянин Евгений Андреевич (new)</author>
+  </authors>
+  <commentList>
+    <comment ref="AH5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Выполнить 60% поставленных на работе задач
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AH6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Не отвлекаться на работе, работа без остановки</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="88">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -1092,6 +1130,9 @@
   <si>
     <t>Курс по Figma</t>
   </si>
+  <si>
+    <t>87.7</t>
+  </si>
 </sst>
 </file>
 
@@ -1100,7 +1141,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mmm"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1358,6 +1399,19 @@
       <color theme="1"/>
       <name val="Tw Cen MT"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="36">
@@ -2269,6 +2323,9 @@
     <xf numFmtId="0" fontId="17" fillId="21" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="27" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2296,6 +2353,60 @@
     <xf numFmtId="0" fontId="19" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2314,84 +2425,20 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFB6EA86"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2839,18 +2886,18 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:17" ht="45" customHeight="1">
-      <c r="H9" s="110" t="s">
+      <c r="H9" s="111" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="111"/>
-      <c r="J9" s="111"/>
-      <c r="K9" s="111"/>
-      <c r="L9" s="111"/>
-      <c r="M9" s="111"/>
-      <c r="N9" s="111"/>
-      <c r="O9" s="111"/>
-      <c r="P9" s="111"/>
-      <c r="Q9" s="112"/>
+      <c r="I9" s="112"/>
+      <c r="J9" s="112"/>
+      <c r="K9" s="112"/>
+      <c r="L9" s="112"/>
+      <c r="M9" s="112"/>
+      <c r="N9" s="112"/>
+      <c r="O9" s="112"/>
+      <c r="P9" s="112"/>
+      <c r="Q9" s="113"/>
     </row>
     <row r="10" spans="8:17" ht="30" customHeight="1">
       <c r="H10" s="55" t="s">
@@ -3119,11 +3166,11 @@
       <c r="Q21" s="60"/>
     </row>
     <row r="22" spans="8:17" ht="15.75">
-      <c r="H22" s="113" t="s">
+      <c r="H22" s="114" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="114"/>
-      <c r="J22" s="115"/>
+      <c r="I22" s="115"/>
+      <c r="J22" s="116"/>
       <c r="K22" s="61">
         <f>COUNTA(K11:K21)</f>
         <v>6</v>
@@ -3159,12 +3206,12 @@
     <mergeCell ref="H22:J22"/>
   </mergeCells>
   <conditionalFormatting sqref="K22:Q22">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>Q22="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11:Q21">
-    <cfRule type="expression" dxfId="16" priority="2">
+    <cfRule type="expression" dxfId="15" priority="2">
       <formula>Q11="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3200,39 +3247,39 @@
   </cols>
   <sheetData>
     <row r="9" spans="8:38" ht="45" customHeight="1">
-      <c r="H9" s="116" t="s">
+      <c r="H9" s="117" t="s">
         <v>0</v>
       </c>
-      <c r="I9" s="117"/>
-      <c r="J9" s="117"/>
-      <c r="K9" s="117"/>
-      <c r="L9" s="117"/>
-      <c r="M9" s="117"/>
-      <c r="N9" s="117"/>
-      <c r="O9" s="117"/>
-      <c r="P9" s="117"/>
-      <c r="Q9" s="117"/>
-      <c r="R9" s="117"/>
-      <c r="S9" s="117"/>
-      <c r="T9" s="117"/>
-      <c r="U9" s="117"/>
-      <c r="V9" s="117"/>
-      <c r="W9" s="117"/>
-      <c r="X9" s="117"/>
-      <c r="Y9" s="117"/>
-      <c r="Z9" s="117"/>
-      <c r="AA9" s="117"/>
-      <c r="AB9" s="117"/>
-      <c r="AC9" s="117"/>
-      <c r="AD9" s="117"/>
-      <c r="AE9" s="117"/>
-      <c r="AF9" s="117"/>
-      <c r="AG9" s="117"/>
-      <c r="AH9" s="117"/>
-      <c r="AI9" s="117"/>
-      <c r="AJ9" s="117"/>
-      <c r="AK9" s="117"/>
-      <c r="AL9" s="117"/>
+      <c r="I9" s="118"/>
+      <c r="J9" s="118"/>
+      <c r="K9" s="118"/>
+      <c r="L9" s="118"/>
+      <c r="M9" s="118"/>
+      <c r="N9" s="118"/>
+      <c r="O9" s="118"/>
+      <c r="P9" s="118"/>
+      <c r="Q9" s="118"/>
+      <c r="R9" s="118"/>
+      <c r="S9" s="118"/>
+      <c r="T9" s="118"/>
+      <c r="U9" s="118"/>
+      <c r="V9" s="118"/>
+      <c r="W9" s="118"/>
+      <c r="X9" s="118"/>
+      <c r="Y9" s="118"/>
+      <c r="Z9" s="118"/>
+      <c r="AA9" s="118"/>
+      <c r="AB9" s="118"/>
+      <c r="AC9" s="118"/>
+      <c r="AD9" s="118"/>
+      <c r="AE9" s="118"/>
+      <c r="AF9" s="118"/>
+      <c r="AG9" s="118"/>
+      <c r="AH9" s="118"/>
+      <c r="AI9" s="118"/>
+      <c r="AJ9" s="118"/>
+      <c r="AK9" s="118"/>
+      <c r="AL9" s="118"/>
     </row>
     <row r="10" spans="8:38" ht="30" customHeight="1">
       <c r="H10" s="32" t="s">
@@ -4912,11 +4959,11 @@
       </c>
     </row>
     <row r="42" spans="8:38" ht="15.75">
-      <c r="H42" s="118" t="s">
+      <c r="H42" s="119" t="s">
         <v>19</v>
       </c>
-      <c r="I42" s="118"/>
-      <c r="J42" s="118"/>
+      <c r="I42" s="119"/>
+      <c r="J42" s="119"/>
       <c r="K42" s="32">
         <f>COUNTA(K11:K41)</f>
         <v>6</v>
@@ -5030,12 +5077,12 @@
     <mergeCell ref="H42:J42"/>
   </mergeCells>
   <conditionalFormatting sqref="AL42">
-    <cfRule type="expression" dxfId="15" priority="10">
+    <cfRule type="expression" dxfId="14" priority="10">
       <formula>AU42="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K11:AK41">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>K11&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5081,66 +5128,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="130"/>
-      <c r="B1" s="131"/>
-      <c r="C1" s="132"/>
+      <c r="A1" s="125"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="127"/>
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="136" t="s">
+      <c r="E1" s="131" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
-      <c r="H1" s="136"/>
-      <c r="I1" s="136"/>
-      <c r="J1" s="136"/>
-      <c r="K1" s="136"/>
-      <c r="L1" s="137" t="s">
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="132" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="137"/>
-      <c r="N1" s="137"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="137"/>
-      <c r="R1" s="137"/>
-      <c r="S1" s="138" t="s">
+      <c r="M1" s="132"/>
+      <c r="N1" s="132"/>
+      <c r="O1" s="132"/>
+      <c r="P1" s="132"/>
+      <c r="Q1" s="132"/>
+      <c r="R1" s="132"/>
+      <c r="S1" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="T1" s="138"/>
-      <c r="U1" s="139" t="s">
+      <c r="T1" s="133"/>
+      <c r="U1" s="134" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="140"/>
-      <c r="W1" s="140"/>
-      <c r="X1" s="140"/>
-      <c r="Y1" s="141"/>
-      <c r="Z1" s="142" t="s">
+      <c r="V1" s="135"/>
+      <c r="W1" s="135"/>
+      <c r="X1" s="135"/>
+      <c r="Y1" s="136"/>
+      <c r="Z1" s="137" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="142"/>
-      <c r="AB1" s="142"/>
-      <c r="AC1" s="142"/>
-      <c r="AD1" s="142"/>
-      <c r="AE1" s="125" t="s">
+      <c r="AA1" s="137"/>
+      <c r="AB1" s="137"/>
+      <c r="AC1" s="137"/>
+      <c r="AD1" s="137"/>
+      <c r="AE1" s="120" t="s">
         <v>42</v>
       </c>
-      <c r="AF1" s="125"/>
-      <c r="AG1" s="125"/>
-      <c r="AH1" s="126" t="s">
+      <c r="AF1" s="120"/>
+      <c r="AG1" s="120"/>
+      <c r="AH1" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="AI1" s="126"/>
-      <c r="AJ1" s="126"/>
-      <c r="AK1" s="127" t="s">
+      <c r="AI1" s="121"/>
+      <c r="AJ1" s="121"/>
+      <c r="AK1" s="122" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1">
-      <c r="A2" s="133"/>
-      <c r="B2" s="134"/>
-      <c r="C2" s="135"/>
+      <c r="A2" s="128"/>
+      <c r="B2" s="129"/>
+      <c r="C2" s="130"/>
       <c r="D2" s="5" t="s">
         <v>44</v>
       </c>
@@ -5234,7 +5281,7 @@
       <c r="AH2" s="12"/>
       <c r="AI2" s="12"/>
       <c r="AJ2" s="12"/>
-      <c r="AK2" s="128"/>
+      <c r="AK2" s="123"/>
     </row>
     <row r="3" spans="1:37">
       <c r="A3" s="13" t="s">
@@ -5345,7 +5392,7 @@
       <c r="AJ3" s="20">
         <v>2</v>
       </c>
-      <c r="AK3" s="129"/>
+      <c r="AK3" s="124"/>
     </row>
     <row r="4" spans="1:37">
       <c r="A4" s="21">
@@ -7396,12 +7443,12 @@
       </c>
     </row>
     <row r="35" spans="1:37" ht="30" customHeight="1">
-      <c r="A35" s="122" t="s">
+      <c r="A35" s="141" t="s">
         <v>77</v>
       </c>
-      <c r="B35" s="123"/>
-      <c r="C35" s="123"/>
-      <c r="D35" s="124"/>
+      <c r="B35" s="142"/>
+      <c r="C35" s="142"/>
+      <c r="D35" s="143"/>
       <c r="E35" s="106">
         <f>COUNTA(E4:E34)</f>
         <v>14</v>
@@ -7533,84 +7580,84 @@
       <c r="AK35" s="25"/>
     </row>
     <row r="36" spans="1:37" ht="30" customHeight="1">
-      <c r="AG36" s="119" t="s">
+      <c r="AG36" s="138" t="s">
         <v>78</v>
       </c>
-      <c r="AH36" s="120"/>
-      <c r="AI36" s="120"/>
-      <c r="AJ36" s="121"/>
+      <c r="AH36" s="139"/>
+      <c r="AI36" s="139"/>
+      <c r="AJ36" s="140"/>
       <c r="AK36" s="107">
         <f>ROUND(AVERAGE(AK4:AK34),0)</f>
         <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:37" ht="30" customHeight="1">
-      <c r="AG37" s="119" t="s">
+      <c r="AG37" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="AH37" s="120"/>
-      <c r="AI37" s="120"/>
-      <c r="AJ37" s="121"/>
+      <c r="AH37" s="139"/>
+      <c r="AI37" s="139"/>
+      <c r="AJ37" s="140"/>
       <c r="AK37" s="107">
         <f>MAX(AK4:AK34)</f>
         <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:37" ht="30" customHeight="1">
-      <c r="AG38" s="119" t="s">
+      <c r="AG38" s="138" t="s">
         <v>80</v>
       </c>
-      <c r="AH38" s="120"/>
-      <c r="AI38" s="120"/>
-      <c r="AJ38" s="121"/>
+      <c r="AH38" s="139"/>
+      <c r="AI38" s="139"/>
+      <c r="AJ38" s="140"/>
       <c r="AK38" s="107">
         <f>MIN(AK4:AK34)</f>
         <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:37" ht="30" customHeight="1">
-      <c r="AG39" s="119" t="s">
+      <c r="AG39" s="138" t="s">
         <v>81</v>
       </c>
-      <c r="AH39" s="120"/>
-      <c r="AI39" s="120"/>
-      <c r="AJ39" s="121"/>
+      <c r="AH39" s="139"/>
+      <c r="AI39" s="139"/>
+      <c r="AJ39" s="140"/>
       <c r="AK39" s="107">
         <f>COUNTIF(AK4:AK34, "&gt;"&amp;AK36)</f>
         <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:37" ht="30" customHeight="1">
-      <c r="AG40" s="119" t="s">
+      <c r="AG40" s="138" t="s">
         <v>82</v>
       </c>
-      <c r="AH40" s="120"/>
-      <c r="AI40" s="120"/>
-      <c r="AJ40" s="121"/>
+      <c r="AH40" s="139"/>
+      <c r="AI40" s="139"/>
+      <c r="AJ40" s="140"/>
       <c r="AK40" s="107">
         <f>COUNTIF(AK4:AK34, "&lt;"&amp;AK36)</f>
         <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:37" ht="30" customHeight="1">
-      <c r="AG41" s="119" t="s">
+      <c r="AG41" s="138" t="s">
         <v>83</v>
       </c>
-      <c r="AH41" s="120"/>
-      <c r="AI41" s="120"/>
-      <c r="AJ41" s="121"/>
+      <c r="AH41" s="139"/>
+      <c r="AI41" s="139"/>
+      <c r="AJ41" s="140"/>
       <c r="AK41" s="107">
         <f>COUNTIF(AK4:AK34, "&gt;"&amp;20)</f>
         <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:37" ht="30" customHeight="1">
-      <c r="AG42" s="119" t="s">
+      <c r="AG42" s="138" t="s">
         <v>84</v>
       </c>
-      <c r="AH42" s="120"/>
-      <c r="AI42" s="120"/>
-      <c r="AJ42" s="121"/>
+      <c r="AH42" s="139"/>
+      <c r="AI42" s="139"/>
+      <c r="AJ42" s="140"/>
       <c r="AK42" s="107">
         <f>COUNTIF(AK4:AK34, "&lt;"&amp;20)</f>
         <v>21</v>
@@ -7621,6 +7668,14 @@
     <row r="45" spans="1:37" ht="30" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="AG40:AJ40"/>
+    <mergeCell ref="AG41:AJ41"/>
+    <mergeCell ref="AG42:AJ42"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="AG36:AJ36"/>
+    <mergeCell ref="AG37:AJ37"/>
+    <mergeCell ref="AG38:AJ38"/>
+    <mergeCell ref="AG39:AJ39"/>
     <mergeCell ref="AE1:AG1"/>
     <mergeCell ref="AH1:AJ1"/>
     <mergeCell ref="AK1:AK3"/>
@@ -7630,47 +7685,39 @@
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="U1:Y1"/>
     <mergeCell ref="Z1:AD1"/>
-    <mergeCell ref="AG40:AJ40"/>
-    <mergeCell ref="AG41:AJ41"/>
-    <mergeCell ref="AG42:AJ42"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="AG36:AJ36"/>
-    <mergeCell ref="AG37:AJ37"/>
-    <mergeCell ref="AG38:AJ38"/>
-    <mergeCell ref="AG39:AJ39"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:AJ34">
-    <cfRule type="expression" dxfId="13" priority="7">
+    <cfRule type="expression" dxfId="12" priority="7">
       <formula>E4="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L35:R35">
-    <cfRule type="expression" dxfId="12" priority="6">
+    <cfRule type="expression" dxfId="11" priority="6">
       <formula>L35="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S35:T35">
-    <cfRule type="expression" dxfId="11" priority="5">
+    <cfRule type="expression" dxfId="10" priority="5">
       <formula>S35="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U35:Y35">
-    <cfRule type="expression" dxfId="10" priority="4">
+    <cfRule type="expression" dxfId="9" priority="4">
       <formula>U35="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z35:AD35">
-    <cfRule type="expression" dxfId="9" priority="3">
+    <cfRule type="expression" dxfId="8" priority="3">
       <formula>Z35="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE35:AG35">
-    <cfRule type="expression" dxfId="8" priority="2">
+    <cfRule type="expression" dxfId="7" priority="2">
       <formula>AE35="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH35:AJ35">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>AH35="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7715,66 +7762,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="130"/>
-      <c r="B1" s="131"/>
-      <c r="C1" s="132"/>
+      <c r="A1" s="125"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="127"/>
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="136" t="s">
+      <c r="E1" s="131" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
-      <c r="H1" s="136"/>
-      <c r="I1" s="136"/>
-      <c r="J1" s="136"/>
-      <c r="K1" s="136"/>
-      <c r="L1" s="137" t="s">
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="132" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="137"/>
-      <c r="N1" s="137"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="137"/>
+      <c r="M1" s="132"/>
+      <c r="N1" s="132"/>
+      <c r="O1" s="132"/>
+      <c r="P1" s="132"/>
+      <c r="Q1" s="132"/>
       <c r="R1" s="144" t="s">
         <v>39</v>
       </c>
-      <c r="S1" s="146"/>
-      <c r="T1" s="145"/>
-      <c r="U1" s="139" t="s">
+      <c r="S1" s="145"/>
+      <c r="T1" s="146"/>
+      <c r="U1" s="134" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="140"/>
-      <c r="W1" s="140"/>
-      <c r="X1" s="140"/>
-      <c r="Y1" s="141"/>
-      <c r="Z1" s="142" t="s">
+      <c r="V1" s="135"/>
+      <c r="W1" s="135"/>
+      <c r="X1" s="135"/>
+      <c r="Y1" s="136"/>
+      <c r="Z1" s="137" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="142"/>
-      <c r="AB1" s="142"/>
-      <c r="AC1" s="142"/>
-      <c r="AD1" s="142"/>
-      <c r="AE1" s="125" t="s">
+      <c r="AA1" s="137"/>
+      <c r="AB1" s="137"/>
+      <c r="AC1" s="137"/>
+      <c r="AD1" s="137"/>
+      <c r="AE1" s="120" t="s">
         <v>42</v>
       </c>
-      <c r="AF1" s="125"/>
-      <c r="AG1" s="125"/>
-      <c r="AH1" s="126" t="s">
+      <c r="AF1" s="120"/>
+      <c r="AG1" s="120"/>
+      <c r="AH1" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="AI1" s="126"/>
-      <c r="AJ1" s="126"/>
-      <c r="AK1" s="127" t="s">
+      <c r="AI1" s="121"/>
+      <c r="AJ1" s="121"/>
+      <c r="AK1" s="122" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:37" s="2" customFormat="1" ht="45" customHeight="1">
-      <c r="A2" s="133"/>
-      <c r="B2" s="134"/>
-      <c r="C2" s="135"/>
+      <c r="A2" s="128"/>
+      <c r="B2" s="129"/>
+      <c r="C2" s="130"/>
       <c r="D2" s="5" t="s">
         <v>44</v>
       </c>
@@ -7868,7 +7915,7 @@
       <c r="AH2" s="12"/>
       <c r="AI2" s="12"/>
       <c r="AJ2" s="12"/>
-      <c r="AK2" s="128"/>
+      <c r="AK2" s="123"/>
     </row>
     <row r="3" spans="1:37">
       <c r="A3" s="13" t="s">
@@ -7979,7 +8026,7 @@
       <c r="AJ3" s="20">
         <v>1</v>
       </c>
-      <c r="AK3" s="129"/>
+      <c r="AK3" s="124"/>
     </row>
     <row r="4" spans="1:37">
       <c r="A4" s="30">
@@ -8015,8 +8062,12 @@
       <c r="M4" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="N4" s="63"/>
-      <c r="O4" s="63"/>
+      <c r="N4" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="O4" s="63" t="s">
+        <v>12</v>
+      </c>
       <c r="P4" s="63"/>
       <c r="Q4" s="63"/>
       <c r="R4" s="24"/>
@@ -8027,11 +8078,17 @@
       <c r="W4" s="64"/>
       <c r="X4" s="64"/>
       <c r="Y4" s="64"/>
-      <c r="Z4" s="65"/>
+      <c r="Z4" s="65" t="s">
+        <v>12</v>
+      </c>
       <c r="AA4" s="65"/>
       <c r="AB4" s="65"/>
-      <c r="AC4" s="65"/>
-      <c r="AD4" s="65"/>
+      <c r="AC4" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD4" s="65" t="s">
+        <v>12</v>
+      </c>
       <c r="AE4" s="66"/>
       <c r="AF4" s="66"/>
       <c r="AG4" s="66"/>
@@ -8039,8 +8096,8 @@
       <c r="AI4" s="67"/>
       <c r="AJ4" s="67"/>
       <c r="AK4" s="25">
-        <f>SUMIF(E4:AJ4,"&lt;&gt;",$E$3:$AJ$3)</f>
-        <v>10</v>
+        <f t="shared" ref="AK4:AK33" si="0">SUMIF(E4:AJ4,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -8053,7 +8110,9 @@
       <c r="C5" s="22">
         <v>46267</v>
       </c>
-      <c r="D5" s="30"/>
+      <c r="D5" s="30" t="s">
+        <v>87</v>
+      </c>
       <c r="E5" s="62"/>
       <c r="F5" s="62"/>
       <c r="G5" s="62"/>
@@ -8062,9 +8121,13 @@
       <c r="J5" s="62"/>
       <c r="K5" s="62"/>
       <c r="L5" s="63"/>
-      <c r="M5" s="63"/>
+      <c r="M5" s="63" t="s">
+        <v>12</v>
+      </c>
       <c r="N5" s="63"/>
-      <c r="O5" s="63"/>
+      <c r="O5" s="63" t="s">
+        <v>12</v>
+      </c>
       <c r="P5" s="63"/>
       <c r="Q5" s="63"/>
       <c r="R5" s="24"/>
@@ -8079,7 +8142,9 @@
       <c r="AA5" s="65"/>
       <c r="AB5" s="65"/>
       <c r="AC5" s="65"/>
-      <c r="AD5" s="65"/>
+      <c r="AD5" s="65" t="s">
+        <v>12</v>
+      </c>
       <c r="AE5" s="66"/>
       <c r="AF5" s="66"/>
       <c r="AG5" s="66"/>
@@ -8087,8 +8152,8 @@
       <c r="AI5" s="67"/>
       <c r="AJ5" s="67"/>
       <c r="AK5" s="25">
-        <f>SUMIF(E5:AJ5,"&lt;&gt;",$E$3:$AJ$3)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -8101,17 +8166,27 @@
       <c r="C6" s="22">
         <v>46268</v>
       </c>
-      <c r="D6" s="30"/>
+      <c r="D6" s="30" t="s">
+        <v>62</v>
+      </c>
       <c r="E6" s="62"/>
       <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
+      <c r="G6" s="62" t="s">
+        <v>12</v>
+      </c>
       <c r="H6" s="62"/>
       <c r="I6" s="62"/>
       <c r="J6" s="62"/>
       <c r="K6" s="62"/>
-      <c r="L6" s="63"/>
-      <c r="M6" s="63"/>
-      <c r="N6" s="63"/>
+      <c r="L6" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="M6" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="N6" s="63" t="s">
+        <v>12</v>
+      </c>
       <c r="O6" s="63"/>
       <c r="P6" s="63"/>
       <c r="Q6" s="63"/>
@@ -8127,16 +8202,20 @@
       <c r="AA6" s="65"/>
       <c r="AB6" s="65"/>
       <c r="AC6" s="65"/>
-      <c r="AD6" s="65"/>
+      <c r="AD6" s="65" t="s">
+        <v>12</v>
+      </c>
       <c r="AE6" s="66"/>
       <c r="AF6" s="66"/>
       <c r="AG6" s="66"/>
-      <c r="AH6" s="67"/>
+      <c r="AH6" s="67" t="s">
+        <v>12</v>
+      </c>
       <c r="AI6" s="67"/>
       <c r="AJ6" s="67"/>
       <c r="AK6" s="25">
-        <f>SUMIF(E6:AJ6,"&lt;&gt;",$E$3:$AJ$3)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -8157,8 +8236,12 @@
       <c r="I7" s="62"/>
       <c r="J7" s="62"/>
       <c r="K7" s="62"/>
-      <c r="L7" s="63"/>
-      <c r="M7" s="63"/>
+      <c r="L7" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="M7" s="63" t="s">
+        <v>12</v>
+      </c>
       <c r="N7" s="63"/>
       <c r="O7" s="63"/>
       <c r="P7" s="63"/>
@@ -8177,21 +8260,23 @@
       <c r="AC7" s="65"/>
       <c r="AD7" s="65"/>
       <c r="AE7" s="66"/>
-      <c r="AF7" s="66"/>
+      <c r="AF7" s="66" t="s">
+        <v>12</v>
+      </c>
       <c r="AG7" s="66"/>
       <c r="AH7" s="67"/>
       <c r="AI7" s="67"/>
       <c r="AJ7" s="67"/>
       <c r="AK7" s="25">
-        <f>SUMIF(E7:AJ7,"&lt;&gt;",$E$3:$AJ$3)</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:37">
       <c r="A8" s="30">
         <v>5</v>
       </c>
-      <c r="B8" s="143" t="s">
+      <c r="B8" s="110" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="22">
@@ -8231,7 +8316,7 @@
       <c r="AI8" s="67"/>
       <c r="AJ8" s="67"/>
       <c r="AK8" s="25">
-        <f>SUMIF(E8:AJ8,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -8239,7 +8324,7 @@
       <c r="A9" s="30">
         <v>6</v>
       </c>
-      <c r="B9" s="143" t="s">
+      <c r="B9" s="110" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="22">
@@ -8279,7 +8364,7 @@
       <c r="AI9" s="67"/>
       <c r="AJ9" s="67"/>
       <c r="AK9" s="25">
-        <f>SUMIF(E9:AJ9,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -8327,7 +8412,7 @@
       <c r="AI10" s="67"/>
       <c r="AJ10" s="67"/>
       <c r="AK10" s="25">
-        <f>SUMIF(E10:AJ10,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -8375,7 +8460,7 @@
       <c r="AI11" s="67"/>
       <c r="AJ11" s="67"/>
       <c r="AK11" s="25">
-        <f>SUMIF(E11:AJ11,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -8423,7 +8508,7 @@
       <c r="AI12" s="67"/>
       <c r="AJ12" s="67"/>
       <c r="AK12" s="25">
-        <f>SUMIF(E12:AJ12,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -8471,7 +8556,7 @@
       <c r="AI13" s="67"/>
       <c r="AJ13" s="67"/>
       <c r="AK13" s="25">
-        <f>SUMIF(E13:AJ13,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -8519,7 +8604,7 @@
       <c r="AI14" s="67"/>
       <c r="AJ14" s="67"/>
       <c r="AK14" s="25">
-        <f>SUMIF(E14:AJ14,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -8527,7 +8612,7 @@
       <c r="A15" s="30">
         <v>12</v>
       </c>
-      <c r="B15" s="143" t="s">
+      <c r="B15" s="110" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="22">
@@ -8567,7 +8652,7 @@
       <c r="AI15" s="67"/>
       <c r="AJ15" s="67"/>
       <c r="AK15" s="25">
-        <f>SUMIF(E15:AJ15,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -8575,7 +8660,7 @@
       <c r="A16" s="30">
         <v>13</v>
       </c>
-      <c r="B16" s="143" t="s">
+      <c r="B16" s="110" t="s">
         <v>13</v>
       </c>
       <c r="C16" s="22">
@@ -8615,7 +8700,7 @@
       <c r="AI16" s="76"/>
       <c r="AJ16" s="76"/>
       <c r="AK16" s="25">
-        <f>SUMIF(E16:AJ16,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -8663,7 +8748,7 @@
       <c r="AI17" s="76"/>
       <c r="AJ17" s="76"/>
       <c r="AK17" s="68">
-        <f>SUMIF(E17:AJ17,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -8711,7 +8796,7 @@
       <c r="AI18" s="67"/>
       <c r="AJ18" s="67"/>
       <c r="AK18" s="68">
-        <f>SUMIF(E18:AJ18,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -8759,7 +8844,7 @@
       <c r="AI19" s="92"/>
       <c r="AJ19" s="92"/>
       <c r="AK19" s="93">
-        <f>SUMIF(E19:AJ19,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -8807,7 +8892,7 @@
       <c r="AI20" s="76"/>
       <c r="AJ20" s="76"/>
       <c r="AK20" s="93">
-        <f>SUMIF(E20:AJ20,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -8855,7 +8940,7 @@
       <c r="AI21" s="76"/>
       <c r="AJ21" s="76"/>
       <c r="AK21" s="93">
-        <f>SUMIF(E21:AJ21,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -8863,7 +8948,7 @@
       <c r="A22" s="30">
         <v>19</v>
       </c>
-      <c r="B22" s="143" t="s">
+      <c r="B22" s="110" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="22">
@@ -8903,7 +8988,7 @@
       <c r="AI22" s="67"/>
       <c r="AJ22" s="67"/>
       <c r="AK22" s="25">
-        <f>SUMIF(E22:AJ22,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -8911,7 +8996,7 @@
       <c r="A23" s="84">
         <v>20</v>
       </c>
-      <c r="B23" s="143" t="s">
+      <c r="B23" s="110" t="s">
         <v>13</v>
       </c>
       <c r="C23" s="22">
@@ -8951,7 +9036,7 @@
       <c r="AI23" s="92"/>
       <c r="AJ23" s="92"/>
       <c r="AK23" s="95">
-        <f>SUMIF(E23:AJ23,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -8999,7 +9084,7 @@
       <c r="AI24" s="103"/>
       <c r="AJ24" s="103"/>
       <c r="AK24" s="104">
-        <f>SUMIF(E24:AJ24,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9047,7 +9132,7 @@
       <c r="AI25" s="76"/>
       <c r="AJ25" s="76"/>
       <c r="AK25" s="93">
-        <f>SUMIF(E25:AJ25,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9095,7 +9180,7 @@
       <c r="AI26" s="76"/>
       <c r="AJ26" s="76"/>
       <c r="AK26" s="93">
-        <f>SUMIF(E26:AJ26,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9143,7 +9228,7 @@
       <c r="AI27" s="76"/>
       <c r="AJ27" s="76"/>
       <c r="AK27" s="93">
-        <f>SUMIF(E27:AJ27,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9191,7 +9276,7 @@
       <c r="AI28" s="76"/>
       <c r="AJ28" s="76"/>
       <c r="AK28" s="93">
-        <f>SUMIF(E28:AJ28,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9199,7 +9284,7 @@
       <c r="A29" s="30">
         <v>26</v>
       </c>
-      <c r="B29" s="143" t="s">
+      <c r="B29" s="110" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="22">
@@ -9239,7 +9324,7 @@
       <c r="AI29" s="76"/>
       <c r="AJ29" s="76"/>
       <c r="AK29" s="93">
-        <f>SUMIF(E29:AJ29,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9247,7 +9332,7 @@
       <c r="A30" s="84">
         <v>27</v>
       </c>
-      <c r="B30" s="143" t="s">
+      <c r="B30" s="110" t="s">
         <v>13</v>
       </c>
       <c r="C30" s="22">
@@ -9287,7 +9372,7 @@
       <c r="AI30" s="67"/>
       <c r="AJ30" s="67"/>
       <c r="AK30" s="25">
-        <f>SUMIF(E30:AJ30,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9335,7 +9420,7 @@
       <c r="AI31" s="83"/>
       <c r="AJ31" s="83"/>
       <c r="AK31" s="94">
-        <f>SUMIF(E31:AJ31,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9383,7 +9468,7 @@
       <c r="AI32" s="67"/>
       <c r="AJ32" s="67"/>
       <c r="AK32" s="25">
-        <f>SUMIF(E32:AJ32,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9431,226 +9516,226 @@
       <c r="AI33" s="67"/>
       <c r="AJ33" s="67"/>
       <c r="AK33" s="25">
-        <f>SUMIF(E33:AJ33,"&lt;&gt;",$E$3:$AJ$3)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:37" ht="30" customHeight="1">
-      <c r="A34" s="122" t="s">
+      <c r="A34" s="141" t="s">
         <v>77</v>
       </c>
-      <c r="B34" s="123"/>
-      <c r="C34" s="123"/>
-      <c r="D34" s="124"/>
+      <c r="B34" s="142"/>
+      <c r="C34" s="142"/>
+      <c r="D34" s="143"/>
       <c r="E34" s="106">
-        <f>COUNTA(E4:E33)</f>
+        <f t="shared" ref="E34:AJ34" si="1">COUNTA(E4:E33)</f>
         <v>1</v>
       </c>
       <c r="F34" s="106">
-        <f>COUNTA(F4:F33)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G34" s="106">
-        <f>COUNTA(G4:G33)</f>
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="H34" s="106">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="H34" s="106">
-        <f>COUNTA(H4:H33)</f>
+      <c r="I34" s="106">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="106">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="106">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L34" s="63">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="M34" s="63">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="N34" s="63">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="O34" s="63">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="P34" s="63">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q34" s="63">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R34" s="29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U34" s="64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W34" s="64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y34" s="64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z34" s="65">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="I34" s="106">
-        <f>COUNTA(I4:I33)</f>
+      <c r="AA34" s="65">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J34" s="106">
-        <f>COUNTA(J4:J33)</f>
+      <c r="AB34" s="65">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K34" s="106">
-        <f>COUNTA(K4:K33)</f>
+      <c r="AC34" s="65">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AD34" s="65">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="AE34" s="66">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L34" s="63">
-        <f>COUNTA(L4:L33)</f>
+      <c r="AF34" s="66">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="M34" s="63">
-        <f>COUNTA(M4:M33)</f>
+      <c r="AG34" s="66">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AH34" s="67">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="N34" s="63">
-        <f>COUNTA(N4:N33)</f>
+      <c r="AI34" s="67">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O34" s="63">
-        <f>COUNTA(O4:O33)</f>
+      <c r="AJ34" s="67">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="P34" s="63">
-        <f>COUNTA(P4:P33)</f>
-        <v>0</v>
-      </c>
-      <c r="Q34" s="63">
-        <f>COUNTA(Q4:Q33)</f>
-        <v>0</v>
-      </c>
-      <c r="R34" s="29">
-        <f>COUNTA(R4:R33)</f>
-        <v>0</v>
-      </c>
-      <c r="S34" s="29">
-        <f>COUNTA(S4:S33)</f>
-        <v>0</v>
-      </c>
-      <c r="T34" s="29">
-        <f>COUNTA(T4:T33)</f>
-        <v>0</v>
-      </c>
-      <c r="U34" s="64">
-        <f>COUNTA(U4:U33)</f>
-        <v>0</v>
-      </c>
-      <c r="V34" s="64">
-        <f>COUNTA(V4:V33)</f>
-        <v>0</v>
-      </c>
-      <c r="W34" s="64">
-        <f>COUNTA(W4:W33)</f>
-        <v>0</v>
-      </c>
-      <c r="X34" s="64">
-        <f>COUNTA(X4:X33)</f>
-        <v>0</v>
-      </c>
-      <c r="Y34" s="64">
-        <f>COUNTA(Y4:Y33)</f>
-        <v>0</v>
-      </c>
-      <c r="Z34" s="65">
-        <f>COUNTA(Z4:Z33)</f>
-        <v>0</v>
-      </c>
-      <c r="AA34" s="65">
-        <f>COUNTA(AA4:AA33)</f>
-        <v>0</v>
-      </c>
-      <c r="AB34" s="65">
-        <f>COUNTA(AB4:AB33)</f>
-        <v>0</v>
-      </c>
-      <c r="AC34" s="65">
-        <f>COUNTA(AC4:AC33)</f>
-        <v>0</v>
-      </c>
-      <c r="AD34" s="65">
-        <f>COUNTA(AD4:AD33)</f>
-        <v>0</v>
-      </c>
-      <c r="AE34" s="66">
-        <f>COUNTA(AE4:AE33)</f>
-        <v>0</v>
-      </c>
-      <c r="AF34" s="66">
-        <f>COUNTA(AF4:AF33)</f>
-        <v>0</v>
-      </c>
-      <c r="AG34" s="66">
-        <f>COUNTA(AG4:AG33)</f>
-        <v>0</v>
-      </c>
-      <c r="AH34" s="67">
-        <f>COUNTA(AH4:AH33)</f>
-        <v>0</v>
-      </c>
-      <c r="AI34" s="67">
-        <f>COUNTA(AI4:AI33)</f>
-        <v>0</v>
-      </c>
-      <c r="AJ34" s="67">
-        <f>COUNTA(AJ4:AJ33)</f>
-        <v>0</v>
-      </c>
       <c r="AK34" s="25"/>
     </row>
     <row r="35" spans="1:37" ht="30" customHeight="1">
-      <c r="AG35" s="119" t="s">
+      <c r="AG35" s="138" t="s">
         <v>78</v>
       </c>
-      <c r="AH35" s="120"/>
-      <c r="AI35" s="120"/>
-      <c r="AJ35" s="121"/>
+      <c r="AH35" s="139"/>
+      <c r="AI35" s="139"/>
+      <c r="AJ35" s="140"/>
       <c r="AK35" s="107">
         <f>ROUND(AVERAGE(AK4:AK33),0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:37" ht="30" customHeight="1">
-      <c r="AG36" s="119" t="s">
+      <c r="AG36" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="AH36" s="120"/>
-      <c r="AI36" s="120"/>
-      <c r="AJ36" s="121"/>
+      <c r="AH36" s="139"/>
+      <c r="AI36" s="139"/>
+      <c r="AJ36" s="140"/>
       <c r="AK36" s="107">
         <f>MAX(AK4:AK33)</f>
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:37" ht="30" customHeight="1">
-      <c r="AG37" s="119" t="s">
+      <c r="AG37" s="138" t="s">
         <v>80</v>
       </c>
-      <c r="AH37" s="120"/>
-      <c r="AI37" s="120"/>
-      <c r="AJ37" s="121"/>
+      <c r="AH37" s="139"/>
+      <c r="AI37" s="139"/>
+      <c r="AJ37" s="140"/>
       <c r="AK37" s="107">
         <f>MIN(AK4:AK33)</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:37" ht="30" customHeight="1">
-      <c r="AG38" s="119" t="s">
+      <c r="AG38" s="138" t="s">
         <v>81</v>
       </c>
-      <c r="AH38" s="120"/>
-      <c r="AI38" s="120"/>
-      <c r="AJ38" s="121"/>
+      <c r="AH38" s="139"/>
+      <c r="AI38" s="139"/>
+      <c r="AJ38" s="140"/>
       <c r="AK38" s="107">
         <f>COUNTIF(AK4:AK33, "&gt;"&amp;AK35)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:37" ht="30" customHeight="1">
-      <c r="AG39" s="119" t="s">
+      <c r="AG39" s="138" t="s">
         <v>82</v>
       </c>
-      <c r="AH39" s="120"/>
-      <c r="AI39" s="120"/>
-      <c r="AJ39" s="121"/>
+      <c r="AH39" s="139"/>
+      <c r="AI39" s="139"/>
+      <c r="AJ39" s="140"/>
       <c r="AK39" s="107">
         <f>COUNTIF(AK4:AK33, "&lt;"&amp;AK35)</f>
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:37" ht="30" customHeight="1">
-      <c r="AG40" s="119" t="s">
+      <c r="AG40" s="138" t="s">
         <v>83</v>
       </c>
-      <c r="AH40" s="120"/>
-      <c r="AI40" s="120"/>
-      <c r="AJ40" s="121"/>
+      <c r="AH40" s="139"/>
+      <c r="AI40" s="139"/>
+      <c r="AJ40" s="140"/>
       <c r="AK40" s="107">
         <f>COUNTIF(AK4:AK33, "&gt;"&amp;20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:37" ht="30" customHeight="1">
-      <c r="AG41" s="119" t="s">
+      <c r="AG41" s="138" t="s">
         <v>84</v>
       </c>
-      <c r="AH41" s="120"/>
-      <c r="AI41" s="120"/>
-      <c r="AJ41" s="121"/>
+      <c r="AH41" s="139"/>
+      <c r="AI41" s="139"/>
+      <c r="AJ41" s="140"/>
       <c r="AK41" s="107">
         <f>COUNTIF(AK4:AK33, "&lt;"&amp;20)</f>
         <v>30</v>
@@ -9661,55 +9746,56 @@
     <row r="44" spans="1:37" ht="30" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="AG37:AJ37"/>
-    <mergeCell ref="AG38:AJ38"/>
-    <mergeCell ref="AG39:AJ39"/>
-    <mergeCell ref="AG40:AJ40"/>
-    <mergeCell ref="AG41:AJ41"/>
-    <mergeCell ref="R1:T1"/>
-    <mergeCell ref="AE1:AG1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="AK1:AK3"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="AG35:AJ35"/>
-    <mergeCell ref="AG36:AJ36"/>
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="E1:K1"/>
     <mergeCell ref="L1:Q1"/>
     <mergeCell ref="U1:Y1"/>
     <mergeCell ref="Z1:AD1"/>
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="AG37:AJ37"/>
+    <mergeCell ref="AG38:AJ38"/>
+    <mergeCell ref="AG39:AJ39"/>
+    <mergeCell ref="AG35:AJ35"/>
+    <mergeCell ref="AG36:AJ36"/>
+    <mergeCell ref="AE1:AG1"/>
+    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="AG40:AJ40"/>
+    <mergeCell ref="AG41:AJ41"/>
+    <mergeCell ref="AK1:AK3"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:AJ33 L34:Q34">
-    <cfRule type="expression" dxfId="6" priority="7">
+    <cfRule type="expression" dxfId="5" priority="7">
       <formula>E4="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R34:T34">
-    <cfRule type="expression" dxfId="5" priority="5">
+    <cfRule type="expression" dxfId="4" priority="5">
       <formula>R34="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U34:Y34">
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="3" priority="4">
       <formula>U34="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z34:AD34">
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>Z34="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE34:AG34">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>AE34="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AH34:AJ34">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>AH34="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Другое/study_chart.xlsx
+++ b/Другое/study_chart.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROG\Git\Repository_1\Другое\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10380" activeTab="3"/>
   </bookViews>
@@ -12,7 +17,7 @@
     <sheet name="Август" sheetId="5" r:id="rId3"/>
     <sheet name="Сентябрь" sheetId="6" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +40,7 @@
     <author>Собянин Евгений Андреевич (new)</author>
   </authors>
   <commentList>
-    <comment ref="AF21" authorId="0">
+    <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -60,7 +65,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF22" authorId="0">
+    <comment ref="AF22" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -86,7 +91,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF23" authorId="0">
+    <comment ref="AF23" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -114,7 +119,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF24" authorId="0">
+    <comment ref="AF24" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -140,7 +145,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG24" authorId="0">
+    <comment ref="AG24" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -164,7 +169,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH24" authorId="0">
+    <comment ref="AH24" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -188,7 +193,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF25" authorId="0">
+    <comment ref="AF25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -216,7 +221,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG25" authorId="0">
+    <comment ref="AG25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -240,7 +245,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH25" authorId="0">
+    <comment ref="AH25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -264,7 +269,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AI25" authorId="0">
+    <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -288,7 +293,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AJ25" authorId="0">
+    <comment ref="AJ25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -312,7 +317,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AK25" authorId="0">
+    <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -336,7 +341,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF26" authorId="0">
+    <comment ref="AF26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -360,7 +365,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG26" authorId="0">
+    <comment ref="AG26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -384,7 +389,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH26" authorId="0">
+    <comment ref="AH26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -408,7 +413,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AI26" authorId="0">
+    <comment ref="AI26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -432,7 +437,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AJ26" authorId="0">
+    <comment ref="AJ26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -456,7 +461,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AK26" authorId="0">
+    <comment ref="AK26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -480,7 +485,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF27" authorId="0">
+    <comment ref="AF27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -504,7 +509,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG27" authorId="0">
+    <comment ref="AG27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -528,7 +533,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH27" authorId="0">
+    <comment ref="AH27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -552,7 +557,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF28" authorId="0">
+    <comment ref="AF28" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -576,7 +581,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF29" authorId="0">
+    <comment ref="AF29" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -601,7 +606,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF30" authorId="0">
+    <comment ref="AF30" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -627,7 +632,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF31" authorId="0">
+    <comment ref="AF31" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -652,7 +657,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF32" authorId="0">
+    <comment ref="AF32" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -678,7 +683,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF33" authorId="0">
+    <comment ref="AF33" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -703,7 +708,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF35" authorId="0">
+    <comment ref="AF35" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -727,7 +732,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF36" authorId="0">
+    <comment ref="AF36" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -751,7 +756,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF37" authorId="0">
+    <comment ref="AF37" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -775,7 +780,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF38" authorId="0">
+    <comment ref="AF38" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -809,7 +814,7 @@
     <author>Собянин Евгений Андреевич (new)</author>
   </authors>
   <commentList>
-    <comment ref="AH14" authorId="0">
+    <comment ref="AH14" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -835,7 +840,7 @@
     <author>Собянин Евгений Андреевич (new)</author>
   </authors>
   <commentList>
-    <comment ref="AH5" authorId="0">
+    <comment ref="AH5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -849,7 +854,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH6" authorId="0">
+    <comment ref="AH6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -868,7 +873,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="88">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -1137,11 +1142,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mmm"/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="37" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2353,6 +2358,24 @@
     <xf numFmtId="0" fontId="19" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2405,24 +2428,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2628,7 +2633,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2660,9 +2665,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2694,6 +2700,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -2869,9 +2876,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="H9:Q22"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="7" width="9.140625" style="31"/>
     <col min="8" max="8" width="5" style="31" customWidth="1"/>
@@ -2885,7 +2892,7 @@
     <col min="18" max="16384" width="9.140625" style="31"/>
   </cols>
   <sheetData>
-    <row r="9" spans="8:17" ht="45" customHeight="1">
+    <row r="9" spans="8:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H9" s="111" t="s">
         <v>0</v>
       </c>
@@ -2899,7 +2906,7 @@
       <c r="P9" s="112"/>
       <c r="Q9" s="113"/>
     </row>
-    <row r="10" spans="8:17" ht="30" customHeight="1">
+    <row r="10" spans="8:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H10" s="55" t="s">
         <v>1</v>
       </c>
@@ -2931,7 +2938,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="8:17">
+    <row r="11" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H11" s="57">
         <v>1</v>
       </c>
@@ -2957,7 +2964,7 @@
       <c r="P11" s="60"/>
       <c r="Q11" s="60"/>
     </row>
-    <row r="12" spans="8:17">
+    <row r="12" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H12" s="57">
         <v>2</v>
       </c>
@@ -2981,7 +2988,7 @@
       <c r="P12" s="60"/>
       <c r="Q12" s="60"/>
     </row>
-    <row r="13" spans="8:17">
+    <row r="13" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H13" s="57">
         <v>3</v>
       </c>
@@ -3003,7 +3010,7 @@
       <c r="P13" s="60"/>
       <c r="Q13" s="60"/>
     </row>
-    <row r="14" spans="8:17">
+    <row r="14" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H14" s="57">
         <v>4</v>
       </c>
@@ -3025,7 +3032,7 @@
       <c r="P14" s="60"/>
       <c r="Q14" s="60"/>
     </row>
-    <row r="15" spans="8:17">
+    <row r="15" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H15" s="57">
         <v>5</v>
       </c>
@@ -3045,7 +3052,7 @@
       <c r="P15" s="60"/>
       <c r="Q15" s="60"/>
     </row>
-    <row r="16" spans="8:17">
+    <row r="16" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H16" s="57">
         <v>6</v>
       </c>
@@ -3069,7 +3076,7 @@
       <c r="P16" s="60"/>
       <c r="Q16" s="60"/>
     </row>
-    <row r="17" spans="8:17">
+    <row r="17" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H17" s="57">
         <v>7</v>
       </c>
@@ -3091,7 +3098,7 @@
       <c r="P17" s="60"/>
       <c r="Q17" s="60"/>
     </row>
-    <row r="18" spans="8:17">
+    <row r="18" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H18" s="57">
         <v>8</v>
       </c>
@@ -3109,7 +3116,7 @@
       <c r="P18" s="60"/>
       <c r="Q18" s="60"/>
     </row>
-    <row r="19" spans="8:17">
+    <row r="19" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H19" s="57">
         <v>9</v>
       </c>
@@ -3129,7 +3136,7 @@
       <c r="P19" s="60"/>
       <c r="Q19" s="60"/>
     </row>
-    <row r="20" spans="8:17">
+    <row r="20" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H20" s="57">
         <v>10</v>
       </c>
@@ -3147,7 +3154,7 @@
       <c r="P20" s="60"/>
       <c r="Q20" s="60"/>
     </row>
-    <row r="21" spans="8:17">
+    <row r="21" spans="8:17" x14ac:dyDescent="0.25">
       <c r="H21" s="57">
         <v>11</v>
       </c>
@@ -3165,7 +3172,7 @@
       <c r="P21" s="60"/>
       <c r="Q21" s="60"/>
     </row>
-    <row r="22" spans="8:17" ht="15.75">
+    <row r="22" spans="8:17" ht="15.75" x14ac:dyDescent="0.3">
       <c r="H22" s="114" t="s">
         <v>19</v>
       </c>
@@ -3221,9 +3228,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="H9:AL42"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="7" width="9.140625" style="31"/>
     <col min="8" max="8" width="5" style="31" customWidth="1"/>
@@ -3246,7 +3253,7 @@
     <col min="39" max="16384" width="9.140625" style="31"/>
   </cols>
   <sheetData>
-    <row r="9" spans="8:38" ht="45" customHeight="1">
+    <row r="9" spans="8:38" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H9" s="117" t="s">
         <v>0</v>
       </c>
@@ -3281,7 +3288,7 @@
       <c r="AK9" s="118"/>
       <c r="AL9" s="118"/>
     </row>
-    <row r="10" spans="8:38" ht="30" customHeight="1">
+    <row r="10" spans="8:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H10" s="32" t="s">
         <v>1</v>
       </c>
@@ -3376,7 +3383,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="8:38" ht="15.75">
+    <row r="11" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H11" s="46">
         <v>1</v>
       </c>
@@ -3420,7 +3427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="8:38" ht="15.75">
+    <row r="12" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H12" s="46">
         <v>2</v>
       </c>
@@ -3468,7 +3475,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="8:38" ht="15.75">
+    <row r="13" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H13" s="46">
         <v>3</v>
       </c>
@@ -3526,7 +3533,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="8:38" ht="15.75">
+    <row r="14" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H14" s="46">
         <v>4</v>
       </c>
@@ -3572,7 +3579,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="8:38" ht="15.75">
+    <row r="15" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H15" s="46">
         <v>5</v>
       </c>
@@ -3620,7 +3627,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="8:38" ht="15.75">
+    <row r="16" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H16" s="46">
         <v>6</v>
       </c>
@@ -3678,7 +3685,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="8:38" ht="15.75">
+    <row r="17" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H17" s="46">
         <v>7</v>
       </c>
@@ -3734,7 +3741,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="8:38" ht="15.75">
+    <row r="18" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H18" s="46">
         <v>8</v>
       </c>
@@ -3792,7 +3799,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="8:38" ht="15.75">
+    <row r="19" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H19" s="46">
         <v>9</v>
       </c>
@@ -3836,7 +3843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="8:38" ht="15.75">
+    <row r="20" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H20" s="46">
         <v>10</v>
       </c>
@@ -3880,7 +3887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="8:38" ht="15.75">
+    <row r="21" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H21" s="46">
         <v>11</v>
       </c>
@@ -3924,7 +3931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="8:38" ht="15.75">
+    <row r="22" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H22" s="46">
         <v>12</v>
       </c>
@@ -3976,7 +3983,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="8:38" ht="15.75">
+    <row r="23" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H23" s="46">
         <v>13</v>
       </c>
@@ -4044,7 +4051,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="8:38" ht="15.75">
+    <row r="24" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H24" s="46">
         <v>14</v>
       </c>
@@ -4102,7 +4109,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="8:38" ht="15.75">
+    <row r="25" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H25" s="46">
         <v>15</v>
       </c>
@@ -4162,7 +4169,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="8:38" ht="15.75">
+    <row r="26" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H26" s="46">
         <v>16</v>
       </c>
@@ -4220,7 +4227,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="8:38" ht="15.75">
+    <row r="27" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H27" s="46">
         <v>17</v>
       </c>
@@ -4288,7 +4295,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="8:38" ht="15.75">
+    <row r="28" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H28" s="46">
         <v>18</v>
       </c>
@@ -4340,7 +4347,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="8:38" ht="15.75">
+    <row r="29" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H29" s="46">
         <v>19</v>
       </c>
@@ -4388,7 +4395,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="8:38" ht="15.75">
+    <row r="30" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H30" s="46">
         <v>20</v>
       </c>
@@ -4438,7 +4445,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="8:38" ht="15.75">
+    <row r="31" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H31" s="46">
         <v>21</v>
       </c>
@@ -4480,7 +4487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="8:38" ht="15.75">
+    <row r="32" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H32" s="46">
         <v>22</v>
       </c>
@@ -4522,7 +4529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="8:38" ht="15.75">
+    <row r="33" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H33" s="46">
         <v>23</v>
       </c>
@@ -4564,7 +4571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="8:38" ht="15.75">
+    <row r="34" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H34" s="46">
         <v>24</v>
       </c>
@@ -4620,7 +4627,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="8:38" ht="15.75">
+    <row r="35" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H35" s="46">
         <v>25</v>
       </c>
@@ -4664,7 +4671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="8:38" ht="15.75">
+    <row r="36" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H36" s="46">
         <v>26</v>
       </c>
@@ -4712,7 +4719,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="8:38" ht="15.75">
+    <row r="37" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H37" s="46">
         <v>27</v>
       </c>
@@ -4756,7 +4763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="8:38" ht="15.75">
+    <row r="38" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H38" s="46">
         <v>28</v>
       </c>
@@ -4808,7 +4815,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="8:38" ht="15.75">
+    <row r="39" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H39" s="46">
         <v>29</v>
       </c>
@@ -4860,7 +4867,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="8:38" ht="15.75">
+    <row r="40" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H40" s="46">
         <v>30</v>
       </c>
@@ -4908,7 +4915,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="8:38" ht="15.75">
+    <row r="41" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="H41" s="46">
         <v>31</v>
       </c>
@@ -4958,7 +4965,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="8:38" ht="15.75">
+    <row r="42" spans="8:38" ht="15.75" x14ac:dyDescent="0.3">
       <c r="H42" s="119" t="s">
         <v>19</v>
       </c>
@@ -5093,9 +5100,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AK45"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="15.7109375" style="3" customWidth="1"/>
     <col min="4" max="4" width="26" style="3" customWidth="1"/>
@@ -5127,67 +5134,67 @@
     <col min="39" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="125"/>
-      <c r="B1" s="126"/>
-      <c r="C1" s="127"/>
+    <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="131"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="133"/>
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="131" t="s">
+      <c r="E1" s="137" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="131"/>
-      <c r="G1" s="131"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
-      <c r="K1" s="131"/>
-      <c r="L1" s="132" t="s">
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="138" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="132"/>
-      <c r="N1" s="132"/>
-      <c r="O1" s="132"/>
-      <c r="P1" s="132"/>
-      <c r="Q1" s="132"/>
-      <c r="R1" s="132"/>
-      <c r="S1" s="133" t="s">
+      <c r="M1" s="138"/>
+      <c r="N1" s="138"/>
+      <c r="O1" s="138"/>
+      <c r="P1" s="138"/>
+      <c r="Q1" s="138"/>
+      <c r="R1" s="138"/>
+      <c r="S1" s="139" t="s">
         <v>39</v>
       </c>
-      <c r="T1" s="133"/>
-      <c r="U1" s="134" t="s">
+      <c r="T1" s="139"/>
+      <c r="U1" s="140" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="135"/>
-      <c r="W1" s="135"/>
-      <c r="X1" s="135"/>
-      <c r="Y1" s="136"/>
-      <c r="Z1" s="137" t="s">
+      <c r="V1" s="141"/>
+      <c r="W1" s="141"/>
+      <c r="X1" s="141"/>
+      <c r="Y1" s="142"/>
+      <c r="Z1" s="143" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="137"/>
-      <c r="AB1" s="137"/>
-      <c r="AC1" s="137"/>
-      <c r="AD1" s="137"/>
-      <c r="AE1" s="120" t="s">
+      <c r="AA1" s="143"/>
+      <c r="AB1" s="143"/>
+      <c r="AC1" s="143"/>
+      <c r="AD1" s="143"/>
+      <c r="AE1" s="126" t="s">
         <v>42</v>
       </c>
-      <c r="AF1" s="120"/>
-      <c r="AG1" s="120"/>
-      <c r="AH1" s="121" t="s">
+      <c r="AF1" s="126"/>
+      <c r="AG1" s="126"/>
+      <c r="AH1" s="127" t="s">
         <v>43</v>
       </c>
-      <c r="AI1" s="121"/>
-      <c r="AJ1" s="121"/>
-      <c r="AK1" s="122" t="s">
+      <c r="AI1" s="127"/>
+      <c r="AJ1" s="127"/>
+      <c r="AK1" s="128" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1">
-      <c r="A2" s="128"/>
-      <c r="B2" s="129"/>
-      <c r="C2" s="130"/>
+    <row r="2" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="134"/>
+      <c r="B2" s="135"/>
+      <c r="C2" s="136"/>
       <c r="D2" s="5" t="s">
         <v>44</v>
       </c>
@@ -5281,9 +5288,9 @@
       <c r="AH2" s="12"/>
       <c r="AI2" s="12"/>
       <c r="AJ2" s="12"/>
-      <c r="AK2" s="123"/>
-    </row>
-    <row r="3" spans="1:37">
+      <c r="AK2" s="129"/>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>1</v>
       </c>
@@ -5392,9 +5399,9 @@
       <c r="AJ3" s="20">
         <v>2</v>
       </c>
-      <c r="AK3" s="124"/>
-    </row>
-    <row r="4" spans="1:37">
+      <c r="AK3" s="130"/>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A4" s="21">
         <v>1</v>
       </c>
@@ -5454,7 +5461,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:37">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A5" s="21">
         <v>2</v>
       </c>
@@ -5506,7 +5513,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:37">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A6" s="21">
         <v>3</v>
       </c>
@@ -5582,7 +5589,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:37">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A7" s="21">
         <v>4</v>
       </c>
@@ -5656,7 +5663,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:37">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A8" s="21">
         <v>5</v>
       </c>
@@ -5726,7 +5733,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:37">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A9" s="21">
         <v>6</v>
       </c>
@@ -5794,7 +5801,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:37">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A10" s="21">
         <v>7</v>
       </c>
@@ -5852,7 +5859,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:37">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A11" s="21">
         <v>8</v>
       </c>
@@ -5912,7 +5919,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:37">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A12" s="21">
         <v>9</v>
       </c>
@@ -5982,7 +5989,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:37">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A13" s="21">
         <v>10</v>
       </c>
@@ -6054,7 +6061,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:37">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A14" s="21">
         <v>11</v>
       </c>
@@ -6136,7 +6143,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:37">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A15" s="21">
         <v>12</v>
       </c>
@@ -6204,7 +6211,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:37">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A16" s="21">
         <v>13</v>
       </c>
@@ -6264,7 +6271,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:37">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A17" s="21">
         <v>14</v>
       </c>
@@ -6322,7 +6329,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:37">
+    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A18" s="21">
         <v>15</v>
       </c>
@@ -6380,7 +6387,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:37">
+    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A19" s="69">
         <v>16</v>
       </c>
@@ -6442,7 +6449,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:37">
+    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A20" s="69">
         <v>17</v>
       </c>
@@ -6520,7 +6527,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:37">
+    <row r="21" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A21" s="69">
         <v>18</v>
       </c>
@@ -6600,7 +6607,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:37">
+    <row r="22" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A22" s="30">
         <v>19</v>
       </c>
@@ -6662,7 +6669,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:37">
+    <row r="23" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A23" s="84">
         <v>20</v>
       </c>
@@ -6724,7 +6731,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:37">
+    <row r="24" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A24" s="21">
         <v>21</v>
       </c>
@@ -6794,7 +6801,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:37">
+    <row r="25" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A25" s="21">
         <v>22</v>
       </c>
@@ -6862,7 +6869,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:37">
+    <row r="26" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A26" s="69">
         <v>23</v>
       </c>
@@ -6924,7 +6931,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:37">
+    <row r="27" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A27" s="69">
         <v>24</v>
       </c>
@@ -6996,7 +7003,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:37">
+    <row r="28" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A28" s="69">
         <v>25</v>
       </c>
@@ -7072,7 +7079,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:37">
+    <row r="29" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A29" s="30">
         <v>26</v>
       </c>
@@ -7146,7 +7153,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:37">
+    <row r="30" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A30" s="84">
         <v>27</v>
       </c>
@@ -7204,7 +7211,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:37">
+    <row r="31" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A31" s="21">
         <v>28</v>
       </c>
@@ -7270,7 +7277,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:37">
+    <row r="32" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A32" s="21">
         <v>29</v>
       </c>
@@ -7332,7 +7339,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:37">
+    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A33" s="21">
         <v>30</v>
       </c>
@@ -7386,7 +7393,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:37">
+    <row r="34" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A34" s="21">
         <v>31</v>
       </c>
@@ -7442,13 +7449,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="1:37" ht="30" customHeight="1">
-      <c r="A35" s="141" t="s">
+    <row r="35" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="123" t="s">
         <v>77</v>
       </c>
-      <c r="B35" s="142"/>
-      <c r="C35" s="142"/>
-      <c r="D35" s="143"/>
+      <c r="B35" s="124"/>
+      <c r="C35" s="124"/>
+      <c r="D35" s="125"/>
       <c r="E35" s="106">
         <f>COUNTA(E4:E34)</f>
         <v>14</v>
@@ -7579,103 +7586,95 @@
       </c>
       <c r="AK35" s="25"/>
     </row>
-    <row r="36" spans="1:37" ht="30" customHeight="1">
-      <c r="AG36" s="138" t="s">
+    <row r="36" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG36" s="120" t="s">
         <v>78</v>
       </c>
-      <c r="AH36" s="139"/>
-      <c r="AI36" s="139"/>
-      <c r="AJ36" s="140"/>
+      <c r="AH36" s="121"/>
+      <c r="AI36" s="121"/>
+      <c r="AJ36" s="122"/>
       <c r="AK36" s="107">
         <f>ROUND(AVERAGE(AK4:AK34),0)</f>
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:37" ht="30" customHeight="1">
-      <c r="AG37" s="138" t="s">
+    <row r="37" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG37" s="120" t="s">
         <v>79</v>
       </c>
-      <c r="AH37" s="139"/>
-      <c r="AI37" s="139"/>
-      <c r="AJ37" s="140"/>
+      <c r="AH37" s="121"/>
+      <c r="AI37" s="121"/>
+      <c r="AJ37" s="122"/>
       <c r="AK37" s="107">
         <f>MAX(AK4:AK34)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:37" ht="30" customHeight="1">
-      <c r="AG38" s="138" t="s">
+    <row r="38" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG38" s="120" t="s">
         <v>80</v>
       </c>
-      <c r="AH38" s="139"/>
-      <c r="AI38" s="139"/>
-      <c r="AJ38" s="140"/>
+      <c r="AH38" s="121"/>
+      <c r="AI38" s="121"/>
+      <c r="AJ38" s="122"/>
       <c r="AK38" s="107">
         <f>MIN(AK4:AK34)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:37" ht="30" customHeight="1">
-      <c r="AG39" s="138" t="s">
+    <row r="39" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG39" s="120" t="s">
         <v>81</v>
       </c>
-      <c r="AH39" s="139"/>
-      <c r="AI39" s="139"/>
-      <c r="AJ39" s="140"/>
+      <c r="AH39" s="121"/>
+      <c r="AI39" s="121"/>
+      <c r="AJ39" s="122"/>
       <c r="AK39" s="107">
         <f>COUNTIF(AK4:AK34, "&gt;"&amp;AK36)</f>
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:37" ht="30" customHeight="1">
-      <c r="AG40" s="138" t="s">
+    <row r="40" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG40" s="120" t="s">
         <v>82</v>
       </c>
-      <c r="AH40" s="139"/>
-      <c r="AI40" s="139"/>
-      <c r="AJ40" s="140"/>
+      <c r="AH40" s="121"/>
+      <c r="AI40" s="121"/>
+      <c r="AJ40" s="122"/>
       <c r="AK40" s="107">
         <f>COUNTIF(AK4:AK34, "&lt;"&amp;AK36)</f>
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:37" ht="30" customHeight="1">
-      <c r="AG41" s="138" t="s">
+    <row r="41" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG41" s="120" t="s">
         <v>83</v>
       </c>
-      <c r="AH41" s="139"/>
-      <c r="AI41" s="139"/>
-      <c r="AJ41" s="140"/>
+      <c r="AH41" s="121"/>
+      <c r="AI41" s="121"/>
+      <c r="AJ41" s="122"/>
       <c r="AK41" s="107">
         <f>COUNTIF(AK4:AK34, "&gt;"&amp;20)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:37" ht="30" customHeight="1">
-      <c r="AG42" s="138" t="s">
+    <row r="42" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG42" s="120" t="s">
         <v>84</v>
       </c>
-      <c r="AH42" s="139"/>
-      <c r="AI42" s="139"/>
-      <c r="AJ42" s="140"/>
+      <c r="AH42" s="121"/>
+      <c r="AI42" s="121"/>
+      <c r="AJ42" s="122"/>
       <c r="AK42" s="107">
         <f>COUNTIF(AK4:AK34, "&lt;"&amp;20)</f>
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:37" ht="30" customHeight="1"/>
-    <row r="44" spans="1:37" ht="30" customHeight="1"/>
-    <row r="45" spans="1:37" ht="30" customHeight="1"/>
+    <row r="43" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="AG40:AJ40"/>
-    <mergeCell ref="AG41:AJ41"/>
-    <mergeCell ref="AG42:AJ42"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="AG36:AJ36"/>
-    <mergeCell ref="AG37:AJ37"/>
-    <mergeCell ref="AG38:AJ38"/>
-    <mergeCell ref="AG39:AJ39"/>
     <mergeCell ref="AE1:AG1"/>
     <mergeCell ref="AH1:AJ1"/>
     <mergeCell ref="AK1:AK3"/>
@@ -7685,6 +7684,14 @@
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="U1:Y1"/>
     <mergeCell ref="Z1:AD1"/>
+    <mergeCell ref="AG40:AJ40"/>
+    <mergeCell ref="AG41:AJ41"/>
+    <mergeCell ref="AG42:AJ42"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="AG36:AJ36"/>
+    <mergeCell ref="AG37:AJ37"/>
+    <mergeCell ref="AG38:AJ38"/>
+    <mergeCell ref="AG39:AJ39"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:AJ34">
     <cfRule type="expression" dxfId="12" priority="7">
@@ -7728,9 +7735,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AK44"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="15.7109375" style="3" customWidth="1"/>
     <col min="4" max="4" width="26" style="3" customWidth="1"/>
@@ -7761,67 +7768,67 @@
     <col min="39" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="125"/>
-      <c r="B1" s="126"/>
-      <c r="C1" s="127"/>
+    <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="131"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="133"/>
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="131" t="s">
+      <c r="E1" s="137" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="131"/>
-      <c r="G1" s="131"/>
-      <c r="H1" s="131"/>
-      <c r="I1" s="131"/>
-      <c r="J1" s="131"/>
-      <c r="K1" s="131"/>
-      <c r="L1" s="132" t="s">
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="138" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="132"/>
-      <c r="N1" s="132"/>
-      <c r="O1" s="132"/>
-      <c r="P1" s="132"/>
-      <c r="Q1" s="132"/>
+      <c r="M1" s="138"/>
+      <c r="N1" s="138"/>
+      <c r="O1" s="138"/>
+      <c r="P1" s="138"/>
+      <c r="Q1" s="138"/>
       <c r="R1" s="144" t="s">
         <v>39</v>
       </c>
       <c r="S1" s="145"/>
       <c r="T1" s="146"/>
-      <c r="U1" s="134" t="s">
+      <c r="U1" s="140" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="135"/>
-      <c r="W1" s="135"/>
-      <c r="X1" s="135"/>
-      <c r="Y1" s="136"/>
-      <c r="Z1" s="137" t="s">
+      <c r="V1" s="141"/>
+      <c r="W1" s="141"/>
+      <c r="X1" s="141"/>
+      <c r="Y1" s="142"/>
+      <c r="Z1" s="143" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="137"/>
-      <c r="AB1" s="137"/>
-      <c r="AC1" s="137"/>
-      <c r="AD1" s="137"/>
-      <c r="AE1" s="120" t="s">
+      <c r="AA1" s="143"/>
+      <c r="AB1" s="143"/>
+      <c r="AC1" s="143"/>
+      <c r="AD1" s="143"/>
+      <c r="AE1" s="126" t="s">
         <v>42</v>
       </c>
-      <c r="AF1" s="120"/>
-      <c r="AG1" s="120"/>
-      <c r="AH1" s="121" t="s">
+      <c r="AF1" s="126"/>
+      <c r="AG1" s="126"/>
+      <c r="AH1" s="127" t="s">
         <v>43</v>
       </c>
-      <c r="AI1" s="121"/>
-      <c r="AJ1" s="121"/>
-      <c r="AK1" s="122" t="s">
+      <c r="AI1" s="127"/>
+      <c r="AJ1" s="127"/>
+      <c r="AK1" s="128" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:37" s="2" customFormat="1" ht="45" customHeight="1">
-      <c r="A2" s="128"/>
-      <c r="B2" s="129"/>
-      <c r="C2" s="130"/>
+    <row r="2" spans="1:37" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="134"/>
+      <c r="B2" s="135"/>
+      <c r="C2" s="136"/>
       <c r="D2" s="5" t="s">
         <v>44</v>
       </c>
@@ -7915,9 +7922,9 @@
       <c r="AH2" s="12"/>
       <c r="AI2" s="12"/>
       <c r="AJ2" s="12"/>
-      <c r="AK2" s="123"/>
-    </row>
-    <row r="3" spans="1:37">
+      <c r="AK2" s="129"/>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>1</v>
       </c>
@@ -8026,9 +8033,9 @@
       <c r="AJ3" s="20">
         <v>1</v>
       </c>
-      <c r="AK3" s="124"/>
-    </row>
-    <row r="4" spans="1:37">
+      <c r="AK3" s="130"/>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A4" s="30">
         <v>1</v>
       </c>
@@ -8100,7 +8107,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:37">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A5" s="30">
         <v>2</v>
       </c>
@@ -8156,7 +8163,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:37">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A6" s="30">
         <v>3</v>
       </c>
@@ -8188,7 +8195,9 @@
         <v>12</v>
       </c>
       <c r="O6" s="63"/>
-      <c r="P6" s="63"/>
+      <c r="P6" s="63" t="s">
+        <v>12</v>
+      </c>
       <c r="Q6" s="63"/>
       <c r="R6" s="24"/>
       <c r="S6" s="24"/>
@@ -8215,10 +8224,10 @@
       <c r="AJ6" s="67"/>
       <c r="AK6" s="25">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:37">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A7" s="30">
         <v>4</v>
       </c>
@@ -8228,7 +8237,9 @@
       <c r="C7" s="22">
         <v>46269</v>
       </c>
-      <c r="D7" s="30"/>
+      <c r="D7" s="30" t="s">
+        <v>62</v>
+      </c>
       <c r="E7" s="62"/>
       <c r="F7" s="62"/>
       <c r="G7" s="62"/>
@@ -8242,9 +8253,15 @@
       <c r="M7" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="63"/>
-      <c r="O7" s="63"/>
-      <c r="P7" s="63"/>
+      <c r="N7" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="O7" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="P7" s="63" t="s">
+        <v>12</v>
+      </c>
       <c r="Q7" s="63"/>
       <c r="R7" s="24"/>
       <c r="S7" s="24"/>
@@ -8257,8 +8274,12 @@
       <c r="Z7" s="65"/>
       <c r="AA7" s="65"/>
       <c r="AB7" s="65"/>
-      <c r="AC7" s="65"/>
-      <c r="AD7" s="65"/>
+      <c r="AC7" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD7" s="65" t="s">
+        <v>12</v>
+      </c>
       <c r="AE7" s="66"/>
       <c r="AF7" s="66" t="s">
         <v>12</v>
@@ -8269,10 +8290,10 @@
       <c r="AJ7" s="67"/>
       <c r="AK7" s="25">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:37">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A8" s="30">
         <v>5</v>
       </c>
@@ -8282,13 +8303,19 @@
       <c r="C8" s="22">
         <v>46270</v>
       </c>
-      <c r="D8" s="30"/>
+      <c r="D8" s="30" t="s">
+        <v>62</v>
+      </c>
       <c r="E8" s="62"/>
       <c r="F8" s="62"/>
       <c r="G8" s="62"/>
       <c r="H8" s="62"/>
-      <c r="I8" s="62"/>
-      <c r="J8" s="62"/>
+      <c r="I8" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="62" t="s">
+        <v>12</v>
+      </c>
       <c r="K8" s="62"/>
       <c r="L8" s="63"/>
       <c r="M8" s="63"/>
@@ -8304,7 +8331,9 @@
       <c r="W8" s="64"/>
       <c r="X8" s="64"/>
       <c r="Y8" s="64"/>
-      <c r="Z8" s="65"/>
+      <c r="Z8" s="65" t="s">
+        <v>12</v>
+      </c>
       <c r="AA8" s="65"/>
       <c r="AB8" s="65"/>
       <c r="AC8" s="65"/>
@@ -8317,10 +8346,10 @@
       <c r="AJ8" s="67"/>
       <c r="AK8" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:37">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A9" s="30">
         <v>6</v>
       </c>
@@ -8368,7 +8397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:37">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A10" s="30">
         <v>7</v>
       </c>
@@ -8416,7 +8445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:37">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A11" s="30">
         <v>8</v>
       </c>
@@ -8464,7 +8493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:37">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A12" s="30">
         <v>9</v>
       </c>
@@ -8512,7 +8541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:37">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A13" s="30">
         <v>10</v>
       </c>
@@ -8560,7 +8589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:37">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A14" s="30">
         <v>11</v>
       </c>
@@ -8608,7 +8637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:37">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A15" s="30">
         <v>12</v>
       </c>
@@ -8656,7 +8685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:37">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A16" s="30">
         <v>13</v>
       </c>
@@ -8704,7 +8733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:37">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A17" s="30">
         <v>14</v>
       </c>
@@ -8752,7 +8781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:37">
+    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A18" s="30">
         <v>15</v>
       </c>
@@ -8800,7 +8829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:37">
+    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A19" s="69">
         <v>16</v>
       </c>
@@ -8848,7 +8877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:37">
+    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A20" s="69">
         <v>17</v>
       </c>
@@ -8896,7 +8925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:37">
+    <row r="21" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A21" s="69">
         <v>18</v>
       </c>
@@ -8944,7 +8973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:37">
+    <row r="22" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A22" s="30">
         <v>19</v>
       </c>
@@ -8992,7 +9021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:37">
+    <row r="23" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A23" s="84">
         <v>20</v>
       </c>
@@ -9040,7 +9069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:37">
+    <row r="24" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A24" s="30">
         <v>21</v>
       </c>
@@ -9088,7 +9117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:37">
+    <row r="25" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A25" s="30">
         <v>22</v>
       </c>
@@ -9136,7 +9165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:37">
+    <row r="26" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A26" s="69">
         <v>23</v>
       </c>
@@ -9184,7 +9213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:37">
+    <row r="27" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A27" s="69">
         <v>24</v>
       </c>
@@ -9232,7 +9261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:37">
+    <row r="28" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A28" s="69">
         <v>25</v>
       </c>
@@ -9280,7 +9309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:37">
+    <row r="29" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A29" s="30">
         <v>26</v>
       </c>
@@ -9328,7 +9357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:37">
+    <row r="30" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A30" s="84">
         <v>27</v>
       </c>
@@ -9376,7 +9405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:37">
+    <row r="31" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A31" s="30">
         <v>28</v>
       </c>
@@ -9424,7 +9453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:37">
+    <row r="32" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A32" s="30">
         <v>29</v>
       </c>
@@ -9472,7 +9501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:37">
+    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A33" s="30">
         <v>30</v>
       </c>
@@ -9520,13 +9549,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:37" ht="30" customHeight="1">
-      <c r="A34" s="141" t="s">
+    <row r="34" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="123" t="s">
         <v>77</v>
       </c>
-      <c r="B34" s="142"/>
-      <c r="C34" s="142"/>
-      <c r="D34" s="143"/>
+      <c r="B34" s="124"/>
+      <c r="C34" s="124"/>
+      <c r="D34" s="125"/>
       <c r="E34" s="106">
         <f t="shared" ref="E34:AJ34" si="1">COUNTA(E4:E33)</f>
         <v>1</v>
@@ -9545,11 +9574,11 @@
       </c>
       <c r="I34" s="106">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" s="106">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" s="106">
         <f t="shared" si="1"/>
@@ -9565,15 +9594,15 @@
       </c>
       <c r="N34" s="63">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O34" s="63">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P34" s="63">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q34" s="63">
         <f t="shared" si="1"/>
@@ -9613,7 +9642,7 @@
       </c>
       <c r="Z34" s="65">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA34" s="65">
         <f t="shared" si="1"/>
@@ -9625,11 +9654,11 @@
       </c>
       <c r="AC34" s="65">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD34" s="65">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE34" s="66">
         <f t="shared" si="1"/>
@@ -9657,112 +9686,112 @@
       </c>
       <c r="AK34" s="25"/>
     </row>
-    <row r="35" spans="1:37" ht="30" customHeight="1">
-      <c r="AG35" s="138" t="s">
+    <row r="35" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG35" s="120" t="s">
         <v>78</v>
       </c>
-      <c r="AH35" s="139"/>
-      <c r="AI35" s="139"/>
-      <c r="AJ35" s="140"/>
+      <c r="AH35" s="121"/>
+      <c r="AI35" s="121"/>
+      <c r="AJ35" s="122"/>
       <c r="AK35" s="107">
         <f>ROUND(AVERAGE(AK4:AK33),0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:37" ht="30" customHeight="1">
-      <c r="AG36" s="138" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG36" s="120" t="s">
         <v>79</v>
       </c>
-      <c r="AH36" s="139"/>
-      <c r="AI36" s="139"/>
-      <c r="AJ36" s="140"/>
+      <c r="AH36" s="121"/>
+      <c r="AI36" s="121"/>
+      <c r="AJ36" s="122"/>
       <c r="AK36" s="107">
         <f>MAX(AK4:AK33)</f>
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:37" ht="30" customHeight="1">
-      <c r="AG37" s="138" t="s">
+    <row r="37" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG37" s="120" t="s">
         <v>80</v>
       </c>
-      <c r="AH37" s="139"/>
-      <c r="AI37" s="139"/>
-      <c r="AJ37" s="140"/>
+      <c r="AH37" s="121"/>
+      <c r="AI37" s="121"/>
+      <c r="AJ37" s="122"/>
       <c r="AK37" s="107">
         <f>MIN(AK4:AK33)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:37" ht="30" customHeight="1">
-      <c r="AG38" s="138" t="s">
+    <row r="38" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG38" s="120" t="s">
         <v>81</v>
       </c>
-      <c r="AH38" s="139"/>
-      <c r="AI38" s="139"/>
-      <c r="AJ38" s="140"/>
+      <c r="AH38" s="121"/>
+      <c r="AI38" s="121"/>
+      <c r="AJ38" s="122"/>
       <c r="AK38" s="107">
         <f>COUNTIF(AK4:AK33, "&gt;"&amp;AK35)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:37" ht="30" customHeight="1">
-      <c r="AG39" s="138" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG39" s="120" t="s">
         <v>82</v>
       </c>
-      <c r="AH39" s="139"/>
-      <c r="AI39" s="139"/>
-      <c r="AJ39" s="140"/>
+      <c r="AH39" s="121"/>
+      <c r="AI39" s="121"/>
+      <c r="AJ39" s="122"/>
       <c r="AK39" s="107">
         <f>COUNTIF(AK4:AK33, "&lt;"&amp;AK35)</f>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="40" spans="1:37" ht="30" customHeight="1">
-      <c r="AG40" s="138" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG40" s="120" t="s">
         <v>83</v>
       </c>
-      <c r="AH40" s="139"/>
-      <c r="AI40" s="139"/>
-      <c r="AJ40" s="140"/>
+      <c r="AH40" s="121"/>
+      <c r="AI40" s="121"/>
+      <c r="AJ40" s="122"/>
       <c r="AK40" s="107">
         <f>COUNTIF(AK4:AK33, "&gt;"&amp;20)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:37" ht="30" customHeight="1">
-      <c r="AG41" s="138" t="s">
+    <row r="41" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG41" s="120" t="s">
         <v>84</v>
       </c>
-      <c r="AH41" s="139"/>
-      <c r="AI41" s="139"/>
-      <c r="AJ41" s="140"/>
+      <c r="AH41" s="121"/>
+      <c r="AI41" s="121"/>
+      <c r="AJ41" s="122"/>
       <c r="AK41" s="107">
         <f>COUNTIF(AK4:AK33, "&lt;"&amp;20)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="1:37" ht="30" customHeight="1"/>
-    <row r="43" spans="1:37" ht="30" customHeight="1"/>
-    <row r="44" spans="1:37" ht="30" customHeight="1"/>
+    <row r="42" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="AE1:AG1"/>
+    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="AG40:AJ40"/>
+    <mergeCell ref="AG41:AJ41"/>
+    <mergeCell ref="AK1:AK3"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="AG37:AJ37"/>
+    <mergeCell ref="AG38:AJ38"/>
+    <mergeCell ref="AG39:AJ39"/>
+    <mergeCell ref="AG35:AJ35"/>
+    <mergeCell ref="AG36:AJ36"/>
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="E1:K1"/>
     <mergeCell ref="L1:Q1"/>
     <mergeCell ref="U1:Y1"/>
     <mergeCell ref="Z1:AD1"/>
     <mergeCell ref="R1:T1"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="AG37:AJ37"/>
-    <mergeCell ref="AG38:AJ38"/>
-    <mergeCell ref="AG39:AJ39"/>
-    <mergeCell ref="AG35:AJ35"/>
-    <mergeCell ref="AG36:AJ36"/>
-    <mergeCell ref="AE1:AG1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="AG40:AJ40"/>
-    <mergeCell ref="AG41:AJ41"/>
-    <mergeCell ref="AK1:AK3"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:AJ33 L34:Q34">
     <cfRule type="expression" dxfId="5" priority="7">

--- a/Другое/study_chart.xlsx
+++ b/Другое/study_chart.xlsx
@@ -1,13 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROG\Git\Repository_1\Другое\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10380" activeTab="3"/>
   </bookViews>
@@ -17,7 +12,7 @@
     <sheet name="Август" sheetId="5" r:id="rId3"/>
     <sheet name="Сентябрь" sheetId="6" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="125725"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -40,7 +35,7 @@
     <author>Собянин Евгений Андреевич (new)</author>
   </authors>
   <commentList>
-    <comment ref="AF21" authorId="0" shapeId="0">
+    <comment ref="AF21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -65,7 +60,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF22" authorId="0" shapeId="0">
+    <comment ref="AF22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -91,7 +86,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF23" authorId="0" shapeId="0">
+    <comment ref="AF23" authorId="0">
       <text>
         <r>
           <rPr>
@@ -119,7 +114,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF24" authorId="0" shapeId="0">
+    <comment ref="AF24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -145,7 +140,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG24" authorId="0" shapeId="0">
+    <comment ref="AG24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -169,7 +164,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH24" authorId="0" shapeId="0">
+    <comment ref="AH24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -193,7 +188,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF25" authorId="0" shapeId="0">
+    <comment ref="AF25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -221,7 +216,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG25" authorId="0" shapeId="0">
+    <comment ref="AG25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -245,7 +240,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH25" authorId="0" shapeId="0">
+    <comment ref="AH25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -269,7 +264,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AI25" authorId="0" shapeId="0">
+    <comment ref="AI25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -293,7 +288,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AJ25" authorId="0" shapeId="0">
+    <comment ref="AJ25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -317,7 +312,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AK25" authorId="0" shapeId="0">
+    <comment ref="AK25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -341,7 +336,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF26" authorId="0" shapeId="0">
+    <comment ref="AF26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -365,7 +360,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG26" authorId="0" shapeId="0">
+    <comment ref="AG26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -389,7 +384,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH26" authorId="0" shapeId="0">
+    <comment ref="AH26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -413,7 +408,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AI26" authorId="0" shapeId="0">
+    <comment ref="AI26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -437,7 +432,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AJ26" authorId="0" shapeId="0">
+    <comment ref="AJ26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -461,7 +456,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AK26" authorId="0" shapeId="0">
+    <comment ref="AK26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -485,7 +480,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF27" authorId="0" shapeId="0">
+    <comment ref="AF27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -509,7 +504,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG27" authorId="0" shapeId="0">
+    <comment ref="AG27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -533,7 +528,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH27" authorId="0" shapeId="0">
+    <comment ref="AH27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -557,7 +552,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF28" authorId="0" shapeId="0">
+    <comment ref="AF28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -581,7 +576,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF29" authorId="0" shapeId="0">
+    <comment ref="AF29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -606,7 +601,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF30" authorId="0" shapeId="0">
+    <comment ref="AF30" authorId="0">
       <text>
         <r>
           <rPr>
@@ -632,7 +627,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF31" authorId="0" shapeId="0">
+    <comment ref="AF31" authorId="0">
       <text>
         <r>
           <rPr>
@@ -657,7 +652,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF32" authorId="0" shapeId="0">
+    <comment ref="AF32" authorId="0">
       <text>
         <r>
           <rPr>
@@ -683,7 +678,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF33" authorId="0" shapeId="0">
+    <comment ref="AF33" authorId="0">
       <text>
         <r>
           <rPr>
@@ -708,7 +703,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF35" authorId="0" shapeId="0">
+    <comment ref="AF35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -732,7 +727,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF36" authorId="0" shapeId="0">
+    <comment ref="AF36" authorId="0">
       <text>
         <r>
           <rPr>
@@ -756,7 +751,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF37" authorId="0" shapeId="0">
+    <comment ref="AF37" authorId="0">
       <text>
         <r>
           <rPr>
@@ -780,7 +775,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF38" authorId="0" shapeId="0">
+    <comment ref="AF38" authorId="0">
       <text>
         <r>
           <rPr>
@@ -814,7 +809,7 @@
     <author>Собянин Евгений Андреевич (new)</author>
   </authors>
   <commentList>
-    <comment ref="AH14" authorId="0" shapeId="0">
+    <comment ref="AH14" authorId="0">
       <text>
         <r>
           <rPr>
@@ -840,7 +835,7 @@
     <author>Собянин Евгений Андреевич (new)</author>
   </authors>
   <commentList>
-    <comment ref="AH5" authorId="0" shapeId="0">
+    <comment ref="AH5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -854,7 +849,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH6" authorId="0" shapeId="0">
+    <comment ref="AH6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -868,12 +863,54 @@
         </r>
       </text>
     </comment>
+    <comment ref="AH8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Поделать работу которую взял на дом</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AH9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Должностные инструкции
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AI9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">KPI
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="90">
   <si>
     <t>СТАТИСТИКА</t>
   </si>
@@ -1138,15 +1175,21 @@
   <si>
     <t>87.7</t>
   </si>
+  <si>
+    <t>Упражнение Ситуация - Приговор - Факт</t>
+  </si>
+  <si>
+    <t>Упражнения для голоса</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mmm"/>
   </numFmts>
-  <fonts count="37" x14ac:knownFonts="1">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1631,7 +1674,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -2009,11 +2052,56 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2358,6 +2446,60 @@
     <xf numFmtId="0" fontId="19" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2376,60 +2518,6 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2437,6 +2525,51 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="35" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2633,7 +2766,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2665,10 +2798,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2700,7 +2832,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -2876,9 +3007,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="H9:Q22"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="7" width="9.140625" style="31"/>
     <col min="8" max="8" width="5" style="31" customWidth="1"/>
@@ -2892,7 +3023,7 @@
     <col min="18" max="16384" width="9.140625" style="31"/>
   </cols>
   <sheetData>
-    <row r="9" spans="8:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="8:17" ht="45" customHeight="1">
       <c r="H9" s="111" t="s">
         <v>0</v>
       </c>
@@ -2906,7 +3037,7 @@
       <c r="P9" s="112"/>
       <c r="Q9" s="113"/>
     </row>
-    <row r="10" spans="8:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="8:17" ht="30" customHeight="1">
       <c r="H10" s="55" t="s">
         <v>1</v>
       </c>
@@ -2938,7 +3069,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="8:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="8:17">
       <c r="H11" s="57">
         <v>1</v>
       </c>
@@ -2964,7 +3095,7 @@
       <c r="P11" s="60"/>
       <c r="Q11" s="60"/>
     </row>
-    <row r="12" spans="8:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="8:17">
       <c r="H12" s="57">
         <v>2</v>
       </c>
@@ -2988,7 +3119,7 @@
       <c r="P12" s="60"/>
       <c r="Q12" s="60"/>
     </row>
-    <row r="13" spans="8:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="8:17">
       <c r="H13" s="57">
         <v>3</v>
       </c>
@@ -3010,7 +3141,7 @@
       <c r="P13" s="60"/>
       <c r="Q13" s="60"/>
     </row>
-    <row r="14" spans="8:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="8:17">
       <c r="H14" s="57">
         <v>4</v>
       </c>
@@ -3032,7 +3163,7 @@
       <c r="P14" s="60"/>
       <c r="Q14" s="60"/>
     </row>
-    <row r="15" spans="8:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="8:17">
       <c r="H15" s="57">
         <v>5</v>
       </c>
@@ -3052,7 +3183,7 @@
       <c r="P15" s="60"/>
       <c r="Q15" s="60"/>
     </row>
-    <row r="16" spans="8:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="8:17">
       <c r="H16" s="57">
         <v>6</v>
       </c>
@@ -3076,7 +3207,7 @@
       <c r="P16" s="60"/>
       <c r="Q16" s="60"/>
     </row>
-    <row r="17" spans="8:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="8:17">
       <c r="H17" s="57">
         <v>7</v>
       </c>
@@ -3098,7 +3229,7 @@
       <c r="P17" s="60"/>
       <c r="Q17" s="60"/>
     </row>
-    <row r="18" spans="8:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="8:17">
       <c r="H18" s="57">
         <v>8</v>
       </c>
@@ -3116,7 +3247,7 @@
       <c r="P18" s="60"/>
       <c r="Q18" s="60"/>
     </row>
-    <row r="19" spans="8:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="8:17">
       <c r="H19" s="57">
         <v>9</v>
       </c>
@@ -3136,7 +3267,7 @@
       <c r="P19" s="60"/>
       <c r="Q19" s="60"/>
     </row>
-    <row r="20" spans="8:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="8:17">
       <c r="H20" s="57">
         <v>10</v>
       </c>
@@ -3154,7 +3285,7 @@
       <c r="P20" s="60"/>
       <c r="Q20" s="60"/>
     </row>
-    <row r="21" spans="8:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="8:17">
       <c r="H21" s="57">
         <v>11</v>
       </c>
@@ -3172,7 +3303,7 @@
       <c r="P21" s="60"/>
       <c r="Q21" s="60"/>
     </row>
-    <row r="22" spans="8:17" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="22" spans="8:17" ht="15.75">
       <c r="H22" s="114" t="s">
         <v>19</v>
       </c>
@@ -3228,9 +3359,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="H9:AL42"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="7" width="9.140625" style="31"/>
     <col min="8" max="8" width="5" style="31" customWidth="1"/>
@@ -3253,7 +3384,7 @@
     <col min="39" max="16384" width="9.140625" style="31"/>
   </cols>
   <sheetData>
-    <row r="9" spans="8:38" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="8:38" ht="45" customHeight="1">
       <c r="H9" s="117" t="s">
         <v>0</v>
       </c>
@@ -3288,7 +3419,7 @@
       <c r="AK9" s="118"/>
       <c r="AL9" s="118"/>
     </row>
-    <row r="10" spans="8:38" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="8:38" ht="30" customHeight="1">
       <c r="H10" s="32" t="s">
         <v>1</v>
       </c>
@@ -3383,7 +3514,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="8:38" ht="15.75">
       <c r="H11" s="46">
         <v>1</v>
       </c>
@@ -3427,7 +3558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="8:38" ht="15.75">
       <c r="H12" s="46">
         <v>2</v>
       </c>
@@ -3475,7 +3606,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="8:38" ht="15.75">
       <c r="H13" s="46">
         <v>3</v>
       </c>
@@ -3533,7 +3664,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="8:38" ht="15.75">
       <c r="H14" s="46">
         <v>4</v>
       </c>
@@ -3579,7 +3710,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="8:38" ht="15.75">
       <c r="H15" s="46">
         <v>5</v>
       </c>
@@ -3627,7 +3758,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="8:38" ht="15.75">
       <c r="H16" s="46">
         <v>6</v>
       </c>
@@ -3685,7 +3816,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="8:38" ht="15.75">
       <c r="H17" s="46">
         <v>7</v>
       </c>
@@ -3741,7 +3872,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="8:38" ht="15.75">
       <c r="H18" s="46">
         <v>8</v>
       </c>
@@ -3799,7 +3930,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="8:38" ht="15.75">
       <c r="H19" s="46">
         <v>9</v>
       </c>
@@ -3843,7 +3974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="8:38" ht="15.75">
       <c r="H20" s="46">
         <v>10</v>
       </c>
@@ -3887,7 +4018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="8:38" ht="15.75">
       <c r="H21" s="46">
         <v>11</v>
       </c>
@@ -3931,7 +4062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="8:38" ht="15.75">
       <c r="H22" s="46">
         <v>12</v>
       </c>
@@ -3983,7 +4114,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="8:38" ht="15.75">
       <c r="H23" s="46">
         <v>13</v>
       </c>
@@ -4051,7 +4182,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="8:38" ht="15.75">
       <c r="H24" s="46">
         <v>14</v>
       </c>
@@ -4109,7 +4240,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="8:38" ht="15.75">
       <c r="H25" s="46">
         <v>15</v>
       </c>
@@ -4169,7 +4300,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="8:38" ht="15.75">
       <c r="H26" s="46">
         <v>16</v>
       </c>
@@ -4227,7 +4358,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="8:38" ht="15.75">
       <c r="H27" s="46">
         <v>17</v>
       </c>
@@ -4295,7 +4426,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="8:38" ht="15.75">
       <c r="H28" s="46">
         <v>18</v>
       </c>
@@ -4347,7 +4478,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="8:38" ht="15.75">
       <c r="H29" s="46">
         <v>19</v>
       </c>
@@ -4395,7 +4526,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="8:38" ht="15.75">
       <c r="H30" s="46">
         <v>20</v>
       </c>
@@ -4445,7 +4576,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="8:38" ht="15.75">
       <c r="H31" s="46">
         <v>21</v>
       </c>
@@ -4487,7 +4618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="8:38" ht="15.75">
       <c r="H32" s="46">
         <v>22</v>
       </c>
@@ -4529,7 +4660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="8:38" ht="15.75">
       <c r="H33" s="46">
         <v>23</v>
       </c>
@@ -4571,7 +4702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="8:38" ht="15.75">
       <c r="H34" s="46">
         <v>24</v>
       </c>
@@ -4627,7 +4758,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="8:38" ht="15.75">
       <c r="H35" s="46">
         <v>25</v>
       </c>
@@ -4671,7 +4802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="8:38" ht="15.75">
       <c r="H36" s="46">
         <v>26</v>
       </c>
@@ -4719,7 +4850,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="8:38" ht="15.75">
       <c r="H37" s="46">
         <v>27</v>
       </c>
@@ -4763,7 +4894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="8:38" ht="15.75">
       <c r="H38" s="46">
         <v>28</v>
       </c>
@@ -4815,7 +4946,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="8:38" ht="15.75">
       <c r="H39" s="46">
         <v>29</v>
       </c>
@@ -4867,7 +4998,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="8:38" ht="15.75">
       <c r="H40" s="46">
         <v>30</v>
       </c>
@@ -4915,7 +5046,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="8:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="8:38" ht="15.75">
       <c r="H41" s="46">
         <v>31</v>
       </c>
@@ -4965,7 +5096,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="8:38" ht="15.75" x14ac:dyDescent="0.3">
+    <row r="42" spans="8:38" ht="15.75">
       <c r="H42" s="119" t="s">
         <v>19</v>
       </c>
@@ -5100,9 +5231,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AK45"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="15.7109375" style="3" customWidth="1"/>
     <col min="4" max="4" width="26" style="3" customWidth="1"/>
@@ -5134,67 +5265,67 @@
     <col min="39" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="131"/>
-      <c r="B1" s="132"/>
-      <c r="C1" s="133"/>
+    <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
+      <c r="A1" s="125"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="127"/>
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="137" t="s">
+      <c r="E1" s="131" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="137"/>
-      <c r="G1" s="137"/>
-      <c r="H1" s="137"/>
-      <c r="I1" s="137"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="137"/>
-      <c r="L1" s="138" t="s">
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="132" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="138"/>
-      <c r="N1" s="138"/>
-      <c r="O1" s="138"/>
-      <c r="P1" s="138"/>
-      <c r="Q1" s="138"/>
-      <c r="R1" s="138"/>
-      <c r="S1" s="139" t="s">
+      <c r="M1" s="132"/>
+      <c r="N1" s="132"/>
+      <c r="O1" s="132"/>
+      <c r="P1" s="132"/>
+      <c r="Q1" s="132"/>
+      <c r="R1" s="132"/>
+      <c r="S1" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="T1" s="139"/>
-      <c r="U1" s="140" t="s">
+      <c r="T1" s="133"/>
+      <c r="U1" s="134" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="141"/>
-      <c r="W1" s="141"/>
-      <c r="X1" s="141"/>
-      <c r="Y1" s="142"/>
-      <c r="Z1" s="143" t="s">
+      <c r="V1" s="135"/>
+      <c r="W1" s="135"/>
+      <c r="X1" s="135"/>
+      <c r="Y1" s="136"/>
+      <c r="Z1" s="137" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="143"/>
-      <c r="AB1" s="143"/>
-      <c r="AC1" s="143"/>
-      <c r="AD1" s="143"/>
-      <c r="AE1" s="126" t="s">
+      <c r="AA1" s="137"/>
+      <c r="AB1" s="137"/>
+      <c r="AC1" s="137"/>
+      <c r="AD1" s="137"/>
+      <c r="AE1" s="120" t="s">
         <v>42</v>
       </c>
-      <c r="AF1" s="126"/>
-      <c r="AG1" s="126"/>
-      <c r="AH1" s="127" t="s">
+      <c r="AF1" s="120"/>
+      <c r="AG1" s="120"/>
+      <c r="AH1" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="AI1" s="127"/>
-      <c r="AJ1" s="127"/>
-      <c r="AK1" s="128" t="s">
+      <c r="AI1" s="121"/>
+      <c r="AJ1" s="121"/>
+      <c r="AK1" s="122" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="134"/>
-      <c r="B2" s="135"/>
-      <c r="C2" s="136"/>
+    <row r="2" spans="1:37" s="2" customFormat="1" ht="30" customHeight="1">
+      <c r="A2" s="128"/>
+      <c r="B2" s="129"/>
+      <c r="C2" s="130"/>
       <c r="D2" s="5" t="s">
         <v>44</v>
       </c>
@@ -5288,9 +5419,9 @@
       <c r="AH2" s="12"/>
       <c r="AI2" s="12"/>
       <c r="AJ2" s="12"/>
-      <c r="AK2" s="129"/>
-    </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK2" s="123"/>
+    </row>
+    <row r="3" spans="1:37">
       <c r="A3" s="13" t="s">
         <v>1</v>
       </c>
@@ -5399,9 +5530,9 @@
       <c r="AJ3" s="20">
         <v>2</v>
       </c>
-      <c r="AK3" s="130"/>
-    </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK3" s="124"/>
+    </row>
+    <row r="4" spans="1:37">
       <c r="A4" s="21">
         <v>1</v>
       </c>
@@ -5461,7 +5592,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37">
       <c r="A5" s="21">
         <v>2</v>
       </c>
@@ -5513,7 +5644,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37">
       <c r="A6" s="21">
         <v>3</v>
       </c>
@@ -5589,7 +5720,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:37">
       <c r="A7" s="21">
         <v>4</v>
       </c>
@@ -5663,7 +5794,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37">
       <c r="A8" s="21">
         <v>5</v>
       </c>
@@ -5733,7 +5864,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:37">
       <c r="A9" s="21">
         <v>6</v>
       </c>
@@ -5801,7 +5932,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:37">
       <c r="A10" s="21">
         <v>7</v>
       </c>
@@ -5859,7 +5990,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:37">
       <c r="A11" s="21">
         <v>8</v>
       </c>
@@ -5919,7 +6050,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:37">
       <c r="A12" s="21">
         <v>9</v>
       </c>
@@ -5989,7 +6120,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:37">
       <c r="A13" s="21">
         <v>10</v>
       </c>
@@ -6061,7 +6192,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:37">
       <c r="A14" s="21">
         <v>11</v>
       </c>
@@ -6143,7 +6274,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:37">
       <c r="A15" s="21">
         <v>12</v>
       </c>
@@ -6211,7 +6342,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:37">
       <c r="A16" s="21">
         <v>13</v>
       </c>
@@ -6271,7 +6402,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:37">
       <c r="A17" s="21">
         <v>14</v>
       </c>
@@ -6329,7 +6460,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:37">
       <c r="A18" s="21">
         <v>15</v>
       </c>
@@ -6387,7 +6518,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:37">
       <c r="A19" s="69">
         <v>16</v>
       </c>
@@ -6449,7 +6580,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:37">
       <c r="A20" s="69">
         <v>17</v>
       </c>
@@ -6527,7 +6658,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:37">
       <c r="A21" s="69">
         <v>18</v>
       </c>
@@ -6607,7 +6738,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:37">
       <c r="A22" s="30">
         <v>19</v>
       </c>
@@ -6669,7 +6800,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:37">
       <c r="A23" s="84">
         <v>20</v>
       </c>
@@ -6731,7 +6862,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:37">
       <c r="A24" s="21">
         <v>21</v>
       </c>
@@ -6801,7 +6932,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:37">
       <c r="A25" s="21">
         <v>22</v>
       </c>
@@ -6869,7 +7000,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:37">
       <c r="A26" s="69">
         <v>23</v>
       </c>
@@ -6931,7 +7062,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:37">
       <c r="A27" s="69">
         <v>24</v>
       </c>
@@ -7003,7 +7134,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:37">
       <c r="A28" s="69">
         <v>25</v>
       </c>
@@ -7079,7 +7210,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:37">
       <c r="A29" s="30">
         <v>26</v>
       </c>
@@ -7153,7 +7284,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:37">
       <c r="A30" s="84">
         <v>27</v>
       </c>
@@ -7211,7 +7342,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:37">
       <c r="A31" s="21">
         <v>28</v>
       </c>
@@ -7277,7 +7408,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:37">
       <c r="A32" s="21">
         <v>29</v>
       </c>
@@ -7339,7 +7470,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:37">
       <c r="A33" s="21">
         <v>30</v>
       </c>
@@ -7393,7 +7524,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:37">
       <c r="A34" s="21">
         <v>31</v>
       </c>
@@ -7449,13 +7580,13 @@
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="123" t="s">
+    <row r="35" spans="1:37" ht="30" customHeight="1">
+      <c r="A35" s="141" t="s">
         <v>77</v>
       </c>
-      <c r="B35" s="124"/>
-      <c r="C35" s="124"/>
-      <c r="D35" s="125"/>
+      <c r="B35" s="142"/>
+      <c r="C35" s="142"/>
+      <c r="D35" s="143"/>
       <c r="E35" s="106">
         <f>COUNTA(E4:E34)</f>
         <v>14</v>
@@ -7586,95 +7717,103 @@
       </c>
       <c r="AK35" s="25"/>
     </row>
-    <row r="36" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AG36" s="120" t="s">
+    <row r="36" spans="1:37" ht="30" customHeight="1">
+      <c r="AG36" s="138" t="s">
         <v>78</v>
       </c>
-      <c r="AH36" s="121"/>
-      <c r="AI36" s="121"/>
-      <c r="AJ36" s="122"/>
+      <c r="AH36" s="139"/>
+      <c r="AI36" s="139"/>
+      <c r="AJ36" s="140"/>
       <c r="AK36" s="107">
         <f>ROUND(AVERAGE(AK4:AK34),0)</f>
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AG37" s="120" t="s">
+    <row r="37" spans="1:37" ht="30" customHeight="1">
+      <c r="AG37" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="AH37" s="121"/>
-      <c r="AI37" s="121"/>
-      <c r="AJ37" s="122"/>
+      <c r="AH37" s="139"/>
+      <c r="AI37" s="139"/>
+      <c r="AJ37" s="140"/>
       <c r="AK37" s="107">
         <f>MAX(AK4:AK34)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AG38" s="120" t="s">
+    <row r="38" spans="1:37" ht="30" customHeight="1">
+      <c r="AG38" s="138" t="s">
         <v>80</v>
       </c>
-      <c r="AH38" s="121"/>
-      <c r="AI38" s="121"/>
-      <c r="AJ38" s="122"/>
+      <c r="AH38" s="139"/>
+      <c r="AI38" s="139"/>
+      <c r="AJ38" s="140"/>
       <c r="AK38" s="107">
         <f>MIN(AK4:AK34)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AG39" s="120" t="s">
+    <row r="39" spans="1:37" ht="30" customHeight="1">
+      <c r="AG39" s="138" t="s">
         <v>81</v>
       </c>
-      <c r="AH39" s="121"/>
-      <c r="AI39" s="121"/>
-      <c r="AJ39" s="122"/>
+      <c r="AH39" s="139"/>
+      <c r="AI39" s="139"/>
+      <c r="AJ39" s="140"/>
       <c r="AK39" s="107">
         <f>COUNTIF(AK4:AK34, "&gt;"&amp;AK36)</f>
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AG40" s="120" t="s">
+    <row r="40" spans="1:37" ht="30" customHeight="1">
+      <c r="AG40" s="138" t="s">
         <v>82</v>
       </c>
-      <c r="AH40" s="121"/>
-      <c r="AI40" s="121"/>
-      <c r="AJ40" s="122"/>
+      <c r="AH40" s="139"/>
+      <c r="AI40" s="139"/>
+      <c r="AJ40" s="140"/>
       <c r="AK40" s="107">
         <f>COUNTIF(AK4:AK34, "&lt;"&amp;AK36)</f>
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AG41" s="120" t="s">
+    <row r="41" spans="1:37" ht="30" customHeight="1">
+      <c r="AG41" s="138" t="s">
         <v>83</v>
       </c>
-      <c r="AH41" s="121"/>
-      <c r="AI41" s="121"/>
-      <c r="AJ41" s="122"/>
+      <c r="AH41" s="139"/>
+      <c r="AI41" s="139"/>
+      <c r="AJ41" s="140"/>
       <c r="AK41" s="107">
         <f>COUNTIF(AK4:AK34, "&gt;"&amp;20)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AG42" s="120" t="s">
+    <row r="42" spans="1:37" ht="30" customHeight="1">
+      <c r="AG42" s="138" t="s">
         <v>84</v>
       </c>
-      <c r="AH42" s="121"/>
-      <c r="AI42" s="121"/>
-      <c r="AJ42" s="122"/>
+      <c r="AH42" s="139"/>
+      <c r="AI42" s="139"/>
+      <c r="AJ42" s="140"/>
       <c r="AK42" s="107">
         <f>COUNTIF(AK4:AK34, "&lt;"&amp;20)</f>
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:37" ht="30" customHeight="1"/>
+    <row r="44" spans="1:37" ht="30" customHeight="1"/>
+    <row r="45" spans="1:37" ht="30" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="AG40:AJ40"/>
+    <mergeCell ref="AG41:AJ41"/>
+    <mergeCell ref="AG42:AJ42"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="AG36:AJ36"/>
+    <mergeCell ref="AG37:AJ37"/>
+    <mergeCell ref="AG38:AJ38"/>
+    <mergeCell ref="AG39:AJ39"/>
     <mergeCell ref="AE1:AG1"/>
     <mergeCell ref="AH1:AJ1"/>
     <mergeCell ref="AK1:AK3"/>
@@ -7684,14 +7823,6 @@
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="U1:Y1"/>
     <mergeCell ref="Z1:AD1"/>
-    <mergeCell ref="AG40:AJ40"/>
-    <mergeCell ref="AG41:AJ41"/>
-    <mergeCell ref="AG42:AJ42"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="AG36:AJ36"/>
-    <mergeCell ref="AG37:AJ37"/>
-    <mergeCell ref="AG38:AJ38"/>
-    <mergeCell ref="AG39:AJ39"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:AJ34">
     <cfRule type="expression" dxfId="12" priority="7">
@@ -7735,9 +7866,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AK44"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="15.7109375" style="3" customWidth="1"/>
     <col min="4" max="4" width="26" style="3" customWidth="1"/>
@@ -7768,67 +7899,67 @@
     <col min="39" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="131"/>
-      <c r="B1" s="132"/>
-      <c r="C1" s="133"/>
+    <row r="1" spans="1:37" s="1" customFormat="1" ht="30" customHeight="1">
+      <c r="A1" s="125"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="127"/>
       <c r="D1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="137" t="s">
+      <c r="E1" s="131" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="137"/>
-      <c r="G1" s="137"/>
-      <c r="H1" s="137"/>
-      <c r="I1" s="137"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="137"/>
-      <c r="L1" s="138" t="s">
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
+      <c r="K1" s="131"/>
+      <c r="L1" s="132" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="138"/>
-      <c r="N1" s="138"/>
-      <c r="O1" s="138"/>
-      <c r="P1" s="138"/>
-      <c r="Q1" s="138"/>
+      <c r="M1" s="132"/>
+      <c r="N1" s="132"/>
+      <c r="O1" s="132"/>
+      <c r="P1" s="132"/>
+      <c r="Q1" s="132"/>
       <c r="R1" s="144" t="s">
         <v>39</v>
       </c>
       <c r="S1" s="145"/>
       <c r="T1" s="146"/>
-      <c r="U1" s="140" t="s">
+      <c r="U1" s="134" t="s">
         <v>40</v>
       </c>
-      <c r="V1" s="141"/>
-      <c r="W1" s="141"/>
-      <c r="X1" s="141"/>
-      <c r="Y1" s="142"/>
-      <c r="Z1" s="143" t="s">
+      <c r="V1" s="135"/>
+      <c r="W1" s="135"/>
+      <c r="X1" s="135"/>
+      <c r="Y1" s="136"/>
+      <c r="Z1" s="137" t="s">
         <v>41</v>
       </c>
-      <c r="AA1" s="143"/>
-      <c r="AB1" s="143"/>
-      <c r="AC1" s="143"/>
-      <c r="AD1" s="143"/>
-      <c r="AE1" s="126" t="s">
+      <c r="AA1" s="137"/>
+      <c r="AB1" s="137"/>
+      <c r="AC1" s="137"/>
+      <c r="AD1" s="137"/>
+      <c r="AE1" s="120" t="s">
         <v>42</v>
       </c>
-      <c r="AF1" s="126"/>
-      <c r="AG1" s="126"/>
-      <c r="AH1" s="127" t="s">
+      <c r="AF1" s="120"/>
+      <c r="AG1" s="120"/>
+      <c r="AH1" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="AI1" s="127"/>
-      <c r="AJ1" s="127"/>
-      <c r="AK1" s="128" t="s">
+      <c r="AI1" s="121"/>
+      <c r="AJ1" s="121"/>
+      <c r="AK1" s="122" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:37" s="2" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="134"/>
-      <c r="B2" s="135"/>
-      <c r="C2" s="136"/>
+    <row r="2" spans="1:37" s="2" customFormat="1" ht="45" customHeight="1">
+      <c r="A2" s="128"/>
+      <c r="B2" s="129"/>
+      <c r="C2" s="130"/>
       <c r="D2" s="5" t="s">
         <v>44</v>
       </c>
@@ -7914,17 +8045,17 @@
         <v>61</v>
       </c>
       <c r="AF2" s="11" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="AG2" s="11" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="AH2" s="12"/>
       <c r="AI2" s="12"/>
       <c r="AJ2" s="12"/>
-      <c r="AK2" s="129"/>
-    </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK2" s="123"/>
+    </row>
+    <row r="3" spans="1:37">
       <c r="A3" s="13" t="s">
         <v>1</v>
       </c>
@@ -8033,9 +8164,9 @@
       <c r="AJ3" s="20">
         <v>1</v>
       </c>
-      <c r="AK3" s="130"/>
-    </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AK3" s="124"/>
+    </row>
+    <row r="4" spans="1:37">
       <c r="A4" s="30">
         <v>1</v>
       </c>
@@ -8107,7 +8238,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37">
       <c r="A5" s="30">
         <v>2</v>
       </c>
@@ -8163,7 +8294,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37">
       <c r="A6" s="30">
         <v>3</v>
       </c>
@@ -8227,7 +8358,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:37">
       <c r="A7" s="30">
         <v>4</v>
       </c>
@@ -8293,7 +8424,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37">
       <c r="A8" s="30">
         <v>5</v>
       </c>
@@ -8308,7 +8439,9 @@
       </c>
       <c r="E8" s="62"/>
       <c r="F8" s="62"/>
-      <c r="G8" s="62"/>
+      <c r="G8" s="62" t="s">
+        <v>12</v>
+      </c>
       <c r="H8" s="62"/>
       <c r="I8" s="62" t="s">
         <v>12</v>
@@ -8336,164 +8469,204 @@
       </c>
       <c r="AA8" s="65"/>
       <c r="AB8" s="65"/>
-      <c r="AC8" s="65"/>
-      <c r="AD8" s="65"/>
+      <c r="AC8" s="65" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD8" s="65" t="s">
+        <v>12</v>
+      </c>
       <c r="AE8" s="66"/>
       <c r="AF8" s="66"/>
       <c r="AG8" s="66"/>
-      <c r="AH8" s="67"/>
+      <c r="AH8" s="67" t="s">
+        <v>12</v>
+      </c>
       <c r="AI8" s="67"/>
       <c r="AJ8" s="67"/>
       <c r="AK8" s="25">
         <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37" ht="15.75" thickBot="1">
+      <c r="A9" s="69">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A9" s="30">
-        <v>6</v>
-      </c>
-      <c r="B9" s="110" t="s">
+      <c r="B9" s="147" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="148">
         <v>46271</v>
       </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="62"/>
-      <c r="F9" s="62"/>
-      <c r="G9" s="62"/>
-      <c r="H9" s="62"/>
-      <c r="I9" s="62"/>
-      <c r="J9" s="62"/>
-      <c r="K9" s="62"/>
-      <c r="L9" s="63"/>
-      <c r="M9" s="63"/>
-      <c r="N9" s="63"/>
-      <c r="O9" s="63"/>
-      <c r="P9" s="63"/>
-      <c r="Q9" s="63"/>
-      <c r="R9" s="24"/>
-      <c r="S9" s="24"/>
-      <c r="T9" s="24"/>
-      <c r="U9" s="64"/>
-      <c r="V9" s="64"/>
-      <c r="W9" s="64"/>
-      <c r="X9" s="64"/>
-      <c r="Y9" s="64"/>
-      <c r="Z9" s="65"/>
-      <c r="AA9" s="65"/>
-      <c r="AB9" s="65"/>
-      <c r="AC9" s="65"/>
-      <c r="AD9" s="65"/>
-      <c r="AE9" s="66"/>
-      <c r="AF9" s="66"/>
-      <c r="AG9" s="66"/>
-      <c r="AH9" s="67"/>
-      <c r="AI9" s="67"/>
-      <c r="AJ9" s="67"/>
-      <c r="AK9" s="25">
+      <c r="D9" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="70"/>
+      <c r="F9" s="70"/>
+      <c r="G9" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="K9" s="70" t="s">
+        <v>12</v>
+      </c>
+      <c r="L9" s="71"/>
+      <c r="M9" s="71"/>
+      <c r="N9" s="71"/>
+      <c r="O9" s="71"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="149"/>
+      <c r="S9" s="149"/>
+      <c r="T9" s="149"/>
+      <c r="U9" s="73"/>
+      <c r="V9" s="73"/>
+      <c r="W9" s="73"/>
+      <c r="X9" s="73"/>
+      <c r="Y9" s="73"/>
+      <c r="Z9" s="74"/>
+      <c r="AA9" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB9" s="74"/>
+      <c r="AC9" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD9" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE9" s="75"/>
+      <c r="AF9" s="75"/>
+      <c r="AG9" s="75"/>
+      <c r="AH9" s="76" t="s">
+        <v>12</v>
+      </c>
+      <c r="AI9" s="76" t="s">
+        <v>12</v>
+      </c>
+      <c r="AJ9" s="76"/>
+      <c r="AK9" s="93">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37" ht="15.75" thickBot="1">
+      <c r="A10" s="151">
+        <v>7</v>
+      </c>
+      <c r="B10" s="152" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="153">
+        <v>46272</v>
+      </c>
+      <c r="D10" s="152" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="154"/>
+      <c r="F10" s="154"/>
+      <c r="G10" s="154" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="154"/>
+      <c r="I10" s="154"/>
+      <c r="J10" s="154"/>
+      <c r="K10" s="154"/>
+      <c r="L10" s="155" t="s">
+        <v>12</v>
+      </c>
+      <c r="M10" s="155" t="s">
+        <v>12</v>
+      </c>
+      <c r="N10" s="155" t="s">
+        <v>12</v>
+      </c>
+      <c r="O10" s="155" t="s">
+        <v>12</v>
+      </c>
+      <c r="P10" s="155"/>
+      <c r="Q10" s="155"/>
+      <c r="R10" s="156"/>
+      <c r="S10" s="156"/>
+      <c r="T10" s="156"/>
+      <c r="U10" s="157"/>
+      <c r="V10" s="157"/>
+      <c r="W10" s="157"/>
+      <c r="X10" s="157"/>
+      <c r="Y10" s="157"/>
+      <c r="Z10" s="158"/>
+      <c r="AA10" s="158"/>
+      <c r="AB10" s="158"/>
+      <c r="AC10" s="158"/>
+      <c r="AD10" s="158"/>
+      <c r="AE10" s="159"/>
+      <c r="AF10" s="159" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG10" s="159"/>
+      <c r="AH10" s="160"/>
+      <c r="AI10" s="160"/>
+      <c r="AJ10" s="160"/>
+      <c r="AK10" s="161">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37">
+      <c r="A11" s="84">
+        <v>8</v>
+      </c>
+      <c r="B11" s="84" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="150">
+        <v>46273</v>
+      </c>
+      <c r="D11" s="84"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
+      <c r="J11" s="77"/>
+      <c r="K11" s="77"/>
+      <c r="L11" s="78"/>
+      <c r="M11" s="78"/>
+      <c r="N11" s="78"/>
+      <c r="O11" s="78"/>
+      <c r="P11" s="78"/>
+      <c r="Q11" s="78"/>
+      <c r="R11" s="79"/>
+      <c r="S11" s="79"/>
+      <c r="T11" s="79"/>
+      <c r="U11" s="80"/>
+      <c r="V11" s="80"/>
+      <c r="W11" s="80"/>
+      <c r="X11" s="80"/>
+      <c r="Y11" s="80"/>
+      <c r="Z11" s="81"/>
+      <c r="AA11" s="81"/>
+      <c r="AB11" s="81"/>
+      <c r="AC11" s="81"/>
+      <c r="AD11" s="81"/>
+      <c r="AE11" s="82"/>
+      <c r="AF11" s="82"/>
+      <c r="AG11" s="82"/>
+      <c r="AH11" s="83"/>
+      <c r="AI11" s="83"/>
+      <c r="AJ11" s="83"/>
+      <c r="AK11" s="94">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A10" s="30">
-        <v>7</v>
-      </c>
-      <c r="B10" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="22">
-        <v>46272</v>
-      </c>
-      <c r="D10" s="30"/>
-      <c r="E10" s="62"/>
-      <c r="F10" s="62"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="62"/>
-      <c r="I10" s="62"/>
-      <c r="J10" s="62"/>
-      <c r="K10" s="62"/>
-      <c r="L10" s="63"/>
-      <c r="M10" s="63"/>
-      <c r="N10" s="63"/>
-      <c r="O10" s="63"/>
-      <c r="P10" s="63"/>
-      <c r="Q10" s="63"/>
-      <c r="R10" s="27"/>
-      <c r="S10" s="27"/>
-      <c r="T10" s="27"/>
-      <c r="U10" s="64"/>
-      <c r="V10" s="64"/>
-      <c r="W10" s="64"/>
-      <c r="X10" s="64"/>
-      <c r="Y10" s="64"/>
-      <c r="Z10" s="65"/>
-      <c r="AA10" s="65"/>
-      <c r="AB10" s="65"/>
-      <c r="AC10" s="65"/>
-      <c r="AD10" s="65"/>
-      <c r="AE10" s="66"/>
-      <c r="AF10" s="66"/>
-      <c r="AG10" s="66"/>
-      <c r="AH10" s="67"/>
-      <c r="AI10" s="67"/>
-      <c r="AJ10" s="67"/>
-      <c r="AK10" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A11" s="30">
-        <v>8</v>
-      </c>
-      <c r="B11" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="22">
-        <v>46273</v>
-      </c>
-      <c r="D11" s="30"/>
-      <c r="E11" s="62"/>
-      <c r="F11" s="62"/>
-      <c r="G11" s="62"/>
-      <c r="H11" s="62"/>
-      <c r="I11" s="62"/>
-      <c r="J11" s="62"/>
-      <c r="K11" s="62"/>
-      <c r="L11" s="63"/>
-      <c r="M11" s="63"/>
-      <c r="N11" s="63"/>
-      <c r="O11" s="63"/>
-      <c r="P11" s="63"/>
-      <c r="Q11" s="63"/>
-      <c r="R11" s="29"/>
-      <c r="S11" s="29"/>
-      <c r="T11" s="29"/>
-      <c r="U11" s="64"/>
-      <c r="V11" s="64"/>
-      <c r="W11" s="64"/>
-      <c r="X11" s="64"/>
-      <c r="Y11" s="64"/>
-      <c r="Z11" s="65"/>
-      <c r="AA11" s="65"/>
-      <c r="AB11" s="65"/>
-      <c r="AC11" s="65"/>
-      <c r="AD11" s="65"/>
-      <c r="AE11" s="66"/>
-      <c r="AF11" s="66"/>
-      <c r="AG11" s="66"/>
-      <c r="AH11" s="67"/>
-      <c r="AI11" s="67"/>
-      <c r="AJ11" s="67"/>
-      <c r="AK11" s="25">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:37">
       <c r="A12" s="30">
         <v>9</v>
       </c>
@@ -8541,7 +8714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:37">
       <c r="A13" s="30">
         <v>10</v>
       </c>
@@ -8589,7 +8762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:37">
       <c r="A14" s="30">
         <v>11</v>
       </c>
@@ -8637,7 +8810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:37">
       <c r="A15" s="30">
         <v>12</v>
       </c>
@@ -8685,7 +8858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:37">
       <c r="A16" s="30">
         <v>13</v>
       </c>
@@ -8733,7 +8906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:37">
       <c r="A17" s="30">
         <v>14</v>
       </c>
@@ -8781,7 +8954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:37">
       <c r="A18" s="30">
         <v>15</v>
       </c>
@@ -8829,7 +9002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:37">
       <c r="A19" s="69">
         <v>16</v>
       </c>
@@ -8877,7 +9050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:37">
       <c r="A20" s="69">
         <v>17</v>
       </c>
@@ -8925,7 +9098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:37">
       <c r="A21" s="69">
         <v>18</v>
       </c>
@@ -8973,7 +9146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:37">
       <c r="A22" s="30">
         <v>19</v>
       </c>
@@ -9021,7 +9194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:37">
       <c r="A23" s="84">
         <v>20</v>
       </c>
@@ -9069,7 +9242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:37">
       <c r="A24" s="30">
         <v>21</v>
       </c>
@@ -9117,7 +9290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:37">
       <c r="A25" s="30">
         <v>22</v>
       </c>
@@ -9165,7 +9338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:37">
       <c r="A26" s="69">
         <v>23</v>
       </c>
@@ -9213,7 +9386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:37">
       <c r="A27" s="69">
         <v>24</v>
       </c>
@@ -9261,7 +9434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:37">
       <c r="A28" s="69">
         <v>25</v>
       </c>
@@ -9309,7 +9482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:37">
       <c r="A29" s="30">
         <v>26</v>
       </c>
@@ -9357,7 +9530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:37">
       <c r="A30" s="84">
         <v>27</v>
       </c>
@@ -9405,7 +9578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:37">
       <c r="A31" s="30">
         <v>28</v>
       </c>
@@ -9453,7 +9626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:37">
       <c r="A32" s="30">
         <v>29</v>
       </c>
@@ -9501,7 +9674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:37">
       <c r="A33" s="30">
         <v>30</v>
       </c>
@@ -9549,13 +9722,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="123" t="s">
+    <row r="34" spans="1:37" ht="30" customHeight="1">
+      <c r="A34" s="141" t="s">
         <v>77</v>
       </c>
-      <c r="B34" s="124"/>
-      <c r="C34" s="124"/>
-      <c r="D34" s="125"/>
+      <c r="B34" s="142"/>
+      <c r="C34" s="142"/>
+      <c r="D34" s="143"/>
       <c r="E34" s="106">
         <f t="shared" ref="E34:AJ34" si="1">COUNTA(E4:E33)</f>
         <v>1</v>
@@ -9566,7 +9739,7 @@
       </c>
       <c r="G34" s="106">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H34" s="106">
         <f t="shared" si="1"/>
@@ -9574,31 +9747,31 @@
       </c>
       <c r="I34" s="106">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J34" s="106">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K34" s="106">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="63">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M34" s="63">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N34" s="63">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O34" s="63">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P34" s="63">
         <f t="shared" si="1"/>
@@ -9646,7 +9819,7 @@
       </c>
       <c r="AA34" s="65">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB34" s="65">
         <f t="shared" si="1"/>
@@ -9654,11 +9827,11 @@
       </c>
       <c r="AC34" s="65">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD34" s="65">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AE34" s="66">
         <f t="shared" si="1"/>
@@ -9666,7 +9839,7 @@
       </c>
       <c r="AF34" s="66">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG34" s="66">
         <f t="shared" si="1"/>
@@ -9674,11 +9847,11 @@
       </c>
       <c r="AH34" s="67">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI34" s="67">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ34" s="67">
         <f t="shared" si="1"/>
@@ -9686,112 +9859,112 @@
       </c>
       <c r="AK34" s="25"/>
     </row>
-    <row r="35" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AG35" s="120" t="s">
+    <row r="35" spans="1:37" ht="30" customHeight="1">
+      <c r="AG35" s="138" t="s">
         <v>78</v>
       </c>
-      <c r="AH35" s="121"/>
-      <c r="AI35" s="121"/>
-      <c r="AJ35" s="122"/>
+      <c r="AH35" s="139"/>
+      <c r="AI35" s="139"/>
+      <c r="AJ35" s="140"/>
       <c r="AK35" s="107">
         <f>ROUND(AVERAGE(AK4:AK33),0)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AG36" s="120" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:37" ht="30" customHeight="1">
+      <c r="AG36" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="AH36" s="121"/>
-      <c r="AI36" s="121"/>
-      <c r="AJ36" s="122"/>
+      <c r="AH36" s="139"/>
+      <c r="AI36" s="139"/>
+      <c r="AJ36" s="140"/>
       <c r="AK36" s="107">
         <f>MAX(AK4:AK33)</f>
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AG37" s="120" t="s">
+    <row r="37" spans="1:37" ht="30" customHeight="1">
+      <c r="AG37" s="138" t="s">
         <v>80</v>
       </c>
-      <c r="AH37" s="121"/>
-      <c r="AI37" s="121"/>
-      <c r="AJ37" s="122"/>
+      <c r="AH37" s="139"/>
+      <c r="AI37" s="139"/>
+      <c r="AJ37" s="140"/>
       <c r="AK37" s="107">
         <f>MIN(AK4:AK33)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AG38" s="120" t="s">
+    <row r="38" spans="1:37" ht="30" customHeight="1">
+      <c r="AG38" s="138" t="s">
         <v>81</v>
       </c>
-      <c r="AH38" s="121"/>
-      <c r="AI38" s="121"/>
-      <c r="AJ38" s="122"/>
+      <c r="AH38" s="139"/>
+      <c r="AI38" s="139"/>
+      <c r="AJ38" s="140"/>
       <c r="AK38" s="107">
         <f>COUNTIF(AK4:AK33, "&gt;"&amp;AK35)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AG39" s="120" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:37" ht="30" customHeight="1">
+      <c r="AG39" s="138" t="s">
         <v>82</v>
       </c>
-      <c r="AH39" s="121"/>
-      <c r="AI39" s="121"/>
-      <c r="AJ39" s="122"/>
+      <c r="AH39" s="139"/>
+      <c r="AI39" s="139"/>
+      <c r="AJ39" s="140"/>
       <c r="AK39" s="107">
         <f>COUNTIF(AK4:AK33, "&lt;"&amp;AK35)</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="40" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AG40" s="120" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:37" ht="30" customHeight="1">
+      <c r="AG40" s="138" t="s">
         <v>83</v>
       </c>
-      <c r="AH40" s="121"/>
-      <c r="AI40" s="121"/>
-      <c r="AJ40" s="122"/>
+      <c r="AH40" s="139"/>
+      <c r="AI40" s="139"/>
+      <c r="AJ40" s="140"/>
       <c r="AK40" s="107">
         <f>COUNTIF(AK4:AK33, "&gt;"&amp;20)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AG41" s="120" t="s">
+    <row r="41" spans="1:37" ht="30" customHeight="1">
+      <c r="AG41" s="138" t="s">
         <v>84</v>
       </c>
-      <c r="AH41" s="121"/>
-      <c r="AI41" s="121"/>
-      <c r="AJ41" s="122"/>
+      <c r="AH41" s="139"/>
+      <c r="AI41" s="139"/>
+      <c r="AJ41" s="140"/>
       <c r="AK41" s="107">
         <f>COUNTIF(AK4:AK33, "&lt;"&amp;20)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:37" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:37" ht="30" customHeight="1"/>
+    <row r="43" spans="1:37" ht="30" customHeight="1"/>
+    <row r="44" spans="1:37" ht="30" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="AE1:AG1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="AG40:AJ40"/>
-    <mergeCell ref="AG41:AJ41"/>
-    <mergeCell ref="AK1:AK3"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="E1:K1"/>
+    <mergeCell ref="L1:Q1"/>
+    <mergeCell ref="U1:Y1"/>
+    <mergeCell ref="Z1:AD1"/>
+    <mergeCell ref="R1:T1"/>
     <mergeCell ref="A34:D34"/>
     <mergeCell ref="AG37:AJ37"/>
     <mergeCell ref="AG38:AJ38"/>
     <mergeCell ref="AG39:AJ39"/>
     <mergeCell ref="AG35:AJ35"/>
     <mergeCell ref="AG36:AJ36"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="E1:K1"/>
-    <mergeCell ref="L1:Q1"/>
-    <mergeCell ref="U1:Y1"/>
-    <mergeCell ref="Z1:AD1"/>
-    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="AE1:AG1"/>
+    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="AG40:AJ40"/>
+    <mergeCell ref="AG41:AJ41"/>
+    <mergeCell ref="AK1:AK3"/>
   </mergeCells>
   <conditionalFormatting sqref="E4:AJ33 L34:Q34">
     <cfRule type="expression" dxfId="5" priority="7">
